--- a/templates/ERC000056/metadata_template_ERC000056.xlsx
+++ b/templates/ERC000056/metadata_template_ERC000056.xlsx
@@ -20,17 +20,17 @@
     <definedName name="assemblyquality">'cv_sample'!$BX$1:$BX$3</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
     <definedName name="frequencyofcleaning">'cv_sample'!$DY$1:$DY$5</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$DC$1:$DC$289</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$DC$1:$DC$294</definedName>
     <definedName name="growthhabit">'cv_sample'!$CZ$1:$CZ$4</definedName>
     <definedName name="historytillage">'cv_sample'!$EQ$1:$EQ$9</definedName>
     <definedName name="hostpredictionapproach">'cv_sample'!$FA$1:$FA$7</definedName>
     <definedName name="indoorsurface">'cv_sample'!$CN$1:$CN$8</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
     <definedName name="observedbioticrelationship">'cv_sample'!$N$1:$N$5</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="relationshiptooxygen">'cv_sample'!$P$1:$P$7</definedName>
     <definedName name="sequencequalitycheck">'cv_sample'!$BO$1:$BO$3</definedName>
     <definedName name="singlecellorviralparticlelysisapproach">'cv_sample'!$GX$1:$GX$4</definedName>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1254" uniqueCount="1244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="1251">
   <si>
     <t>alias</t>
   </si>
@@ -461,6 +461,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -551,6 +554,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -1112,13 +1118,13 @@
     <t>size-fraction lower threshold</t>
   </si>
   <si>
-    <t>(Optional) Refers to the mesh/pore size used to retain the sample. materials smaller than the size threshold are excluded from the sample (Units: µm)</t>
+    <t>(Optional) Refers to the mesh/pore size used to retain the sample. materials smaller than the size threshold are excluded from the sample (Units: nm)</t>
   </si>
   <si>
     <t>size-fraction upper threshold</t>
   </si>
   <si>
-    <t>(Optional) Refers to the mesh/pore size used to pre-filter/pre-sort the sample. materials larger than the size threshold are excluded from the sample (Units: µm)</t>
+    <t>(Optional) Refers to the mesh/pore size used to pre-filter/pre-sort the sample. materials larger than the size threshold are excluded from the sample (Units: nm)</t>
   </si>
   <si>
     <t>Acrisol</t>
@@ -1274,7 +1280,7 @@
     <t>collection site geographic feature</t>
   </si>
   <si>
-    <t>(Optional) Text or terms that describe the geographic feature where the food sample was obtained by the researcher. this field accepts selected terms listed under the following ontologies: anthropogenic geographic feature (http://purl.obolibrary.org/obo/envo_00000002), for example agricultural fairground [envo:01000986]; garden [envo:00000011} or any of its subclasses; market [envo:01000987]; water well [envo:01000002]; or human construction (http://purl.obolibrary.org/obo/envo_00000070). (Units: m2)</t>
+    <t>(Optional) Text or terms that describe the geographic feature where the food sample was obtained by the researcher. this field accepts selected terms listed under the following ontologies: anthropogenic geographic feature (http://purl.obolibrary.org/obo/envo_00000002), for example agricultural fairground [envo:01000986]; garden [envo:00000011} or any of its subclasses; market [envo:01000987]; water well [envo:01000002]; or human construction (http://purl.obolibrary.org/obo/envo_00000070). (Units: ha)</t>
   </si>
   <si>
     <t>area sampled size</t>
@@ -1604,7 +1610,7 @@
     <t>time course duration</t>
   </si>
   <si>
-    <t>(Optional) For time-course research studies involving samples of the food commodity, indicate the total duration of the time-course study. (Units: year)</t>
+    <t>(Optional) For time-course research studies involving samples of the food commodity, indicate the total duration of the time-course study. (Units: day)</t>
   </si>
   <si>
     <t>number of samples collected</t>
@@ -1736,19 +1742,19 @@
     <t>sample surface moisture</t>
   </si>
   <si>
-    <t>(Optional) Degree of water held on a sampled surface. if present, user can state the degree of water held on surface (intermittent moisture, submerged). if no surface moisture is present indicate not present. (Units: year)</t>
+    <t>(Optional) Degree of water held on a sampled surface. if present, user can state the degree of water held on surface (intermittent moisture, submerged). if no surface moisture is present indicate not present. (Units: minute)</t>
   </si>
   <si>
     <t>sampling room id or name</t>
   </si>
   <si>
-    <t>(Optional) Explain how and for how long the soil sample was stored before dna extraction (fresh/frozen/other). (Units: year)</t>
+    <t>(Optional) Explain how and for how long the soil sample was stored before dna extraction (fresh/frozen/other). (Units: day)</t>
   </si>
   <si>
     <t>fermentation relative humidity</t>
   </si>
   <si>
-    <t>(Optional) The relative humidity of the fermented food fermentation process. (Units: g/m3)</t>
+    <t>(Optional) The relative humidity of the fermented food fermentation process. (Units: %)</t>
   </si>
   <si>
     <t>room dimensions</t>
@@ -1760,7 +1766,7 @@
     <t>amount or size of sample collected</t>
   </si>
   <si>
-    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: m3)</t>
+    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: kg)</t>
   </si>
   <si>
     <t>organism count</t>
@@ -2018,9 +2024,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -2039,6 +2042,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -2240,6 +2246,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -2249,9 +2258,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -2291,7 +2297,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -2360,6 +2366,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -2435,6 +2444,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -2456,6 +2468,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -2501,6 +2516,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -2513,6 +2531,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -2522,9 +2543,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -2549,6 +2567,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -2609,12 +2630,12 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
   </si>
   <si>
-    <t>Wake Island</t>
-  </si>
-  <si>
     <t>Wallis and Futuna</t>
   </si>
   <si>
@@ -2699,13 +2720,13 @@
     <t>host height</t>
   </si>
   <si>
-    <t>(Optional) The height of subject (Units: mm)</t>
+    <t>(Optional) The height of subject (Units: m)</t>
   </si>
   <si>
     <t>host length</t>
   </si>
   <si>
-    <t>(Optional) The length of subject (Units: mm)</t>
+    <t>(Optional) The length of subject (Units: m)</t>
   </si>
   <si>
     <t>host total mass</t>
@@ -2741,7 +2762,7 @@
     <t>humidity</t>
   </si>
   <si>
-    <t>(Optional) Amount of water vapour in the air, at the time of sampling (Units: g/m3)</t>
+    <t>(Optional) Amount of water vapour in the air, at the time of sampling (Units: %)</t>
   </si>
   <si>
     <t>conductivity</t>
@@ -2765,7 +2786,7 @@
     <t>wind speed</t>
   </si>
   <si>
-    <t>(Optional) Speed of wind measured at the time of sampling (Units: m/s)</t>
+    <t>(Optional) Speed of wind measured at the time of sampling (Units: km/h)</t>
   </si>
   <si>
     <t>temperature</t>
@@ -2822,7 +2843,7 @@
     <t>frequency of cleaning</t>
   </si>
   <si>
-    <t>(Optional) The number of times the sample location is cleaned. frequency of cleaning might be on a daily basis, weekly, monthly, quarterly or annually. (Units: year)</t>
+    <t>(Optional) The number of times the sample location is cleaned. frequency of cleaning might be on a daily basis, weekly, monthly, quarterly or annually. (Units: minute)</t>
   </si>
   <si>
     <t>total organic carbon method</t>
@@ -2870,7 +2891,7 @@
     <t>total nitrogen content</t>
   </si>
   <si>
-    <t>(Optional) Total nitrogen content of the sample (Units: µmol/L)</t>
+    <t>(Optional) Total nitrogen content of the sample (Units: µg/L)</t>
   </si>
   <si>
     <t>water pH</t>
@@ -2888,7 +2909,7 @@
     <t>bacteria density</t>
   </si>
   <si>
-    <t>(Optional) Number of bacteria in sample, as defined by bacteria density (http://purl.obolibrary.org/obo/genepio_0000043). (Units: g/m3)</t>
+    <t>(Optional) Number of bacteria in sample, as defined by bacteria density (http://purl.obolibrary.org/obo/genepio_0000043). (Units: %)</t>
   </si>
   <si>
     <t>salinity method</t>
@@ -2963,7 +2984,7 @@
     <t>mean seasonal humidity</t>
   </si>
   <si>
-    <t>(Optional) Average humidity of the region throughout the growing season. (Units: g/m3)</t>
+    <t>(Optional) Average humidity of the region throughout the growing season. (Units: %)</t>
   </si>
   <si>
     <t>mean seasonal temperature</t>
@@ -3011,7 +3032,7 @@
     <t>host dry mass</t>
   </si>
   <si>
-    <t>(Optional) Measurement of dry mass (Units: mg)</t>
+    <t>(Optional) Measurement of dry mass (Units: kg)</t>
   </si>
   <si>
     <t>CRISPR spacer match</t>
@@ -3071,13 +3092,13 @@
     <t>spike-in organism</t>
   </si>
   <si>
-    <t>(Optional) Taxonomic information about the spike-in organism(s). this field accepts terms under organism (http://purl.obolibrary.org/obo/ncit_c14250). this field also accepts identification numbers from ncbi under https://www.ncbi.nlm.nih.gov/taxonomy. multiple terms can be separated by pipes. (Units: g/m3)</t>
+    <t>(Optional) Taxonomic information about the spike-in organism(s). this field accepts terms under organism (http://purl.obolibrary.org/obo/ncit_c14250). this field also accepts identification numbers from ncbi under https://www.ncbi.nlm.nih.gov/taxonomy. multiple terms can be separated by pipes. (Units: %)</t>
   </si>
   <si>
     <t>spike-in organism count</t>
   </si>
   <si>
-    <t>(Optional) Total cell count of any organism (or group of organisms) per gram, volume or area of sample, should include name of organism followed by count. the method that was used for the enumeration (e.g. qpcr, atp, mpn, etc.) should also be provided (example: total prokaryotes; 3.5e7 cells per ml; qpcr). (Units: mm)</t>
+    <t>(Optional) Total cell count of any organism (or group of organisms) per gram, volume or area of sample, should include name of organism followed by count. the method that was used for the enumeration (e.g. qpcr, atp, mpn, etc.) should also be provided (example: total prokaryotes; 3.5e7 cells per ml; qpcr). (Units: m)</t>
   </si>
   <si>
     <t>fermentation temperature</t>
@@ -3101,19 +3122,19 @@
     <t>microbial starter source</t>
   </si>
   <si>
-    <t>(Optional) The source from which the microbial starter culture was sourced. if commercially supplied, list supplier. (Units: year)</t>
+    <t>(Optional) The source from which the microbial starter culture was sourced. if commercially supplied, list supplier. (Units: minute)</t>
   </si>
   <si>
     <t>microbial starter preparation</t>
   </si>
   <si>
-    <t>(Optional) Information about the protocol or method used to prepare the starter inoculum. (Units: year)</t>
+    <t>(Optional) Information about the protocol or method used to prepare the starter inoculum. (Units: minute)</t>
   </si>
   <si>
     <t>spike-in bacterial serovar or serotype</t>
   </si>
   <si>
-    <t>(Optional) Taxonomic information about the spike-in organism(s) at the serovar or serotype level. this field accepts terms under organism (http://purl.obolibrary.org/obo/ncit_c14250). this field also accepts identification numbers from ncbi under https://www.ncbi.nlm.nih.gov/taxonomy. multiple terms can be separated by pipes. (Units: year)</t>
+    <t>(Optional) Taxonomic information about the spike-in organism(s) at the serovar or serotype level. this field accepts terms under organism (http://purl.obolibrary.org/obo/ncit_c14250). this field also accepts identification numbers from ncbi under https://www.ncbi.nlm.nih.gov/taxonomy. multiple terms can be separated by pipes. (Units: minute)</t>
   </si>
   <si>
     <t>antimicrobial phenotype of spike-in bacteria</t>
@@ -3125,7 +3146,7 @@
     <t>fermentation time</t>
   </si>
   <si>
-    <t>(Optional) The time duration of the fermented food fermentation process. (Units: year)</t>
+    <t>(Optional) The time duration of the fermented food fermentation process. (Units: minute)</t>
   </si>
   <si>
     <t>microbial starter organism count</t>
@@ -3155,7 +3176,7 @@
     <t>study incubation duration</t>
   </si>
   <si>
-    <t>(Optional) Sample incubation duration if unpublished or unvalidated method is used. indicate the timepoint written in iso 8601 format. (Units: year)</t>
+    <t>(Optional) Sample incubation duration if unpublished or unvalidated method is used. indicate the timepoint written in iso 8601 format. (Units: minute)</t>
   </si>
   <si>
     <t>biocide</t>
@@ -3251,7 +3272,7 @@
     <t>microbiological culture medium</t>
   </si>
   <si>
-    <t>(Optional) A culture medium used to select for, grow, and maintain prokaryotic microorganisms. can be in either liquid (broth) or solidified (e.g. with agar) forms. this field accepts terms listed under microbiological culture medium (http://purl.obolibrary.org/obo/micro_0000067). if the proper descriptor is not listed please use text to describe the culture medium. (Units: Pa)</t>
+    <t>(Optional) A culture medium used to select for, grow, and maintain prokaryotic microorganisms. can be in either liquid (broth) or solidified (e.g. with agar) forms. this field accepts terms listed under microbiological culture medium (http://purl.obolibrary.org/obo/micro_0000067). if the proper descriptor is not listed please use text to describe the culture medium. (Units: N/m2)</t>
   </si>
   <si>
     <t>spike-in growth medium</t>
@@ -3311,7 +3332,7 @@
     <t>nucleic acid extraction kit</t>
   </si>
   <si>
-    <t>(Optional) The name of the extraction kit used to recover the nucleic acid fraction of an input material is performed. (Units: ppm)</t>
+    <t>(Optional) The name of the extraction kit used to recover the nucleic acid fraction of an input material is performed.</t>
   </si>
   <si>
     <t>sample pooling</t>
@@ -3362,7 +3383,7 @@
     <t>sample volume or weight for DNA extraction</t>
   </si>
   <si>
-    <t>(Optional) Volume (ml) or mass (g) of total collected sample processed for dna extraction. note: total sample collected should be entered under the term 'sample size'. (Units: ng)</t>
+    <t>(Optional) Volume (ml) or mass (g) of total collected sample processed for dna extraction. note: total sample collected should be entered under the term 'sample size'. (Units: mL)</t>
   </si>
   <si>
     <t>nucleic acid extraction</t>
@@ -3500,13 +3521,13 @@
     <t>food product by quality</t>
   </si>
   <si>
-    <t>(Optional) Descriptors for describing food visually or via other senses, which is useful for tasks like food inspection where little prior knowledge of how the food came to be is available. some terms like "food (frozen)" are both a quality descriptor and the output of a process. this field accepts terms listed under food product by quality (http://purl.obolibrary.org/obo/foodon_00002454). (Units: year)</t>
+    <t>(Optional) Descriptors for describing food visually or via other senses, which is useful for tasks like food inspection where little prior knowledge of how the food came to be is available. some terms like "food (frozen)" are both a quality descriptor and the output of a process. this field accepts terms listed under food product by quality (http://purl.obolibrary.org/obo/foodon_00002454). (Units: minute)</t>
   </si>
   <si>
     <t>food animal antimicrobial route of administration</t>
   </si>
   <si>
-    <t>(Optional) The route by which the antimicrobial is administered into the body of the food animal. (Units: m2)</t>
+    <t>(Optional) The route by which the antimicrobial is administered into the body of the food animal. (Units: ha)</t>
   </si>
   <si>
     <t>food allergen labeling</t>
@@ -3590,25 +3611,25 @@
     <t>food stored by consumer (storage duration)</t>
   </si>
   <si>
-    <t>(Optional) The storage duration of the food commodity by the consumer, prior to onset of illness or sample collection. indicate the timepoint written in iso 8601 format. (Units: year)</t>
+    <t>(Optional) The storage duration of the food commodity by the consumer, prior to onset of illness or sample collection. indicate the timepoint written in iso 8601 format. (Units: minute)</t>
   </si>
   <si>
     <t>food animal antimicrobial duration</t>
   </si>
   <si>
-    <t>(Optional) The duration of time (days) that the antimicrobial was administered to the food animal. (Units: year)</t>
+    <t>(Optional) The duration of time (days) that the antimicrobial was administered to the food animal. (Units: minute)</t>
   </si>
   <si>
     <t>part of plant or animal</t>
   </si>
   <si>
-    <t>(Optional) The anatomical part of the organism being involved in food production or consumption; e.g., a carrot is the root of the plant (root vegetable). this field accepts terms listed under part of plant or animal (http://purl.obolibrary.org/obo/foodon_03420116). (Units: year)</t>
+    <t>(Optional) The anatomical part of the organism being involved in food production or consumption; e.g., a carrot is the root of the plant (root vegetable). this field accepts terms listed under part of plant or animal (http://purl.obolibrary.org/obo/foodon_03420116). (Units: minute)</t>
   </si>
   <si>
     <t>hazard analysis critical control points (haccp) guide food safety term</t>
   </si>
   <si>
-    <t>(Optional) Hazard analysis critical control points (haccp) food safety terms; this field accepts terms listed under haccp guide food safety term (http://purl.obolibrary.org/obo/foodon_03530221). (Units: year)</t>
+    <t>(Optional) Hazard analysis critical control points (haccp) food safety terms; this field accepts terms listed under haccp guide food safety term (http://purl.obolibrary.org/obo/foodon_03530221). (Units: minute)</t>
   </si>
   <si>
     <t>dietary claim or use</t>
@@ -3620,7 +3641,7 @@
     <t>degree of plant part maturity</t>
   </si>
   <si>
-    <t>(Optional) A description of the stage of development of a plant or plant part based on maturity or ripeness. this field accepts terms listed under degree of plant maturity (http://purl.obolibrary.org/obo/foodon_03530050). (Units: year)</t>
+    <t>(Optional) A description of the stage of development of a plant or plant part based on maturity or ripeness. this field accepts terms listed under degree of plant maturity (http://purl.obolibrary.org/obo/foodon_03530050). (Units: day)</t>
   </si>
   <si>
     <t>food production environmental monitoring zone</t>
@@ -3638,7 +3659,7 @@
     <t>food traceability list category</t>
   </si>
   <si>
-    <t>(Optional) The fda is proposing to establish additional traceability recordkeeping requirements (beyond what is already required in existing regulations) for persons who manufacture, process, pack, or hold foods the agency has designated for inclusion on the food traceability list. the food traceability list (ftl) identifies the foods for which the additional traceability records described in the proposed rule would be required. the term “food traceability list” (ftl) refers not only to the foods specifically listed (https://www.fda.gov/media/142303/download), but also to any foods that contain listed foods as ingredients. (Units: mm)</t>
+    <t>(Optional) The fda is proposing to establish additional traceability recordkeeping requirements (beyond what is already required in existing regulations) for persons who manufacture, process, pack, or hold foods the agency has designated for inclusion on the food traceability list. the food traceability list (ftl) identifies the foods for which the additional traceability records described in the proposed rule would be required. the term “food traceability list” (ftl) refers not only to the foods specifically listed (https://www.fda.gov/media/142303/download), but also to any foods that contain listed foods as ingredients. (Units: cm)</t>
   </si>
   <si>
     <t>food animal antimicrobial frequency</t>
@@ -3668,19 +3689,19 @@
     <t>food additive</t>
   </si>
   <si>
-    <t>(Optional) A substance or substances added to food to maintain or improve safety and freshness, to improve or maintain nutritional value, or improve taste, texture and appearance. this field accepts terms listed under food additive (http://purl.obolibrary.org/obo/foodon_03412972). multiple terms can be separated by one or more pipes, but please consider limiting this list to the top 5 ingredients listed in order as on the food label. see also, https://www.fda.gov/food/food-ingredients-packaging/overview-food-ingredients-additives-colors. (Units: g/m3)</t>
+    <t>(Optional) A substance or substances added to food to maintain or improve safety and freshness, to improve or maintain nutritional value, or improve taste, texture and appearance. this field accepts terms listed under food additive (http://purl.obolibrary.org/obo/foodon_03412972). multiple terms can be separated by one or more pipes, but please consider limiting this list to the top 5 ingredients listed in order as on the food label. see also, https://www.fda.gov/food/food-ingredients-packaging/overview-food-ingredients-additives-colors. (Units: %)</t>
   </si>
   <si>
     <t>food source age</t>
   </si>
   <si>
-    <t>(Optional) The age of the food source host organism. depending on the type of host organism, age may be more appropriate to report in days, weeks, or years. (Units: year)</t>
+    <t>(Optional) The age of the food source host organism. depending on the type of host organism, age may be more appropriate to report in days, weeks, or years. (Units: day)</t>
   </si>
   <si>
     <t>food animal antimicrobial intended use</t>
   </si>
   <si>
-    <t>(Optional) The prescribed intended use of or the condition treated by the antimicrobial given to the food animal by any route of administration. (Units: year)</t>
+    <t>(Optional) The prescribed intended use of or the condition treated by the antimicrobial given to the food animal by any route of administration. (Units: day)</t>
   </si>
   <si>
     <t>food packing medium</t>
@@ -3746,7 +3767,7 @@
     <t>depth</t>
   </si>
   <si>
-    <t>(Optional) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: mm)</t>
+    <t>(Optional) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: m)</t>
   </si>
   <si>
     <t>environment adjacent to site</t>
@@ -4303,10 +4324,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -4347,10 +4368,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -4377,7 +4398,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -4394,7 +4415,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -4411,7 +4432,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -4428,7 +4449,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -4445,7 +4466,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -4462,7 +4483,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -4479,7 +4500,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -4496,7 +4517,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -4513,7 +4534,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -4530,7 +4551,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -4544,7 +4565,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -4558,7 +4579,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -4572,7 +4593,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -4586,7 +4607,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -4600,7 +4621,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -4614,7 +4635,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -4628,7 +4649,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -4642,7 +4663,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -4652,8 +4673,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -4664,7 +4688,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -4675,7 +4699,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -4686,7 +4710,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -4697,7 +4721,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -4708,7 +4732,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -4719,7 +4743,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -4730,7 +4754,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -4741,7 +4765,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -4752,7 +4776,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -4763,7 +4787,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -4774,7 +4798,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -4785,7 +4809,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -4796,7 +4820,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -4804,7 +4828,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -4812,7 +4836,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -4820,7 +4844,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -4828,7 +4852,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -4836,7 +4860,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -4844,7 +4868,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -4852,7 +4876,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -4860,7 +4884,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -4868,7 +4892,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -4876,236 +4900,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -5127,27 +5156,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -5167,122 +5196,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -5306,1674 +5335,1674 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>875</v>
+        <v>882</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>877</v>
+        <v>884</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>879</v>
+        <v>886</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>881</v>
+        <v>888</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>883</v>
+        <v>890</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>887</v>
+        <v>894</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>891</v>
+        <v>898</v>
       </c>
       <c r="DL1" s="1" t="s">
-        <v>893</v>
+        <v>900</v>
       </c>
       <c r="DM1" s="1" t="s">
-        <v>895</v>
+        <v>902</v>
       </c>
       <c r="DN1" s="1" t="s">
-        <v>897</v>
+        <v>904</v>
       </c>
       <c r="DO1" s="1" t="s">
-        <v>899</v>
+        <v>906</v>
       </c>
       <c r="DP1" s="1" t="s">
-        <v>901</v>
+        <v>908</v>
       </c>
       <c r="DQ1" s="1" t="s">
-        <v>903</v>
+        <v>910</v>
       </c>
       <c r="DR1" s="1" t="s">
-        <v>905</v>
+        <v>912</v>
       </c>
       <c r="DS1" s="1" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="DT1" s="1" t="s">
-        <v>909</v>
+        <v>916</v>
       </c>
       <c r="DU1" s="1" t="s">
-        <v>911</v>
+        <v>918</v>
       </c>
       <c r="DV1" s="1" t="s">
-        <v>913</v>
+        <v>920</v>
       </c>
       <c r="DW1" s="1" t="s">
-        <v>915</v>
+        <v>922</v>
       </c>
       <c r="DX1" s="1" t="s">
-        <v>917</v>
+        <v>924</v>
       </c>
       <c r="DY1" s="1" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="DZ1" s="1" t="s">
-        <v>926</v>
+        <v>933</v>
       </c>
       <c r="EA1" s="1" t="s">
-        <v>928</v>
+        <v>935</v>
       </c>
       <c r="EB1" s="1" t="s">
-        <v>930</v>
+        <v>937</v>
       </c>
       <c r="EC1" s="1" t="s">
-        <v>932</v>
+        <v>939</v>
       </c>
       <c r="ED1" s="1" t="s">
-        <v>934</v>
+        <v>941</v>
       </c>
       <c r="EE1" s="1" t="s">
-        <v>936</v>
+        <v>943</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>938</v>
+        <v>945</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>940</v>
+        <v>947</v>
       </c>
       <c r="EH1" s="1" t="s">
-        <v>942</v>
+        <v>949</v>
       </c>
       <c r="EI1" s="1" t="s">
-        <v>944</v>
+        <v>951</v>
       </c>
       <c r="EJ1" s="1" t="s">
-        <v>946</v>
+        <v>953</v>
       </c>
       <c r="EK1" s="1" t="s">
-        <v>948</v>
+        <v>955</v>
       </c>
       <c r="EL1" s="1" t="s">
-        <v>950</v>
+        <v>957</v>
       </c>
       <c r="EM1" s="1" t="s">
-        <v>952</v>
+        <v>959</v>
       </c>
       <c r="EN1" s="1" t="s">
-        <v>954</v>
+        <v>961</v>
       </c>
       <c r="EO1" s="1" t="s">
-        <v>956</v>
+        <v>963</v>
       </c>
       <c r="EP1" s="1" t="s">
-        <v>958</v>
+        <v>965</v>
       </c>
       <c r="EQ1" s="1" t="s">
-        <v>969</v>
+        <v>976</v>
       </c>
       <c r="ER1" s="1" t="s">
-        <v>971</v>
+        <v>978</v>
       </c>
       <c r="ES1" s="1" t="s">
-        <v>973</v>
+        <v>980</v>
       </c>
       <c r="ET1" s="1" t="s">
-        <v>975</v>
+        <v>982</v>
       </c>
       <c r="EU1" s="1" t="s">
-        <v>977</v>
+        <v>984</v>
       </c>
       <c r="EV1" s="1" t="s">
-        <v>979</v>
+        <v>986</v>
       </c>
       <c r="EW1" s="1" t="s">
-        <v>981</v>
+        <v>988</v>
       </c>
       <c r="EX1" s="1" t="s">
-        <v>983</v>
+        <v>990</v>
       </c>
       <c r="EY1" s="1" t="s">
-        <v>985</v>
+        <v>992</v>
       </c>
       <c r="EZ1" s="1" t="s">
-        <v>987</v>
+        <v>994</v>
       </c>
       <c r="FA1" s="1" t="s">
-        <v>995</v>
+        <v>1002</v>
       </c>
       <c r="FB1" s="1" t="s">
-        <v>997</v>
+        <v>1004</v>
       </c>
       <c r="FC1" s="1" t="s">
-        <v>999</v>
+        <v>1006</v>
       </c>
       <c r="FD1" s="1" t="s">
-        <v>1001</v>
+        <v>1008</v>
       </c>
       <c r="FE1" s="1" t="s">
-        <v>1003</v>
+        <v>1010</v>
       </c>
       <c r="FF1" s="1" t="s">
-        <v>1005</v>
+        <v>1012</v>
       </c>
       <c r="FG1" s="1" t="s">
-        <v>1007</v>
+        <v>1014</v>
       </c>
       <c r="FH1" s="1" t="s">
-        <v>1009</v>
+        <v>1016</v>
       </c>
       <c r="FI1" s="1" t="s">
-        <v>1011</v>
+        <v>1018</v>
       </c>
       <c r="FJ1" s="1" t="s">
-        <v>1013</v>
+        <v>1020</v>
       </c>
       <c r="FK1" s="1" t="s">
-        <v>1015</v>
+        <v>1022</v>
       </c>
       <c r="FL1" s="1" t="s">
-        <v>1017</v>
+        <v>1024</v>
       </c>
       <c r="FM1" s="1" t="s">
-        <v>1019</v>
+        <v>1026</v>
       </c>
       <c r="FN1" s="1" t="s">
-        <v>1021</v>
+        <v>1028</v>
       </c>
       <c r="FO1" s="1" t="s">
-        <v>1023</v>
+        <v>1030</v>
       </c>
       <c r="FP1" s="1" t="s">
-        <v>1025</v>
+        <v>1032</v>
       </c>
       <c r="FQ1" s="1" t="s">
-        <v>1027</v>
+        <v>1034</v>
       </c>
       <c r="FR1" s="1" t="s">
-        <v>1029</v>
+        <v>1036</v>
       </c>
       <c r="FS1" s="1" t="s">
-        <v>1031</v>
+        <v>1038</v>
       </c>
       <c r="FT1" s="1" t="s">
-        <v>1033</v>
+        <v>1040</v>
       </c>
       <c r="FU1" s="1" t="s">
-        <v>1035</v>
+        <v>1042</v>
       </c>
       <c r="FV1" s="1" t="s">
-        <v>1037</v>
+        <v>1044</v>
       </c>
       <c r="FW1" s="1" t="s">
-        <v>1039</v>
+        <v>1046</v>
       </c>
       <c r="FX1" s="1" t="s">
-        <v>1041</v>
+        <v>1048</v>
       </c>
       <c r="FY1" s="1" t="s">
-        <v>1043</v>
+        <v>1050</v>
       </c>
       <c r="FZ1" s="1" t="s">
-        <v>1045</v>
+        <v>1052</v>
       </c>
       <c r="GA1" s="1" t="s">
-        <v>1047</v>
+        <v>1054</v>
       </c>
       <c r="GB1" s="1" t="s">
-        <v>1049</v>
+        <v>1056</v>
       </c>
       <c r="GC1" s="1" t="s">
-        <v>1051</v>
+        <v>1058</v>
       </c>
       <c r="GD1" s="1" t="s">
-        <v>1053</v>
+        <v>1060</v>
       </c>
       <c r="GE1" s="1" t="s">
-        <v>1055</v>
+        <v>1062</v>
       </c>
       <c r="GF1" s="1" t="s">
-        <v>1057</v>
+        <v>1064</v>
       </c>
       <c r="GG1" s="1" t="s">
-        <v>1059</v>
+        <v>1066</v>
       </c>
       <c r="GH1" s="1" t="s">
-        <v>1061</v>
+        <v>1068</v>
       </c>
       <c r="GI1" s="1" t="s">
-        <v>1063</v>
+        <v>1070</v>
       </c>
       <c r="GJ1" s="1" t="s">
-        <v>1065</v>
+        <v>1072</v>
       </c>
       <c r="GK1" s="1" t="s">
-        <v>1067</v>
+        <v>1074</v>
       </c>
       <c r="GL1" s="1" t="s">
-        <v>1069</v>
+        <v>1076</v>
       </c>
       <c r="GM1" s="1" t="s">
-        <v>1071</v>
+        <v>1078</v>
       </c>
       <c r="GN1" s="1" t="s">
-        <v>1073</v>
+        <v>1080</v>
       </c>
       <c r="GO1" s="1" t="s">
-        <v>1075</v>
+        <v>1082</v>
       </c>
       <c r="GP1" s="1" t="s">
-        <v>1077</v>
+        <v>1084</v>
       </c>
       <c r="GQ1" s="1" t="s">
-        <v>1079</v>
+        <v>1086</v>
       </c>
       <c r="GR1" s="1" t="s">
-        <v>1081</v>
+        <v>1088</v>
       </c>
       <c r="GS1" s="1" t="s">
-        <v>1083</v>
+        <v>1090</v>
       </c>
       <c r="GT1" s="1" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="GU1" s="1" t="s">
-        <v>1087</v>
+        <v>1094</v>
       </c>
       <c r="GV1" s="1" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="GW1" s="1" t="s">
-        <v>1091</v>
+        <v>1098</v>
       </c>
       <c r="GX1" s="1" t="s">
-        <v>1096</v>
+        <v>1103</v>
       </c>
       <c r="GY1" s="1" t="s">
-        <v>1098</v>
+        <v>1105</v>
       </c>
       <c r="GZ1" s="1" t="s">
-        <v>1100</v>
+        <v>1107</v>
       </c>
       <c r="HA1" s="1" t="s">
-        <v>1102</v>
+        <v>1109</v>
       </c>
       <c r="HB1" s="1" t="s">
-        <v>1104</v>
+        <v>1111</v>
       </c>
       <c r="HC1" s="1" t="s">
-        <v>1106</v>
+        <v>1113</v>
       </c>
       <c r="HD1" s="1" t="s">
-        <v>1108</v>
+        <v>1115</v>
       </c>
       <c r="HE1" s="1" t="s">
-        <v>1110</v>
+        <v>1117</v>
       </c>
       <c r="HF1" s="1" t="s">
-        <v>1112</v>
+        <v>1119</v>
       </c>
       <c r="HG1" s="1" t="s">
-        <v>1114</v>
+        <v>1121</v>
       </c>
       <c r="HH1" s="1" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="HI1" s="1" t="s">
-        <v>1118</v>
+        <v>1125</v>
       </c>
       <c r="HJ1" s="1" t="s">
-        <v>1120</v>
+        <v>1127</v>
       </c>
       <c r="HK1" s="1" t="s">
-        <v>1122</v>
+        <v>1129</v>
       </c>
       <c r="HL1" s="1" t="s">
-        <v>1124</v>
+        <v>1131</v>
       </c>
       <c r="HM1" s="1" t="s">
-        <v>1126</v>
+        <v>1133</v>
       </c>
       <c r="HN1" s="1" t="s">
-        <v>1128</v>
+        <v>1135</v>
       </c>
       <c r="HO1" s="1" t="s">
-        <v>1130</v>
+        <v>1137</v>
       </c>
       <c r="HP1" s="1" t="s">
-        <v>1132</v>
+        <v>1139</v>
       </c>
       <c r="HQ1" s="1" t="s">
-        <v>1134</v>
+        <v>1141</v>
       </c>
       <c r="HR1" s="1" t="s">
-        <v>1136</v>
+        <v>1143</v>
       </c>
       <c r="HS1" s="1" t="s">
-        <v>1138</v>
+        <v>1145</v>
       </c>
       <c r="HT1" s="1" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="HU1" s="1" t="s">
-        <v>1142</v>
+        <v>1149</v>
       </c>
       <c r="HV1" s="1" t="s">
-        <v>1144</v>
+        <v>1151</v>
       </c>
       <c r="HW1" s="1" t="s">
-        <v>1146</v>
+        <v>1153</v>
       </c>
       <c r="HX1" s="1" t="s">
-        <v>1148</v>
+        <v>1155</v>
       </c>
       <c r="HY1" s="1" t="s">
-        <v>1150</v>
+        <v>1157</v>
       </c>
       <c r="HZ1" s="1" t="s">
-        <v>1152</v>
+        <v>1159</v>
       </c>
       <c r="IA1" s="1" t="s">
-        <v>1154</v>
+        <v>1161</v>
       </c>
       <c r="IB1" s="1" t="s">
-        <v>1156</v>
+        <v>1163</v>
       </c>
       <c r="IC1" s="1" t="s">
-        <v>1158</v>
+        <v>1165</v>
       </c>
       <c r="ID1" s="1" t="s">
-        <v>1160</v>
+        <v>1167</v>
       </c>
       <c r="IE1" s="1" t="s">
-        <v>1162</v>
+        <v>1169</v>
       </c>
       <c r="IF1" s="1" t="s">
-        <v>1164</v>
+        <v>1171</v>
       </c>
       <c r="IG1" s="1" t="s">
-        <v>1166</v>
+        <v>1173</v>
       </c>
       <c r="IH1" s="1" t="s">
-        <v>1168</v>
+        <v>1175</v>
       </c>
       <c r="II1" s="1" t="s">
-        <v>1170</v>
+        <v>1177</v>
       </c>
       <c r="IJ1" s="1" t="s">
-        <v>1172</v>
+        <v>1179</v>
       </c>
       <c r="IK1" s="1" t="s">
-        <v>1174</v>
+        <v>1181</v>
       </c>
       <c r="IL1" s="1" t="s">
-        <v>1176</v>
+        <v>1183</v>
       </c>
       <c r="IM1" s="1" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="IN1" s="1" t="s">
-        <v>1180</v>
+        <v>1187</v>
       </c>
       <c r="IO1" s="1" t="s">
-        <v>1182</v>
+        <v>1189</v>
       </c>
       <c r="IP1" s="1" t="s">
-        <v>1184</v>
+        <v>1191</v>
       </c>
       <c r="IQ1" s="1" t="s">
-        <v>1186</v>
+        <v>1193</v>
       </c>
       <c r="IR1" s="1" t="s">
-        <v>1188</v>
+        <v>1195</v>
       </c>
       <c r="IS1" s="1" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
       <c r="IT1" s="1" t="s">
-        <v>1192</v>
+        <v>1199</v>
       </c>
       <c r="IU1" s="1" t="s">
-        <v>1194</v>
+        <v>1201</v>
       </c>
       <c r="IV1" s="1" t="s">
-        <v>1196</v>
+        <v>1203</v>
       </c>
       <c r="IW1" s="1" t="s">
-        <v>1198</v>
+        <v>1205</v>
       </c>
       <c r="IX1" s="1" t="s">
-        <v>1200</v>
+        <v>1207</v>
       </c>
       <c r="IY1" s="1" t="s">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="IZ1" s="1" t="s">
-        <v>1204</v>
+        <v>1211</v>
       </c>
       <c r="JA1" s="1" t="s">
-        <v>1206</v>
+        <v>1213</v>
       </c>
       <c r="JB1" s="1" t="s">
-        <v>1208</v>
+        <v>1215</v>
       </c>
       <c r="JC1" s="1" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="JD1" s="1" t="s">
-        <v>1212</v>
+        <v>1219</v>
       </c>
       <c r="JE1" s="1" t="s">
-        <v>1214</v>
+        <v>1221</v>
       </c>
       <c r="JF1" s="1" t="s">
-        <v>1216</v>
+        <v>1223</v>
       </c>
       <c r="JG1" s="1" t="s">
-        <v>1218</v>
+        <v>1225</v>
       </c>
       <c r="JH1" s="1" t="s">
-        <v>1220</v>
+        <v>1227</v>
       </c>
       <c r="JI1" s="1" t="s">
-        <v>1222</v>
+        <v>1229</v>
       </c>
       <c r="JJ1" s="1" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="JK1" s="1" t="s">
-        <v>1226</v>
+        <v>1233</v>
       </c>
       <c r="JL1" s="1" t="s">
-        <v>1228</v>
+        <v>1235</v>
       </c>
       <c r="JM1" s="1" t="s">
-        <v>1230</v>
+        <v>1237</v>
       </c>
       <c r="JN1" s="1" t="s">
-        <v>1232</v>
+        <v>1239</v>
       </c>
       <c r="JO1" s="1" t="s">
-        <v>1234</v>
+        <v>1241</v>
       </c>
       <c r="JP1" s="1" t="s">
-        <v>1236</v>
+        <v>1243</v>
       </c>
       <c r="JQ1" s="1" t="s">
-        <v>1238</v>
+        <v>1245</v>
       </c>
       <c r="JR1" s="1" t="s">
-        <v>1240</v>
+        <v>1247</v>
       </c>
       <c r="JS1" s="1" t="s">
-        <v>1242</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="2" spans="1:279" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="DC2" s="2" t="s">
-        <v>876</v>
+        <v>883</v>
       </c>
       <c r="DD2" s="2" t="s">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="DE2" s="2" t="s">
-        <v>880</v>
+        <v>887</v>
       </c>
       <c r="DF2" s="2" t="s">
-        <v>882</v>
+        <v>889</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>884</v>
+        <v>891</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>886</v>
+        <v>893</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>888</v>
+        <v>895</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>890</v>
+        <v>897</v>
       </c>
       <c r="DK2" s="2" t="s">
-        <v>892</v>
+        <v>899</v>
       </c>
       <c r="DL2" s="2" t="s">
-        <v>894</v>
+        <v>901</v>
       </c>
       <c r="DM2" s="2" t="s">
-        <v>896</v>
+        <v>903</v>
       </c>
       <c r="DN2" s="2" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="DO2" s="2" t="s">
-        <v>900</v>
+        <v>907</v>
       </c>
       <c r="DP2" s="2" t="s">
-        <v>902</v>
+        <v>909</v>
       </c>
       <c r="DQ2" s="2" t="s">
-        <v>904</v>
+        <v>911</v>
       </c>
       <c r="DR2" s="2" t="s">
-        <v>906</v>
+        <v>913</v>
       </c>
       <c r="DS2" s="2" t="s">
-        <v>908</v>
+        <v>915</v>
       </c>
       <c r="DT2" s="2" t="s">
-        <v>910</v>
+        <v>917</v>
       </c>
       <c r="DU2" s="2" t="s">
-        <v>912</v>
+        <v>919</v>
       </c>
       <c r="DV2" s="2" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="DW2" s="2" t="s">
-        <v>916</v>
+        <v>923</v>
       </c>
       <c r="DX2" s="2" t="s">
-        <v>918</v>
+        <v>925</v>
       </c>
       <c r="DY2" s="2" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="DZ2" s="2" t="s">
-        <v>927</v>
+        <v>934</v>
       </c>
       <c r="EA2" s="2" t="s">
-        <v>929</v>
+        <v>936</v>
       </c>
       <c r="EB2" s="2" t="s">
-        <v>931</v>
+        <v>938</v>
       </c>
       <c r="EC2" s="2" t="s">
-        <v>933</v>
+        <v>940</v>
       </c>
       <c r="ED2" s="2" t="s">
-        <v>935</v>
+        <v>942</v>
       </c>
       <c r="EE2" s="2" t="s">
-        <v>937</v>
+        <v>944</v>
       </c>
       <c r="EF2" s="2" t="s">
-        <v>939</v>
+        <v>946</v>
       </c>
       <c r="EG2" s="2" t="s">
-        <v>941</v>
+        <v>948</v>
       </c>
       <c r="EH2" s="2" t="s">
-        <v>943</v>
+        <v>950</v>
       </c>
       <c r="EI2" s="2" t="s">
-        <v>945</v>
+        <v>952</v>
       </c>
       <c r="EJ2" s="2" t="s">
-        <v>947</v>
+        <v>954</v>
       </c>
       <c r="EK2" s="2" t="s">
-        <v>949</v>
+        <v>956</v>
       </c>
       <c r="EL2" s="2" t="s">
-        <v>951</v>
+        <v>958</v>
       </c>
       <c r="EM2" s="2" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="EN2" s="2" t="s">
-        <v>955</v>
+        <v>962</v>
       </c>
       <c r="EO2" s="2" t="s">
-        <v>957</v>
+        <v>964</v>
       </c>
       <c r="EP2" s="2" t="s">
-        <v>959</v>
+        <v>966</v>
       </c>
       <c r="EQ2" s="2" t="s">
-        <v>970</v>
+        <v>977</v>
       </c>
       <c r="ER2" s="2" t="s">
-        <v>972</v>
+        <v>979</v>
       </c>
       <c r="ES2" s="2" t="s">
-        <v>974</v>
+        <v>981</v>
       </c>
       <c r="ET2" s="2" t="s">
-        <v>976</v>
+        <v>983</v>
       </c>
       <c r="EU2" s="2" t="s">
-        <v>978</v>
+        <v>985</v>
       </c>
       <c r="EV2" s="2" t="s">
-        <v>980</v>
+        <v>987</v>
       </c>
       <c r="EW2" s="2" t="s">
-        <v>982</v>
+        <v>989</v>
       </c>
       <c r="EX2" s="2" t="s">
-        <v>984</v>
+        <v>991</v>
       </c>
       <c r="EY2" s="2" t="s">
-        <v>986</v>
+        <v>993</v>
       </c>
       <c r="EZ2" s="2" t="s">
-        <v>988</v>
+        <v>995</v>
       </c>
       <c r="FA2" s="2" t="s">
-        <v>996</v>
+        <v>1003</v>
       </c>
       <c r="FB2" s="2" t="s">
-        <v>998</v>
+        <v>1005</v>
       </c>
       <c r="FC2" s="2" t="s">
-        <v>1000</v>
+        <v>1007</v>
       </c>
       <c r="FD2" s="2" t="s">
-        <v>1002</v>
+        <v>1009</v>
       </c>
       <c r="FE2" s="2" t="s">
-        <v>1004</v>
+        <v>1011</v>
       </c>
       <c r="FF2" s="2" t="s">
-        <v>1006</v>
+        <v>1013</v>
       </c>
       <c r="FG2" s="2" t="s">
-        <v>1008</v>
+        <v>1015</v>
       </c>
       <c r="FH2" s="2" t="s">
-        <v>1010</v>
+        <v>1017</v>
       </c>
       <c r="FI2" s="2" t="s">
-        <v>1012</v>
+        <v>1019</v>
       </c>
       <c r="FJ2" s="2" t="s">
-        <v>1014</v>
+        <v>1021</v>
       </c>
       <c r="FK2" s="2" t="s">
-        <v>1016</v>
+        <v>1023</v>
       </c>
       <c r="FL2" s="2" t="s">
-        <v>1018</v>
+        <v>1025</v>
       </c>
       <c r="FM2" s="2" t="s">
-        <v>1020</v>
+        <v>1027</v>
       </c>
       <c r="FN2" s="2" t="s">
-        <v>1022</v>
+        <v>1029</v>
       </c>
       <c r="FO2" s="2" t="s">
-        <v>1024</v>
+        <v>1031</v>
       </c>
       <c r="FP2" s="2" t="s">
-        <v>1026</v>
+        <v>1033</v>
       </c>
       <c r="FQ2" s="2" t="s">
-        <v>1028</v>
+        <v>1035</v>
       </c>
       <c r="FR2" s="2" t="s">
-        <v>1030</v>
+        <v>1037</v>
       </c>
       <c r="FS2" s="2" t="s">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="FT2" s="2" t="s">
-        <v>1034</v>
+        <v>1041</v>
       </c>
       <c r="FU2" s="2" t="s">
-        <v>1036</v>
+        <v>1043</v>
       </c>
       <c r="FV2" s="2" t="s">
-        <v>1038</v>
+        <v>1045</v>
       </c>
       <c r="FW2" s="2" t="s">
-        <v>1040</v>
+        <v>1047</v>
       </c>
       <c r="FX2" s="2" t="s">
-        <v>1042</v>
+        <v>1049</v>
       </c>
       <c r="FY2" s="2" t="s">
-        <v>1044</v>
+        <v>1051</v>
       </c>
       <c r="FZ2" s="2" t="s">
-        <v>1046</v>
+        <v>1053</v>
       </c>
       <c r="GA2" s="2" t="s">
-        <v>1048</v>
+        <v>1055</v>
       </c>
       <c r="GB2" s="2" t="s">
-        <v>1050</v>
+        <v>1057</v>
       </c>
       <c r="GC2" s="2" t="s">
-        <v>1052</v>
+        <v>1059</v>
       </c>
       <c r="GD2" s="2" t="s">
-        <v>1054</v>
+        <v>1061</v>
       </c>
       <c r="GE2" s="2" t="s">
-        <v>1056</v>
+        <v>1063</v>
       </c>
       <c r="GF2" s="2" t="s">
-        <v>1058</v>
+        <v>1065</v>
       </c>
       <c r="GG2" s="2" t="s">
-        <v>1060</v>
+        <v>1067</v>
       </c>
       <c r="GH2" s="2" t="s">
-        <v>1062</v>
+        <v>1069</v>
       </c>
       <c r="GI2" s="2" t="s">
-        <v>1064</v>
+        <v>1071</v>
       </c>
       <c r="GJ2" s="2" t="s">
-        <v>1066</v>
+        <v>1073</v>
       </c>
       <c r="GK2" s="2" t="s">
-        <v>1068</v>
+        <v>1075</v>
       </c>
       <c r="GL2" s="2" t="s">
-        <v>1070</v>
+        <v>1077</v>
       </c>
       <c r="GM2" s="2" t="s">
-        <v>1072</v>
+        <v>1079</v>
       </c>
       <c r="GN2" s="2" t="s">
-        <v>1074</v>
+        <v>1081</v>
       </c>
       <c r="GO2" s="2" t="s">
-        <v>1076</v>
+        <v>1083</v>
       </c>
       <c r="GP2" s="2" t="s">
-        <v>1078</v>
+        <v>1085</v>
       </c>
       <c r="GQ2" s="2" t="s">
-        <v>1080</v>
+        <v>1087</v>
       </c>
       <c r="GR2" s="2" t="s">
-        <v>1082</v>
+        <v>1089</v>
       </c>
       <c r="GS2" s="2" t="s">
-        <v>1084</v>
+        <v>1091</v>
       </c>
       <c r="GT2" s="2" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="GU2" s="2" t="s">
-        <v>1088</v>
+        <v>1095</v>
       </c>
       <c r="GV2" s="2" t="s">
-        <v>1090</v>
+        <v>1097</v>
       </c>
       <c r="GW2" s="2" t="s">
-        <v>1092</v>
+        <v>1099</v>
       </c>
       <c r="GX2" s="2" t="s">
-        <v>1097</v>
+        <v>1104</v>
       </c>
       <c r="GY2" s="2" t="s">
-        <v>1099</v>
+        <v>1106</v>
       </c>
       <c r="GZ2" s="2" t="s">
-        <v>1101</v>
+        <v>1108</v>
       </c>
       <c r="HA2" s="2" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="HB2" s="2" t="s">
-        <v>1105</v>
+        <v>1112</v>
       </c>
       <c r="HC2" s="2" t="s">
-        <v>1107</v>
+        <v>1114</v>
       </c>
       <c r="HD2" s="2" t="s">
-        <v>1109</v>
+        <v>1116</v>
       </c>
       <c r="HE2" s="2" t="s">
-        <v>1111</v>
+        <v>1118</v>
       </c>
       <c r="HF2" s="2" t="s">
-        <v>1113</v>
+        <v>1120</v>
       </c>
       <c r="HG2" s="2" t="s">
-        <v>1115</v>
+        <v>1122</v>
       </c>
       <c r="HH2" s="2" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="HI2" s="2" t="s">
-        <v>1119</v>
+        <v>1126</v>
       </c>
       <c r="HJ2" s="2" t="s">
-        <v>1121</v>
+        <v>1128</v>
       </c>
       <c r="HK2" s="2" t="s">
-        <v>1123</v>
+        <v>1130</v>
       </c>
       <c r="HL2" s="2" t="s">
-        <v>1125</v>
+        <v>1132</v>
       </c>
       <c r="HM2" s="2" t="s">
-        <v>1127</v>
+        <v>1134</v>
       </c>
       <c r="HN2" s="2" t="s">
-        <v>1129</v>
+        <v>1136</v>
       </c>
       <c r="HO2" s="2" t="s">
-        <v>1131</v>
+        <v>1138</v>
       </c>
       <c r="HP2" s="2" t="s">
-        <v>1133</v>
+        <v>1140</v>
       </c>
       <c r="HQ2" s="2" t="s">
-        <v>1135</v>
+        <v>1142</v>
       </c>
       <c r="HR2" s="2" t="s">
-        <v>1137</v>
+        <v>1144</v>
       </c>
       <c r="HS2" s="2" t="s">
-        <v>1139</v>
+        <v>1146</v>
       </c>
       <c r="HT2" s="2" t="s">
-        <v>1141</v>
+        <v>1148</v>
       </c>
       <c r="HU2" s="2" t="s">
-        <v>1143</v>
+        <v>1150</v>
       </c>
       <c r="HV2" s="2" t="s">
-        <v>1145</v>
+        <v>1152</v>
       </c>
       <c r="HW2" s="2" t="s">
-        <v>1147</v>
+        <v>1154</v>
       </c>
       <c r="HX2" s="2" t="s">
-        <v>1149</v>
+        <v>1156</v>
       </c>
       <c r="HY2" s="2" t="s">
-        <v>1151</v>
+        <v>1158</v>
       </c>
       <c r="HZ2" s="2" t="s">
-        <v>1153</v>
+        <v>1160</v>
       </c>
       <c r="IA2" s="2" t="s">
-        <v>1155</v>
+        <v>1162</v>
       </c>
       <c r="IB2" s="2" t="s">
-        <v>1157</v>
+        <v>1164</v>
       </c>
       <c r="IC2" s="2" t="s">
-        <v>1159</v>
+        <v>1166</v>
       </c>
       <c r="ID2" s="2" t="s">
-        <v>1161</v>
+        <v>1168</v>
       </c>
       <c r="IE2" s="2" t="s">
-        <v>1163</v>
+        <v>1170</v>
       </c>
       <c r="IF2" s="2" t="s">
-        <v>1165</v>
+        <v>1172</v>
       </c>
       <c r="IG2" s="2" t="s">
-        <v>1167</v>
+        <v>1174</v>
       </c>
       <c r="IH2" s="2" t="s">
-        <v>1169</v>
+        <v>1176</v>
       </c>
       <c r="II2" s="2" t="s">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="IJ2" s="2" t="s">
-        <v>1173</v>
+        <v>1180</v>
       </c>
       <c r="IK2" s="2" t="s">
-        <v>1175</v>
+        <v>1182</v>
       </c>
       <c r="IL2" s="2" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="IM2" s="2" t="s">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="IN2" s="2" t="s">
-        <v>1181</v>
+        <v>1188</v>
       </c>
       <c r="IO2" s="2" t="s">
-        <v>1183</v>
+        <v>1190</v>
       </c>
       <c r="IP2" s="2" t="s">
-        <v>1185</v>
+        <v>1192</v>
       </c>
       <c r="IQ2" s="2" t="s">
-        <v>1187</v>
+        <v>1194</v>
       </c>
       <c r="IR2" s="2" t="s">
-        <v>1189</v>
+        <v>1196</v>
       </c>
       <c r="IS2" s="2" t="s">
-        <v>1191</v>
+        <v>1198</v>
       </c>
       <c r="IT2" s="2" t="s">
-        <v>1193</v>
+        <v>1200</v>
       </c>
       <c r="IU2" s="2" t="s">
-        <v>1195</v>
+        <v>1202</v>
       </c>
       <c r="IV2" s="2" t="s">
-        <v>1197</v>
+        <v>1204</v>
       </c>
       <c r="IW2" s="2" t="s">
-        <v>1199</v>
+        <v>1206</v>
       </c>
       <c r="IX2" s="2" t="s">
-        <v>1201</v>
+        <v>1208</v>
       </c>
       <c r="IY2" s="2" t="s">
-        <v>1203</v>
+        <v>1210</v>
       </c>
       <c r="IZ2" s="2" t="s">
-        <v>1205</v>
+        <v>1212</v>
       </c>
       <c r="JA2" s="2" t="s">
-        <v>1207</v>
+        <v>1214</v>
       </c>
       <c r="JB2" s="2" t="s">
-        <v>1209</v>
+        <v>1216</v>
       </c>
       <c r="JC2" s="2" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="JD2" s="2" t="s">
-        <v>1213</v>
+        <v>1220</v>
       </c>
       <c r="JE2" s="2" t="s">
-        <v>1215</v>
+        <v>1222</v>
       </c>
       <c r="JF2" s="2" t="s">
-        <v>1217</v>
+        <v>1224</v>
       </c>
       <c r="JG2" s="2" t="s">
-        <v>1219</v>
+        <v>1226</v>
       </c>
       <c r="JH2" s="2" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="JI2" s="2" t="s">
-        <v>1223</v>
+        <v>1230</v>
       </c>
       <c r="JJ2" s="2" t="s">
-        <v>1225</v>
+        <v>1232</v>
       </c>
       <c r="JK2" s="2" t="s">
-        <v>1227</v>
+        <v>1234</v>
       </c>
       <c r="JL2" s="2" t="s">
-        <v>1229</v>
+        <v>1236</v>
       </c>
       <c r="JM2" s="2" t="s">
-        <v>1231</v>
+        <v>1238</v>
       </c>
       <c r="JN2" s="2" t="s">
-        <v>1233</v>
+        <v>1240</v>
       </c>
       <c r="JO2" s="2" t="s">
-        <v>1235</v>
+        <v>1242</v>
       </c>
       <c r="JP2" s="2" t="s">
-        <v>1237</v>
+        <v>1244</v>
       </c>
       <c r="JQ2" s="2" t="s">
-        <v>1239</v>
+        <v>1246</v>
       </c>
       <c r="JR2" s="2" t="s">
-        <v>1241</v>
+        <v>1248</v>
       </c>
       <c r="JS2" s="2" t="s">
-        <v>1243</v>
+        <v>1250</v>
       </c>
     </row>
   </sheetData>
@@ -7033,247 +7062,247 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="M1:GX289"/>
+  <dimension ref="M1:GX294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="13:206">
       <c r="M1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="N1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AB1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="BO1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="BS1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="BX1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="CL1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="CN1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="CO1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="CZ1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="DC1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="DY1" t="s">
-        <v>919</v>
+        <v>926</v>
       </c>
       <c r="EQ1" t="s">
-        <v>960</v>
+        <v>967</v>
       </c>
       <c r="FA1" t="s">
-        <v>989</v>
+        <v>996</v>
       </c>
       <c r="GX1" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="2" spans="13:206">
       <c r="M2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AB2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="BO2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="BS2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="BX2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="CL2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="CN2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="CO2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="CZ2" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="DC2" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="DY2" t="s">
-        <v>920</v>
+        <v>927</v>
       </c>
       <c r="EQ2" t="s">
-        <v>961</v>
+        <v>968</v>
       </c>
       <c r="FA2" t="s">
-        <v>990</v>
+        <v>997</v>
       </c>
       <c r="GX2" t="s">
-        <v>991</v>
+        <v>998</v>
       </c>
     </row>
     <row r="3" spans="13:206">
       <c r="M3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="N3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="P3" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AB3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="BO3" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="BX3" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="CL3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="CN3" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="CO3" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="CZ3" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="DC3" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="DY3" t="s">
-        <v>921</v>
+        <v>928</v>
       </c>
       <c r="EQ3" t="s">
-        <v>962</v>
+        <v>969</v>
       </c>
       <c r="FA3" t="s">
-        <v>991</v>
+        <v>998</v>
       </c>
       <c r="GX3" t="s">
-        <v>1094</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="4" spans="13:206">
       <c r="M4" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="N4" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="P4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AB4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="CL4" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="CN4" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="CZ4" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="DC4" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="DY4" t="s">
-        <v>922</v>
+        <v>929</v>
       </c>
       <c r="EQ4" t="s">
-        <v>963</v>
+        <v>970</v>
       </c>
       <c r="FA4" t="s">
-        <v>992</v>
+        <v>999</v>
       </c>
       <c r="GX4" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="5" spans="13:206">
       <c r="M5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N5" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="P5" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AB5" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="CL5" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="CN5" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="DC5" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="DY5" t="s">
-        <v>923</v>
+        <v>930</v>
       </c>
       <c r="EQ5" t="s">
-        <v>964</v>
+        <v>971</v>
       </c>
       <c r="FA5" t="s">
-        <v>993</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6" spans="13:206">
       <c r="M6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="P6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AB6" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="CL6" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="CN6" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="DC6" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="EQ6" t="s">
-        <v>965</v>
+        <v>972</v>
       </c>
       <c r="FA6" t="s">
         <v>116</v>
@@ -7281,1615 +7310,1640 @@
     </row>
     <row r="7" spans="13:206">
       <c r="M7" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="P7" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AB7" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="CL7" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="CN7" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="DC7" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="EQ7" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="FA7" t="s">
-        <v>994</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="8" spans="13:206">
       <c r="M8" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AB8" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="CL8" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="CN8" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="DC8" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="EQ8" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
     </row>
     <row r="9" spans="13:206">
       <c r="M9" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AB9" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="CL9" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="DC9" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="EQ9" t="s">
-        <v>968</v>
+        <v>975</v>
       </c>
     </row>
     <row r="10" spans="13:206">
       <c r="M10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AB10" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="CL10" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="DC10" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="11" spans="13:206">
       <c r="M11" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AB11" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="CL11" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="DC11" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="12" spans="13:206">
       <c r="M12" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AB12" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="CL12" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="DC12" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="13" spans="13:206">
       <c r="M13" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AB13" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="CL13" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="DC13" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="14" spans="13:206">
       <c r="M14" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AB14" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="CL14" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="DC14" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="15" spans="13:206">
       <c r="M15" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AB15" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="CL15" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="DC15" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="16" spans="13:206">
       <c r="M16" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AB16" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="DC16" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="17" spans="13:107">
       <c r="M17" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AB17" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="DC17" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="18" spans="13:107">
       <c r="M18" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AB18" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="DC18" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="19" spans="13:107">
       <c r="M19" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AB19" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="DC19" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="20" spans="13:107">
       <c r="M20" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AB20" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="DC20" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="21" spans="13:107">
       <c r="M21" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AB21" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="DC21" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="22" spans="13:107">
       <c r="M22" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AB22" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="DC22" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="23" spans="13:107">
       <c r="M23" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AB23" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="DC23" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="24" spans="13:107">
       <c r="M24" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AB24" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="DC24" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="25" spans="13:107">
       <c r="M25" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AB25" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="DC25" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="26" spans="13:107">
       <c r="M26" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AB26" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="DC26" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="27" spans="13:107">
       <c r="M27" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AB27" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="DC27" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="28" spans="13:107">
       <c r="M28" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AB28" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="DC28" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="29" spans="13:107">
       <c r="M29" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AB29" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="DC29" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="30" spans="13:107">
       <c r="M30" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AB30" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="DC30" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="31" spans="13:107">
       <c r="AB31" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="DC31" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="32" spans="13:107">
       <c r="AB32" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="DC32" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="33" spans="107:107">
       <c r="DC33" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="34" spans="107:107">
       <c r="DC34" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="35" spans="107:107">
       <c r="DC35" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="36" spans="107:107">
       <c r="DC36" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="37" spans="107:107">
       <c r="DC37" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="38" spans="107:107">
       <c r="DC38" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="39" spans="107:107">
       <c r="DC39" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="40" spans="107:107">
       <c r="DC40" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="41" spans="107:107">
       <c r="DC41" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="42" spans="107:107">
       <c r="DC42" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="43" spans="107:107">
       <c r="DC43" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="44" spans="107:107">
       <c r="DC44" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="45" spans="107:107">
       <c r="DC45" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="46" spans="107:107">
       <c r="DC46" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="47" spans="107:107">
       <c r="DC47" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="48" spans="107:107">
       <c r="DC48" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="49" spans="107:107">
       <c r="DC49" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="50" spans="107:107">
       <c r="DC50" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="51" spans="107:107">
       <c r="DC51" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="52" spans="107:107">
       <c r="DC52" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="53" spans="107:107">
       <c r="DC53" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="54" spans="107:107">
       <c r="DC54" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="55" spans="107:107">
       <c r="DC55" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="56" spans="107:107">
       <c r="DC56" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="57" spans="107:107">
       <c r="DC57" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="58" spans="107:107">
       <c r="DC58" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="59" spans="107:107">
       <c r="DC59" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="60" spans="107:107">
       <c r="DC60" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="61" spans="107:107">
       <c r="DC61" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="62" spans="107:107">
       <c r="DC62" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="63" spans="107:107">
       <c r="DC63" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="64" spans="107:107">
       <c r="DC64" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="65" spans="107:107">
       <c r="DC65" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="66" spans="107:107">
       <c r="DC66" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="67" spans="107:107">
       <c r="DC67" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="68" spans="107:107">
       <c r="DC68" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="69" spans="107:107">
       <c r="DC69" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="70" spans="107:107">
       <c r="DC70" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="71" spans="107:107">
       <c r="DC71" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="72" spans="107:107">
       <c r="DC72" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="73" spans="107:107">
       <c r="DC73" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="74" spans="107:107">
       <c r="DC74" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="75" spans="107:107">
       <c r="DC75" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="76" spans="107:107">
       <c r="DC76" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="77" spans="107:107">
       <c r="DC77" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="78" spans="107:107">
       <c r="DC78" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="79" spans="107:107">
       <c r="DC79" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="80" spans="107:107">
       <c r="DC80" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="81" spans="107:107">
       <c r="DC81" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="82" spans="107:107">
       <c r="DC82" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="83" spans="107:107">
       <c r="DC83" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="84" spans="107:107">
       <c r="DC84" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="85" spans="107:107">
       <c r="DC85" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="86" spans="107:107">
       <c r="DC86" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="87" spans="107:107">
       <c r="DC87" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="88" spans="107:107">
       <c r="DC88" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="89" spans="107:107">
       <c r="DC89" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="90" spans="107:107">
       <c r="DC90" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="91" spans="107:107">
       <c r="DC91" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="92" spans="107:107">
       <c r="DC92" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="93" spans="107:107">
       <c r="DC93" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="94" spans="107:107">
       <c r="DC94" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="95" spans="107:107">
       <c r="DC95" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="96" spans="107:107">
       <c r="DC96" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="97" spans="107:107">
       <c r="DC97" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="98" spans="107:107">
       <c r="DC98" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="99" spans="107:107">
       <c r="DC99" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="100" spans="107:107">
       <c r="DC100" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="101" spans="107:107">
       <c r="DC101" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="102" spans="107:107">
       <c r="DC102" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="103" spans="107:107">
       <c r="DC103" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="104" spans="107:107">
       <c r="DC104" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="105" spans="107:107">
       <c r="DC105" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="106" spans="107:107">
       <c r="DC106" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="107" spans="107:107">
       <c r="DC107" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="108" spans="107:107">
       <c r="DC108" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="109" spans="107:107">
       <c r="DC109" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="110" spans="107:107">
       <c r="DC110" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="111" spans="107:107">
       <c r="DC111" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="112" spans="107:107">
       <c r="DC112" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="113" spans="107:107">
       <c r="DC113" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="114" spans="107:107">
       <c r="DC114" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="115" spans="107:107">
       <c r="DC115" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="116" spans="107:107">
       <c r="DC116" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="117" spans="107:107">
       <c r="DC117" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="118" spans="107:107">
       <c r="DC118" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="119" spans="107:107">
       <c r="DC119" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="120" spans="107:107">
       <c r="DC120" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="121" spans="107:107">
       <c r="DC121" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="122" spans="107:107">
       <c r="DC122" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="123" spans="107:107">
       <c r="DC123" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="124" spans="107:107">
       <c r="DC124" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
     </row>
     <row r="125" spans="107:107">
       <c r="DC125" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="126" spans="107:107">
       <c r="DC126" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
     </row>
     <row r="127" spans="107:107">
       <c r="DC127" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="128" spans="107:107">
       <c r="DC128" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="129" spans="107:107">
       <c r="DC129" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="130" spans="107:107">
       <c r="DC130" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
     </row>
     <row r="131" spans="107:107">
       <c r="DC131" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
     </row>
     <row r="132" spans="107:107">
       <c r="DC132" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
     </row>
     <row r="133" spans="107:107">
       <c r="DC133" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
     </row>
     <row r="134" spans="107:107">
       <c r="DC134" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
     </row>
     <row r="135" spans="107:107">
       <c r="DC135" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="136" spans="107:107">
       <c r="DC136" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
     </row>
     <row r="137" spans="107:107">
       <c r="DC137" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
     </row>
     <row r="138" spans="107:107">
       <c r="DC138" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
     </row>
     <row r="139" spans="107:107">
       <c r="DC139" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="140" spans="107:107">
       <c r="DC140" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
     </row>
     <row r="141" spans="107:107">
       <c r="DC141" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
     </row>
     <row r="142" spans="107:107">
       <c r="DC142" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="143" spans="107:107">
       <c r="DC143" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
     </row>
     <row r="144" spans="107:107">
       <c r="DC144" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="145" spans="107:107">
       <c r="DC145" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
     </row>
     <row r="146" spans="107:107">
       <c r="DC146" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
     </row>
     <row r="147" spans="107:107">
       <c r="DC147" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
     </row>
     <row r="148" spans="107:107">
       <c r="DC148" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
     </row>
     <row r="149" spans="107:107">
       <c r="DC149" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
     </row>
     <row r="150" spans="107:107">
       <c r="DC150" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
     </row>
     <row r="151" spans="107:107">
       <c r="DC151" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
     </row>
     <row r="152" spans="107:107">
       <c r="DC152" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
     </row>
     <row r="153" spans="107:107">
       <c r="DC153" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
     </row>
     <row r="154" spans="107:107">
       <c r="DC154" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
     </row>
     <row r="155" spans="107:107">
       <c r="DC155" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
     </row>
     <row r="156" spans="107:107">
       <c r="DC156" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
     </row>
     <row r="157" spans="107:107">
       <c r="DC157" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
     </row>
     <row r="158" spans="107:107">
       <c r="DC158" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
     </row>
     <row r="159" spans="107:107">
       <c r="DC159" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
     </row>
     <row r="160" spans="107:107">
       <c r="DC160" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="161" spans="107:107">
       <c r="DC161" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
     </row>
     <row r="162" spans="107:107">
       <c r="DC162" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
     </row>
     <row r="163" spans="107:107">
       <c r="DC163" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
     </row>
     <row r="164" spans="107:107">
       <c r="DC164" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
     </row>
     <row r="165" spans="107:107">
       <c r="DC165" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
     </row>
     <row r="166" spans="107:107">
       <c r="DC166" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
     </row>
     <row r="167" spans="107:107">
       <c r="DC167" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
     </row>
     <row r="168" spans="107:107">
       <c r="DC168" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
     </row>
     <row r="169" spans="107:107">
       <c r="DC169" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
     </row>
     <row r="170" spans="107:107">
       <c r="DC170" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
     </row>
     <row r="171" spans="107:107">
       <c r="DC171" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
     </row>
     <row r="172" spans="107:107">
       <c r="DC172" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
     </row>
     <row r="173" spans="107:107">
       <c r="DC173" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
     </row>
     <row r="174" spans="107:107">
       <c r="DC174" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
     </row>
     <row r="175" spans="107:107">
       <c r="DC175" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
     </row>
     <row r="176" spans="107:107">
       <c r="DC176" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
     </row>
     <row r="177" spans="107:107">
       <c r="DC177" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
     </row>
     <row r="178" spans="107:107">
       <c r="DC178" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
     </row>
     <row r="179" spans="107:107">
       <c r="DC179" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
     </row>
     <row r="180" spans="107:107">
       <c r="DC180" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
     </row>
     <row r="181" spans="107:107">
       <c r="DC181" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
     </row>
     <row r="182" spans="107:107">
       <c r="DC182" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
     </row>
     <row r="183" spans="107:107">
       <c r="DC183" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
     </row>
     <row r="184" spans="107:107">
       <c r="DC184" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
     </row>
     <row r="185" spans="107:107">
       <c r="DC185" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
     </row>
     <row r="186" spans="107:107">
       <c r="DC186" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
     </row>
     <row r="187" spans="107:107">
       <c r="DC187" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
     </row>
     <row r="188" spans="107:107">
       <c r="DC188" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
     </row>
     <row r="189" spans="107:107">
       <c r="DC189" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
     </row>
     <row r="190" spans="107:107">
       <c r="DC190" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
     </row>
     <row r="191" spans="107:107">
       <c r="DC191" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
     </row>
     <row r="192" spans="107:107">
       <c r="DC192" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
     </row>
     <row r="193" spans="107:107">
       <c r="DC193" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
     </row>
     <row r="194" spans="107:107">
       <c r="DC194" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
     </row>
     <row r="195" spans="107:107">
       <c r="DC195" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
     </row>
     <row r="196" spans="107:107">
       <c r="DC196" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
     </row>
     <row r="197" spans="107:107">
       <c r="DC197" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
     </row>
     <row r="198" spans="107:107">
       <c r="DC198" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
     </row>
     <row r="199" spans="107:107">
       <c r="DC199" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
     </row>
     <row r="200" spans="107:107">
       <c r="DC200" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
     </row>
     <row r="201" spans="107:107">
       <c r="DC201" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
     </row>
     <row r="202" spans="107:107">
       <c r="DC202" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
     </row>
     <row r="203" spans="107:107">
       <c r="DC203" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
     </row>
     <row r="204" spans="107:107">
       <c r="DC204" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
     </row>
     <row r="205" spans="107:107">
       <c r="DC205" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
     </row>
     <row r="206" spans="107:107">
       <c r="DC206" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
     </row>
     <row r="207" spans="107:107">
       <c r="DC207" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
     </row>
     <row r="208" spans="107:107">
       <c r="DC208" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
     </row>
     <row r="209" spans="107:107">
       <c r="DC209" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
     </row>
     <row r="210" spans="107:107">
       <c r="DC210" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
     </row>
     <row r="211" spans="107:107">
       <c r="DC211" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
     </row>
     <row r="212" spans="107:107">
       <c r="DC212" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
     </row>
     <row r="213" spans="107:107">
       <c r="DC213" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
     </row>
     <row r="214" spans="107:107">
       <c r="DC214" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
     </row>
     <row r="215" spans="107:107">
       <c r="DC215" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
     </row>
     <row r="216" spans="107:107">
       <c r="DC216" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
     </row>
     <row r="217" spans="107:107">
       <c r="DC217" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="218" spans="107:107">
       <c r="DC218" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
     </row>
     <row r="219" spans="107:107">
       <c r="DC219" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
     </row>
     <row r="220" spans="107:107">
       <c r="DC220" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
     </row>
     <row r="221" spans="107:107">
       <c r="DC221" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="222" spans="107:107">
       <c r="DC222" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
     </row>
     <row r="223" spans="107:107">
       <c r="DC223" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
     </row>
     <row r="224" spans="107:107">
       <c r="DC224" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
     </row>
     <row r="225" spans="107:107">
       <c r="DC225" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
     </row>
     <row r="226" spans="107:107">
       <c r="DC226" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
     </row>
     <row r="227" spans="107:107">
       <c r="DC227" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
     </row>
     <row r="228" spans="107:107">
       <c r="DC228" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
     </row>
     <row r="229" spans="107:107">
       <c r="DC229" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
     </row>
     <row r="230" spans="107:107">
       <c r="DC230" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
     </row>
     <row r="231" spans="107:107">
       <c r="DC231" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
     </row>
     <row r="232" spans="107:107">
       <c r="DC232" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
     </row>
     <row r="233" spans="107:107">
       <c r="DC233" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
     </row>
     <row r="234" spans="107:107">
       <c r="DC234" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
     </row>
     <row r="235" spans="107:107">
       <c r="DC235" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
     </row>
     <row r="236" spans="107:107">
       <c r="DC236" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
     </row>
     <row r="237" spans="107:107">
       <c r="DC237" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
     </row>
     <row r="238" spans="107:107">
       <c r="DC238" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
     </row>
     <row r="239" spans="107:107">
       <c r="DC239" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
     </row>
     <row r="240" spans="107:107">
       <c r="DC240" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
     </row>
     <row r="241" spans="107:107">
       <c r="DC241" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
     </row>
     <row r="242" spans="107:107">
       <c r="DC242" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
     </row>
     <row r="243" spans="107:107">
       <c r="DC243" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
     </row>
     <row r="244" spans="107:107">
       <c r="DC244" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
     </row>
     <row r="245" spans="107:107">
       <c r="DC245" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
     </row>
     <row r="246" spans="107:107">
       <c r="DC246" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
     </row>
     <row r="247" spans="107:107">
       <c r="DC247" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
     </row>
     <row r="248" spans="107:107">
       <c r="DC248" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
     </row>
     <row r="249" spans="107:107">
       <c r="DC249" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
     </row>
     <row r="250" spans="107:107">
       <c r="DC250" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
     </row>
     <row r="251" spans="107:107">
       <c r="DC251" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
     </row>
     <row r="252" spans="107:107">
       <c r="DC252" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
     </row>
     <row r="253" spans="107:107">
       <c r="DC253" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
     </row>
     <row r="254" spans="107:107">
       <c r="DC254" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
     </row>
     <row r="255" spans="107:107">
       <c r="DC255" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
     </row>
     <row r="256" spans="107:107">
       <c r="DC256" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
     </row>
     <row r="257" spans="107:107">
       <c r="DC257" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
     </row>
     <row r="258" spans="107:107">
       <c r="DC258" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
     </row>
     <row r="259" spans="107:107">
       <c r="DC259" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
     </row>
     <row r="260" spans="107:107">
       <c r="DC260" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
     </row>
     <row r="261" spans="107:107">
       <c r="DC261" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
     </row>
     <row r="262" spans="107:107">
       <c r="DC262" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
     </row>
     <row r="263" spans="107:107">
       <c r="DC263" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
     </row>
     <row r="264" spans="107:107">
       <c r="DC264" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
     </row>
     <row r="265" spans="107:107">
       <c r="DC265" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
     </row>
     <row r="266" spans="107:107">
       <c r="DC266" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="267" spans="107:107">
       <c r="DC267" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
     </row>
     <row r="268" spans="107:107">
       <c r="DC268" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
     </row>
     <row r="269" spans="107:107">
       <c r="DC269" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
     </row>
     <row r="270" spans="107:107">
       <c r="DC270" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
     </row>
     <row r="271" spans="107:107">
       <c r="DC271" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
     </row>
     <row r="272" spans="107:107">
       <c r="DC272" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
     </row>
     <row r="273" spans="107:107">
       <c r="DC273" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
     </row>
     <row r="274" spans="107:107">
       <c r="DC274" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
     </row>
     <row r="275" spans="107:107">
       <c r="DC275" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
     </row>
     <row r="276" spans="107:107">
       <c r="DC276" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
     </row>
     <row r="277" spans="107:107">
       <c r="DC277" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
     </row>
     <row r="278" spans="107:107">
       <c r="DC278" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
     </row>
     <row r="279" spans="107:107">
       <c r="DC279" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
     </row>
     <row r="280" spans="107:107">
       <c r="DC280" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
     </row>
     <row r="281" spans="107:107">
       <c r="DC281" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
     </row>
     <row r="282" spans="107:107">
       <c r="DC282" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
     </row>
     <row r="283" spans="107:107">
       <c r="DC283" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
     </row>
     <row r="284" spans="107:107">
       <c r="DC284" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
     </row>
     <row r="285" spans="107:107">
       <c r="DC285" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
     </row>
     <row r="286" spans="107:107">
       <c r="DC286" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
     </row>
     <row r="287" spans="107:107">
       <c r="DC287" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
     </row>
     <row r="288" spans="107:107">
       <c r="DC288" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
     </row>
     <row r="289" spans="107:107">
       <c r="DC289" t="s">
-        <v>874</v>
+        <v>876</v>
+      </c>
+    </row>
+    <row r="290" spans="107:107">
+      <c r="DC290" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="291" spans="107:107">
+      <c r="DC291" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="292" spans="107:107">
+      <c r="DC292" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="293" spans="107:107">
+      <c r="DC293" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="294" spans="107:107">
+      <c r="DC294" t="s">
+        <v>881</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000056/metadata_template_ERC000056.xlsx
+++ b/templates/ERC000056/metadata_template_ERC000056.xlsx
@@ -17,35 +17,35 @@
     <sheet name="cv_sample" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="assemblyquality">'cv_sample'!$BV$1:$BV$3</definedName>
+    <definedName name="assemblyquality">'cv_sample'!$BW$1:$BW$3</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="frequencyofcleaning">'cv_sample'!$DW$1:$DW$5</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$DA$1:$DA$289</definedName>
-    <definedName name="growthhabit">'cv_sample'!$CX$1:$CX$4</definedName>
-    <definedName name="historytillage">'cv_sample'!$EO$1:$EO$9</definedName>
-    <definedName name="hostpredictionapproach">'cv_sample'!$EY$1:$EY$7</definedName>
-    <definedName name="indoorsurface">'cv_sample'!$CL$1:$CL$8</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="frequencyofcleaning">'cv_sample'!$DX$1:$DX$5</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$DB$1:$DB$294</definedName>
+    <definedName name="growthhabit">'cv_sample'!$CY$1:$CY$4</definedName>
+    <definedName name="historytillage">'cv_sample'!$EP$1:$EP$9</definedName>
+    <definedName name="hostpredictionapproach">'cv_sample'!$EZ$1:$EZ$7</definedName>
+    <definedName name="indoorsurface">'cv_sample'!$CM$1:$CM$8</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="observedbioticrelationship">'cv_sample'!$L$1:$L$5</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
-    <definedName name="relationshiptooxygen">'cv_sample'!$N$1:$N$7</definedName>
-    <definedName name="sequencequalitycheck">'cv_sample'!$BM$1:$BM$3</definedName>
-    <definedName name="singlecellorviralparticlelysisapproach">'cv_sample'!$GV$1:$GV$4</definedName>
-    <definedName name="soiltype">'cv_sample'!$Z$1:$Z$32</definedName>
+    <definedName name="observedbioticrelationship">'cv_sample'!$M$1:$M$5</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
+    <definedName name="relationshiptooxygen">'cv_sample'!$O$1:$O$7</definedName>
+    <definedName name="sequencequalitycheck">'cv_sample'!$BN$1:$BN$3</definedName>
+    <definedName name="singlecellorviralparticlelysisapproach">'cv_sample'!$GW$1:$GW$4</definedName>
+    <definedName name="soiltype">'cv_sample'!$AA$1:$AA$32</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
-    <definedName name="surfacematerial">'cv_sample'!$CJ$1:$CJ$15</definedName>
-    <definedName name="trophiclevel">'cv_sample'!$K$1:$K$30</definedName>
-    <definedName name="ventilationtype">'cv_sample'!$CM$1:$CM$3</definedName>
+    <definedName name="surfacematerial">'cv_sample'!$CK$1:$CK$15</definedName>
+    <definedName name="trophiclevel">'cv_sample'!$L$1:$L$30</definedName>
+    <definedName name="ventilationtype">'cv_sample'!$CN$1:$CN$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="1240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1259" uniqueCount="1249">
   <si>
     <t>alias</t>
   </si>
@@ -461,6 +461,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -551,6 +554,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -851,6 +857,12 @@
     <t>(Mandatory) Ncbi taxonomy identifier.  this is appropriate for individual organisms and some environmental samples.</t>
   </si>
   <si>
+    <t>scientific_name</t>
+  </si>
+  <si>
+    <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
     <t>sample_description</t>
   </si>
   <si>
@@ -2006,9 +2018,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -2027,6 +2036,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -2228,6 +2240,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -2237,9 +2252,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -2279,7 +2291,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -2348,6 +2360,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -2423,6 +2438,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -2444,6 +2462,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -2489,6 +2510,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -2501,6 +2525,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -2510,9 +2537,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -2537,6 +2561,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -2597,12 +2624,12 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
   </si>
   <si>
-    <t>Wake Island</t>
-  </si>
-  <si>
     <t>Wallis and Futuna</t>
   </si>
   <si>
@@ -3299,7 +3326,7 @@
     <t>nucleic acid extraction kit</t>
   </si>
   <si>
-    <t>(Optional) The name of the extraction kit used to recover the nucleic acid fraction of an input material is performed. (Units: ppm)</t>
+    <t>(Optional) The name of the extraction kit used to recover the nucleic acid fraction of an input material is performed.</t>
   </si>
   <si>
     <t>sample pooling</t>
@@ -4291,10 +4318,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -4335,10 +4362,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -4365,7 +4392,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -4382,7 +4409,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -4399,7 +4426,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -4416,7 +4443,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -4433,7 +4460,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -4450,7 +4477,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -4467,7 +4494,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -4484,7 +4511,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -4501,7 +4528,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -4518,7 +4545,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -4532,7 +4559,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -4546,7 +4573,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -4560,7 +4587,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -4574,7 +4601,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -4588,7 +4615,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -4602,7 +4629,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -4616,7 +4643,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -4630,7 +4657,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -4640,8 +4667,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -4652,7 +4682,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -4663,7 +4693,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -4674,7 +4704,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -4685,7 +4715,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -4696,7 +4726,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -4707,7 +4737,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -4718,7 +4748,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -4729,7 +4759,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -4740,7 +4770,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -4751,7 +4781,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -4762,7 +4792,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -4773,7 +4803,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -4784,7 +4814,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -4792,7 +4822,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -4800,7 +4830,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -4808,7 +4838,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -4816,7 +4846,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -4824,7 +4854,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -4832,7 +4862,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -4840,7 +4870,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -4848,7 +4878,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -4856,7 +4886,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -4864,236 +4894,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -5115,27 +5150,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -5155,122 +5190,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -5280,13 +5315,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:JQ2"/>
+  <dimension ref="A1:JR2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:277">
+    <row r="1" spans="1:278">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5294,1712 +5329,1718 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>312</v>
+        <v>284</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>386</v>
+        <v>356</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="BQ1" s="1" t="s">
         <v>477</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>533</v>
+        <v>520</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>871</v>
+        <v>584</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>873</v>
+        <v>880</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>875</v>
+        <v>882</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>877</v>
+        <v>884</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>879</v>
+        <v>886</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>881</v>
+        <v>888</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>883</v>
+        <v>890</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>887</v>
+        <v>894</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>891</v>
+        <v>898</v>
       </c>
       <c r="DL1" s="1" t="s">
-        <v>893</v>
+        <v>900</v>
       </c>
       <c r="DM1" s="1" t="s">
-        <v>895</v>
+        <v>902</v>
       </c>
       <c r="DN1" s="1" t="s">
-        <v>897</v>
+        <v>904</v>
       </c>
       <c r="DO1" s="1" t="s">
-        <v>899</v>
+        <v>906</v>
       </c>
       <c r="DP1" s="1" t="s">
-        <v>901</v>
+        <v>908</v>
       </c>
       <c r="DQ1" s="1" t="s">
-        <v>903</v>
+        <v>910</v>
       </c>
       <c r="DR1" s="1" t="s">
-        <v>905</v>
+        <v>912</v>
       </c>
       <c r="DS1" s="1" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="DT1" s="1" t="s">
-        <v>909</v>
+        <v>916</v>
       </c>
       <c r="DU1" s="1" t="s">
-        <v>911</v>
+        <v>918</v>
       </c>
       <c r="DV1" s="1" t="s">
-        <v>913</v>
+        <v>920</v>
       </c>
       <c r="DW1" s="1" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="DX1" s="1" t="s">
-        <v>922</v>
+        <v>929</v>
       </c>
       <c r="DY1" s="1" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="DZ1" s="1" t="s">
-        <v>926</v>
+        <v>933</v>
       </c>
       <c r="EA1" s="1" t="s">
-        <v>928</v>
+        <v>935</v>
       </c>
       <c r="EB1" s="1" t="s">
-        <v>930</v>
+        <v>937</v>
       </c>
       <c r="EC1" s="1" t="s">
-        <v>932</v>
+        <v>939</v>
       </c>
       <c r="ED1" s="1" t="s">
-        <v>934</v>
+        <v>941</v>
       </c>
       <c r="EE1" s="1" t="s">
-        <v>936</v>
+        <v>943</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>938</v>
+        <v>945</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>940</v>
+        <v>947</v>
       </c>
       <c r="EH1" s="1" t="s">
-        <v>942</v>
+        <v>949</v>
       </c>
       <c r="EI1" s="1" t="s">
-        <v>944</v>
+        <v>951</v>
       </c>
       <c r="EJ1" s="1" t="s">
-        <v>946</v>
+        <v>953</v>
       </c>
       <c r="EK1" s="1" t="s">
-        <v>948</v>
+        <v>955</v>
       </c>
       <c r="EL1" s="1" t="s">
-        <v>950</v>
+        <v>957</v>
       </c>
       <c r="EM1" s="1" t="s">
-        <v>952</v>
+        <v>959</v>
       </c>
       <c r="EN1" s="1" t="s">
-        <v>954</v>
+        <v>961</v>
       </c>
       <c r="EO1" s="1" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="EP1" s="1" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="EQ1" s="1" t="s">
-        <v>969</v>
+        <v>976</v>
       </c>
       <c r="ER1" s="1" t="s">
-        <v>971</v>
+        <v>978</v>
       </c>
       <c r="ES1" s="1" t="s">
-        <v>973</v>
+        <v>980</v>
       </c>
       <c r="ET1" s="1" t="s">
-        <v>975</v>
+        <v>982</v>
       </c>
       <c r="EU1" s="1" t="s">
-        <v>977</v>
+        <v>984</v>
       </c>
       <c r="EV1" s="1" t="s">
-        <v>979</v>
+        <v>986</v>
       </c>
       <c r="EW1" s="1" t="s">
-        <v>981</v>
+        <v>988</v>
       </c>
       <c r="EX1" s="1" t="s">
-        <v>983</v>
+        <v>990</v>
       </c>
       <c r="EY1" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="EZ1" s="1" t="s">
-        <v>993</v>
+        <v>1000</v>
       </c>
       <c r="FA1" s="1" t="s">
-        <v>995</v>
+        <v>1002</v>
       </c>
       <c r="FB1" s="1" t="s">
-        <v>997</v>
+        <v>1004</v>
       </c>
       <c r="FC1" s="1" t="s">
-        <v>999</v>
+        <v>1006</v>
       </c>
       <c r="FD1" s="1" t="s">
-        <v>1001</v>
+        <v>1008</v>
       </c>
       <c r="FE1" s="1" t="s">
-        <v>1003</v>
+        <v>1010</v>
       </c>
       <c r="FF1" s="1" t="s">
-        <v>1005</v>
+        <v>1012</v>
       </c>
       <c r="FG1" s="1" t="s">
-        <v>1007</v>
+        <v>1014</v>
       </c>
       <c r="FH1" s="1" t="s">
-        <v>1009</v>
+        <v>1016</v>
       </c>
       <c r="FI1" s="1" t="s">
-        <v>1011</v>
+        <v>1018</v>
       </c>
       <c r="FJ1" s="1" t="s">
-        <v>1013</v>
+        <v>1020</v>
       </c>
       <c r="FK1" s="1" t="s">
-        <v>1015</v>
+        <v>1022</v>
       </c>
       <c r="FL1" s="1" t="s">
-        <v>1017</v>
+        <v>1024</v>
       </c>
       <c r="FM1" s="1" t="s">
-        <v>1019</v>
+        <v>1026</v>
       </c>
       <c r="FN1" s="1" t="s">
-        <v>1021</v>
+        <v>1028</v>
       </c>
       <c r="FO1" s="1" t="s">
-        <v>1023</v>
+        <v>1030</v>
       </c>
       <c r="FP1" s="1" t="s">
-        <v>1025</v>
+        <v>1032</v>
       </c>
       <c r="FQ1" s="1" t="s">
-        <v>1027</v>
+        <v>1034</v>
       </c>
       <c r="FR1" s="1" t="s">
-        <v>1029</v>
+        <v>1036</v>
       </c>
       <c r="FS1" s="1" t="s">
-        <v>1031</v>
+        <v>1038</v>
       </c>
       <c r="FT1" s="1" t="s">
-        <v>1033</v>
+        <v>1040</v>
       </c>
       <c r="FU1" s="1" t="s">
-        <v>1035</v>
+        <v>1042</v>
       </c>
       <c r="FV1" s="1" t="s">
-        <v>1037</v>
+        <v>1044</v>
       </c>
       <c r="FW1" s="1" t="s">
-        <v>1039</v>
+        <v>1046</v>
       </c>
       <c r="FX1" s="1" t="s">
-        <v>1041</v>
+        <v>1048</v>
       </c>
       <c r="FY1" s="1" t="s">
-        <v>1043</v>
+        <v>1050</v>
       </c>
       <c r="FZ1" s="1" t="s">
-        <v>1045</v>
+        <v>1052</v>
       </c>
       <c r="GA1" s="1" t="s">
-        <v>1047</v>
+        <v>1054</v>
       </c>
       <c r="GB1" s="1" t="s">
-        <v>1049</v>
+        <v>1056</v>
       </c>
       <c r="GC1" s="1" t="s">
-        <v>1051</v>
+        <v>1058</v>
       </c>
       <c r="GD1" s="1" t="s">
-        <v>1053</v>
+        <v>1060</v>
       </c>
       <c r="GE1" s="1" t="s">
-        <v>1055</v>
+        <v>1062</v>
       </c>
       <c r="GF1" s="1" t="s">
-        <v>1057</v>
+        <v>1064</v>
       </c>
       <c r="GG1" s="1" t="s">
-        <v>1059</v>
+        <v>1066</v>
       </c>
       <c r="GH1" s="1" t="s">
-        <v>1061</v>
+        <v>1068</v>
       </c>
       <c r="GI1" s="1" t="s">
-        <v>1063</v>
+        <v>1070</v>
       </c>
       <c r="GJ1" s="1" t="s">
-        <v>1065</v>
+        <v>1072</v>
       </c>
       <c r="GK1" s="1" t="s">
-        <v>1067</v>
+        <v>1074</v>
       </c>
       <c r="GL1" s="1" t="s">
-        <v>1069</v>
+        <v>1076</v>
       </c>
       <c r="GM1" s="1" t="s">
-        <v>1071</v>
+        <v>1078</v>
       </c>
       <c r="GN1" s="1" t="s">
-        <v>1073</v>
+        <v>1080</v>
       </c>
       <c r="GO1" s="1" t="s">
-        <v>1075</v>
+        <v>1082</v>
       </c>
       <c r="GP1" s="1" t="s">
-        <v>1077</v>
+        <v>1084</v>
       </c>
       <c r="GQ1" s="1" t="s">
-        <v>1079</v>
+        <v>1086</v>
       </c>
       <c r="GR1" s="1" t="s">
-        <v>1081</v>
+        <v>1088</v>
       </c>
       <c r="GS1" s="1" t="s">
-        <v>1083</v>
+        <v>1090</v>
       </c>
       <c r="GT1" s="1" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="GU1" s="1" t="s">
-        <v>1087</v>
+        <v>1094</v>
       </c>
       <c r="GV1" s="1" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="GW1" s="1" t="s">
-        <v>1094</v>
+        <v>1101</v>
       </c>
       <c r="GX1" s="1" t="s">
-        <v>1096</v>
+        <v>1103</v>
       </c>
       <c r="GY1" s="1" t="s">
-        <v>1098</v>
+        <v>1105</v>
       </c>
       <c r="GZ1" s="1" t="s">
-        <v>1100</v>
+        <v>1107</v>
       </c>
       <c r="HA1" s="1" t="s">
-        <v>1102</v>
+        <v>1109</v>
       </c>
       <c r="HB1" s="1" t="s">
-        <v>1104</v>
+        <v>1111</v>
       </c>
       <c r="HC1" s="1" t="s">
-        <v>1106</v>
+        <v>1113</v>
       </c>
       <c r="HD1" s="1" t="s">
-        <v>1108</v>
+        <v>1115</v>
       </c>
       <c r="HE1" s="1" t="s">
-        <v>1110</v>
+        <v>1117</v>
       </c>
       <c r="HF1" s="1" t="s">
-        <v>1112</v>
+        <v>1119</v>
       </c>
       <c r="HG1" s="1" t="s">
-        <v>1114</v>
+        <v>1121</v>
       </c>
       <c r="HH1" s="1" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="HI1" s="1" t="s">
-        <v>1118</v>
+        <v>1125</v>
       </c>
       <c r="HJ1" s="1" t="s">
-        <v>1120</v>
+        <v>1127</v>
       </c>
       <c r="HK1" s="1" t="s">
-        <v>1122</v>
+        <v>1129</v>
       </c>
       <c r="HL1" s="1" t="s">
-        <v>1124</v>
+        <v>1131</v>
       </c>
       <c r="HM1" s="1" t="s">
-        <v>1126</v>
+        <v>1133</v>
       </c>
       <c r="HN1" s="1" t="s">
-        <v>1128</v>
+        <v>1135</v>
       </c>
       <c r="HO1" s="1" t="s">
-        <v>1130</v>
+        <v>1137</v>
       </c>
       <c r="HP1" s="1" t="s">
-        <v>1132</v>
+        <v>1139</v>
       </c>
       <c r="HQ1" s="1" t="s">
-        <v>1134</v>
+        <v>1141</v>
       </c>
       <c r="HR1" s="1" t="s">
-        <v>1136</v>
+        <v>1143</v>
       </c>
       <c r="HS1" s="1" t="s">
-        <v>1138</v>
+        <v>1145</v>
       </c>
       <c r="HT1" s="1" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="HU1" s="1" t="s">
-        <v>1142</v>
+        <v>1149</v>
       </c>
       <c r="HV1" s="1" t="s">
-        <v>1144</v>
+        <v>1151</v>
       </c>
       <c r="HW1" s="1" t="s">
-        <v>1146</v>
+        <v>1153</v>
       </c>
       <c r="HX1" s="1" t="s">
-        <v>1148</v>
+        <v>1155</v>
       </c>
       <c r="HY1" s="1" t="s">
-        <v>1150</v>
+        <v>1157</v>
       </c>
       <c r="HZ1" s="1" t="s">
-        <v>1152</v>
+        <v>1159</v>
       </c>
       <c r="IA1" s="1" t="s">
-        <v>1154</v>
+        <v>1161</v>
       </c>
       <c r="IB1" s="1" t="s">
-        <v>1156</v>
+        <v>1163</v>
       </c>
       <c r="IC1" s="1" t="s">
-        <v>1158</v>
+        <v>1165</v>
       </c>
       <c r="ID1" s="1" t="s">
-        <v>1160</v>
+        <v>1167</v>
       </c>
       <c r="IE1" s="1" t="s">
-        <v>1162</v>
+        <v>1169</v>
       </c>
       <c r="IF1" s="1" t="s">
-        <v>1164</v>
+        <v>1171</v>
       </c>
       <c r="IG1" s="1" t="s">
-        <v>1166</v>
+        <v>1173</v>
       </c>
       <c r="IH1" s="1" t="s">
-        <v>1168</v>
+        <v>1175</v>
       </c>
       <c r="II1" s="1" t="s">
-        <v>1170</v>
+        <v>1177</v>
       </c>
       <c r="IJ1" s="1" t="s">
-        <v>1172</v>
+        <v>1179</v>
       </c>
       <c r="IK1" s="1" t="s">
-        <v>1174</v>
+        <v>1181</v>
       </c>
       <c r="IL1" s="1" t="s">
-        <v>1176</v>
+        <v>1183</v>
       </c>
       <c r="IM1" s="1" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="IN1" s="1" t="s">
-        <v>1180</v>
+        <v>1187</v>
       </c>
       <c r="IO1" s="1" t="s">
-        <v>1182</v>
+        <v>1189</v>
       </c>
       <c r="IP1" s="1" t="s">
-        <v>1184</v>
+        <v>1191</v>
       </c>
       <c r="IQ1" s="1" t="s">
-        <v>1186</v>
+        <v>1193</v>
       </c>
       <c r="IR1" s="1" t="s">
-        <v>1188</v>
+        <v>1195</v>
       </c>
       <c r="IS1" s="1" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
       <c r="IT1" s="1" t="s">
-        <v>1192</v>
+        <v>1199</v>
       </c>
       <c r="IU1" s="1" t="s">
-        <v>1194</v>
+        <v>1201</v>
       </c>
       <c r="IV1" s="1" t="s">
-        <v>1196</v>
+        <v>1203</v>
       </c>
       <c r="IW1" s="1" t="s">
-        <v>1198</v>
+        <v>1205</v>
       </c>
       <c r="IX1" s="1" t="s">
-        <v>1200</v>
+        <v>1207</v>
       </c>
       <c r="IY1" s="1" t="s">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="IZ1" s="1" t="s">
-        <v>1204</v>
+        <v>1211</v>
       </c>
       <c r="JA1" s="1" t="s">
-        <v>1206</v>
+        <v>1213</v>
       </c>
       <c r="JB1" s="1" t="s">
-        <v>1208</v>
+        <v>1215</v>
       </c>
       <c r="JC1" s="1" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="JD1" s="1" t="s">
-        <v>1212</v>
+        <v>1219</v>
       </c>
       <c r="JE1" s="1" t="s">
-        <v>1214</v>
+        <v>1221</v>
       </c>
       <c r="JF1" s="1" t="s">
-        <v>1216</v>
+        <v>1223</v>
       </c>
       <c r="JG1" s="1" t="s">
-        <v>1218</v>
+        <v>1225</v>
       </c>
       <c r="JH1" s="1" t="s">
-        <v>1220</v>
+        <v>1227</v>
       </c>
       <c r="JI1" s="1" t="s">
-        <v>1222</v>
+        <v>1229</v>
       </c>
       <c r="JJ1" s="1" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="JK1" s="1" t="s">
-        <v>1226</v>
+        <v>1233</v>
       </c>
       <c r="JL1" s="1" t="s">
-        <v>1228</v>
+        <v>1235</v>
       </c>
       <c r="JM1" s="1" t="s">
-        <v>1230</v>
+        <v>1237</v>
       </c>
       <c r="JN1" s="1" t="s">
-        <v>1232</v>
+        <v>1239</v>
       </c>
       <c r="JO1" s="1" t="s">
-        <v>1234</v>
+        <v>1241</v>
       </c>
       <c r="JP1" s="1" t="s">
-        <v>1236</v>
+        <v>1243</v>
       </c>
       <c r="JQ1" s="1" t="s">
-        <v>1238</v>
-      </c>
-    </row>
-    <row r="2" spans="1:277" ht="150" customHeight="1">
+        <v>1245</v>
+      </c>
+      <c r="JR1" s="1" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="2" spans="1:278" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>313</v>
+        <v>285</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>387</v>
+        <v>357</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="BQ2" s="2" t="s">
         <v>478</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>534</v>
+        <v>521</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>872</v>
+        <v>585</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>874</v>
+        <v>881</v>
       </c>
       <c r="DC2" s="2" t="s">
-        <v>876</v>
+        <v>883</v>
       </c>
       <c r="DD2" s="2" t="s">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="DE2" s="2" t="s">
-        <v>880</v>
+        <v>887</v>
       </c>
       <c r="DF2" s="2" t="s">
-        <v>882</v>
+        <v>889</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>884</v>
+        <v>891</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>886</v>
+        <v>893</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>888</v>
+        <v>895</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>890</v>
+        <v>897</v>
       </c>
       <c r="DK2" s="2" t="s">
-        <v>892</v>
+        <v>899</v>
       </c>
       <c r="DL2" s="2" t="s">
-        <v>894</v>
+        <v>901</v>
       </c>
       <c r="DM2" s="2" t="s">
-        <v>896</v>
+        <v>903</v>
       </c>
       <c r="DN2" s="2" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="DO2" s="2" t="s">
-        <v>900</v>
+        <v>907</v>
       </c>
       <c r="DP2" s="2" t="s">
-        <v>902</v>
+        <v>909</v>
       </c>
       <c r="DQ2" s="2" t="s">
-        <v>904</v>
+        <v>911</v>
       </c>
       <c r="DR2" s="2" t="s">
-        <v>906</v>
+        <v>913</v>
       </c>
       <c r="DS2" s="2" t="s">
-        <v>908</v>
+        <v>915</v>
       </c>
       <c r="DT2" s="2" t="s">
-        <v>910</v>
+        <v>917</v>
       </c>
       <c r="DU2" s="2" t="s">
-        <v>912</v>
+        <v>919</v>
       </c>
       <c r="DV2" s="2" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="DW2" s="2" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="DX2" s="2" t="s">
-        <v>923</v>
+        <v>930</v>
       </c>
       <c r="DY2" s="2" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="DZ2" s="2" t="s">
-        <v>927</v>
+        <v>934</v>
       </c>
       <c r="EA2" s="2" t="s">
-        <v>929</v>
+        <v>936</v>
       </c>
       <c r="EB2" s="2" t="s">
-        <v>931</v>
+        <v>938</v>
       </c>
       <c r="EC2" s="2" t="s">
-        <v>933</v>
+        <v>940</v>
       </c>
       <c r="ED2" s="2" t="s">
-        <v>935</v>
+        <v>942</v>
       </c>
       <c r="EE2" s="2" t="s">
-        <v>937</v>
+        <v>944</v>
       </c>
       <c r="EF2" s="2" t="s">
-        <v>939</v>
+        <v>946</v>
       </c>
       <c r="EG2" s="2" t="s">
-        <v>941</v>
+        <v>948</v>
       </c>
       <c r="EH2" s="2" t="s">
-        <v>943</v>
+        <v>950</v>
       </c>
       <c r="EI2" s="2" t="s">
-        <v>945</v>
+        <v>952</v>
       </c>
       <c r="EJ2" s="2" t="s">
-        <v>947</v>
+        <v>954</v>
       </c>
       <c r="EK2" s="2" t="s">
-        <v>949</v>
+        <v>956</v>
       </c>
       <c r="EL2" s="2" t="s">
-        <v>951</v>
+        <v>958</v>
       </c>
       <c r="EM2" s="2" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="EN2" s="2" t="s">
-        <v>955</v>
+        <v>962</v>
       </c>
       <c r="EO2" s="2" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="EP2" s="2" t="s">
-        <v>968</v>
+        <v>975</v>
       </c>
       <c r="EQ2" s="2" t="s">
-        <v>970</v>
+        <v>977</v>
       </c>
       <c r="ER2" s="2" t="s">
-        <v>972</v>
+        <v>979</v>
       </c>
       <c r="ES2" s="2" t="s">
-        <v>974</v>
+        <v>981</v>
       </c>
       <c r="ET2" s="2" t="s">
-        <v>976</v>
+        <v>983</v>
       </c>
       <c r="EU2" s="2" t="s">
-        <v>978</v>
+        <v>985</v>
       </c>
       <c r="EV2" s="2" t="s">
-        <v>980</v>
+        <v>987</v>
       </c>
       <c r="EW2" s="2" t="s">
-        <v>982</v>
+        <v>989</v>
       </c>
       <c r="EX2" s="2" t="s">
-        <v>984</v>
+        <v>991</v>
       </c>
       <c r="EY2" s="2" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="EZ2" s="2" t="s">
-        <v>994</v>
+        <v>1001</v>
       </c>
       <c r="FA2" s="2" t="s">
-        <v>996</v>
+        <v>1003</v>
       </c>
       <c r="FB2" s="2" t="s">
-        <v>998</v>
+        <v>1005</v>
       </c>
       <c r="FC2" s="2" t="s">
-        <v>1000</v>
+        <v>1007</v>
       </c>
       <c r="FD2" s="2" t="s">
-        <v>1002</v>
+        <v>1009</v>
       </c>
       <c r="FE2" s="2" t="s">
-        <v>1004</v>
+        <v>1011</v>
       </c>
       <c r="FF2" s="2" t="s">
-        <v>1006</v>
+        <v>1013</v>
       </c>
       <c r="FG2" s="2" t="s">
-        <v>1008</v>
+        <v>1015</v>
       </c>
       <c r="FH2" s="2" t="s">
-        <v>1010</v>
+        <v>1017</v>
       </c>
       <c r="FI2" s="2" t="s">
-        <v>1012</v>
+        <v>1019</v>
       </c>
       <c r="FJ2" s="2" t="s">
-        <v>1014</v>
+        <v>1021</v>
       </c>
       <c r="FK2" s="2" t="s">
-        <v>1016</v>
+        <v>1023</v>
       </c>
       <c r="FL2" s="2" t="s">
-        <v>1018</v>
+        <v>1025</v>
       </c>
       <c r="FM2" s="2" t="s">
-        <v>1020</v>
+        <v>1027</v>
       </c>
       <c r="FN2" s="2" t="s">
-        <v>1022</v>
+        <v>1029</v>
       </c>
       <c r="FO2" s="2" t="s">
-        <v>1024</v>
+        <v>1031</v>
       </c>
       <c r="FP2" s="2" t="s">
-        <v>1026</v>
+        <v>1033</v>
       </c>
       <c r="FQ2" s="2" t="s">
-        <v>1028</v>
+        <v>1035</v>
       </c>
       <c r="FR2" s="2" t="s">
-        <v>1030</v>
+        <v>1037</v>
       </c>
       <c r="FS2" s="2" t="s">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="FT2" s="2" t="s">
-        <v>1034</v>
+        <v>1041</v>
       </c>
       <c r="FU2" s="2" t="s">
-        <v>1036</v>
+        <v>1043</v>
       </c>
       <c r="FV2" s="2" t="s">
-        <v>1038</v>
+        <v>1045</v>
       </c>
       <c r="FW2" s="2" t="s">
-        <v>1040</v>
+        <v>1047</v>
       </c>
       <c r="FX2" s="2" t="s">
-        <v>1042</v>
+        <v>1049</v>
       </c>
       <c r="FY2" s="2" t="s">
-        <v>1044</v>
+        <v>1051</v>
       </c>
       <c r="FZ2" s="2" t="s">
-        <v>1046</v>
+        <v>1053</v>
       </c>
       <c r="GA2" s="2" t="s">
-        <v>1048</v>
+        <v>1055</v>
       </c>
       <c r="GB2" s="2" t="s">
-        <v>1050</v>
+        <v>1057</v>
       </c>
       <c r="GC2" s="2" t="s">
-        <v>1052</v>
+        <v>1059</v>
       </c>
       <c r="GD2" s="2" t="s">
-        <v>1054</v>
+        <v>1061</v>
       </c>
       <c r="GE2" s="2" t="s">
-        <v>1056</v>
+        <v>1063</v>
       </c>
       <c r="GF2" s="2" t="s">
-        <v>1058</v>
+        <v>1065</v>
       </c>
       <c r="GG2" s="2" t="s">
-        <v>1060</v>
+        <v>1067</v>
       </c>
       <c r="GH2" s="2" t="s">
-        <v>1062</v>
+        <v>1069</v>
       </c>
       <c r="GI2" s="2" t="s">
-        <v>1064</v>
+        <v>1071</v>
       </c>
       <c r="GJ2" s="2" t="s">
-        <v>1066</v>
+        <v>1073</v>
       </c>
       <c r="GK2" s="2" t="s">
-        <v>1068</v>
+        <v>1075</v>
       </c>
       <c r="GL2" s="2" t="s">
-        <v>1070</v>
+        <v>1077</v>
       </c>
       <c r="GM2" s="2" t="s">
-        <v>1072</v>
+        <v>1079</v>
       </c>
       <c r="GN2" s="2" t="s">
-        <v>1074</v>
+        <v>1081</v>
       </c>
       <c r="GO2" s="2" t="s">
-        <v>1076</v>
+        <v>1083</v>
       </c>
       <c r="GP2" s="2" t="s">
-        <v>1078</v>
+        <v>1085</v>
       </c>
       <c r="GQ2" s="2" t="s">
-        <v>1080</v>
+        <v>1087</v>
       </c>
       <c r="GR2" s="2" t="s">
-        <v>1082</v>
+        <v>1089</v>
       </c>
       <c r="GS2" s="2" t="s">
-        <v>1084</v>
+        <v>1091</v>
       </c>
       <c r="GT2" s="2" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="GU2" s="2" t="s">
-        <v>1088</v>
+        <v>1095</v>
       </c>
       <c r="GV2" s="2" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="GW2" s="2" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="GX2" s="2" t="s">
-        <v>1097</v>
+        <v>1104</v>
       </c>
       <c r="GY2" s="2" t="s">
-        <v>1099</v>
+        <v>1106</v>
       </c>
       <c r="GZ2" s="2" t="s">
-        <v>1101</v>
+        <v>1108</v>
       </c>
       <c r="HA2" s="2" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="HB2" s="2" t="s">
-        <v>1105</v>
+        <v>1112</v>
       </c>
       <c r="HC2" s="2" t="s">
-        <v>1107</v>
+        <v>1114</v>
       </c>
       <c r="HD2" s="2" t="s">
-        <v>1109</v>
+        <v>1116</v>
       </c>
       <c r="HE2" s="2" t="s">
-        <v>1111</v>
+        <v>1118</v>
       </c>
       <c r="HF2" s="2" t="s">
-        <v>1113</v>
+        <v>1120</v>
       </c>
       <c r="HG2" s="2" t="s">
-        <v>1115</v>
+        <v>1122</v>
       </c>
       <c r="HH2" s="2" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="HI2" s="2" t="s">
-        <v>1119</v>
+        <v>1126</v>
       </c>
       <c r="HJ2" s="2" t="s">
-        <v>1121</v>
+        <v>1128</v>
       </c>
       <c r="HK2" s="2" t="s">
-        <v>1123</v>
+        <v>1130</v>
       </c>
       <c r="HL2" s="2" t="s">
-        <v>1125</v>
+        <v>1132</v>
       </c>
       <c r="HM2" s="2" t="s">
-        <v>1127</v>
+        <v>1134</v>
       </c>
       <c r="HN2" s="2" t="s">
-        <v>1129</v>
+        <v>1136</v>
       </c>
       <c r="HO2" s="2" t="s">
-        <v>1131</v>
+        <v>1138</v>
       </c>
       <c r="HP2" s="2" t="s">
-        <v>1133</v>
+        <v>1140</v>
       </c>
       <c r="HQ2" s="2" t="s">
-        <v>1135</v>
+        <v>1142</v>
       </c>
       <c r="HR2" s="2" t="s">
-        <v>1137</v>
+        <v>1144</v>
       </c>
       <c r="HS2" s="2" t="s">
-        <v>1139</v>
+        <v>1146</v>
       </c>
       <c r="HT2" s="2" t="s">
-        <v>1141</v>
+        <v>1148</v>
       </c>
       <c r="HU2" s="2" t="s">
-        <v>1143</v>
+        <v>1150</v>
       </c>
       <c r="HV2" s="2" t="s">
-        <v>1145</v>
+        <v>1152</v>
       </c>
       <c r="HW2" s="2" t="s">
-        <v>1147</v>
+        <v>1154</v>
       </c>
       <c r="HX2" s="2" t="s">
-        <v>1149</v>
+        <v>1156</v>
       </c>
       <c r="HY2" s="2" t="s">
-        <v>1151</v>
+        <v>1158</v>
       </c>
       <c r="HZ2" s="2" t="s">
-        <v>1153</v>
+        <v>1160</v>
       </c>
       <c r="IA2" s="2" t="s">
-        <v>1155</v>
+        <v>1162</v>
       </c>
       <c r="IB2" s="2" t="s">
-        <v>1157</v>
+        <v>1164</v>
       </c>
       <c r="IC2" s="2" t="s">
-        <v>1159</v>
+        <v>1166</v>
       </c>
       <c r="ID2" s="2" t="s">
-        <v>1161</v>
+        <v>1168</v>
       </c>
       <c r="IE2" s="2" t="s">
-        <v>1163</v>
+        <v>1170</v>
       </c>
       <c r="IF2" s="2" t="s">
-        <v>1165</v>
+        <v>1172</v>
       </c>
       <c r="IG2" s="2" t="s">
-        <v>1167</v>
+        <v>1174</v>
       </c>
       <c r="IH2" s="2" t="s">
-        <v>1169</v>
+        <v>1176</v>
       </c>
       <c r="II2" s="2" t="s">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="IJ2" s="2" t="s">
-        <v>1173</v>
+        <v>1180</v>
       </c>
       <c r="IK2" s="2" t="s">
-        <v>1175</v>
+        <v>1182</v>
       </c>
       <c r="IL2" s="2" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="IM2" s="2" t="s">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="IN2" s="2" t="s">
-        <v>1181</v>
+        <v>1188</v>
       </c>
       <c r="IO2" s="2" t="s">
-        <v>1183</v>
+        <v>1190</v>
       </c>
       <c r="IP2" s="2" t="s">
-        <v>1185</v>
+        <v>1192</v>
       </c>
       <c r="IQ2" s="2" t="s">
-        <v>1187</v>
+        <v>1194</v>
       </c>
       <c r="IR2" s="2" t="s">
-        <v>1189</v>
+        <v>1196</v>
       </c>
       <c r="IS2" s="2" t="s">
-        <v>1191</v>
+        <v>1198</v>
       </c>
       <c r="IT2" s="2" t="s">
-        <v>1193</v>
+        <v>1200</v>
       </c>
       <c r="IU2" s="2" t="s">
-        <v>1195</v>
+        <v>1202</v>
       </c>
       <c r="IV2" s="2" t="s">
-        <v>1197</v>
+        <v>1204</v>
       </c>
       <c r="IW2" s="2" t="s">
-        <v>1199</v>
+        <v>1206</v>
       </c>
       <c r="IX2" s="2" t="s">
-        <v>1201</v>
+        <v>1208</v>
       </c>
       <c r="IY2" s="2" t="s">
-        <v>1203</v>
+        <v>1210</v>
       </c>
       <c r="IZ2" s="2" t="s">
-        <v>1205</v>
+        <v>1212</v>
       </c>
       <c r="JA2" s="2" t="s">
-        <v>1207</v>
+        <v>1214</v>
       </c>
       <c r="JB2" s="2" t="s">
-        <v>1209</v>
+        <v>1216</v>
       </c>
       <c r="JC2" s="2" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="JD2" s="2" t="s">
-        <v>1213</v>
+        <v>1220</v>
       </c>
       <c r="JE2" s="2" t="s">
-        <v>1215</v>
+        <v>1222</v>
       </c>
       <c r="JF2" s="2" t="s">
-        <v>1217</v>
+        <v>1224</v>
       </c>
       <c r="JG2" s="2" t="s">
-        <v>1219</v>
+        <v>1226</v>
       </c>
       <c r="JH2" s="2" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="JI2" s="2" t="s">
-        <v>1223</v>
+        <v>1230</v>
       </c>
       <c r="JJ2" s="2" t="s">
-        <v>1225</v>
+        <v>1232</v>
       </c>
       <c r="JK2" s="2" t="s">
-        <v>1227</v>
+        <v>1234</v>
       </c>
       <c r="JL2" s="2" t="s">
-        <v>1229</v>
+        <v>1236</v>
       </c>
       <c r="JM2" s="2" t="s">
-        <v>1231</v>
+        <v>1238</v>
       </c>
       <c r="JN2" s="2" t="s">
-        <v>1233</v>
+        <v>1240</v>
       </c>
       <c r="JO2" s="2" t="s">
-        <v>1235</v>
+        <v>1242</v>
       </c>
       <c r="JP2" s="2" t="s">
-        <v>1237</v>
+        <v>1244</v>
       </c>
       <c r="JQ2" s="2" t="s">
-        <v>1239</v>
+        <v>1246</v>
+      </c>
+      <c r="JR2" s="2" t="s">
+        <v>1248</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="16">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3:K101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L101">
       <formula1>trophiclevel</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3:M101">
       <formula1>observedbioticrelationship</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O101">
       <formula1>relationshiptooxygen</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z3:Z101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA3:AA101">
       <formula1>soiltype</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BM3:BM101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BN3:BN101">
       <formula1>sequencequalitycheck</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BQ3:BQ101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BR3:BR101">
       <formula1>16srecovered</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BV3:BV101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BW3:BW101">
       <formula1>assemblyquality</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CJ3:CJ101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CK3:CK101">
       <formula1>surfacematerial</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CL3:CL101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CM3:CM101">
       <formula1>indoorsurface</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CM3:CM101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CN3:CN101">
       <formula1>ventilationtype</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CX3:CX101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CY3:CY101">
       <formula1>growthhabit</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DA3:DA101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DB3:DB101">
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DW3:DW101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DX3:DX101">
       <formula1>frequencyofcleaning</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EO3:EO101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EP3:EP101">
       <formula1>historytillage</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EY3:EY101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EZ3:EZ101">
       <formula1>hostpredictionapproach</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="GV3:GV101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="GW3:GW101">
       <formula1>singlecellorviralparticlelysisapproach</formula1>
     </dataValidation>
   </dataValidations>
@@ -7009,1863 +7050,1888 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="K1:GV289"/>
+  <dimension ref="L1:GW294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="11:204">
-      <c r="K1" t="s">
-        <v>282</v>
-      </c>
+    <row r="1" spans="12:205">
       <c r="L1" t="s">
+        <v>286</v>
+      </c>
+      <c r="M1" t="s">
+        <v>318</v>
+      </c>
+      <c r="O1" t="s">
+        <v>327</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>358</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>468</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>479</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>491</v>
+      </c>
+      <c r="CK1" t="s">
+        <v>522</v>
+      </c>
+      <c r="CM1" t="s">
+        <v>541</v>
+      </c>
+      <c r="CN1" t="s">
+        <v>551</v>
+      </c>
+      <c r="CY1" t="s">
+        <v>576</v>
+      </c>
+      <c r="DB1" t="s">
+        <v>586</v>
+      </c>
+      <c r="DX1" t="s">
+        <v>924</v>
+      </c>
+      <c r="EP1" t="s">
+        <v>965</v>
+      </c>
+      <c r="EZ1" t="s">
+        <v>994</v>
+      </c>
+      <c r="GW1" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="2" spans="12:205">
+      <c r="L2" t="s">
+        <v>287</v>
+      </c>
+      <c r="M2" t="s">
+        <v>319</v>
+      </c>
+      <c r="O2" t="s">
+        <v>328</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>359</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>469</v>
+      </c>
+      <c r="BR2" t="s">
+        <v>480</v>
+      </c>
+      <c r="BW2" t="s">
+        <v>492</v>
+      </c>
+      <c r="CK2" t="s">
+        <v>523</v>
+      </c>
+      <c r="CM2" t="s">
+        <v>542</v>
+      </c>
+      <c r="CN2" t="s">
+        <v>552</v>
+      </c>
+      <c r="CY2" t="s">
+        <v>577</v>
+      </c>
+      <c r="DB2" t="s">
+        <v>587</v>
+      </c>
+      <c r="DX2" t="s">
+        <v>925</v>
+      </c>
+      <c r="EP2" t="s">
+        <v>966</v>
+      </c>
+      <c r="EZ2" t="s">
+        <v>995</v>
+      </c>
+      <c r="GW2" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="3" spans="12:205">
+      <c r="L3" t="s">
+        <v>288</v>
+      </c>
+      <c r="M3" t="s">
+        <v>320</v>
+      </c>
+      <c r="O3" t="s">
+        <v>329</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>360</v>
+      </c>
+      <c r="BN3" t="s">
+        <v>470</v>
+      </c>
+      <c r="BW3" t="s">
+        <v>493</v>
+      </c>
+      <c r="CK3" t="s">
+        <v>524</v>
+      </c>
+      <c r="CM3" t="s">
+        <v>543</v>
+      </c>
+      <c r="CN3" t="s">
+        <v>553</v>
+      </c>
+      <c r="CY3" t="s">
+        <v>578</v>
+      </c>
+      <c r="DB3" t="s">
+        <v>588</v>
+      </c>
+      <c r="DX3" t="s">
+        <v>926</v>
+      </c>
+      <c r="EP3" t="s">
+        <v>967</v>
+      </c>
+      <c r="EZ3" t="s">
+        <v>996</v>
+      </c>
+      <c r="GW3" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="4" spans="12:205">
+      <c r="L4" t="s">
+        <v>289</v>
+      </c>
+      <c r="M4" t="s">
+        <v>321</v>
+      </c>
+      <c r="O4" t="s">
+        <v>330</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>361</v>
+      </c>
+      <c r="CK4" t="s">
+        <v>525</v>
+      </c>
+      <c r="CM4" t="s">
+        <v>544</v>
+      </c>
+      <c r="CY4" t="s">
+        <v>579</v>
+      </c>
+      <c r="DB4" t="s">
+        <v>589</v>
+      </c>
+      <c r="DX4" t="s">
+        <v>927</v>
+      </c>
+      <c r="EP4" t="s">
+        <v>968</v>
+      </c>
+      <c r="EZ4" t="s">
+        <v>997</v>
+      </c>
+      <c r="GW4" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="5" spans="12:205">
+      <c r="L5" t="s">
+        <v>290</v>
+      </c>
+      <c r="M5" t="s">
+        <v>322</v>
+      </c>
+      <c r="O5" t="s">
+        <v>331</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>362</v>
+      </c>
+      <c r="CK5" t="s">
+        <v>526</v>
+      </c>
+      <c r="CM5" t="s">
+        <v>545</v>
+      </c>
+      <c r="DB5" t="s">
+        <v>590</v>
+      </c>
+      <c r="DX5" t="s">
+        <v>928</v>
+      </c>
+      <c r="EP5" t="s">
+        <v>969</v>
+      </c>
+      <c r="EZ5" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="6" spans="12:205">
+      <c r="L6" t="s">
+        <v>291</v>
+      </c>
+      <c r="O6" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>363</v>
+      </c>
+      <c r="CK6" t="s">
+        <v>527</v>
+      </c>
+      <c r="CM6" t="s">
+        <v>546</v>
+      </c>
+      <c r="DB6" t="s">
+        <v>591</v>
+      </c>
+      <c r="EP6" t="s">
+        <v>970</v>
+      </c>
+      <c r="EZ6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="12:205">
+      <c r="L7" t="s">
+        <v>292</v>
+      </c>
+      <c r="O7" t="s">
+        <v>333</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>364</v>
+      </c>
+      <c r="CK7" t="s">
+        <v>528</v>
+      </c>
+      <c r="CM7" t="s">
+        <v>547</v>
+      </c>
+      <c r="DB7" t="s">
+        <v>592</v>
+      </c>
+      <c r="EP7" t="s">
+        <v>971</v>
+      </c>
+      <c r="EZ7" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="8" spans="12:205">
+      <c r="L8" t="s">
+        <v>293</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>365</v>
+      </c>
+      <c r="CK8" t="s">
+        <v>529</v>
+      </c>
+      <c r="CM8" t="s">
+        <v>548</v>
+      </c>
+      <c r="DB8" t="s">
+        <v>593</v>
+      </c>
+      <c r="EP8" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="9" spans="12:205">
+      <c r="L9" t="s">
+        <v>294</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>366</v>
+      </c>
+      <c r="CK9" t="s">
+        <v>530</v>
+      </c>
+      <c r="DB9" t="s">
+        <v>594</v>
+      </c>
+      <c r="EP9" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="10" spans="12:205">
+      <c r="L10" t="s">
+        <v>295</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>367</v>
+      </c>
+      <c r="CK10" t="s">
+        <v>531</v>
+      </c>
+      <c r="DB10" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="11" spans="12:205">
+      <c r="L11" t="s">
+        <v>296</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>368</v>
+      </c>
+      <c r="CK11" t="s">
+        <v>532</v>
+      </c>
+      <c r="DB11" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="12" spans="12:205">
+      <c r="L12" t="s">
+        <v>297</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>369</v>
+      </c>
+      <c r="CK12" t="s">
+        <v>533</v>
+      </c>
+      <c r="DB12" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="13" spans="12:205">
+      <c r="L13" t="s">
+        <v>298</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>370</v>
+      </c>
+      <c r="CK13" t="s">
+        <v>534</v>
+      </c>
+      <c r="DB13" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="14" spans="12:205">
+      <c r="L14" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>371</v>
+      </c>
+      <c r="CK14" t="s">
+        <v>535</v>
+      </c>
+      <c r="DB14" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="15" spans="12:205">
+      <c r="L15" t="s">
+        <v>300</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>372</v>
+      </c>
+      <c r="CK15" t="s">
+        <v>536</v>
+      </c>
+      <c r="DB15" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="16" spans="12:205">
+      <c r="L16" t="s">
+        <v>301</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>373</v>
+      </c>
+      <c r="DB16" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="17" spans="12:106">
+      <c r="L17" t="s">
+        <v>302</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>374</v>
+      </c>
+      <c r="DB17" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="18" spans="12:106">
+      <c r="L18" t="s">
+        <v>303</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>375</v>
+      </c>
+      <c r="DB18" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="19" spans="12:106">
+      <c r="L19" t="s">
+        <v>304</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>376</v>
+      </c>
+      <c r="DB19" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="20" spans="12:106">
+      <c r="L20" t="s">
+        <v>305</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>377</v>
+      </c>
+      <c r="DB20" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="21" spans="12:106">
+      <c r="L21" t="s">
+        <v>306</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>378</v>
+      </c>
+      <c r="DB21" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="22" spans="12:106">
+      <c r="L22" t="s">
+        <v>307</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>379</v>
+      </c>
+      <c r="DB22" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="23" spans="12:106">
+      <c r="L23" t="s">
+        <v>308</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>380</v>
+      </c>
+      <c r="DB23" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="24" spans="12:106">
+      <c r="L24" t="s">
+        <v>309</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>381</v>
+      </c>
+      <c r="DB24" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="25" spans="12:106">
+      <c r="L25" t="s">
+        <v>310</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>382</v>
+      </c>
+      <c r="DB25" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="26" spans="12:106">
+      <c r="L26" t="s">
+        <v>311</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>383</v>
+      </c>
+      <c r="DB26" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="27" spans="12:106">
+      <c r="L27" t="s">
+        <v>312</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>384</v>
+      </c>
+      <c r="DB27" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="28" spans="12:106">
+      <c r="L28" t="s">
+        <v>313</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>385</v>
+      </c>
+      <c r="DB28" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="29" spans="12:106">
+      <c r="L29" t="s">
         <v>314</v>
       </c>
-      <c r="N1" t="s">
-        <v>323</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>354</v>
-      </c>
-      <c r="BM1" t="s">
-        <v>464</v>
-      </c>
-      <c r="BQ1" t="s">
-        <v>475</v>
-      </c>
-      <c r="BV1" t="s">
-        <v>487</v>
-      </c>
-      <c r="CJ1" t="s">
-        <v>518</v>
-      </c>
-      <c r="CL1" t="s">
-        <v>537</v>
-      </c>
-      <c r="CM1" t="s">
-        <v>547</v>
-      </c>
-      <c r="CX1" t="s">
-        <v>572</v>
-      </c>
-      <c r="DA1" t="s">
-        <v>582</v>
-      </c>
-      <c r="DW1" t="s">
-        <v>915</v>
-      </c>
-      <c r="EO1" t="s">
-        <v>956</v>
-      </c>
-      <c r="EY1" t="s">
-        <v>985</v>
-      </c>
-      <c r="GV1" t="s">
-        <v>1089</v>
-      </c>
-    </row>
-    <row r="2" spans="11:204">
-      <c r="K2" t="s">
-        <v>283</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="AA29" t="s">
+        <v>386</v>
+      </c>
+      <c r="DB29" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="30" spans="12:106">
+      <c r="L30" t="s">
         <v>315</v>
       </c>
-      <c r="N2" t="s">
-        <v>324</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>355</v>
-      </c>
-      <c r="BM2" t="s">
-        <v>465</v>
-      </c>
-      <c r="BQ2" t="s">
-        <v>476</v>
-      </c>
-      <c r="BV2" t="s">
-        <v>488</v>
-      </c>
-      <c r="CJ2" t="s">
-        <v>519</v>
-      </c>
-      <c r="CL2" t="s">
-        <v>538</v>
-      </c>
-      <c r="CM2" t="s">
-        <v>548</v>
-      </c>
-      <c r="CX2" t="s">
-        <v>573</v>
-      </c>
-      <c r="DA2" t="s">
-        <v>583</v>
-      </c>
-      <c r="DW2" t="s">
-        <v>916</v>
-      </c>
-      <c r="EO2" t="s">
-        <v>957</v>
-      </c>
-      <c r="EY2" t="s">
-        <v>986</v>
-      </c>
-      <c r="GV2" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="3" spans="11:204">
-      <c r="K3" t="s">
-        <v>284</v>
-      </c>
-      <c r="L3" t="s">
-        <v>316</v>
-      </c>
-      <c r="N3" t="s">
-        <v>325</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>356</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>466</v>
-      </c>
-      <c r="BV3" t="s">
-        <v>489</v>
-      </c>
-      <c r="CJ3" t="s">
-        <v>520</v>
-      </c>
-      <c r="CL3" t="s">
-        <v>539</v>
-      </c>
-      <c r="CM3" t="s">
-        <v>549</v>
-      </c>
-      <c r="CX3" t="s">
-        <v>574</v>
-      </c>
-      <c r="DA3" t="s">
-        <v>584</v>
-      </c>
-      <c r="DW3" t="s">
-        <v>917</v>
-      </c>
-      <c r="EO3" t="s">
-        <v>958</v>
-      </c>
-      <c r="EY3" t="s">
-        <v>987</v>
-      </c>
-      <c r="GV3" t="s">
-        <v>1090</v>
-      </c>
-    </row>
-    <row r="4" spans="11:204">
-      <c r="K4" t="s">
-        <v>285</v>
-      </c>
-      <c r="L4" t="s">
-        <v>317</v>
-      </c>
-      <c r="N4" t="s">
-        <v>326</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>357</v>
-      </c>
-      <c r="CJ4" t="s">
-        <v>521</v>
-      </c>
-      <c r="CL4" t="s">
-        <v>540</v>
-      </c>
-      <c r="CX4" t="s">
-        <v>575</v>
-      </c>
-      <c r="DA4" t="s">
-        <v>585</v>
-      </c>
-      <c r="DW4" t="s">
-        <v>918</v>
-      </c>
-      <c r="EO4" t="s">
-        <v>959</v>
-      </c>
-      <c r="EY4" t="s">
-        <v>988</v>
-      </c>
-      <c r="GV4" t="s">
-        <v>1091</v>
-      </c>
-    </row>
-    <row r="5" spans="11:204">
-      <c r="K5" t="s">
-        <v>286</v>
-      </c>
-      <c r="L5" t="s">
-        <v>318</v>
-      </c>
-      <c r="N5" t="s">
-        <v>327</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>358</v>
-      </c>
-      <c r="CJ5" t="s">
-        <v>522</v>
-      </c>
-      <c r="CL5" t="s">
-        <v>541</v>
-      </c>
-      <c r="DA5" t="s">
-        <v>586</v>
-      </c>
-      <c r="DW5" t="s">
-        <v>919</v>
-      </c>
-      <c r="EO5" t="s">
-        <v>960</v>
-      </c>
-      <c r="EY5" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="6" spans="11:204">
-      <c r="K6" t="s">
-        <v>287</v>
-      </c>
-      <c r="N6" t="s">
-        <v>328</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>359</v>
-      </c>
-      <c r="CJ6" t="s">
-        <v>523</v>
-      </c>
-      <c r="CL6" t="s">
-        <v>542</v>
-      </c>
-      <c r="DA6" t="s">
-        <v>587</v>
-      </c>
-      <c r="EO6" t="s">
-        <v>961</v>
-      </c>
-      <c r="EY6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="7" spans="11:204">
-      <c r="K7" t="s">
-        <v>288</v>
-      </c>
-      <c r="N7" t="s">
-        <v>329</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>360</v>
-      </c>
-      <c r="CJ7" t="s">
-        <v>524</v>
-      </c>
-      <c r="CL7" t="s">
-        <v>543</v>
-      </c>
-      <c r="DA7" t="s">
-        <v>588</v>
-      </c>
-      <c r="EO7" t="s">
-        <v>962</v>
-      </c>
-      <c r="EY7" t="s">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="8" spans="11:204">
-      <c r="K8" t="s">
-        <v>289</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>361</v>
-      </c>
-      <c r="CJ8" t="s">
-        <v>525</v>
-      </c>
-      <c r="CL8" t="s">
-        <v>544</v>
-      </c>
-      <c r="DA8" t="s">
-        <v>589</v>
-      </c>
-      <c r="EO8" t="s">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="9" spans="11:204">
-      <c r="K9" t="s">
-        <v>290</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>362</v>
-      </c>
-      <c r="CJ9" t="s">
-        <v>526</v>
-      </c>
-      <c r="DA9" t="s">
-        <v>590</v>
-      </c>
-      <c r="EO9" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="10" spans="11:204">
-      <c r="K10" t="s">
-        <v>291</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>363</v>
-      </c>
-      <c r="CJ10" t="s">
-        <v>527</v>
-      </c>
-      <c r="DA10" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="11" spans="11:204">
-      <c r="K11" t="s">
-        <v>292</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>364</v>
-      </c>
-      <c r="CJ11" t="s">
-        <v>528</v>
-      </c>
-      <c r="DA11" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="12" spans="11:204">
-      <c r="K12" t="s">
-        <v>293</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>365</v>
-      </c>
-      <c r="CJ12" t="s">
-        <v>529</v>
-      </c>
-      <c r="DA12" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="13" spans="11:204">
-      <c r="K13" t="s">
-        <v>294</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>366</v>
-      </c>
-      <c r="CJ13" t="s">
-        <v>530</v>
-      </c>
-      <c r="DA13" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="14" spans="11:204">
-      <c r="K14" t="s">
-        <v>295</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>367</v>
-      </c>
-      <c r="CJ14" t="s">
-        <v>531</v>
-      </c>
-      <c r="DA14" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="15" spans="11:204">
-      <c r="K15" t="s">
-        <v>296</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>368</v>
-      </c>
-      <c r="CJ15" t="s">
-        <v>532</v>
-      </c>
-      <c r="DA15" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="16" spans="11:204">
-      <c r="K16" t="s">
-        <v>297</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>369</v>
-      </c>
-      <c r="DA16" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="17" spans="11:105">
-      <c r="K17" t="s">
-        <v>298</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>370</v>
-      </c>
-      <c r="DA17" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="18" spans="11:105">
-      <c r="K18" t="s">
-        <v>299</v>
-      </c>
-      <c r="Z18" t="s">
-        <v>371</v>
-      </c>
-      <c r="DA18" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="19" spans="11:105">
-      <c r="K19" t="s">
-        <v>300</v>
-      </c>
-      <c r="Z19" t="s">
-        <v>372</v>
-      </c>
-      <c r="DA19" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="20" spans="11:105">
-      <c r="K20" t="s">
-        <v>301</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>373</v>
-      </c>
-      <c r="DA20" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="21" spans="11:105">
-      <c r="K21" t="s">
-        <v>302</v>
-      </c>
-      <c r="Z21" t="s">
-        <v>374</v>
-      </c>
-      <c r="DA21" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="22" spans="11:105">
-      <c r="K22" t="s">
-        <v>303</v>
-      </c>
-      <c r="Z22" t="s">
-        <v>375</v>
-      </c>
-      <c r="DA22" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="23" spans="11:105">
-      <c r="K23" t="s">
-        <v>304</v>
-      </c>
-      <c r="Z23" t="s">
-        <v>376</v>
-      </c>
-      <c r="DA23" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="24" spans="11:105">
-      <c r="K24" t="s">
-        <v>305</v>
-      </c>
-      <c r="Z24" t="s">
-        <v>377</v>
-      </c>
-      <c r="DA24" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="25" spans="11:105">
-      <c r="K25" t="s">
-        <v>306</v>
-      </c>
-      <c r="Z25" t="s">
-        <v>378</v>
-      </c>
-      <c r="DA25" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="26" spans="11:105">
-      <c r="K26" t="s">
-        <v>307</v>
-      </c>
-      <c r="Z26" t="s">
-        <v>379</v>
-      </c>
-      <c r="DA26" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="27" spans="11:105">
-      <c r="K27" t="s">
-        <v>308</v>
-      </c>
-      <c r="Z27" t="s">
-        <v>380</v>
-      </c>
-      <c r="DA27" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="28" spans="11:105">
-      <c r="K28" t="s">
-        <v>309</v>
-      </c>
-      <c r="Z28" t="s">
-        <v>381</v>
-      </c>
-      <c r="DA28" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="29" spans="11:105">
-      <c r="K29" t="s">
-        <v>310</v>
-      </c>
-      <c r="Z29" t="s">
-        <v>382</v>
-      </c>
-      <c r="DA29" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="30" spans="11:105">
-      <c r="K30" t="s">
-        <v>311</v>
-      </c>
-      <c r="Z30" t="s">
-        <v>383</v>
-      </c>
-      <c r="DA30" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="31" spans="11:105">
-      <c r="Z31" t="s">
-        <v>384</v>
-      </c>
-      <c r="DA31" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="32" spans="11:105">
-      <c r="Z32" t="s">
-        <v>385</v>
-      </c>
-      <c r="DA32" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="33" spans="105:105">
-      <c r="DA33" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="34" spans="105:105">
-      <c r="DA34" t="s">
+      <c r="AA30" t="s">
+        <v>387</v>
+      </c>
+      <c r="DB30" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="35" spans="105:105">
-      <c r="DA35" t="s">
+    <row r="31" spans="12:106">
+      <c r="AA31" t="s">
+        <v>388</v>
+      </c>
+      <c r="DB31" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="36" spans="105:105">
-      <c r="DA36" t="s">
+    <row r="32" spans="12:106">
+      <c r="AA32" t="s">
+        <v>389</v>
+      </c>
+      <c r="DB32" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="37" spans="105:105">
-      <c r="DA37" t="s">
+    <row r="33" spans="106:106">
+      <c r="DB33" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="38" spans="105:105">
-      <c r="DA38" t="s">
+    <row r="34" spans="106:106">
+      <c r="DB34" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="39" spans="105:105">
-      <c r="DA39" t="s">
+    <row r="35" spans="106:106">
+      <c r="DB35" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="40" spans="105:105">
-      <c r="DA40" t="s">
+    <row r="36" spans="106:106">
+      <c r="DB36" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="41" spans="105:105">
-      <c r="DA41" t="s">
+    <row r="37" spans="106:106">
+      <c r="DB37" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="42" spans="105:105">
-      <c r="DA42" t="s">
+    <row r="38" spans="106:106">
+      <c r="DB38" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="43" spans="105:105">
-      <c r="DA43" t="s">
+    <row r="39" spans="106:106">
+      <c r="DB39" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="44" spans="105:105">
-      <c r="DA44" t="s">
+    <row r="40" spans="106:106">
+      <c r="DB40" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="45" spans="105:105">
-      <c r="DA45" t="s">
+    <row r="41" spans="106:106">
+      <c r="DB41" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="46" spans="105:105">
-      <c r="DA46" t="s">
+    <row r="42" spans="106:106">
+      <c r="DB42" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="47" spans="105:105">
-      <c r="DA47" t="s">
+    <row r="43" spans="106:106">
+      <c r="DB43" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="48" spans="105:105">
-      <c r="DA48" t="s">
+    <row r="44" spans="106:106">
+      <c r="DB44" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="49" spans="105:105">
-      <c r="DA49" t="s">
+    <row r="45" spans="106:106">
+      <c r="DB45" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="50" spans="105:105">
-      <c r="DA50" t="s">
+    <row r="46" spans="106:106">
+      <c r="DB46" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="51" spans="105:105">
-      <c r="DA51" t="s">
+    <row r="47" spans="106:106">
+      <c r="DB47" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="52" spans="105:105">
-      <c r="DA52" t="s">
+    <row r="48" spans="106:106">
+      <c r="DB48" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="53" spans="105:105">
-      <c r="DA53" t="s">
+    <row r="49" spans="106:106">
+      <c r="DB49" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="54" spans="105:105">
-      <c r="DA54" t="s">
+    <row r="50" spans="106:106">
+      <c r="DB50" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="55" spans="105:105">
-      <c r="DA55" t="s">
+    <row r="51" spans="106:106">
+      <c r="DB51" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="56" spans="105:105">
-      <c r="DA56" t="s">
+    <row r="52" spans="106:106">
+      <c r="DB52" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="57" spans="105:105">
-      <c r="DA57" t="s">
+    <row r="53" spans="106:106">
+      <c r="DB53" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="58" spans="105:105">
-      <c r="DA58" t="s">
+    <row r="54" spans="106:106">
+      <c r="DB54" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="59" spans="105:105">
-      <c r="DA59" t="s">
+    <row r="55" spans="106:106">
+      <c r="DB55" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="60" spans="105:105">
-      <c r="DA60" t="s">
+    <row r="56" spans="106:106">
+      <c r="DB56" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="61" spans="105:105">
-      <c r="DA61" t="s">
+    <row r="57" spans="106:106">
+      <c r="DB57" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="62" spans="105:105">
-      <c r="DA62" t="s">
+    <row r="58" spans="106:106">
+      <c r="DB58" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="63" spans="105:105">
-      <c r="DA63" t="s">
+    <row r="59" spans="106:106">
+      <c r="DB59" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="64" spans="105:105">
-      <c r="DA64" t="s">
+    <row r="60" spans="106:106">
+      <c r="DB60" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="65" spans="105:105">
-      <c r="DA65" t="s">
+    <row r="61" spans="106:106">
+      <c r="DB61" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="66" spans="105:105">
-      <c r="DA66" t="s">
+    <row r="62" spans="106:106">
+      <c r="DB62" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="67" spans="105:105">
-      <c r="DA67" t="s">
+    <row r="63" spans="106:106">
+      <c r="DB63" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="68" spans="105:105">
-      <c r="DA68" t="s">
+    <row r="64" spans="106:106">
+      <c r="DB64" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="69" spans="105:105">
-      <c r="DA69" t="s">
+    <row r="65" spans="106:106">
+      <c r="DB65" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="70" spans="105:105">
-      <c r="DA70" t="s">
+    <row r="66" spans="106:106">
+      <c r="DB66" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="71" spans="105:105">
-      <c r="DA71" t="s">
+    <row r="67" spans="106:106">
+      <c r="DB67" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="72" spans="105:105">
-      <c r="DA72" t="s">
+    <row r="68" spans="106:106">
+      <c r="DB68" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="73" spans="105:105">
-      <c r="DA73" t="s">
+    <row r="69" spans="106:106">
+      <c r="DB69" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="74" spans="105:105">
-      <c r="DA74" t="s">
+    <row r="70" spans="106:106">
+      <c r="DB70" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="75" spans="105:105">
-      <c r="DA75" t="s">
+    <row r="71" spans="106:106">
+      <c r="DB71" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="76" spans="105:105">
-      <c r="DA76" t="s">
+    <row r="72" spans="106:106">
+      <c r="DB72" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="77" spans="105:105">
-      <c r="DA77" t="s">
+    <row r="73" spans="106:106">
+      <c r="DB73" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="78" spans="105:105">
-      <c r="DA78" t="s">
+    <row r="74" spans="106:106">
+      <c r="DB74" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="79" spans="105:105">
-      <c r="DA79" t="s">
+    <row r="75" spans="106:106">
+      <c r="DB75" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="80" spans="105:105">
-      <c r="DA80" t="s">
+    <row r="76" spans="106:106">
+      <c r="DB76" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="81" spans="105:105">
-      <c r="DA81" t="s">
+    <row r="77" spans="106:106">
+      <c r="DB77" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="82" spans="105:105">
-      <c r="DA82" t="s">
+    <row r="78" spans="106:106">
+      <c r="DB78" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="83" spans="105:105">
-      <c r="DA83" t="s">
+    <row r="79" spans="106:106">
+      <c r="DB79" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="84" spans="105:105">
-      <c r="DA84" t="s">
+    <row r="80" spans="106:106">
+      <c r="DB80" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="85" spans="105:105">
-      <c r="DA85" t="s">
+    <row r="81" spans="106:106">
+      <c r="DB81" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="86" spans="105:105">
-      <c r="DA86" t="s">
+    <row r="82" spans="106:106">
+      <c r="DB82" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="87" spans="105:105">
-      <c r="DA87" t="s">
+    <row r="83" spans="106:106">
+      <c r="DB83" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="88" spans="105:105">
-      <c r="DA88" t="s">
+    <row r="84" spans="106:106">
+      <c r="DB84" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="89" spans="105:105">
-      <c r="DA89" t="s">
+    <row r="85" spans="106:106">
+      <c r="DB85" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="90" spans="105:105">
-      <c r="DA90" t="s">
+    <row r="86" spans="106:106">
+      <c r="DB86" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="91" spans="105:105">
-      <c r="DA91" t="s">
+    <row r="87" spans="106:106">
+      <c r="DB87" t="s">
         <v>672</v>
       </c>
     </row>
-    <row r="92" spans="105:105">
-      <c r="DA92" t="s">
+    <row r="88" spans="106:106">
+      <c r="DB88" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="93" spans="105:105">
-      <c r="DA93" t="s">
+    <row r="89" spans="106:106">
+      <c r="DB89" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="94" spans="105:105">
-      <c r="DA94" t="s">
+    <row r="90" spans="106:106">
+      <c r="DB90" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="95" spans="105:105">
-      <c r="DA95" t="s">
+    <row r="91" spans="106:106">
+      <c r="DB91" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="96" spans="105:105">
-      <c r="DA96" t="s">
+    <row r="92" spans="106:106">
+      <c r="DB92" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="97" spans="105:105">
-      <c r="DA97" t="s">
+    <row r="93" spans="106:106">
+      <c r="DB93" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="98" spans="105:105">
-      <c r="DA98" t="s">
+    <row r="94" spans="106:106">
+      <c r="DB94" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="99" spans="105:105">
-      <c r="DA99" t="s">
+    <row r="95" spans="106:106">
+      <c r="DB95" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="100" spans="105:105">
-      <c r="DA100" t="s">
+    <row r="96" spans="106:106">
+      <c r="DB96" t="s">
         <v>681</v>
       </c>
     </row>
-    <row r="101" spans="105:105">
-      <c r="DA101" t="s">
+    <row r="97" spans="106:106">
+      <c r="DB97" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="102" spans="105:105">
-      <c r="DA102" t="s">
+    <row r="98" spans="106:106">
+      <c r="DB98" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="103" spans="105:105">
-      <c r="DA103" t="s">
+    <row r="99" spans="106:106">
+      <c r="DB99" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="104" spans="105:105">
-      <c r="DA104" t="s">
+    <row r="100" spans="106:106">
+      <c r="DB100" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="105" spans="105:105">
-      <c r="DA105" t="s">
+    <row r="101" spans="106:106">
+      <c r="DB101" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="106" spans="105:105">
-      <c r="DA106" t="s">
+    <row r="102" spans="106:106">
+      <c r="DB102" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="107" spans="105:105">
-      <c r="DA107" t="s">
+    <row r="103" spans="106:106">
+      <c r="DB103" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="108" spans="105:105">
-      <c r="DA108" t="s">
+    <row r="104" spans="106:106">
+      <c r="DB104" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="109" spans="105:105">
-      <c r="DA109" t="s">
+    <row r="105" spans="106:106">
+      <c r="DB105" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="110" spans="105:105">
-      <c r="DA110" t="s">
+    <row r="106" spans="106:106">
+      <c r="DB106" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="111" spans="105:105">
-      <c r="DA111" t="s">
+    <row r="107" spans="106:106">
+      <c r="DB107" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="112" spans="105:105">
-      <c r="DA112" t="s">
+    <row r="108" spans="106:106">
+      <c r="DB108" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="113" spans="105:105">
-      <c r="DA113" t="s">
+    <row r="109" spans="106:106">
+      <c r="DB109" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="114" spans="105:105">
-      <c r="DA114" t="s">
+    <row r="110" spans="106:106">
+      <c r="DB110" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="115" spans="105:105">
-      <c r="DA115" t="s">
+    <row r="111" spans="106:106">
+      <c r="DB111" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="116" spans="105:105">
-      <c r="DA116" t="s">
+    <row r="112" spans="106:106">
+      <c r="DB112" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="117" spans="105:105">
-      <c r="DA117" t="s">
+    <row r="113" spans="106:106">
+      <c r="DB113" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="118" spans="105:105">
-      <c r="DA118" t="s">
+    <row r="114" spans="106:106">
+      <c r="DB114" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="119" spans="105:105">
-      <c r="DA119" t="s">
+    <row r="115" spans="106:106">
+      <c r="DB115" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="120" spans="105:105">
-      <c r="DA120" t="s">
+    <row r="116" spans="106:106">
+      <c r="DB116" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="121" spans="105:105">
-      <c r="DA121" t="s">
+    <row r="117" spans="106:106">
+      <c r="DB117" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="122" spans="105:105">
-      <c r="DA122" t="s">
+    <row r="118" spans="106:106">
+      <c r="DB118" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="123" spans="105:105">
-      <c r="DA123" t="s">
+    <row r="119" spans="106:106">
+      <c r="DB119" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="124" spans="105:105">
-      <c r="DA124" t="s">
+    <row r="120" spans="106:106">
+      <c r="DB120" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="125" spans="105:105">
-      <c r="DA125" t="s">
+    <row r="121" spans="106:106">
+      <c r="DB121" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="126" spans="105:105">
-      <c r="DA126" t="s">
+    <row r="122" spans="106:106">
+      <c r="DB122" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="127" spans="105:105">
-      <c r="DA127" t="s">
+    <row r="123" spans="106:106">
+      <c r="DB123" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="128" spans="105:105">
-      <c r="DA128" t="s">
+    <row r="124" spans="106:106">
+      <c r="DB124" t="s">
         <v>709</v>
       </c>
     </row>
-    <row r="129" spans="105:105">
-      <c r="DA129" t="s">
+    <row r="125" spans="106:106">
+      <c r="DB125" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="130" spans="105:105">
-      <c r="DA130" t="s">
+    <row r="126" spans="106:106">
+      <c r="DB126" t="s">
         <v>711</v>
       </c>
     </row>
-    <row r="131" spans="105:105">
-      <c r="DA131" t="s">
+    <row r="127" spans="106:106">
+      <c r="DB127" t="s">
         <v>712</v>
       </c>
     </row>
-    <row r="132" spans="105:105">
-      <c r="DA132" t="s">
+    <row r="128" spans="106:106">
+      <c r="DB128" t="s">
         <v>713</v>
       </c>
     </row>
-    <row r="133" spans="105:105">
-      <c r="DA133" t="s">
+    <row r="129" spans="106:106">
+      <c r="DB129" t="s">
         <v>714</v>
       </c>
     </row>
-    <row r="134" spans="105:105">
-      <c r="DA134" t="s">
+    <row r="130" spans="106:106">
+      <c r="DB130" t="s">
         <v>715</v>
       </c>
     </row>
-    <row r="135" spans="105:105">
-      <c r="DA135" t="s">
+    <row r="131" spans="106:106">
+      <c r="DB131" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="136" spans="105:105">
-      <c r="DA136" t="s">
+    <row r="132" spans="106:106">
+      <c r="DB132" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="137" spans="105:105">
-      <c r="DA137" t="s">
+    <row r="133" spans="106:106">
+      <c r="DB133" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="138" spans="105:105">
-      <c r="DA138" t="s">
+    <row r="134" spans="106:106">
+      <c r="DB134" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="139" spans="105:105">
-      <c r="DA139" t="s">
+    <row r="135" spans="106:106">
+      <c r="DB135" t="s">
         <v>720</v>
       </c>
     </row>
-    <row r="140" spans="105:105">
-      <c r="DA140" t="s">
+    <row r="136" spans="106:106">
+      <c r="DB136" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="141" spans="105:105">
-      <c r="DA141" t="s">
+    <row r="137" spans="106:106">
+      <c r="DB137" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="142" spans="105:105">
-      <c r="DA142" t="s">
+    <row r="138" spans="106:106">
+      <c r="DB138" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="143" spans="105:105">
-      <c r="DA143" t="s">
+    <row r="139" spans="106:106">
+      <c r="DB139" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="144" spans="105:105">
-      <c r="DA144" t="s">
+    <row r="140" spans="106:106">
+      <c r="DB140" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="145" spans="105:105">
-      <c r="DA145" t="s">
+    <row r="141" spans="106:106">
+      <c r="DB141" t="s">
         <v>726</v>
       </c>
     </row>
-    <row r="146" spans="105:105">
-      <c r="DA146" t="s">
+    <row r="142" spans="106:106">
+      <c r="DB142" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="147" spans="105:105">
-      <c r="DA147" t="s">
+    <row r="143" spans="106:106">
+      <c r="DB143" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="148" spans="105:105">
-      <c r="DA148" t="s">
+    <row r="144" spans="106:106">
+      <c r="DB144" t="s">
         <v>729</v>
       </c>
     </row>
-    <row r="149" spans="105:105">
-      <c r="DA149" t="s">
+    <row r="145" spans="106:106">
+      <c r="DB145" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="150" spans="105:105">
-      <c r="DA150" t="s">
+    <row r="146" spans="106:106">
+      <c r="DB146" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="151" spans="105:105">
-      <c r="DA151" t="s">
+    <row r="147" spans="106:106">
+      <c r="DB147" t="s">
         <v>732</v>
       </c>
     </row>
-    <row r="152" spans="105:105">
-      <c r="DA152" t="s">
+    <row r="148" spans="106:106">
+      <c r="DB148" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="153" spans="105:105">
-      <c r="DA153" t="s">
+    <row r="149" spans="106:106">
+      <c r="DB149" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="154" spans="105:105">
-      <c r="DA154" t="s">
+    <row r="150" spans="106:106">
+      <c r="DB150" t="s">
         <v>735</v>
       </c>
     </row>
-    <row r="155" spans="105:105">
-      <c r="DA155" t="s">
+    <row r="151" spans="106:106">
+      <c r="DB151" t="s">
         <v>736</v>
       </c>
     </row>
-    <row r="156" spans="105:105">
-      <c r="DA156" t="s">
+    <row r="152" spans="106:106">
+      <c r="DB152" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="157" spans="105:105">
-      <c r="DA157" t="s">
+    <row r="153" spans="106:106">
+      <c r="DB153" t="s">
         <v>738</v>
       </c>
     </row>
-    <row r="158" spans="105:105">
-      <c r="DA158" t="s">
+    <row r="154" spans="106:106">
+      <c r="DB154" t="s">
         <v>739</v>
       </c>
     </row>
-    <row r="159" spans="105:105">
-      <c r="DA159" t="s">
+    <row r="155" spans="106:106">
+      <c r="DB155" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="160" spans="105:105">
-      <c r="DA160" t="s">
+    <row r="156" spans="106:106">
+      <c r="DB156" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="161" spans="105:105">
-      <c r="DA161" t="s">
+    <row r="157" spans="106:106">
+      <c r="DB157" t="s">
         <v>742</v>
       </c>
     </row>
-    <row r="162" spans="105:105">
-      <c r="DA162" t="s">
+    <row r="158" spans="106:106">
+      <c r="DB158" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="163" spans="105:105">
-      <c r="DA163" t="s">
+    <row r="159" spans="106:106">
+      <c r="DB159" t="s">
         <v>744</v>
       </c>
     </row>
-    <row r="164" spans="105:105">
-      <c r="DA164" t="s">
+    <row r="160" spans="106:106">
+      <c r="DB160" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="165" spans="105:105">
-      <c r="DA165" t="s">
+    <row r="161" spans="106:106">
+      <c r="DB161" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="166" spans="105:105">
-      <c r="DA166" t="s">
+    <row r="162" spans="106:106">
+      <c r="DB162" t="s">
         <v>747</v>
       </c>
     </row>
-    <row r="167" spans="105:105">
-      <c r="DA167" t="s">
+    <row r="163" spans="106:106">
+      <c r="DB163" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="168" spans="105:105">
-      <c r="DA168" t="s">
+    <row r="164" spans="106:106">
+      <c r="DB164" t="s">
         <v>749</v>
       </c>
     </row>
-    <row r="169" spans="105:105">
-      <c r="DA169" t="s">
+    <row r="165" spans="106:106">
+      <c r="DB165" t="s">
         <v>750</v>
       </c>
     </row>
-    <row r="170" spans="105:105">
-      <c r="DA170" t="s">
+    <row r="166" spans="106:106">
+      <c r="DB166" t="s">
         <v>751</v>
       </c>
     </row>
-    <row r="171" spans="105:105">
-      <c r="DA171" t="s">
+    <row r="167" spans="106:106">
+      <c r="DB167" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="172" spans="105:105">
-      <c r="DA172" t="s">
+    <row r="168" spans="106:106">
+      <c r="DB168" t="s">
         <v>753</v>
       </c>
     </row>
-    <row r="173" spans="105:105">
-      <c r="DA173" t="s">
+    <row r="169" spans="106:106">
+      <c r="DB169" t="s">
         <v>754</v>
       </c>
     </row>
-    <row r="174" spans="105:105">
-      <c r="DA174" t="s">
+    <row r="170" spans="106:106">
+      <c r="DB170" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="175" spans="105:105">
-      <c r="DA175" t="s">
+    <row r="171" spans="106:106">
+      <c r="DB171" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="176" spans="105:105">
-      <c r="DA176" t="s">
+    <row r="172" spans="106:106">
+      <c r="DB172" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="177" spans="105:105">
-      <c r="DA177" t="s">
+    <row r="173" spans="106:106">
+      <c r="DB173" t="s">
         <v>758</v>
       </c>
     </row>
-    <row r="178" spans="105:105">
-      <c r="DA178" t="s">
+    <row r="174" spans="106:106">
+      <c r="DB174" t="s">
         <v>759</v>
       </c>
     </row>
-    <row r="179" spans="105:105">
-      <c r="DA179" t="s">
+    <row r="175" spans="106:106">
+      <c r="DB175" t="s">
         <v>760</v>
       </c>
     </row>
-    <row r="180" spans="105:105">
-      <c r="DA180" t="s">
+    <row r="176" spans="106:106">
+      <c r="DB176" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="181" spans="105:105">
-      <c r="DA181" t="s">
+    <row r="177" spans="106:106">
+      <c r="DB177" t="s">
         <v>762</v>
       </c>
     </row>
-    <row r="182" spans="105:105">
-      <c r="DA182" t="s">
+    <row r="178" spans="106:106">
+      <c r="DB178" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="183" spans="105:105">
-      <c r="DA183" t="s">
+    <row r="179" spans="106:106">
+      <c r="DB179" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="184" spans="105:105">
-      <c r="DA184" t="s">
+    <row r="180" spans="106:106">
+      <c r="DB180" t="s">
         <v>765</v>
       </c>
     </row>
-    <row r="185" spans="105:105">
-      <c r="DA185" t="s">
+    <row r="181" spans="106:106">
+      <c r="DB181" t="s">
         <v>766</v>
       </c>
     </row>
-    <row r="186" spans="105:105">
-      <c r="DA186" t="s">
+    <row r="182" spans="106:106">
+      <c r="DB182" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="187" spans="105:105">
-      <c r="DA187" t="s">
+    <row r="183" spans="106:106">
+      <c r="DB183" t="s">
         <v>768</v>
       </c>
     </row>
-    <row r="188" spans="105:105">
-      <c r="DA188" t="s">
+    <row r="184" spans="106:106">
+      <c r="DB184" t="s">
         <v>769</v>
       </c>
     </row>
-    <row r="189" spans="105:105">
-      <c r="DA189" t="s">
+    <row r="185" spans="106:106">
+      <c r="DB185" t="s">
         <v>770</v>
       </c>
     </row>
-    <row r="190" spans="105:105">
-      <c r="DA190" t="s">
+    <row r="186" spans="106:106">
+      <c r="DB186" t="s">
         <v>771</v>
       </c>
     </row>
-    <row r="191" spans="105:105">
-      <c r="DA191" t="s">
+    <row r="187" spans="106:106">
+      <c r="DB187" t="s">
         <v>772</v>
       </c>
     </row>
-    <row r="192" spans="105:105">
-      <c r="DA192" t="s">
+    <row r="188" spans="106:106">
+      <c r="DB188" t="s">
         <v>773</v>
       </c>
     </row>
-    <row r="193" spans="105:105">
-      <c r="DA193" t="s">
+    <row r="189" spans="106:106">
+      <c r="DB189" t="s">
         <v>774</v>
       </c>
     </row>
-    <row r="194" spans="105:105">
-      <c r="DA194" t="s">
+    <row r="190" spans="106:106">
+      <c r="DB190" t="s">
         <v>775</v>
       </c>
     </row>
-    <row r="195" spans="105:105">
-      <c r="DA195" t="s">
+    <row r="191" spans="106:106">
+      <c r="DB191" t="s">
         <v>776</v>
       </c>
     </row>
-    <row r="196" spans="105:105">
-      <c r="DA196" t="s">
+    <row r="192" spans="106:106">
+      <c r="DB192" t="s">
         <v>777</v>
       </c>
     </row>
-    <row r="197" spans="105:105">
-      <c r="DA197" t="s">
+    <row r="193" spans="106:106">
+      <c r="DB193" t="s">
         <v>778</v>
       </c>
     </row>
-    <row r="198" spans="105:105">
-      <c r="DA198" t="s">
+    <row r="194" spans="106:106">
+      <c r="DB194" t="s">
         <v>779</v>
       </c>
     </row>
-    <row r="199" spans="105:105">
-      <c r="DA199" t="s">
+    <row r="195" spans="106:106">
+      <c r="DB195" t="s">
         <v>780</v>
       </c>
     </row>
-    <row r="200" spans="105:105">
-      <c r="DA200" t="s">
+    <row r="196" spans="106:106">
+      <c r="DB196" t="s">
         <v>781</v>
       </c>
     </row>
-    <row r="201" spans="105:105">
-      <c r="DA201" t="s">
+    <row r="197" spans="106:106">
+      <c r="DB197" t="s">
         <v>782</v>
       </c>
     </row>
-    <row r="202" spans="105:105">
-      <c r="DA202" t="s">
+    <row r="198" spans="106:106">
+      <c r="DB198" t="s">
         <v>783</v>
       </c>
     </row>
-    <row r="203" spans="105:105">
-      <c r="DA203" t="s">
+    <row r="199" spans="106:106">
+      <c r="DB199" t="s">
         <v>784</v>
       </c>
     </row>
-    <row r="204" spans="105:105">
-      <c r="DA204" t="s">
+    <row r="200" spans="106:106">
+      <c r="DB200" t="s">
         <v>785</v>
       </c>
     </row>
-    <row r="205" spans="105:105">
-      <c r="DA205" t="s">
+    <row r="201" spans="106:106">
+      <c r="DB201" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="206" spans="105:105">
-      <c r="DA206" t="s">
+    <row r="202" spans="106:106">
+      <c r="DB202" t="s">
         <v>787</v>
       </c>
     </row>
-    <row r="207" spans="105:105">
-      <c r="DA207" t="s">
+    <row r="203" spans="106:106">
+      <c r="DB203" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="208" spans="105:105">
-      <c r="DA208" t="s">
+    <row r="204" spans="106:106">
+      <c r="DB204" t="s">
         <v>789</v>
       </c>
     </row>
-    <row r="209" spans="105:105">
-      <c r="DA209" t="s">
+    <row r="205" spans="106:106">
+      <c r="DB205" t="s">
         <v>790</v>
       </c>
     </row>
-    <row r="210" spans="105:105">
-      <c r="DA210" t="s">
+    <row r="206" spans="106:106">
+      <c r="DB206" t="s">
         <v>791</v>
       </c>
     </row>
-    <row r="211" spans="105:105">
-      <c r="DA211" t="s">
+    <row r="207" spans="106:106">
+      <c r="DB207" t="s">
         <v>792</v>
       </c>
     </row>
-    <row r="212" spans="105:105">
-      <c r="DA212" t="s">
+    <row r="208" spans="106:106">
+      <c r="DB208" t="s">
         <v>793</v>
       </c>
     </row>
-    <row r="213" spans="105:105">
-      <c r="DA213" t="s">
+    <row r="209" spans="106:106">
+      <c r="DB209" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="214" spans="105:105">
-      <c r="DA214" t="s">
+    <row r="210" spans="106:106">
+      <c r="DB210" t="s">
         <v>795</v>
       </c>
     </row>
-    <row r="215" spans="105:105">
-      <c r="DA215" t="s">
+    <row r="211" spans="106:106">
+      <c r="DB211" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="216" spans="105:105">
-      <c r="DA216" t="s">
+    <row r="212" spans="106:106">
+      <c r="DB212" t="s">
         <v>797</v>
       </c>
     </row>
-    <row r="217" spans="105:105">
-      <c r="DA217" t="s">
+    <row r="213" spans="106:106">
+      <c r="DB213" t="s">
         <v>798</v>
       </c>
     </row>
-    <row r="218" spans="105:105">
-      <c r="DA218" t="s">
+    <row r="214" spans="106:106">
+      <c r="DB214" t="s">
         <v>799</v>
       </c>
     </row>
-    <row r="219" spans="105:105">
-      <c r="DA219" t="s">
+    <row r="215" spans="106:106">
+      <c r="DB215" t="s">
         <v>800</v>
       </c>
     </row>
-    <row r="220" spans="105:105">
-      <c r="DA220" t="s">
+    <row r="216" spans="106:106">
+      <c r="DB216" t="s">
         <v>801</v>
       </c>
     </row>
-    <row r="221" spans="105:105">
-      <c r="DA221" t="s">
+    <row r="217" spans="106:106">
+      <c r="DB217" t="s">
         <v>802</v>
       </c>
     </row>
-    <row r="222" spans="105:105">
-      <c r="DA222" t="s">
+    <row r="218" spans="106:106">
+      <c r="DB218" t="s">
         <v>803</v>
       </c>
     </row>
-    <row r="223" spans="105:105">
-      <c r="DA223" t="s">
+    <row r="219" spans="106:106">
+      <c r="DB219" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="224" spans="105:105">
-      <c r="DA224" t="s">
+    <row r="220" spans="106:106">
+      <c r="DB220" t="s">
         <v>805</v>
       </c>
     </row>
-    <row r="225" spans="105:105">
-      <c r="DA225" t="s">
+    <row r="221" spans="106:106">
+      <c r="DB221" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="226" spans="105:105">
-      <c r="DA226" t="s">
+    <row r="222" spans="106:106">
+      <c r="DB222" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="227" spans="105:105">
-      <c r="DA227" t="s">
+    <row r="223" spans="106:106">
+      <c r="DB223" t="s">
         <v>808</v>
       </c>
     </row>
-    <row r="228" spans="105:105">
-      <c r="DA228" t="s">
+    <row r="224" spans="106:106">
+      <c r="DB224" t="s">
         <v>809</v>
       </c>
     </row>
-    <row r="229" spans="105:105">
-      <c r="DA229" t="s">
+    <row r="225" spans="106:106">
+      <c r="DB225" t="s">
         <v>810</v>
       </c>
     </row>
-    <row r="230" spans="105:105">
-      <c r="DA230" t="s">
+    <row r="226" spans="106:106">
+      <c r="DB226" t="s">
         <v>811</v>
       </c>
     </row>
-    <row r="231" spans="105:105">
-      <c r="DA231" t="s">
+    <row r="227" spans="106:106">
+      <c r="DB227" t="s">
         <v>812</v>
       </c>
     </row>
-    <row r="232" spans="105:105">
-      <c r="DA232" t="s">
+    <row r="228" spans="106:106">
+      <c r="DB228" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="233" spans="105:105">
-      <c r="DA233" t="s">
+    <row r="229" spans="106:106">
+      <c r="DB229" t="s">
         <v>814</v>
       </c>
     </row>
-    <row r="234" spans="105:105">
-      <c r="DA234" t="s">
+    <row r="230" spans="106:106">
+      <c r="DB230" t="s">
         <v>815</v>
       </c>
     </row>
-    <row r="235" spans="105:105">
-      <c r="DA235" t="s">
+    <row r="231" spans="106:106">
+      <c r="DB231" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="236" spans="105:105">
-      <c r="DA236" t="s">
+    <row r="232" spans="106:106">
+      <c r="DB232" t="s">
         <v>817</v>
       </c>
     </row>
-    <row r="237" spans="105:105">
-      <c r="DA237" t="s">
+    <row r="233" spans="106:106">
+      <c r="DB233" t="s">
         <v>818</v>
       </c>
     </row>
-    <row r="238" spans="105:105">
-      <c r="DA238" t="s">
+    <row r="234" spans="106:106">
+      <c r="DB234" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="239" spans="105:105">
-      <c r="DA239" t="s">
+    <row r="235" spans="106:106">
+      <c r="DB235" t="s">
         <v>820</v>
       </c>
     </row>
-    <row r="240" spans="105:105">
-      <c r="DA240" t="s">
+    <row r="236" spans="106:106">
+      <c r="DB236" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="241" spans="105:105">
-      <c r="DA241" t="s">
+    <row r="237" spans="106:106">
+      <c r="DB237" t="s">
         <v>822</v>
       </c>
     </row>
-    <row r="242" spans="105:105">
-      <c r="DA242" t="s">
+    <row r="238" spans="106:106">
+      <c r="DB238" t="s">
         <v>823</v>
       </c>
     </row>
-    <row r="243" spans="105:105">
-      <c r="DA243" t="s">
+    <row r="239" spans="106:106">
+      <c r="DB239" t="s">
         <v>824</v>
       </c>
     </row>
-    <row r="244" spans="105:105">
-      <c r="DA244" t="s">
+    <row r="240" spans="106:106">
+      <c r="DB240" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="245" spans="105:105">
-      <c r="DA245" t="s">
+    <row r="241" spans="106:106">
+      <c r="DB241" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="246" spans="105:105">
-      <c r="DA246" t="s">
+    <row r="242" spans="106:106">
+      <c r="DB242" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="247" spans="105:105">
-      <c r="DA247" t="s">
+    <row r="243" spans="106:106">
+      <c r="DB243" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="248" spans="105:105">
-      <c r="DA248" t="s">
+    <row r="244" spans="106:106">
+      <c r="DB244" t="s">
         <v>829</v>
       </c>
     </row>
-    <row r="249" spans="105:105">
-      <c r="DA249" t="s">
+    <row r="245" spans="106:106">
+      <c r="DB245" t="s">
         <v>830</v>
       </c>
     </row>
-    <row r="250" spans="105:105">
-      <c r="DA250" t="s">
+    <row r="246" spans="106:106">
+      <c r="DB246" t="s">
         <v>831</v>
       </c>
     </row>
-    <row r="251" spans="105:105">
-      <c r="DA251" t="s">
+    <row r="247" spans="106:106">
+      <c r="DB247" t="s">
         <v>832</v>
       </c>
     </row>
-    <row r="252" spans="105:105">
-      <c r="DA252" t="s">
+    <row r="248" spans="106:106">
+      <c r="DB248" t="s">
         <v>833</v>
       </c>
     </row>
-    <row r="253" spans="105:105">
-      <c r="DA253" t="s">
+    <row r="249" spans="106:106">
+      <c r="DB249" t="s">
         <v>834</v>
       </c>
     </row>
-    <row r="254" spans="105:105">
-      <c r="DA254" t="s">
+    <row r="250" spans="106:106">
+      <c r="DB250" t="s">
         <v>835</v>
       </c>
     </row>
-    <row r="255" spans="105:105">
-      <c r="DA255" t="s">
+    <row r="251" spans="106:106">
+      <c r="DB251" t="s">
         <v>836</v>
       </c>
     </row>
-    <row r="256" spans="105:105">
-      <c r="DA256" t="s">
+    <row r="252" spans="106:106">
+      <c r="DB252" t="s">
         <v>837</v>
       </c>
     </row>
-    <row r="257" spans="105:105">
-      <c r="DA257" t="s">
+    <row r="253" spans="106:106">
+      <c r="DB253" t="s">
         <v>838</v>
       </c>
     </row>
-    <row r="258" spans="105:105">
-      <c r="DA258" t="s">
+    <row r="254" spans="106:106">
+      <c r="DB254" t="s">
         <v>839</v>
       </c>
     </row>
-    <row r="259" spans="105:105">
-      <c r="DA259" t="s">
+    <row r="255" spans="106:106">
+      <c r="DB255" t="s">
         <v>840</v>
       </c>
     </row>
-    <row r="260" spans="105:105">
-      <c r="DA260" t="s">
+    <row r="256" spans="106:106">
+      <c r="DB256" t="s">
         <v>841</v>
       </c>
     </row>
-    <row r="261" spans="105:105">
-      <c r="DA261" t="s">
+    <row r="257" spans="106:106">
+      <c r="DB257" t="s">
         <v>842</v>
       </c>
     </row>
-    <row r="262" spans="105:105">
-      <c r="DA262" t="s">
+    <row r="258" spans="106:106">
+      <c r="DB258" t="s">
         <v>843</v>
       </c>
     </row>
-    <row r="263" spans="105:105">
-      <c r="DA263" t="s">
+    <row r="259" spans="106:106">
+      <c r="DB259" t="s">
         <v>844</v>
       </c>
     </row>
-    <row r="264" spans="105:105">
-      <c r="DA264" t="s">
+    <row r="260" spans="106:106">
+      <c r="DB260" t="s">
         <v>845</v>
       </c>
     </row>
-    <row r="265" spans="105:105">
-      <c r="DA265" t="s">
+    <row r="261" spans="106:106">
+      <c r="DB261" t="s">
         <v>846</v>
       </c>
     </row>
-    <row r="266" spans="105:105">
-      <c r="DA266" t="s">
+    <row r="262" spans="106:106">
+      <c r="DB262" t="s">
         <v>847</v>
       </c>
     </row>
-    <row r="267" spans="105:105">
-      <c r="DA267" t="s">
+    <row r="263" spans="106:106">
+      <c r="DB263" t="s">
         <v>848</v>
       </c>
     </row>
-    <row r="268" spans="105:105">
-      <c r="DA268" t="s">
+    <row r="264" spans="106:106">
+      <c r="DB264" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="269" spans="105:105">
-      <c r="DA269" t="s">
+    <row r="265" spans="106:106">
+      <c r="DB265" t="s">
         <v>850</v>
       </c>
     </row>
-    <row r="270" spans="105:105">
-      <c r="DA270" t="s">
+    <row r="266" spans="106:106">
+      <c r="DB266" t="s">
         <v>851</v>
       </c>
     </row>
-    <row r="271" spans="105:105">
-      <c r="DA271" t="s">
+    <row r="267" spans="106:106">
+      <c r="DB267" t="s">
         <v>852</v>
       </c>
     </row>
-    <row r="272" spans="105:105">
-      <c r="DA272" t="s">
+    <row r="268" spans="106:106">
+      <c r="DB268" t="s">
         <v>853</v>
       </c>
     </row>
-    <row r="273" spans="105:105">
-      <c r="DA273" t="s">
+    <row r="269" spans="106:106">
+      <c r="DB269" t="s">
         <v>854</v>
       </c>
     </row>
-    <row r="274" spans="105:105">
-      <c r="DA274" t="s">
+    <row r="270" spans="106:106">
+      <c r="DB270" t="s">
         <v>855</v>
       </c>
     </row>
-    <row r="275" spans="105:105">
-      <c r="DA275" t="s">
+    <row r="271" spans="106:106">
+      <c r="DB271" t="s">
         <v>856</v>
       </c>
     </row>
-    <row r="276" spans="105:105">
-      <c r="DA276" t="s">
+    <row r="272" spans="106:106">
+      <c r="DB272" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="277" spans="105:105">
-      <c r="DA277" t="s">
+    <row r="273" spans="106:106">
+      <c r="DB273" t="s">
         <v>858</v>
       </c>
     </row>
-    <row r="278" spans="105:105">
-      <c r="DA278" t="s">
+    <row r="274" spans="106:106">
+      <c r="DB274" t="s">
         <v>859</v>
       </c>
     </row>
-    <row r="279" spans="105:105">
-      <c r="DA279" t="s">
+    <row r="275" spans="106:106">
+      <c r="DB275" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="280" spans="105:105">
-      <c r="DA280" t="s">
+    <row r="276" spans="106:106">
+      <c r="DB276" t="s">
         <v>861</v>
       </c>
     </row>
-    <row r="281" spans="105:105">
-      <c r="DA281" t="s">
+    <row r="277" spans="106:106">
+      <c r="DB277" t="s">
         <v>862</v>
       </c>
     </row>
-    <row r="282" spans="105:105">
-      <c r="DA282" t="s">
+    <row r="278" spans="106:106">
+      <c r="DB278" t="s">
         <v>863</v>
       </c>
     </row>
-    <row r="283" spans="105:105">
-      <c r="DA283" t="s">
+    <row r="279" spans="106:106">
+      <c r="DB279" t="s">
         <v>864</v>
       </c>
     </row>
-    <row r="284" spans="105:105">
-      <c r="DA284" t="s">
+    <row r="280" spans="106:106">
+      <c r="DB280" t="s">
         <v>865</v>
       </c>
     </row>
-    <row r="285" spans="105:105">
-      <c r="DA285" t="s">
+    <row r="281" spans="106:106">
+      <c r="DB281" t="s">
         <v>866</v>
       </c>
     </row>
-    <row r="286" spans="105:105">
-      <c r="DA286" t="s">
+    <row r="282" spans="106:106">
+      <c r="DB282" t="s">
         <v>867</v>
       </c>
     </row>
-    <row r="287" spans="105:105">
-      <c r="DA287" t="s">
+    <row r="283" spans="106:106">
+      <c r="DB283" t="s">
         <v>868</v>
       </c>
     </row>
-    <row r="288" spans="105:105">
-      <c r="DA288" t="s">
+    <row r="284" spans="106:106">
+      <c r="DB284" t="s">
         <v>869</v>
       </c>
     </row>
-    <row r="289" spans="105:105">
-      <c r="DA289" t="s">
+    <row r="285" spans="106:106">
+      <c r="DB285" t="s">
         <v>870</v>
+      </c>
+    </row>
+    <row r="286" spans="106:106">
+      <c r="DB286" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="287" spans="106:106">
+      <c r="DB287" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="288" spans="106:106">
+      <c r="DB288" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="289" spans="106:106">
+      <c r="DB289" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="290" spans="106:106">
+      <c r="DB290" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="291" spans="106:106">
+      <c r="DB291" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="292" spans="106:106">
+      <c r="DB292" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="293" spans="106:106">
+      <c r="DB293" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="294" spans="106:106">
+      <c r="DB294" t="s">
+        <v>879</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000056/metadata_template_ERC000056.xlsx
+++ b/templates/ERC000056/metadata_template_ERC000056.xlsx
@@ -17,35 +17,35 @@
     <sheet name="cv_sample" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="assemblyquality">'cv_sample'!$BW$1:$BW$3</definedName>
+    <definedName name="assemblyquality">'cv_sample'!$BX$1:$BX$3</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="frequencyofcleaning">'cv_sample'!$DX$1:$DX$5</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$DB$1:$DB$294</definedName>
-    <definedName name="growthhabit">'cv_sample'!$CY$1:$CY$4</definedName>
-    <definedName name="historytillage">'cv_sample'!$EP$1:$EP$9</definedName>
-    <definedName name="hostpredictionapproach">'cv_sample'!$EZ$1:$EZ$7</definedName>
-    <definedName name="indoorsurface">'cv_sample'!$CM$1:$CM$8</definedName>
+    <definedName name="frequencyofcleaning">'cv_sample'!$DY$1:$DY$5</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$DC$1:$DC$294</definedName>
+    <definedName name="growthhabit">'cv_sample'!$CZ$1:$CZ$4</definedName>
+    <definedName name="historytillage">'cv_sample'!$EQ$1:$EQ$9</definedName>
+    <definedName name="hostpredictionapproach">'cv_sample'!$FA$1:$FA$7</definedName>
+    <definedName name="indoorsurface">'cv_sample'!$CN$1:$CN$8</definedName>
     <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="observedbioticrelationship">'cv_sample'!$M$1:$M$5</definedName>
+    <definedName name="observedbioticrelationship">'cv_sample'!$N$1:$N$5</definedName>
     <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
-    <definedName name="relationshiptooxygen">'cv_sample'!$O$1:$O$7</definedName>
-    <definedName name="sequencequalitycheck">'cv_sample'!$BN$1:$BN$3</definedName>
-    <definedName name="singlecellorviralparticlelysisapproach">'cv_sample'!$GW$1:$GW$4</definedName>
-    <definedName name="soiltype">'cv_sample'!$AA$1:$AA$32</definedName>
+    <definedName name="relationshiptooxygen">'cv_sample'!$P$1:$P$7</definedName>
+    <definedName name="sequencequalitycheck">'cv_sample'!$BO$1:$BO$3</definedName>
+    <definedName name="singlecellorviralparticlelysisapproach">'cv_sample'!$GX$1:$GX$4</definedName>
+    <definedName name="soiltype">'cv_sample'!$AB$1:$AB$32</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
-    <definedName name="surfacematerial">'cv_sample'!$CK$1:$CK$15</definedName>
-    <definedName name="trophiclevel">'cv_sample'!$L$1:$L$30</definedName>
-    <definedName name="ventilationtype">'cv_sample'!$CN$1:$CN$3</definedName>
+    <definedName name="surfacematerial">'cv_sample'!$CL$1:$CL$15</definedName>
+    <definedName name="trophiclevel">'cv_sample'!$M$1:$M$30</definedName>
+    <definedName name="ventilationtype">'cv_sample'!$CO$1:$CO$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1259" uniqueCount="1249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="1251">
   <si>
     <t>alias</t>
   </si>
@@ -861,6 +861,12 @@
   </si>
   <si>
     <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
+    <t>common_name</t>
+  </si>
+  <si>
+    <t>(Optional) Genbank common name of the organism.  examples: human, mouse.</t>
   </si>
   <si>
     <t>sample_description</t>
@@ -5315,13 +5321,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:JR2"/>
+  <dimension ref="A1:JS2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:278">
+    <row r="1" spans="1:279">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5356,16 +5362,16 @@
         <v>284</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>316</v>
+        <v>286</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>325</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>336</v>
@@ -5401,7 +5407,7 @@
         <v>356</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>390</v>
+        <v>358</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>392</v>
@@ -5518,7 +5524,7 @@
         <v>466</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="BO1" s="1" t="s">
         <v>473</v>
@@ -5530,7 +5536,7 @@
         <v>477</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="BS1" s="1" t="s">
         <v>483</v>
@@ -5545,7 +5551,7 @@
         <v>489</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="BX1" s="1" t="s">
         <v>496</v>
@@ -5587,16 +5593,16 @@
         <v>520</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>537</v>
+        <v>522</v>
       </c>
       <c r="CL1" s="1" t="s">
         <v>539</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="CO1" s="1" t="s">
         <v>556</v>
@@ -5629,7 +5635,7 @@
         <v>574</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="CZ1" s="1" t="s">
         <v>582</v>
@@ -5638,7 +5644,7 @@
         <v>584</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>880</v>
+        <v>586</v>
       </c>
       <c r="DC1" s="1" t="s">
         <v>882</v>
@@ -5704,7 +5710,7 @@
         <v>922</v>
       </c>
       <c r="DX1" s="1" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="DY1" s="1" t="s">
         <v>931</v>
@@ -5758,7 +5764,7 @@
         <v>963</v>
       </c>
       <c r="EP1" s="1" t="s">
-        <v>974</v>
+        <v>965</v>
       </c>
       <c r="EQ1" s="1" t="s">
         <v>976</v>
@@ -5788,7 +5794,7 @@
         <v>992</v>
       </c>
       <c r="EZ1" s="1" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="FA1" s="1" t="s">
         <v>1002</v>
@@ -5935,7 +5941,7 @@
         <v>1096</v>
       </c>
       <c r="GW1" s="1" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="GX1" s="1" t="s">
         <v>1103</v>
@@ -6156,8 +6162,11 @@
       <c r="JR1" s="1" t="s">
         <v>1247</v>
       </c>
-    </row>
-    <row r="2" spans="1:278" ht="150" customHeight="1">
+      <c r="JS1" s="1" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="2" spans="1:279" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>266</v>
       </c>
@@ -6192,16 +6201,16 @@
         <v>285</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>317</v>
+        <v>287</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>326</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>337</v>
@@ -6237,7 +6246,7 @@
         <v>357</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>391</v>
+        <v>359</v>
       </c>
       <c r="AB2" s="2" t="s">
         <v>393</v>
@@ -6354,7 +6363,7 @@
         <v>467</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="BO2" s="2" t="s">
         <v>474</v>
@@ -6366,7 +6375,7 @@
         <v>478</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="BS2" s="2" t="s">
         <v>484</v>
@@ -6381,7 +6390,7 @@
         <v>490</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="BX2" s="2" t="s">
         <v>497</v>
@@ -6423,16 +6432,16 @@
         <v>521</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="CL2" s="2" t="s">
         <v>540</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="CO2" s="2" t="s">
         <v>557</v>
@@ -6465,7 +6474,7 @@
         <v>575</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="CZ2" s="2" t="s">
         <v>583</v>
@@ -6474,7 +6483,7 @@
         <v>585</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>881</v>
+        <v>587</v>
       </c>
       <c r="DC2" s="2" t="s">
         <v>883</v>
@@ -6540,7 +6549,7 @@
         <v>923</v>
       </c>
       <c r="DX2" s="2" t="s">
-        <v>930</v>
+        <v>925</v>
       </c>
       <c r="DY2" s="2" t="s">
         <v>932</v>
@@ -6594,7 +6603,7 @@
         <v>964</v>
       </c>
       <c r="EP2" s="2" t="s">
-        <v>975</v>
+        <v>966</v>
       </c>
       <c r="EQ2" s="2" t="s">
         <v>977</v>
@@ -6624,7 +6633,7 @@
         <v>993</v>
       </c>
       <c r="EZ2" s="2" t="s">
-        <v>1001</v>
+        <v>995</v>
       </c>
       <c r="FA2" s="2" t="s">
         <v>1003</v>
@@ -6771,7 +6780,7 @@
         <v>1097</v>
       </c>
       <c r="GW2" s="2" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="GX2" s="2" t="s">
         <v>1104</v>
@@ -6992,55 +7001,58 @@
       <c r="JR2" s="2" t="s">
         <v>1248</v>
       </c>
+      <c r="JS2" s="2" t="s">
+        <v>1250</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="16">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3:M101">
       <formula1>trophiclevel</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3:M101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N101">
       <formula1>observedbioticrelationship</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:P101">
       <formula1>relationshiptooxygen</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA3:AA101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB3:AB101">
       <formula1>soiltype</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BN3:BN101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BO3:BO101">
       <formula1>sequencequalitycheck</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BR3:BR101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BS3:BS101">
       <formula1>16srecovered</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BW3:BW101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BX3:BX101">
       <formula1>assemblyquality</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CK3:CK101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CL3:CL101">
       <formula1>surfacematerial</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CM3:CM101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CN3:CN101">
       <formula1>indoorsurface</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CN3:CN101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CO3:CO101">
       <formula1>ventilationtype</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CY3:CY101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CZ3:CZ101">
       <formula1>growthhabit</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DB3:DB101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DC3:DC101">
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DX3:DX101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="DY3:DY101">
       <formula1>frequencyofcleaning</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EP3:EP101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EQ3:EQ101">
       <formula1>historytillage</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="EZ3:EZ101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="FA3:FA101">
       <formula1>hostpredictionapproach</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="GW3:GW101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="GX3:GX101">
       <formula1>singlecellorviralparticlelysisapproach</formula1>
     </dataValidation>
   </dataValidations>
@@ -7050,1888 +7062,1888 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="L1:GW294"/>
+  <dimension ref="M1:GX294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="12:205">
-      <c r="L1" t="s">
-        <v>286</v>
-      </c>
+    <row r="1" spans="13:206">
       <c r="M1" t="s">
-        <v>318</v>
-      </c>
-      <c r="O1" t="s">
-        <v>327</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>358</v>
-      </c>
-      <c r="BN1" t="s">
-        <v>468</v>
-      </c>
-      <c r="BR1" t="s">
-        <v>479</v>
-      </c>
-      <c r="BW1" t="s">
-        <v>491</v>
-      </c>
-      <c r="CK1" t="s">
-        <v>522</v>
-      </c>
-      <c r="CM1" t="s">
-        <v>541</v>
+        <v>288</v>
+      </c>
+      <c r="N1" t="s">
+        <v>320</v>
+      </c>
+      <c r="P1" t="s">
+        <v>329</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>360</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>470</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>481</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>493</v>
+      </c>
+      <c r="CL1" t="s">
+        <v>524</v>
       </c>
       <c r="CN1" t="s">
-        <v>551</v>
-      </c>
-      <c r="CY1" t="s">
-        <v>576</v>
-      </c>
-      <c r="DB1" t="s">
-        <v>586</v>
-      </c>
-      <c r="DX1" t="s">
-        <v>924</v>
-      </c>
-      <c r="EP1" t="s">
-        <v>965</v>
-      </c>
-      <c r="EZ1" t="s">
-        <v>994</v>
-      </c>
-      <c r="GW1" t="s">
-        <v>1098</v>
-      </c>
-    </row>
-    <row r="2" spans="12:205">
-      <c r="L2" t="s">
-        <v>287</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="CO1" t="s">
+        <v>553</v>
+      </c>
+      <c r="CZ1" t="s">
+        <v>578</v>
+      </c>
+      <c r="DC1" t="s">
+        <v>588</v>
+      </c>
+      <c r="DY1" t="s">
+        <v>926</v>
+      </c>
+      <c r="EQ1" t="s">
+        <v>967</v>
+      </c>
+      <c r="FA1" t="s">
+        <v>996</v>
+      </c>
+      <c r="GX1" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="2" spans="13:206">
       <c r="M2" t="s">
-        <v>319</v>
-      </c>
-      <c r="O2" t="s">
-        <v>328</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>359</v>
-      </c>
-      <c r="BN2" t="s">
-        <v>469</v>
-      </c>
-      <c r="BR2" t="s">
-        <v>480</v>
-      </c>
-      <c r="BW2" t="s">
-        <v>492</v>
-      </c>
-      <c r="CK2" t="s">
-        <v>523</v>
-      </c>
-      <c r="CM2" t="s">
-        <v>542</v>
+        <v>289</v>
+      </c>
+      <c r="N2" t="s">
+        <v>321</v>
+      </c>
+      <c r="P2" t="s">
+        <v>330</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>361</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>471</v>
+      </c>
+      <c r="BS2" t="s">
+        <v>482</v>
+      </c>
+      <c r="BX2" t="s">
+        <v>494</v>
+      </c>
+      <c r="CL2" t="s">
+        <v>525</v>
       </c>
       <c r="CN2" t="s">
-        <v>552</v>
-      </c>
-      <c r="CY2" t="s">
-        <v>577</v>
-      </c>
-      <c r="DB2" t="s">
-        <v>587</v>
-      </c>
-      <c r="DX2" t="s">
-        <v>925</v>
-      </c>
-      <c r="EP2" t="s">
-        <v>966</v>
-      </c>
-      <c r="EZ2" t="s">
-        <v>995</v>
-      </c>
-      <c r="GW2" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="3" spans="12:205">
-      <c r="L3" t="s">
-        <v>288</v>
-      </c>
+        <v>544</v>
+      </c>
+      <c r="CO2" t="s">
+        <v>554</v>
+      </c>
+      <c r="CZ2" t="s">
+        <v>579</v>
+      </c>
+      <c r="DC2" t="s">
+        <v>589</v>
+      </c>
+      <c r="DY2" t="s">
+        <v>927</v>
+      </c>
+      <c r="EQ2" t="s">
+        <v>968</v>
+      </c>
+      <c r="FA2" t="s">
+        <v>997</v>
+      </c>
+      <c r="GX2" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="3" spans="13:206">
       <c r="M3" t="s">
-        <v>320</v>
-      </c>
-      <c r="O3" t="s">
-        <v>329</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>360</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>470</v>
-      </c>
-      <c r="BW3" t="s">
-        <v>493</v>
-      </c>
-      <c r="CK3" t="s">
-        <v>524</v>
-      </c>
-      <c r="CM3" t="s">
-        <v>543</v>
+        <v>290</v>
+      </c>
+      <c r="N3" t="s">
+        <v>322</v>
+      </c>
+      <c r="P3" t="s">
+        <v>331</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>362</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>472</v>
+      </c>
+      <c r="BX3" t="s">
+        <v>495</v>
+      </c>
+      <c r="CL3" t="s">
+        <v>526</v>
       </c>
       <c r="CN3" t="s">
-        <v>553</v>
-      </c>
-      <c r="CY3" t="s">
-        <v>578</v>
-      </c>
-      <c r="DB3" t="s">
-        <v>588</v>
-      </c>
-      <c r="DX3" t="s">
-        <v>926</v>
-      </c>
-      <c r="EP3" t="s">
-        <v>967</v>
-      </c>
-      <c r="EZ3" t="s">
-        <v>996</v>
-      </c>
-      <c r="GW3" t="s">
-        <v>1099</v>
-      </c>
-    </row>
-    <row r="4" spans="12:205">
-      <c r="L4" t="s">
-        <v>289</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="CO3" t="s">
+        <v>555</v>
+      </c>
+      <c r="CZ3" t="s">
+        <v>580</v>
+      </c>
+      <c r="DC3" t="s">
+        <v>590</v>
+      </c>
+      <c r="DY3" t="s">
+        <v>928</v>
+      </c>
+      <c r="EQ3" t="s">
+        <v>969</v>
+      </c>
+      <c r="FA3" t="s">
+        <v>998</v>
+      </c>
+      <c r="GX3" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="4" spans="13:206">
       <c r="M4" t="s">
-        <v>321</v>
-      </c>
-      <c r="O4" t="s">
-        <v>330</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>361</v>
-      </c>
-      <c r="CK4" t="s">
-        <v>525</v>
-      </c>
-      <c r="CM4" t="s">
-        <v>544</v>
-      </c>
-      <c r="CY4" t="s">
-        <v>579</v>
-      </c>
-      <c r="DB4" t="s">
-        <v>589</v>
-      </c>
-      <c r="DX4" t="s">
-        <v>927</v>
-      </c>
-      <c r="EP4" t="s">
-        <v>968</v>
-      </c>
-      <c r="EZ4" t="s">
-        <v>997</v>
-      </c>
-      <c r="GW4" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="5" spans="12:205">
-      <c r="L5" t="s">
-        <v>290</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="N4" t="s">
+        <v>323</v>
+      </c>
+      <c r="P4" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>363</v>
+      </c>
+      <c r="CL4" t="s">
+        <v>527</v>
+      </c>
+      <c r="CN4" t="s">
+        <v>546</v>
+      </c>
+      <c r="CZ4" t="s">
+        <v>581</v>
+      </c>
+      <c r="DC4" t="s">
+        <v>591</v>
+      </c>
+      <c r="DY4" t="s">
+        <v>929</v>
+      </c>
+      <c r="EQ4" t="s">
+        <v>970</v>
+      </c>
+      <c r="FA4" t="s">
+        <v>999</v>
+      </c>
+      <c r="GX4" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="5" spans="13:206">
       <c r="M5" t="s">
-        <v>322</v>
-      </c>
-      <c r="O5" t="s">
-        <v>331</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>362</v>
-      </c>
-      <c r="CK5" t="s">
-        <v>526</v>
-      </c>
-      <c r="CM5" t="s">
-        <v>545</v>
-      </c>
-      <c r="DB5" t="s">
-        <v>590</v>
-      </c>
-      <c r="DX5" t="s">
-        <v>928</v>
-      </c>
-      <c r="EP5" t="s">
-        <v>969</v>
-      </c>
-      <c r="EZ5" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="6" spans="12:205">
-      <c r="L6" t="s">
-        <v>291</v>
-      </c>
-      <c r="O6" t="s">
-        <v>332</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>363</v>
-      </c>
-      <c r="CK6" t="s">
-        <v>527</v>
-      </c>
-      <c r="CM6" t="s">
-        <v>546</v>
-      </c>
-      <c r="DB6" t="s">
-        <v>591</v>
-      </c>
-      <c r="EP6" t="s">
-        <v>970</v>
-      </c>
-      <c r="EZ6" t="s">
+        <v>292</v>
+      </c>
+      <c r="N5" t="s">
+        <v>324</v>
+      </c>
+      <c r="P5" t="s">
+        <v>333</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>364</v>
+      </c>
+      <c r="CL5" t="s">
+        <v>528</v>
+      </c>
+      <c r="CN5" t="s">
+        <v>547</v>
+      </c>
+      <c r="DC5" t="s">
+        <v>592</v>
+      </c>
+      <c r="DY5" t="s">
+        <v>930</v>
+      </c>
+      <c r="EQ5" t="s">
+        <v>971</v>
+      </c>
+      <c r="FA5" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6" spans="13:206">
+      <c r="M6" t="s">
+        <v>293</v>
+      </c>
+      <c r="P6" t="s">
+        <v>334</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>365</v>
+      </c>
+      <c r="CL6" t="s">
+        <v>529</v>
+      </c>
+      <c r="CN6" t="s">
+        <v>548</v>
+      </c>
+      <c r="DC6" t="s">
+        <v>593</v>
+      </c>
+      <c r="EQ6" t="s">
+        <v>972</v>
+      </c>
+      <c r="FA6" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="7" spans="12:205">
-      <c r="L7" t="s">
-        <v>292</v>
-      </c>
-      <c r="O7" t="s">
-        <v>333</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>364</v>
-      </c>
-      <c r="CK7" t="s">
-        <v>528</v>
-      </c>
-      <c r="CM7" t="s">
-        <v>547</v>
-      </c>
-      <c r="DB7" t="s">
-        <v>592</v>
-      </c>
-      <c r="EP7" t="s">
-        <v>971</v>
-      </c>
-      <c r="EZ7" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="8" spans="12:205">
-      <c r="L8" t="s">
-        <v>293</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>365</v>
-      </c>
-      <c r="CK8" t="s">
-        <v>529</v>
-      </c>
-      <c r="CM8" t="s">
-        <v>548</v>
-      </c>
-      <c r="DB8" t="s">
-        <v>593</v>
-      </c>
-      <c r="EP8" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="9" spans="12:205">
-      <c r="L9" t="s">
+    <row r="7" spans="13:206">
+      <c r="M7" t="s">
         <v>294</v>
       </c>
-      <c r="AA9" t="s">
+      <c r="P7" t="s">
+        <v>335</v>
+      </c>
+      <c r="AB7" t="s">
         <v>366</v>
       </c>
-      <c r="CK9" t="s">
+      <c r="CL7" t="s">
         <v>530</v>
       </c>
-      <c r="DB9" t="s">
+      <c r="CN7" t="s">
+        <v>549</v>
+      </c>
+      <c r="DC7" t="s">
         <v>594</v>
       </c>
-      <c r="EP9" t="s">
+      <c r="EQ7" t="s">
         <v>973</v>
       </c>
-    </row>
-    <row r="10" spans="12:205">
-      <c r="L10" t="s">
+      <c r="FA7" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="8" spans="13:206">
+      <c r="M8" t="s">
         <v>295</v>
       </c>
-      <c r="AA10" t="s">
+      <c r="AB8" t="s">
         <v>367</v>
       </c>
-      <c r="CK10" t="s">
+      <c r="CL8" t="s">
         <v>531</v>
       </c>
-      <c r="DB10" t="s">
+      <c r="CN8" t="s">
+        <v>550</v>
+      </c>
+      <c r="DC8" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="11" spans="12:205">
-      <c r="L11" t="s">
+      <c r="EQ8" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="9" spans="13:206">
+      <c r="M9" t="s">
         <v>296</v>
       </c>
-      <c r="AA11" t="s">
+      <c r="AB9" t="s">
         <v>368</v>
       </c>
-      <c r="CK11" t="s">
+      <c r="CL9" t="s">
         <v>532</v>
       </c>
-      <c r="DB11" t="s">
+      <c r="DC9" t="s">
         <v>596</v>
       </c>
-    </row>
-    <row r="12" spans="12:205">
-      <c r="L12" t="s">
+      <c r="EQ9" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="10" spans="13:206">
+      <c r="M10" t="s">
         <v>297</v>
       </c>
-      <c r="AA12" t="s">
+      <c r="AB10" t="s">
         <v>369</v>
       </c>
-      <c r="CK12" t="s">
+      <c r="CL10" t="s">
         <v>533</v>
       </c>
-      <c r="DB12" t="s">
+      <c r="DC10" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="13" spans="12:205">
-      <c r="L13" t="s">
+    <row r="11" spans="13:206">
+      <c r="M11" t="s">
         <v>298</v>
       </c>
-      <c r="AA13" t="s">
+      <c r="AB11" t="s">
         <v>370</v>
       </c>
-      <c r="CK13" t="s">
+      <c r="CL11" t="s">
         <v>534</v>
       </c>
-      <c r="DB13" t="s">
+      <c r="DC11" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="14" spans="12:205">
-      <c r="L14" t="s">
+    <row r="12" spans="13:206">
+      <c r="M12" t="s">
         <v>299</v>
       </c>
-      <c r="AA14" t="s">
+      <c r="AB12" t="s">
         <v>371</v>
       </c>
-      <c r="CK14" t="s">
+      <c r="CL12" t="s">
         <v>535</v>
       </c>
-      <c r="DB14" t="s">
+      <c r="DC12" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="15" spans="12:205">
-      <c r="L15" t="s">
+    <row r="13" spans="13:206">
+      <c r="M13" t="s">
         <v>300</v>
       </c>
-      <c r="AA15" t="s">
+      <c r="AB13" t="s">
         <v>372</v>
       </c>
-      <c r="CK15" t="s">
+      <c r="CL13" t="s">
         <v>536</v>
       </c>
-      <c r="DB15" t="s">
+      <c r="DC13" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="16" spans="12:205">
-      <c r="L16" t="s">
+    <row r="14" spans="13:206">
+      <c r="M14" t="s">
         <v>301</v>
       </c>
-      <c r="AA16" t="s">
+      <c r="AB14" t="s">
         <v>373</v>
       </c>
-      <c r="DB16" t="s">
+      <c r="CL14" t="s">
+        <v>537</v>
+      </c>
+      <c r="DC14" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="17" spans="12:106">
-      <c r="L17" t="s">
+    <row r="15" spans="13:206">
+      <c r="M15" t="s">
         <v>302</v>
       </c>
-      <c r="AA17" t="s">
+      <c r="AB15" t="s">
         <v>374</v>
       </c>
-      <c r="DB17" t="s">
+      <c r="CL15" t="s">
+        <v>538</v>
+      </c>
+      <c r="DC15" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="18" spans="12:106">
-      <c r="L18" t="s">
+    <row r="16" spans="13:206">
+      <c r="M16" t="s">
         <v>303</v>
       </c>
-      <c r="AA18" t="s">
+      <c r="AB16" t="s">
         <v>375</v>
       </c>
-      <c r="DB18" t="s">
+      <c r="DC16" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="19" spans="12:106">
-      <c r="L19" t="s">
+    <row r="17" spans="13:107">
+      <c r="M17" t="s">
         <v>304</v>
       </c>
-      <c r="AA19" t="s">
+      <c r="AB17" t="s">
         <v>376</v>
       </c>
-      <c r="DB19" t="s">
+      <c r="DC17" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="20" spans="12:106">
-      <c r="L20" t="s">
+    <row r="18" spans="13:107">
+      <c r="M18" t="s">
         <v>305</v>
       </c>
-      <c r="AA20" t="s">
+      <c r="AB18" t="s">
         <v>377</v>
       </c>
-      <c r="DB20" t="s">
+      <c r="DC18" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="21" spans="12:106">
-      <c r="L21" t="s">
+    <row r="19" spans="13:107">
+      <c r="M19" t="s">
         <v>306</v>
       </c>
-      <c r="AA21" t="s">
+      <c r="AB19" t="s">
         <v>378</v>
       </c>
-      <c r="DB21" t="s">
+      <c r="DC19" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="22" spans="12:106">
-      <c r="L22" t="s">
+    <row r="20" spans="13:107">
+      <c r="M20" t="s">
         <v>307</v>
       </c>
-      <c r="AA22" t="s">
+      <c r="AB20" t="s">
         <v>379</v>
       </c>
-      <c r="DB22" t="s">
+      <c r="DC20" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="23" spans="12:106">
-      <c r="L23" t="s">
+    <row r="21" spans="13:107">
+      <c r="M21" t="s">
         <v>308</v>
       </c>
-      <c r="AA23" t="s">
+      <c r="AB21" t="s">
         <v>380</v>
       </c>
-      <c r="DB23" t="s">
+      <c r="DC21" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="24" spans="12:106">
-      <c r="L24" t="s">
+    <row r="22" spans="13:107">
+      <c r="M22" t="s">
         <v>309</v>
       </c>
-      <c r="AA24" t="s">
+      <c r="AB22" t="s">
         <v>381</v>
       </c>
-      <c r="DB24" t="s">
+      <c r="DC22" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="25" spans="12:106">
-      <c r="L25" t="s">
+    <row r="23" spans="13:107">
+      <c r="M23" t="s">
         <v>310</v>
       </c>
-      <c r="AA25" t="s">
+      <c r="AB23" t="s">
         <v>382</v>
       </c>
-      <c r="DB25" t="s">
+      <c r="DC23" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="26" spans="12:106">
-      <c r="L26" t="s">
+    <row r="24" spans="13:107">
+      <c r="M24" t="s">
         <v>311</v>
       </c>
-      <c r="AA26" t="s">
+      <c r="AB24" t="s">
         <v>383</v>
       </c>
-      <c r="DB26" t="s">
+      <c r="DC24" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="27" spans="12:106">
-      <c r="L27" t="s">
+    <row r="25" spans="13:107">
+      <c r="M25" t="s">
         <v>312</v>
       </c>
-      <c r="AA27" t="s">
+      <c r="AB25" t="s">
         <v>384</v>
       </c>
-      <c r="DB27" t="s">
+      <c r="DC25" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="28" spans="12:106">
-      <c r="L28" t="s">
+    <row r="26" spans="13:107">
+      <c r="M26" t="s">
         <v>313</v>
       </c>
-      <c r="AA28" t="s">
+      <c r="AB26" t="s">
         <v>385</v>
       </c>
-      <c r="DB28" t="s">
+      <c r="DC26" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="29" spans="12:106">
-      <c r="L29" t="s">
+    <row r="27" spans="13:107">
+      <c r="M27" t="s">
         <v>314</v>
       </c>
-      <c r="AA29" t="s">
+      <c r="AB27" t="s">
         <v>386</v>
       </c>
-      <c r="DB29" t="s">
+      <c r="DC27" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="30" spans="12:106">
-      <c r="L30" t="s">
+    <row r="28" spans="13:107">
+      <c r="M28" t="s">
         <v>315</v>
       </c>
-      <c r="AA30" t="s">
+      <c r="AB28" t="s">
         <v>387</v>
       </c>
-      <c r="DB30" t="s">
+      <c r="DC28" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="31" spans="12:106">
-      <c r="AA31" t="s">
+    <row r="29" spans="13:107">
+      <c r="M29" t="s">
+        <v>316</v>
+      </c>
+      <c r="AB29" t="s">
         <v>388</v>
       </c>
-      <c r="DB31" t="s">
+      <c r="DC29" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="32" spans="12:106">
-      <c r="AA32" t="s">
+    <row r="30" spans="13:107">
+      <c r="M30" t="s">
+        <v>317</v>
+      </c>
+      <c r="AB30" t="s">
         <v>389</v>
       </c>
-      <c r="DB32" t="s">
+      <c r="DC30" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="33" spans="106:106">
-      <c r="DB33" t="s">
+    <row r="31" spans="13:107">
+      <c r="AB31" t="s">
+        <v>390</v>
+      </c>
+      <c r="DC31" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="34" spans="106:106">
-      <c r="DB34" t="s">
+    <row r="32" spans="13:107">
+      <c r="AB32" t="s">
+        <v>391</v>
+      </c>
+      <c r="DC32" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="35" spans="106:106">
-      <c r="DB35" t="s">
+    <row r="33" spans="107:107">
+      <c r="DC33" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="36" spans="106:106">
-      <c r="DB36" t="s">
+    <row r="34" spans="107:107">
+      <c r="DC34" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="37" spans="106:106">
-      <c r="DB37" t="s">
+    <row r="35" spans="107:107">
+      <c r="DC35" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="38" spans="106:106">
-      <c r="DB38" t="s">
+    <row r="36" spans="107:107">
+      <c r="DC36" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="39" spans="106:106">
-      <c r="DB39" t="s">
+    <row r="37" spans="107:107">
+      <c r="DC37" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="40" spans="106:106">
-      <c r="DB40" t="s">
+    <row r="38" spans="107:107">
+      <c r="DC38" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="41" spans="106:106">
-      <c r="DB41" t="s">
+    <row r="39" spans="107:107">
+      <c r="DC39" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="42" spans="106:106">
-      <c r="DB42" t="s">
+    <row r="40" spans="107:107">
+      <c r="DC40" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="43" spans="106:106">
-      <c r="DB43" t="s">
+    <row r="41" spans="107:107">
+      <c r="DC41" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="44" spans="106:106">
-      <c r="DB44" t="s">
+    <row r="42" spans="107:107">
+      <c r="DC42" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="45" spans="106:106">
-      <c r="DB45" t="s">
+    <row r="43" spans="107:107">
+      <c r="DC43" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="46" spans="106:106">
-      <c r="DB46" t="s">
+    <row r="44" spans="107:107">
+      <c r="DC44" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="47" spans="106:106">
-      <c r="DB47" t="s">
+    <row r="45" spans="107:107">
+      <c r="DC45" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="48" spans="106:106">
-      <c r="DB48" t="s">
+    <row r="46" spans="107:107">
+      <c r="DC46" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="49" spans="106:106">
-      <c r="DB49" t="s">
+    <row r="47" spans="107:107">
+      <c r="DC47" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="50" spans="106:106">
-      <c r="DB50" t="s">
+    <row r="48" spans="107:107">
+      <c r="DC48" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="51" spans="106:106">
-      <c r="DB51" t="s">
+    <row r="49" spans="107:107">
+      <c r="DC49" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="52" spans="106:106">
-      <c r="DB52" t="s">
+    <row r="50" spans="107:107">
+      <c r="DC50" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="53" spans="106:106">
-      <c r="DB53" t="s">
+    <row r="51" spans="107:107">
+      <c r="DC51" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="54" spans="106:106">
-      <c r="DB54" t="s">
+    <row r="52" spans="107:107">
+      <c r="DC52" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="55" spans="106:106">
-      <c r="DB55" t="s">
+    <row r="53" spans="107:107">
+      <c r="DC53" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="56" spans="106:106">
-      <c r="DB56" t="s">
+    <row r="54" spans="107:107">
+      <c r="DC54" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="57" spans="106:106">
-      <c r="DB57" t="s">
+    <row r="55" spans="107:107">
+      <c r="DC55" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="58" spans="106:106">
-      <c r="DB58" t="s">
+    <row r="56" spans="107:107">
+      <c r="DC56" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="59" spans="106:106">
-      <c r="DB59" t="s">
+    <row r="57" spans="107:107">
+      <c r="DC57" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="60" spans="106:106">
-      <c r="DB60" t="s">
+    <row r="58" spans="107:107">
+      <c r="DC58" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="61" spans="106:106">
-      <c r="DB61" t="s">
+    <row r="59" spans="107:107">
+      <c r="DC59" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="62" spans="106:106">
-      <c r="DB62" t="s">
+    <row r="60" spans="107:107">
+      <c r="DC60" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="63" spans="106:106">
-      <c r="DB63" t="s">
+    <row r="61" spans="107:107">
+      <c r="DC61" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="64" spans="106:106">
-      <c r="DB64" t="s">
+    <row r="62" spans="107:107">
+      <c r="DC62" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="65" spans="106:106">
-      <c r="DB65" t="s">
+    <row r="63" spans="107:107">
+      <c r="DC63" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="66" spans="106:106">
-      <c r="DB66" t="s">
+    <row r="64" spans="107:107">
+      <c r="DC64" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="67" spans="106:106">
-      <c r="DB67" t="s">
+    <row r="65" spans="107:107">
+      <c r="DC65" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="68" spans="106:106">
-      <c r="DB68" t="s">
+    <row r="66" spans="107:107">
+      <c r="DC66" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="69" spans="106:106">
-      <c r="DB69" t="s">
+    <row r="67" spans="107:107">
+      <c r="DC67" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="70" spans="106:106">
-      <c r="DB70" t="s">
+    <row r="68" spans="107:107">
+      <c r="DC68" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="71" spans="106:106">
-      <c r="DB71" t="s">
+    <row r="69" spans="107:107">
+      <c r="DC69" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="72" spans="106:106">
-      <c r="DB72" t="s">
+    <row r="70" spans="107:107">
+      <c r="DC70" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="73" spans="106:106">
-      <c r="DB73" t="s">
+    <row r="71" spans="107:107">
+      <c r="DC71" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="74" spans="106:106">
-      <c r="DB74" t="s">
+    <row r="72" spans="107:107">
+      <c r="DC72" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="75" spans="106:106">
-      <c r="DB75" t="s">
+    <row r="73" spans="107:107">
+      <c r="DC73" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="76" spans="106:106">
-      <c r="DB76" t="s">
+    <row r="74" spans="107:107">
+      <c r="DC74" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="77" spans="106:106">
-      <c r="DB77" t="s">
+    <row r="75" spans="107:107">
+      <c r="DC75" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="78" spans="106:106">
-      <c r="DB78" t="s">
+    <row r="76" spans="107:107">
+      <c r="DC76" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="79" spans="106:106">
-      <c r="DB79" t="s">
+    <row r="77" spans="107:107">
+      <c r="DC77" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="80" spans="106:106">
-      <c r="DB80" t="s">
+    <row r="78" spans="107:107">
+      <c r="DC78" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="81" spans="106:106">
-      <c r="DB81" t="s">
+    <row r="79" spans="107:107">
+      <c r="DC79" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="82" spans="106:106">
-      <c r="DB82" t="s">
+    <row r="80" spans="107:107">
+      <c r="DC80" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="83" spans="106:106">
-      <c r="DB83" t="s">
+    <row r="81" spans="107:107">
+      <c r="DC81" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="84" spans="106:106">
-      <c r="DB84" t="s">
+    <row r="82" spans="107:107">
+      <c r="DC82" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="85" spans="106:106">
-      <c r="DB85" t="s">
+    <row r="83" spans="107:107">
+      <c r="DC83" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="86" spans="106:106">
-      <c r="DB86" t="s">
+    <row r="84" spans="107:107">
+      <c r="DC84" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="87" spans="106:106">
-      <c r="DB87" t="s">
+    <row r="85" spans="107:107">
+      <c r="DC85" t="s">
         <v>672</v>
       </c>
     </row>
-    <row r="88" spans="106:106">
-      <c r="DB88" t="s">
+    <row r="86" spans="107:107">
+      <c r="DC86" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="89" spans="106:106">
-      <c r="DB89" t="s">
+    <row r="87" spans="107:107">
+      <c r="DC87" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="90" spans="106:106">
-      <c r="DB90" t="s">
+    <row r="88" spans="107:107">
+      <c r="DC88" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="91" spans="106:106">
-      <c r="DB91" t="s">
+    <row r="89" spans="107:107">
+      <c r="DC89" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="92" spans="106:106">
-      <c r="DB92" t="s">
+    <row r="90" spans="107:107">
+      <c r="DC90" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="93" spans="106:106">
-      <c r="DB93" t="s">
+    <row r="91" spans="107:107">
+      <c r="DC91" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="94" spans="106:106">
-      <c r="DB94" t="s">
+    <row r="92" spans="107:107">
+      <c r="DC92" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="95" spans="106:106">
-      <c r="DB95" t="s">
+    <row r="93" spans="107:107">
+      <c r="DC93" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="96" spans="106:106">
-      <c r="DB96" t="s">
+    <row r="94" spans="107:107">
+      <c r="DC94" t="s">
         <v>681</v>
       </c>
     </row>
-    <row r="97" spans="106:106">
-      <c r="DB97" t="s">
+    <row r="95" spans="107:107">
+      <c r="DC95" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="98" spans="106:106">
-      <c r="DB98" t="s">
+    <row r="96" spans="107:107">
+      <c r="DC96" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="99" spans="106:106">
-      <c r="DB99" t="s">
+    <row r="97" spans="107:107">
+      <c r="DC97" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="100" spans="106:106">
-      <c r="DB100" t="s">
+    <row r="98" spans="107:107">
+      <c r="DC98" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="101" spans="106:106">
-      <c r="DB101" t="s">
+    <row r="99" spans="107:107">
+      <c r="DC99" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="102" spans="106:106">
-      <c r="DB102" t="s">
+    <row r="100" spans="107:107">
+      <c r="DC100" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="103" spans="106:106">
-      <c r="DB103" t="s">
+    <row r="101" spans="107:107">
+      <c r="DC101" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="104" spans="106:106">
-      <c r="DB104" t="s">
+    <row r="102" spans="107:107">
+      <c r="DC102" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="105" spans="106:106">
-      <c r="DB105" t="s">
+    <row r="103" spans="107:107">
+      <c r="DC103" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="106" spans="106:106">
-      <c r="DB106" t="s">
+    <row r="104" spans="107:107">
+      <c r="DC104" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="107" spans="106:106">
-      <c r="DB107" t="s">
+    <row r="105" spans="107:107">
+      <c r="DC105" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="108" spans="106:106">
-      <c r="DB108" t="s">
+    <row r="106" spans="107:107">
+      <c r="DC106" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="109" spans="106:106">
-      <c r="DB109" t="s">
+    <row r="107" spans="107:107">
+      <c r="DC107" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="110" spans="106:106">
-      <c r="DB110" t="s">
+    <row r="108" spans="107:107">
+      <c r="DC108" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="111" spans="106:106">
-      <c r="DB111" t="s">
+    <row r="109" spans="107:107">
+      <c r="DC109" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="112" spans="106:106">
-      <c r="DB112" t="s">
+    <row r="110" spans="107:107">
+      <c r="DC110" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="113" spans="106:106">
-      <c r="DB113" t="s">
+    <row r="111" spans="107:107">
+      <c r="DC111" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="114" spans="106:106">
-      <c r="DB114" t="s">
+    <row r="112" spans="107:107">
+      <c r="DC112" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="115" spans="106:106">
-      <c r="DB115" t="s">
+    <row r="113" spans="107:107">
+      <c r="DC113" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="116" spans="106:106">
-      <c r="DB116" t="s">
+    <row r="114" spans="107:107">
+      <c r="DC114" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="117" spans="106:106">
-      <c r="DB117" t="s">
+    <row r="115" spans="107:107">
+      <c r="DC115" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="118" spans="106:106">
-      <c r="DB118" t="s">
+    <row r="116" spans="107:107">
+      <c r="DC116" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="119" spans="106:106">
-      <c r="DB119" t="s">
+    <row r="117" spans="107:107">
+      <c r="DC117" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="120" spans="106:106">
-      <c r="DB120" t="s">
+    <row r="118" spans="107:107">
+      <c r="DC118" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="121" spans="106:106">
-      <c r="DB121" t="s">
+    <row r="119" spans="107:107">
+      <c r="DC119" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="122" spans="106:106">
-      <c r="DB122" t="s">
+    <row r="120" spans="107:107">
+      <c r="DC120" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="123" spans="106:106">
-      <c r="DB123" t="s">
+    <row r="121" spans="107:107">
+      <c r="DC121" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="124" spans="106:106">
-      <c r="DB124" t="s">
+    <row r="122" spans="107:107">
+      <c r="DC122" t="s">
         <v>709</v>
       </c>
     </row>
-    <row r="125" spans="106:106">
-      <c r="DB125" t="s">
+    <row r="123" spans="107:107">
+      <c r="DC123" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="126" spans="106:106">
-      <c r="DB126" t="s">
+    <row r="124" spans="107:107">
+      <c r="DC124" t="s">
         <v>711</v>
       </c>
     </row>
-    <row r="127" spans="106:106">
-      <c r="DB127" t="s">
+    <row r="125" spans="107:107">
+      <c r="DC125" t="s">
         <v>712</v>
       </c>
     </row>
-    <row r="128" spans="106:106">
-      <c r="DB128" t="s">
+    <row r="126" spans="107:107">
+      <c r="DC126" t="s">
         <v>713</v>
       </c>
     </row>
-    <row r="129" spans="106:106">
-      <c r="DB129" t="s">
+    <row r="127" spans="107:107">
+      <c r="DC127" t="s">
         <v>714</v>
       </c>
     </row>
-    <row r="130" spans="106:106">
-      <c r="DB130" t="s">
+    <row r="128" spans="107:107">
+      <c r="DC128" t="s">
         <v>715</v>
       </c>
     </row>
-    <row r="131" spans="106:106">
-      <c r="DB131" t="s">
+    <row r="129" spans="107:107">
+      <c r="DC129" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="132" spans="106:106">
-      <c r="DB132" t="s">
+    <row r="130" spans="107:107">
+      <c r="DC130" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="133" spans="106:106">
-      <c r="DB133" t="s">
+    <row r="131" spans="107:107">
+      <c r="DC131" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="134" spans="106:106">
-      <c r="DB134" t="s">
+    <row r="132" spans="107:107">
+      <c r="DC132" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="135" spans="106:106">
-      <c r="DB135" t="s">
+    <row r="133" spans="107:107">
+      <c r="DC133" t="s">
         <v>720</v>
       </c>
     </row>
-    <row r="136" spans="106:106">
-      <c r="DB136" t="s">
+    <row r="134" spans="107:107">
+      <c r="DC134" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="137" spans="106:106">
-      <c r="DB137" t="s">
+    <row r="135" spans="107:107">
+      <c r="DC135" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="138" spans="106:106">
-      <c r="DB138" t="s">
+    <row r="136" spans="107:107">
+      <c r="DC136" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="139" spans="106:106">
-      <c r="DB139" t="s">
+    <row r="137" spans="107:107">
+      <c r="DC137" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="140" spans="106:106">
-      <c r="DB140" t="s">
+    <row r="138" spans="107:107">
+      <c r="DC138" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="141" spans="106:106">
-      <c r="DB141" t="s">
+    <row r="139" spans="107:107">
+      <c r="DC139" t="s">
         <v>726</v>
       </c>
     </row>
-    <row r="142" spans="106:106">
-      <c r="DB142" t="s">
+    <row r="140" spans="107:107">
+      <c r="DC140" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="143" spans="106:106">
-      <c r="DB143" t="s">
+    <row r="141" spans="107:107">
+      <c r="DC141" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="144" spans="106:106">
-      <c r="DB144" t="s">
+    <row r="142" spans="107:107">
+      <c r="DC142" t="s">
         <v>729</v>
       </c>
     </row>
-    <row r="145" spans="106:106">
-      <c r="DB145" t="s">
+    <row r="143" spans="107:107">
+      <c r="DC143" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="146" spans="106:106">
-      <c r="DB146" t="s">
+    <row r="144" spans="107:107">
+      <c r="DC144" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="147" spans="106:106">
-      <c r="DB147" t="s">
+    <row r="145" spans="107:107">
+      <c r="DC145" t="s">
         <v>732</v>
       </c>
     </row>
-    <row r="148" spans="106:106">
-      <c r="DB148" t="s">
+    <row r="146" spans="107:107">
+      <c r="DC146" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="149" spans="106:106">
-      <c r="DB149" t="s">
+    <row r="147" spans="107:107">
+      <c r="DC147" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="150" spans="106:106">
-      <c r="DB150" t="s">
+    <row r="148" spans="107:107">
+      <c r="DC148" t="s">
         <v>735</v>
       </c>
     </row>
-    <row r="151" spans="106:106">
-      <c r="DB151" t="s">
+    <row r="149" spans="107:107">
+      <c r="DC149" t="s">
         <v>736</v>
       </c>
     </row>
-    <row r="152" spans="106:106">
-      <c r="DB152" t="s">
+    <row r="150" spans="107:107">
+      <c r="DC150" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="153" spans="106:106">
-      <c r="DB153" t="s">
+    <row r="151" spans="107:107">
+      <c r="DC151" t="s">
         <v>738</v>
       </c>
     </row>
-    <row r="154" spans="106:106">
-      <c r="DB154" t="s">
+    <row r="152" spans="107:107">
+      <c r="DC152" t="s">
         <v>739</v>
       </c>
     </row>
-    <row r="155" spans="106:106">
-      <c r="DB155" t="s">
+    <row r="153" spans="107:107">
+      <c r="DC153" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="156" spans="106:106">
-      <c r="DB156" t="s">
+    <row r="154" spans="107:107">
+      <c r="DC154" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="157" spans="106:106">
-      <c r="DB157" t="s">
+    <row r="155" spans="107:107">
+      <c r="DC155" t="s">
         <v>742</v>
       </c>
     </row>
-    <row r="158" spans="106:106">
-      <c r="DB158" t="s">
+    <row r="156" spans="107:107">
+      <c r="DC156" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="159" spans="106:106">
-      <c r="DB159" t="s">
+    <row r="157" spans="107:107">
+      <c r="DC157" t="s">
         <v>744</v>
       </c>
     </row>
-    <row r="160" spans="106:106">
-      <c r="DB160" t="s">
+    <row r="158" spans="107:107">
+      <c r="DC158" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="161" spans="106:106">
-      <c r="DB161" t="s">
+    <row r="159" spans="107:107">
+      <c r="DC159" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="162" spans="106:106">
-      <c r="DB162" t="s">
+    <row r="160" spans="107:107">
+      <c r="DC160" t="s">
         <v>747</v>
       </c>
     </row>
-    <row r="163" spans="106:106">
-      <c r="DB163" t="s">
+    <row r="161" spans="107:107">
+      <c r="DC161" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="164" spans="106:106">
-      <c r="DB164" t="s">
+    <row r="162" spans="107:107">
+      <c r="DC162" t="s">
         <v>749</v>
       </c>
     </row>
-    <row r="165" spans="106:106">
-      <c r="DB165" t="s">
+    <row r="163" spans="107:107">
+      <c r="DC163" t="s">
         <v>750</v>
       </c>
     </row>
-    <row r="166" spans="106:106">
-      <c r="DB166" t="s">
+    <row r="164" spans="107:107">
+      <c r="DC164" t="s">
         <v>751</v>
       </c>
     </row>
-    <row r="167" spans="106:106">
-      <c r="DB167" t="s">
+    <row r="165" spans="107:107">
+      <c r="DC165" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="168" spans="106:106">
-      <c r="DB168" t="s">
+    <row r="166" spans="107:107">
+      <c r="DC166" t="s">
         <v>753</v>
       </c>
     </row>
-    <row r="169" spans="106:106">
-      <c r="DB169" t="s">
+    <row r="167" spans="107:107">
+      <c r="DC167" t="s">
         <v>754</v>
       </c>
     </row>
-    <row r="170" spans="106:106">
-      <c r="DB170" t="s">
+    <row r="168" spans="107:107">
+      <c r="DC168" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="171" spans="106:106">
-      <c r="DB171" t="s">
+    <row r="169" spans="107:107">
+      <c r="DC169" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="172" spans="106:106">
-      <c r="DB172" t="s">
+    <row r="170" spans="107:107">
+      <c r="DC170" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="173" spans="106:106">
-      <c r="DB173" t="s">
+    <row r="171" spans="107:107">
+      <c r="DC171" t="s">
         <v>758</v>
       </c>
     </row>
-    <row r="174" spans="106:106">
-      <c r="DB174" t="s">
+    <row r="172" spans="107:107">
+      <c r="DC172" t="s">
         <v>759</v>
       </c>
     </row>
-    <row r="175" spans="106:106">
-      <c r="DB175" t="s">
+    <row r="173" spans="107:107">
+      <c r="DC173" t="s">
         <v>760</v>
       </c>
     </row>
-    <row r="176" spans="106:106">
-      <c r="DB176" t="s">
+    <row r="174" spans="107:107">
+      <c r="DC174" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="177" spans="106:106">
-      <c r="DB177" t="s">
+    <row r="175" spans="107:107">
+      <c r="DC175" t="s">
         <v>762</v>
       </c>
     </row>
-    <row r="178" spans="106:106">
-      <c r="DB178" t="s">
+    <row r="176" spans="107:107">
+      <c r="DC176" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="179" spans="106:106">
-      <c r="DB179" t="s">
+    <row r="177" spans="107:107">
+      <c r="DC177" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="180" spans="106:106">
-      <c r="DB180" t="s">
+    <row r="178" spans="107:107">
+      <c r="DC178" t="s">
         <v>765</v>
       </c>
     </row>
-    <row r="181" spans="106:106">
-      <c r="DB181" t="s">
+    <row r="179" spans="107:107">
+      <c r="DC179" t="s">
         <v>766</v>
       </c>
     </row>
-    <row r="182" spans="106:106">
-      <c r="DB182" t="s">
+    <row r="180" spans="107:107">
+      <c r="DC180" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="183" spans="106:106">
-      <c r="DB183" t="s">
+    <row r="181" spans="107:107">
+      <c r="DC181" t="s">
         <v>768</v>
       </c>
     </row>
-    <row r="184" spans="106:106">
-      <c r="DB184" t="s">
+    <row r="182" spans="107:107">
+      <c r="DC182" t="s">
         <v>769</v>
       </c>
     </row>
-    <row r="185" spans="106:106">
-      <c r="DB185" t="s">
+    <row r="183" spans="107:107">
+      <c r="DC183" t="s">
         <v>770</v>
       </c>
     </row>
-    <row r="186" spans="106:106">
-      <c r="DB186" t="s">
+    <row r="184" spans="107:107">
+      <c r="DC184" t="s">
         <v>771</v>
       </c>
     </row>
-    <row r="187" spans="106:106">
-      <c r="DB187" t="s">
+    <row r="185" spans="107:107">
+      <c r="DC185" t="s">
         <v>772</v>
       </c>
     </row>
-    <row r="188" spans="106:106">
-      <c r="DB188" t="s">
+    <row r="186" spans="107:107">
+      <c r="DC186" t="s">
         <v>773</v>
       </c>
     </row>
-    <row r="189" spans="106:106">
-      <c r="DB189" t="s">
+    <row r="187" spans="107:107">
+      <c r="DC187" t="s">
         <v>774</v>
       </c>
     </row>
-    <row r="190" spans="106:106">
-      <c r="DB190" t="s">
+    <row r="188" spans="107:107">
+      <c r="DC188" t="s">
         <v>775</v>
       </c>
     </row>
-    <row r="191" spans="106:106">
-      <c r="DB191" t="s">
+    <row r="189" spans="107:107">
+      <c r="DC189" t="s">
         <v>776</v>
       </c>
     </row>
-    <row r="192" spans="106:106">
-      <c r="DB192" t="s">
+    <row r="190" spans="107:107">
+      <c r="DC190" t="s">
         <v>777</v>
       </c>
     </row>
-    <row r="193" spans="106:106">
-      <c r="DB193" t="s">
+    <row r="191" spans="107:107">
+      <c r="DC191" t="s">
         <v>778</v>
       </c>
     </row>
-    <row r="194" spans="106:106">
-      <c r="DB194" t="s">
+    <row r="192" spans="107:107">
+      <c r="DC192" t="s">
         <v>779</v>
       </c>
     </row>
-    <row r="195" spans="106:106">
-      <c r="DB195" t="s">
+    <row r="193" spans="107:107">
+      <c r="DC193" t="s">
         <v>780</v>
       </c>
     </row>
-    <row r="196" spans="106:106">
-      <c r="DB196" t="s">
+    <row r="194" spans="107:107">
+      <c r="DC194" t="s">
         <v>781</v>
       </c>
     </row>
-    <row r="197" spans="106:106">
-      <c r="DB197" t="s">
+    <row r="195" spans="107:107">
+      <c r="DC195" t="s">
         <v>782</v>
       </c>
     </row>
-    <row r="198" spans="106:106">
-      <c r="DB198" t="s">
+    <row r="196" spans="107:107">
+      <c r="DC196" t="s">
         <v>783</v>
       </c>
     </row>
-    <row r="199" spans="106:106">
-      <c r="DB199" t="s">
+    <row r="197" spans="107:107">
+      <c r="DC197" t="s">
         <v>784</v>
       </c>
     </row>
-    <row r="200" spans="106:106">
-      <c r="DB200" t="s">
+    <row r="198" spans="107:107">
+      <c r="DC198" t="s">
         <v>785</v>
       </c>
     </row>
-    <row r="201" spans="106:106">
-      <c r="DB201" t="s">
+    <row r="199" spans="107:107">
+      <c r="DC199" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="202" spans="106:106">
-      <c r="DB202" t="s">
+    <row r="200" spans="107:107">
+      <c r="DC200" t="s">
         <v>787</v>
       </c>
     </row>
-    <row r="203" spans="106:106">
-      <c r="DB203" t="s">
+    <row r="201" spans="107:107">
+      <c r="DC201" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="204" spans="106:106">
-      <c r="DB204" t="s">
+    <row r="202" spans="107:107">
+      <c r="DC202" t="s">
         <v>789</v>
       </c>
     </row>
-    <row r="205" spans="106:106">
-      <c r="DB205" t="s">
+    <row r="203" spans="107:107">
+      <c r="DC203" t="s">
         <v>790</v>
       </c>
     </row>
-    <row r="206" spans="106:106">
-      <c r="DB206" t="s">
+    <row r="204" spans="107:107">
+      <c r="DC204" t="s">
         <v>791</v>
       </c>
     </row>
-    <row r="207" spans="106:106">
-      <c r="DB207" t="s">
+    <row r="205" spans="107:107">
+      <c r="DC205" t="s">
         <v>792</v>
       </c>
     </row>
-    <row r="208" spans="106:106">
-      <c r="DB208" t="s">
+    <row r="206" spans="107:107">
+      <c r="DC206" t="s">
         <v>793</v>
       </c>
     </row>
-    <row r="209" spans="106:106">
-      <c r="DB209" t="s">
+    <row r="207" spans="107:107">
+      <c r="DC207" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="210" spans="106:106">
-      <c r="DB210" t="s">
+    <row r="208" spans="107:107">
+      <c r="DC208" t="s">
         <v>795</v>
       </c>
     </row>
-    <row r="211" spans="106:106">
-      <c r="DB211" t="s">
+    <row r="209" spans="107:107">
+      <c r="DC209" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="212" spans="106:106">
-      <c r="DB212" t="s">
+    <row r="210" spans="107:107">
+      <c r="DC210" t="s">
         <v>797</v>
       </c>
     </row>
-    <row r="213" spans="106:106">
-      <c r="DB213" t="s">
+    <row r="211" spans="107:107">
+      <c r="DC211" t="s">
         <v>798</v>
       </c>
     </row>
-    <row r="214" spans="106:106">
-      <c r="DB214" t="s">
+    <row r="212" spans="107:107">
+      <c r="DC212" t="s">
         <v>799</v>
       </c>
     </row>
-    <row r="215" spans="106:106">
-      <c r="DB215" t="s">
+    <row r="213" spans="107:107">
+      <c r="DC213" t="s">
         <v>800</v>
       </c>
     </row>
-    <row r="216" spans="106:106">
-      <c r="DB216" t="s">
+    <row r="214" spans="107:107">
+      <c r="DC214" t="s">
         <v>801</v>
       </c>
     </row>
-    <row r="217" spans="106:106">
-      <c r="DB217" t="s">
+    <row r="215" spans="107:107">
+      <c r="DC215" t="s">
         <v>802</v>
       </c>
     </row>
-    <row r="218" spans="106:106">
-      <c r="DB218" t="s">
+    <row r="216" spans="107:107">
+      <c r="DC216" t="s">
         <v>803</v>
       </c>
     </row>
-    <row r="219" spans="106:106">
-      <c r="DB219" t="s">
+    <row r="217" spans="107:107">
+      <c r="DC217" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="220" spans="106:106">
-      <c r="DB220" t="s">
+    <row r="218" spans="107:107">
+      <c r="DC218" t="s">
         <v>805</v>
       </c>
     </row>
-    <row r="221" spans="106:106">
-      <c r="DB221" t="s">
+    <row r="219" spans="107:107">
+      <c r="DC219" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="222" spans="106:106">
-      <c r="DB222" t="s">
+    <row r="220" spans="107:107">
+      <c r="DC220" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="223" spans="106:106">
-      <c r="DB223" t="s">
+    <row r="221" spans="107:107">
+      <c r="DC221" t="s">
         <v>808</v>
       </c>
     </row>
-    <row r="224" spans="106:106">
-      <c r="DB224" t="s">
+    <row r="222" spans="107:107">
+      <c r="DC222" t="s">
         <v>809</v>
       </c>
     </row>
-    <row r="225" spans="106:106">
-      <c r="DB225" t="s">
+    <row r="223" spans="107:107">
+      <c r="DC223" t="s">
         <v>810</v>
       </c>
     </row>
-    <row r="226" spans="106:106">
-      <c r="DB226" t="s">
+    <row r="224" spans="107:107">
+      <c r="DC224" t="s">
         <v>811</v>
       </c>
     </row>
-    <row r="227" spans="106:106">
-      <c r="DB227" t="s">
+    <row r="225" spans="107:107">
+      <c r="DC225" t="s">
         <v>812</v>
       </c>
     </row>
-    <row r="228" spans="106:106">
-      <c r="DB228" t="s">
+    <row r="226" spans="107:107">
+      <c r="DC226" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="229" spans="106:106">
-      <c r="DB229" t="s">
+    <row r="227" spans="107:107">
+      <c r="DC227" t="s">
         <v>814</v>
       </c>
     </row>
-    <row r="230" spans="106:106">
-      <c r="DB230" t="s">
+    <row r="228" spans="107:107">
+      <c r="DC228" t="s">
         <v>815</v>
       </c>
     </row>
-    <row r="231" spans="106:106">
-      <c r="DB231" t="s">
+    <row r="229" spans="107:107">
+      <c r="DC229" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="232" spans="106:106">
-      <c r="DB232" t="s">
+    <row r="230" spans="107:107">
+      <c r="DC230" t="s">
         <v>817</v>
       </c>
     </row>
-    <row r="233" spans="106:106">
-      <c r="DB233" t="s">
+    <row r="231" spans="107:107">
+      <c r="DC231" t="s">
         <v>818</v>
       </c>
     </row>
-    <row r="234" spans="106:106">
-      <c r="DB234" t="s">
+    <row r="232" spans="107:107">
+      <c r="DC232" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="235" spans="106:106">
-      <c r="DB235" t="s">
+    <row r="233" spans="107:107">
+      <c r="DC233" t="s">
         <v>820</v>
       </c>
     </row>
-    <row r="236" spans="106:106">
-      <c r="DB236" t="s">
+    <row r="234" spans="107:107">
+      <c r="DC234" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="237" spans="106:106">
-      <c r="DB237" t="s">
+    <row r="235" spans="107:107">
+      <c r="DC235" t="s">
         <v>822</v>
       </c>
     </row>
-    <row r="238" spans="106:106">
-      <c r="DB238" t="s">
+    <row r="236" spans="107:107">
+      <c r="DC236" t="s">
         <v>823</v>
       </c>
     </row>
-    <row r="239" spans="106:106">
-      <c r="DB239" t="s">
+    <row r="237" spans="107:107">
+      <c r="DC237" t="s">
         <v>824</v>
       </c>
     </row>
-    <row r="240" spans="106:106">
-      <c r="DB240" t="s">
+    <row r="238" spans="107:107">
+      <c r="DC238" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="241" spans="106:106">
-      <c r="DB241" t="s">
+    <row r="239" spans="107:107">
+      <c r="DC239" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="242" spans="106:106">
-      <c r="DB242" t="s">
+    <row r="240" spans="107:107">
+      <c r="DC240" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="243" spans="106:106">
-      <c r="DB243" t="s">
+    <row r="241" spans="107:107">
+      <c r="DC241" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="244" spans="106:106">
-      <c r="DB244" t="s">
+    <row r="242" spans="107:107">
+      <c r="DC242" t="s">
         <v>829</v>
       </c>
     </row>
-    <row r="245" spans="106:106">
-      <c r="DB245" t="s">
+    <row r="243" spans="107:107">
+      <c r="DC243" t="s">
         <v>830</v>
       </c>
     </row>
-    <row r="246" spans="106:106">
-      <c r="DB246" t="s">
+    <row r="244" spans="107:107">
+      <c r="DC244" t="s">
         <v>831</v>
       </c>
     </row>
-    <row r="247" spans="106:106">
-      <c r="DB247" t="s">
+    <row r="245" spans="107:107">
+      <c r="DC245" t="s">
         <v>832</v>
       </c>
     </row>
-    <row r="248" spans="106:106">
-      <c r="DB248" t="s">
+    <row r="246" spans="107:107">
+      <c r="DC246" t="s">
         <v>833</v>
       </c>
     </row>
-    <row r="249" spans="106:106">
-      <c r="DB249" t="s">
+    <row r="247" spans="107:107">
+      <c r="DC247" t="s">
         <v>834</v>
       </c>
     </row>
-    <row r="250" spans="106:106">
-      <c r="DB250" t="s">
+    <row r="248" spans="107:107">
+      <c r="DC248" t="s">
         <v>835</v>
       </c>
     </row>
-    <row r="251" spans="106:106">
-      <c r="DB251" t="s">
+    <row r="249" spans="107:107">
+      <c r="DC249" t="s">
         <v>836</v>
       </c>
     </row>
-    <row r="252" spans="106:106">
-      <c r="DB252" t="s">
+    <row r="250" spans="107:107">
+      <c r="DC250" t="s">
         <v>837</v>
       </c>
     </row>
-    <row r="253" spans="106:106">
-      <c r="DB253" t="s">
+    <row r="251" spans="107:107">
+      <c r="DC251" t="s">
         <v>838</v>
       </c>
     </row>
-    <row r="254" spans="106:106">
-      <c r="DB254" t="s">
+    <row r="252" spans="107:107">
+      <c r="DC252" t="s">
         <v>839</v>
       </c>
     </row>
-    <row r="255" spans="106:106">
-      <c r="DB255" t="s">
+    <row r="253" spans="107:107">
+      <c r="DC253" t="s">
         <v>840</v>
       </c>
     </row>
-    <row r="256" spans="106:106">
-      <c r="DB256" t="s">
+    <row r="254" spans="107:107">
+      <c r="DC254" t="s">
         <v>841</v>
       </c>
     </row>
-    <row r="257" spans="106:106">
-      <c r="DB257" t="s">
+    <row r="255" spans="107:107">
+      <c r="DC255" t="s">
         <v>842</v>
       </c>
     </row>
-    <row r="258" spans="106:106">
-      <c r="DB258" t="s">
+    <row r="256" spans="107:107">
+      <c r="DC256" t="s">
         <v>843</v>
       </c>
     </row>
-    <row r="259" spans="106:106">
-      <c r="DB259" t="s">
+    <row r="257" spans="107:107">
+      <c r="DC257" t="s">
         <v>844</v>
       </c>
     </row>
-    <row r="260" spans="106:106">
-      <c r="DB260" t="s">
+    <row r="258" spans="107:107">
+      <c r="DC258" t="s">
         <v>845</v>
       </c>
     </row>
-    <row r="261" spans="106:106">
-      <c r="DB261" t="s">
+    <row r="259" spans="107:107">
+      <c r="DC259" t="s">
         <v>846</v>
       </c>
     </row>
-    <row r="262" spans="106:106">
-      <c r="DB262" t="s">
+    <row r="260" spans="107:107">
+      <c r="DC260" t="s">
         <v>847</v>
       </c>
     </row>
-    <row r="263" spans="106:106">
-      <c r="DB263" t="s">
+    <row r="261" spans="107:107">
+      <c r="DC261" t="s">
         <v>848</v>
       </c>
     </row>
-    <row r="264" spans="106:106">
-      <c r="DB264" t="s">
+    <row r="262" spans="107:107">
+      <c r="DC262" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="265" spans="106:106">
-      <c r="DB265" t="s">
+    <row r="263" spans="107:107">
+      <c r="DC263" t="s">
         <v>850</v>
       </c>
     </row>
-    <row r="266" spans="106:106">
-      <c r="DB266" t="s">
+    <row r="264" spans="107:107">
+      <c r="DC264" t="s">
         <v>851</v>
       </c>
     </row>
-    <row r="267" spans="106:106">
-      <c r="DB267" t="s">
+    <row r="265" spans="107:107">
+      <c r="DC265" t="s">
         <v>852</v>
       </c>
     </row>
-    <row r="268" spans="106:106">
-      <c r="DB268" t="s">
+    <row r="266" spans="107:107">
+      <c r="DC266" t="s">
         <v>853</v>
       </c>
     </row>
-    <row r="269" spans="106:106">
-      <c r="DB269" t="s">
+    <row r="267" spans="107:107">
+      <c r="DC267" t="s">
         <v>854</v>
       </c>
     </row>
-    <row r="270" spans="106:106">
-      <c r="DB270" t="s">
+    <row r="268" spans="107:107">
+      <c r="DC268" t="s">
         <v>855</v>
       </c>
     </row>
-    <row r="271" spans="106:106">
-      <c r="DB271" t="s">
+    <row r="269" spans="107:107">
+      <c r="DC269" t="s">
         <v>856</v>
       </c>
     </row>
-    <row r="272" spans="106:106">
-      <c r="DB272" t="s">
+    <row r="270" spans="107:107">
+      <c r="DC270" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="273" spans="106:106">
-      <c r="DB273" t="s">
+    <row r="271" spans="107:107">
+      <c r="DC271" t="s">
         <v>858</v>
       </c>
     </row>
-    <row r="274" spans="106:106">
-      <c r="DB274" t="s">
+    <row r="272" spans="107:107">
+      <c r="DC272" t="s">
         <v>859</v>
       </c>
     </row>
-    <row r="275" spans="106:106">
-      <c r="DB275" t="s">
+    <row r="273" spans="107:107">
+      <c r="DC273" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="276" spans="106:106">
-      <c r="DB276" t="s">
+    <row r="274" spans="107:107">
+      <c r="DC274" t="s">
         <v>861</v>
       </c>
     </row>
-    <row r="277" spans="106:106">
-      <c r="DB277" t="s">
+    <row r="275" spans="107:107">
+      <c r="DC275" t="s">
         <v>862</v>
       </c>
     </row>
-    <row r="278" spans="106:106">
-      <c r="DB278" t="s">
+    <row r="276" spans="107:107">
+      <c r="DC276" t="s">
         <v>863</v>
       </c>
     </row>
-    <row r="279" spans="106:106">
-      <c r="DB279" t="s">
+    <row r="277" spans="107:107">
+      <c r="DC277" t="s">
         <v>864</v>
       </c>
     </row>
-    <row r="280" spans="106:106">
-      <c r="DB280" t="s">
+    <row r="278" spans="107:107">
+      <c r="DC278" t="s">
         <v>865</v>
       </c>
     </row>
-    <row r="281" spans="106:106">
-      <c r="DB281" t="s">
+    <row r="279" spans="107:107">
+      <c r="DC279" t="s">
         <v>866</v>
       </c>
     </row>
-    <row r="282" spans="106:106">
-      <c r="DB282" t="s">
+    <row r="280" spans="107:107">
+      <c r="DC280" t="s">
         <v>867</v>
       </c>
     </row>
-    <row r="283" spans="106:106">
-      <c r="DB283" t="s">
+    <row r="281" spans="107:107">
+      <c r="DC281" t="s">
         <v>868</v>
       </c>
     </row>
-    <row r="284" spans="106:106">
-      <c r="DB284" t="s">
+    <row r="282" spans="107:107">
+      <c r="DC282" t="s">
         <v>869</v>
       </c>
     </row>
-    <row r="285" spans="106:106">
-      <c r="DB285" t="s">
+    <row r="283" spans="107:107">
+      <c r="DC283" t="s">
         <v>870</v>
       </c>
     </row>
-    <row r="286" spans="106:106">
-      <c r="DB286" t="s">
+    <row r="284" spans="107:107">
+      <c r="DC284" t="s">
         <v>871</v>
       </c>
     </row>
-    <row r="287" spans="106:106">
-      <c r="DB287" t="s">
+    <row r="285" spans="107:107">
+      <c r="DC285" t="s">
         <v>872</v>
       </c>
     </row>
-    <row r="288" spans="106:106">
-      <c r="DB288" t="s">
+    <row r="286" spans="107:107">
+      <c r="DC286" t="s">
         <v>873</v>
       </c>
     </row>
-    <row r="289" spans="106:106">
-      <c r="DB289" t="s">
+    <row r="287" spans="107:107">
+      <c r="DC287" t="s">
         <v>874</v>
       </c>
     </row>
-    <row r="290" spans="106:106">
-      <c r="DB290" t="s">
+    <row r="288" spans="107:107">
+      <c r="DC288" t="s">
         <v>875</v>
       </c>
     </row>
-    <row r="291" spans="106:106">
-      <c r="DB291" t="s">
+    <row r="289" spans="107:107">
+      <c r="DC289" t="s">
         <v>876</v>
       </c>
     </row>
-    <row r="292" spans="106:106">
-      <c r="DB292" t="s">
+    <row r="290" spans="107:107">
+      <c r="DC290" t="s">
         <v>877</v>
       </c>
     </row>
-    <row r="293" spans="106:106">
-      <c r="DB293" t="s">
+    <row r="291" spans="107:107">
+      <c r="DC291" t="s">
         <v>878</v>
       </c>
     </row>
-    <row r="294" spans="106:106">
-      <c r="DB294" t="s">
+    <row r="292" spans="107:107">
+      <c r="DC292" t="s">
         <v>879</v>
+      </c>
+    </row>
+    <row r="293" spans="107:107">
+      <c r="DC293" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="294" spans="107:107">
+      <c r="DC294" t="s">
+        <v>881</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000056/metadata_template_ERC000056.xlsx
+++ b/templates/ERC000056/metadata_template_ERC000056.xlsx
@@ -20,17 +20,17 @@
     <definedName name="assemblyquality">'cv_sample'!$BX$1:$BX$3</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
     <definedName name="frequencyofcleaning">'cv_sample'!$DY$1:$DY$5</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$DC$1:$DC$289</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$DC$1:$DC$294</definedName>
     <definedName name="growthhabit">'cv_sample'!$CZ$1:$CZ$4</definedName>
     <definedName name="historytillage">'cv_sample'!$EQ$1:$EQ$9</definedName>
     <definedName name="hostpredictionapproach">'cv_sample'!$FA$1:$FA$7</definedName>
     <definedName name="indoorsurface">'cv_sample'!$CN$1:$CN$8</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
     <definedName name="observedbioticrelationship">'cv_sample'!$N$1:$N$5</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="relationshiptooxygen">'cv_sample'!$P$1:$P$7</definedName>
     <definedName name="sequencequalitycheck">'cv_sample'!$BO$1:$BO$3</definedName>
     <definedName name="singlecellorviralparticlelysisapproach">'cv_sample'!$GX$1:$GX$4</definedName>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1254" uniqueCount="1244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="1251">
   <si>
     <t>alias</t>
   </si>
@@ -461,6 +461,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -551,6 +554,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -2018,9 +2024,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -2039,6 +2042,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -2240,6 +2246,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -2249,9 +2258,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -2291,7 +2297,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -2360,6 +2366,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -2435,6 +2444,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -2456,6 +2468,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -2501,6 +2516,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -2513,6 +2531,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -2522,9 +2543,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -2549,6 +2567,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -2609,12 +2630,12 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
   </si>
   <si>
-    <t>Wake Island</t>
-  </si>
-  <si>
     <t>Wallis and Futuna</t>
   </si>
   <si>
@@ -3311,7 +3332,7 @@
     <t>nucleic acid extraction kit</t>
   </si>
   <si>
-    <t>(Optional) The name of the extraction kit used to recover the nucleic acid fraction of an input material is performed. (Units: ppm)</t>
+    <t>(Optional) The name of the extraction kit used to recover the nucleic acid fraction of an input material is performed.</t>
   </si>
   <si>
     <t>sample pooling</t>
@@ -4303,10 +4324,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -4347,10 +4368,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -4377,7 +4398,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -4394,7 +4415,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -4411,7 +4432,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -4428,7 +4449,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -4445,7 +4466,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -4462,7 +4483,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -4479,7 +4500,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -4496,7 +4517,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -4513,7 +4534,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -4530,7 +4551,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -4544,7 +4565,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -4558,7 +4579,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -4572,7 +4593,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -4586,7 +4607,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -4600,7 +4621,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -4614,7 +4635,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -4628,7 +4649,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -4642,7 +4663,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -4652,8 +4673,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -4664,7 +4688,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -4675,7 +4699,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -4686,7 +4710,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -4697,7 +4721,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -4708,7 +4732,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -4719,7 +4743,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -4730,7 +4754,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -4741,7 +4765,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -4752,7 +4776,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -4763,7 +4787,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -4774,7 +4798,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -4785,7 +4809,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -4796,7 +4820,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -4804,7 +4828,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -4812,7 +4836,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -4820,7 +4844,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -4828,7 +4852,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -4836,7 +4860,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -4844,7 +4868,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -4852,7 +4876,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -4860,7 +4884,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -4868,7 +4892,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -4876,236 +4900,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -5127,27 +5156,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -5167,122 +5196,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -5306,1674 +5335,1674 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>875</v>
+        <v>882</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>877</v>
+        <v>884</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>879</v>
+        <v>886</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>881</v>
+        <v>888</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>883</v>
+        <v>890</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>887</v>
+        <v>894</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>891</v>
+        <v>898</v>
       </c>
       <c r="DL1" s="1" t="s">
-        <v>893</v>
+        <v>900</v>
       </c>
       <c r="DM1" s="1" t="s">
-        <v>895</v>
+        <v>902</v>
       </c>
       <c r="DN1" s="1" t="s">
-        <v>897</v>
+        <v>904</v>
       </c>
       <c r="DO1" s="1" t="s">
-        <v>899</v>
+        <v>906</v>
       </c>
       <c r="DP1" s="1" t="s">
-        <v>901</v>
+        <v>908</v>
       </c>
       <c r="DQ1" s="1" t="s">
-        <v>903</v>
+        <v>910</v>
       </c>
       <c r="DR1" s="1" t="s">
-        <v>905</v>
+        <v>912</v>
       </c>
       <c r="DS1" s="1" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="DT1" s="1" t="s">
-        <v>909</v>
+        <v>916</v>
       </c>
       <c r="DU1" s="1" t="s">
-        <v>911</v>
+        <v>918</v>
       </c>
       <c r="DV1" s="1" t="s">
-        <v>913</v>
+        <v>920</v>
       </c>
       <c r="DW1" s="1" t="s">
-        <v>915</v>
+        <v>922</v>
       </c>
       <c r="DX1" s="1" t="s">
-        <v>917</v>
+        <v>924</v>
       </c>
       <c r="DY1" s="1" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="DZ1" s="1" t="s">
-        <v>926</v>
+        <v>933</v>
       </c>
       <c r="EA1" s="1" t="s">
-        <v>928</v>
+        <v>935</v>
       </c>
       <c r="EB1" s="1" t="s">
-        <v>930</v>
+        <v>937</v>
       </c>
       <c r="EC1" s="1" t="s">
-        <v>932</v>
+        <v>939</v>
       </c>
       <c r="ED1" s="1" t="s">
-        <v>934</v>
+        <v>941</v>
       </c>
       <c r="EE1" s="1" t="s">
-        <v>936</v>
+        <v>943</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>938</v>
+        <v>945</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>940</v>
+        <v>947</v>
       </c>
       <c r="EH1" s="1" t="s">
-        <v>942</v>
+        <v>949</v>
       </c>
       <c r="EI1" s="1" t="s">
-        <v>944</v>
+        <v>951</v>
       </c>
       <c r="EJ1" s="1" t="s">
-        <v>946</v>
+        <v>953</v>
       </c>
       <c r="EK1" s="1" t="s">
-        <v>948</v>
+        <v>955</v>
       </c>
       <c r="EL1" s="1" t="s">
-        <v>950</v>
+        <v>957</v>
       </c>
       <c r="EM1" s="1" t="s">
-        <v>952</v>
+        <v>959</v>
       </c>
       <c r="EN1" s="1" t="s">
-        <v>954</v>
+        <v>961</v>
       </c>
       <c r="EO1" s="1" t="s">
-        <v>956</v>
+        <v>963</v>
       </c>
       <c r="EP1" s="1" t="s">
-        <v>958</v>
+        <v>965</v>
       </c>
       <c r="EQ1" s="1" t="s">
-        <v>969</v>
+        <v>976</v>
       </c>
       <c r="ER1" s="1" t="s">
-        <v>971</v>
+        <v>978</v>
       </c>
       <c r="ES1" s="1" t="s">
-        <v>973</v>
+        <v>980</v>
       </c>
       <c r="ET1" s="1" t="s">
-        <v>975</v>
+        <v>982</v>
       </c>
       <c r="EU1" s="1" t="s">
-        <v>977</v>
+        <v>984</v>
       </c>
       <c r="EV1" s="1" t="s">
-        <v>979</v>
+        <v>986</v>
       </c>
       <c r="EW1" s="1" t="s">
-        <v>981</v>
+        <v>988</v>
       </c>
       <c r="EX1" s="1" t="s">
-        <v>983</v>
+        <v>990</v>
       </c>
       <c r="EY1" s="1" t="s">
-        <v>985</v>
+        <v>992</v>
       </c>
       <c r="EZ1" s="1" t="s">
-        <v>987</v>
+        <v>994</v>
       </c>
       <c r="FA1" s="1" t="s">
-        <v>995</v>
+        <v>1002</v>
       </c>
       <c r="FB1" s="1" t="s">
-        <v>997</v>
+        <v>1004</v>
       </c>
       <c r="FC1" s="1" t="s">
-        <v>999</v>
+        <v>1006</v>
       </c>
       <c r="FD1" s="1" t="s">
-        <v>1001</v>
+        <v>1008</v>
       </c>
       <c r="FE1" s="1" t="s">
-        <v>1003</v>
+        <v>1010</v>
       </c>
       <c r="FF1" s="1" t="s">
-        <v>1005</v>
+        <v>1012</v>
       </c>
       <c r="FG1" s="1" t="s">
-        <v>1007</v>
+        <v>1014</v>
       </c>
       <c r="FH1" s="1" t="s">
-        <v>1009</v>
+        <v>1016</v>
       </c>
       <c r="FI1" s="1" t="s">
-        <v>1011</v>
+        <v>1018</v>
       </c>
       <c r="FJ1" s="1" t="s">
-        <v>1013</v>
+        <v>1020</v>
       </c>
       <c r="FK1" s="1" t="s">
-        <v>1015</v>
+        <v>1022</v>
       </c>
       <c r="FL1" s="1" t="s">
-        <v>1017</v>
+        <v>1024</v>
       </c>
       <c r="FM1" s="1" t="s">
-        <v>1019</v>
+        <v>1026</v>
       </c>
       <c r="FN1" s="1" t="s">
-        <v>1021</v>
+        <v>1028</v>
       </c>
       <c r="FO1" s="1" t="s">
-        <v>1023</v>
+        <v>1030</v>
       </c>
       <c r="FP1" s="1" t="s">
-        <v>1025</v>
+        <v>1032</v>
       </c>
       <c r="FQ1" s="1" t="s">
-        <v>1027</v>
+        <v>1034</v>
       </c>
       <c r="FR1" s="1" t="s">
-        <v>1029</v>
+        <v>1036</v>
       </c>
       <c r="FS1" s="1" t="s">
-        <v>1031</v>
+        <v>1038</v>
       </c>
       <c r="FT1" s="1" t="s">
-        <v>1033</v>
+        <v>1040</v>
       </c>
       <c r="FU1" s="1" t="s">
-        <v>1035</v>
+        <v>1042</v>
       </c>
       <c r="FV1" s="1" t="s">
-        <v>1037</v>
+        <v>1044</v>
       </c>
       <c r="FW1" s="1" t="s">
-        <v>1039</v>
+        <v>1046</v>
       </c>
       <c r="FX1" s="1" t="s">
-        <v>1041</v>
+        <v>1048</v>
       </c>
       <c r="FY1" s="1" t="s">
-        <v>1043</v>
+        <v>1050</v>
       </c>
       <c r="FZ1" s="1" t="s">
-        <v>1045</v>
+        <v>1052</v>
       </c>
       <c r="GA1" s="1" t="s">
-        <v>1047</v>
+        <v>1054</v>
       </c>
       <c r="GB1" s="1" t="s">
-        <v>1049</v>
+        <v>1056</v>
       </c>
       <c r="GC1" s="1" t="s">
-        <v>1051</v>
+        <v>1058</v>
       </c>
       <c r="GD1" s="1" t="s">
-        <v>1053</v>
+        <v>1060</v>
       </c>
       <c r="GE1" s="1" t="s">
-        <v>1055</v>
+        <v>1062</v>
       </c>
       <c r="GF1" s="1" t="s">
-        <v>1057</v>
+        <v>1064</v>
       </c>
       <c r="GG1" s="1" t="s">
-        <v>1059</v>
+        <v>1066</v>
       </c>
       <c r="GH1" s="1" t="s">
-        <v>1061</v>
+        <v>1068</v>
       </c>
       <c r="GI1" s="1" t="s">
-        <v>1063</v>
+        <v>1070</v>
       </c>
       <c r="GJ1" s="1" t="s">
-        <v>1065</v>
+        <v>1072</v>
       </c>
       <c r="GK1" s="1" t="s">
-        <v>1067</v>
+        <v>1074</v>
       </c>
       <c r="GL1" s="1" t="s">
-        <v>1069</v>
+        <v>1076</v>
       </c>
       <c r="GM1" s="1" t="s">
-        <v>1071</v>
+        <v>1078</v>
       </c>
       <c r="GN1" s="1" t="s">
-        <v>1073</v>
+        <v>1080</v>
       </c>
       <c r="GO1" s="1" t="s">
-        <v>1075</v>
+        <v>1082</v>
       </c>
       <c r="GP1" s="1" t="s">
-        <v>1077</v>
+        <v>1084</v>
       </c>
       <c r="GQ1" s="1" t="s">
-        <v>1079</v>
+        <v>1086</v>
       </c>
       <c r="GR1" s="1" t="s">
-        <v>1081</v>
+        <v>1088</v>
       </c>
       <c r="GS1" s="1" t="s">
-        <v>1083</v>
+        <v>1090</v>
       </c>
       <c r="GT1" s="1" t="s">
-        <v>1085</v>
+        <v>1092</v>
       </c>
       <c r="GU1" s="1" t="s">
-        <v>1087</v>
+        <v>1094</v>
       </c>
       <c r="GV1" s="1" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="GW1" s="1" t="s">
-        <v>1091</v>
+        <v>1098</v>
       </c>
       <c r="GX1" s="1" t="s">
-        <v>1096</v>
+        <v>1103</v>
       </c>
       <c r="GY1" s="1" t="s">
-        <v>1098</v>
+        <v>1105</v>
       </c>
       <c r="GZ1" s="1" t="s">
-        <v>1100</v>
+        <v>1107</v>
       </c>
       <c r="HA1" s="1" t="s">
-        <v>1102</v>
+        <v>1109</v>
       </c>
       <c r="HB1" s="1" t="s">
-        <v>1104</v>
+        <v>1111</v>
       </c>
       <c r="HC1" s="1" t="s">
-        <v>1106</v>
+        <v>1113</v>
       </c>
       <c r="HD1" s="1" t="s">
-        <v>1108</v>
+        <v>1115</v>
       </c>
       <c r="HE1" s="1" t="s">
-        <v>1110</v>
+        <v>1117</v>
       </c>
       <c r="HF1" s="1" t="s">
-        <v>1112</v>
+        <v>1119</v>
       </c>
       <c r="HG1" s="1" t="s">
-        <v>1114</v>
+        <v>1121</v>
       </c>
       <c r="HH1" s="1" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="HI1" s="1" t="s">
-        <v>1118</v>
+        <v>1125</v>
       </c>
       <c r="HJ1" s="1" t="s">
-        <v>1120</v>
+        <v>1127</v>
       </c>
       <c r="HK1" s="1" t="s">
-        <v>1122</v>
+        <v>1129</v>
       </c>
       <c r="HL1" s="1" t="s">
-        <v>1124</v>
+        <v>1131</v>
       </c>
       <c r="HM1" s="1" t="s">
-        <v>1126</v>
+        <v>1133</v>
       </c>
       <c r="HN1" s="1" t="s">
-        <v>1128</v>
+        <v>1135</v>
       </c>
       <c r="HO1" s="1" t="s">
-        <v>1130</v>
+        <v>1137</v>
       </c>
       <c r="HP1" s="1" t="s">
-        <v>1132</v>
+        <v>1139</v>
       </c>
       <c r="HQ1" s="1" t="s">
-        <v>1134</v>
+        <v>1141</v>
       </c>
       <c r="HR1" s="1" t="s">
-        <v>1136</v>
+        <v>1143</v>
       </c>
       <c r="HS1" s="1" t="s">
-        <v>1138</v>
+        <v>1145</v>
       </c>
       <c r="HT1" s="1" t="s">
-        <v>1140</v>
+        <v>1147</v>
       </c>
       <c r="HU1" s="1" t="s">
-        <v>1142</v>
+        <v>1149</v>
       </c>
       <c r="HV1" s="1" t="s">
-        <v>1144</v>
+        <v>1151</v>
       </c>
       <c r="HW1" s="1" t="s">
-        <v>1146</v>
+        <v>1153</v>
       </c>
       <c r="HX1" s="1" t="s">
-        <v>1148</v>
+        <v>1155</v>
       </c>
       <c r="HY1" s="1" t="s">
-        <v>1150</v>
+        <v>1157</v>
       </c>
       <c r="HZ1" s="1" t="s">
-        <v>1152</v>
+        <v>1159</v>
       </c>
       <c r="IA1" s="1" t="s">
-        <v>1154</v>
+        <v>1161</v>
       </c>
       <c r="IB1" s="1" t="s">
-        <v>1156</v>
+        <v>1163</v>
       </c>
       <c r="IC1" s="1" t="s">
-        <v>1158</v>
+        <v>1165</v>
       </c>
       <c r="ID1" s="1" t="s">
-        <v>1160</v>
+        <v>1167</v>
       </c>
       <c r="IE1" s="1" t="s">
-        <v>1162</v>
+        <v>1169</v>
       </c>
       <c r="IF1" s="1" t="s">
-        <v>1164</v>
+        <v>1171</v>
       </c>
       <c r="IG1" s="1" t="s">
-        <v>1166</v>
+        <v>1173</v>
       </c>
       <c r="IH1" s="1" t="s">
-        <v>1168</v>
+        <v>1175</v>
       </c>
       <c r="II1" s="1" t="s">
-        <v>1170</v>
+        <v>1177</v>
       </c>
       <c r="IJ1" s="1" t="s">
-        <v>1172</v>
+        <v>1179</v>
       </c>
       <c r="IK1" s="1" t="s">
-        <v>1174</v>
+        <v>1181</v>
       </c>
       <c r="IL1" s="1" t="s">
-        <v>1176</v>
+        <v>1183</v>
       </c>
       <c r="IM1" s="1" t="s">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="IN1" s="1" t="s">
-        <v>1180</v>
+        <v>1187</v>
       </c>
       <c r="IO1" s="1" t="s">
-        <v>1182</v>
+        <v>1189</v>
       </c>
       <c r="IP1" s="1" t="s">
-        <v>1184</v>
+        <v>1191</v>
       </c>
       <c r="IQ1" s="1" t="s">
-        <v>1186</v>
+        <v>1193</v>
       </c>
       <c r="IR1" s="1" t="s">
-        <v>1188</v>
+        <v>1195</v>
       </c>
       <c r="IS1" s="1" t="s">
-        <v>1190</v>
+        <v>1197</v>
       </c>
       <c r="IT1" s="1" t="s">
-        <v>1192</v>
+        <v>1199</v>
       </c>
       <c r="IU1" s="1" t="s">
-        <v>1194</v>
+        <v>1201</v>
       </c>
       <c r="IV1" s="1" t="s">
-        <v>1196</v>
+        <v>1203</v>
       </c>
       <c r="IW1" s="1" t="s">
-        <v>1198</v>
+        <v>1205</v>
       </c>
       <c r="IX1" s="1" t="s">
-        <v>1200</v>
+        <v>1207</v>
       </c>
       <c r="IY1" s="1" t="s">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="IZ1" s="1" t="s">
-        <v>1204</v>
+        <v>1211</v>
       </c>
       <c r="JA1" s="1" t="s">
-        <v>1206</v>
+        <v>1213</v>
       </c>
       <c r="JB1" s="1" t="s">
-        <v>1208</v>
+        <v>1215</v>
       </c>
       <c r="JC1" s="1" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="JD1" s="1" t="s">
-        <v>1212</v>
+        <v>1219</v>
       </c>
       <c r="JE1" s="1" t="s">
-        <v>1214</v>
+        <v>1221</v>
       </c>
       <c r="JF1" s="1" t="s">
-        <v>1216</v>
+        <v>1223</v>
       </c>
       <c r="JG1" s="1" t="s">
-        <v>1218</v>
+        <v>1225</v>
       </c>
       <c r="JH1" s="1" t="s">
-        <v>1220</v>
+        <v>1227</v>
       </c>
       <c r="JI1" s="1" t="s">
-        <v>1222</v>
+        <v>1229</v>
       </c>
       <c r="JJ1" s="1" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="JK1" s="1" t="s">
-        <v>1226</v>
+        <v>1233</v>
       </c>
       <c r="JL1" s="1" t="s">
-        <v>1228</v>
+        <v>1235</v>
       </c>
       <c r="JM1" s="1" t="s">
-        <v>1230</v>
+        <v>1237</v>
       </c>
       <c r="JN1" s="1" t="s">
-        <v>1232</v>
+        <v>1239</v>
       </c>
       <c r="JO1" s="1" t="s">
-        <v>1234</v>
+        <v>1241</v>
       </c>
       <c r="JP1" s="1" t="s">
-        <v>1236</v>
+        <v>1243</v>
       </c>
       <c r="JQ1" s="1" t="s">
-        <v>1238</v>
+        <v>1245</v>
       </c>
       <c r="JR1" s="1" t="s">
-        <v>1240</v>
+        <v>1247</v>
       </c>
       <c r="JS1" s="1" t="s">
-        <v>1242</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="2" spans="1:279" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="DC2" s="2" t="s">
-        <v>876</v>
+        <v>883</v>
       </c>
       <c r="DD2" s="2" t="s">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="DE2" s="2" t="s">
-        <v>880</v>
+        <v>887</v>
       </c>
       <c r="DF2" s="2" t="s">
-        <v>882</v>
+        <v>889</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>884</v>
+        <v>891</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>886</v>
+        <v>893</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>888</v>
+        <v>895</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>890</v>
+        <v>897</v>
       </c>
       <c r="DK2" s="2" t="s">
-        <v>892</v>
+        <v>899</v>
       </c>
       <c r="DL2" s="2" t="s">
-        <v>894</v>
+        <v>901</v>
       </c>
       <c r="DM2" s="2" t="s">
-        <v>896</v>
+        <v>903</v>
       </c>
       <c r="DN2" s="2" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="DO2" s="2" t="s">
-        <v>900</v>
+        <v>907</v>
       </c>
       <c r="DP2" s="2" t="s">
-        <v>902</v>
+        <v>909</v>
       </c>
       <c r="DQ2" s="2" t="s">
-        <v>904</v>
+        <v>911</v>
       </c>
       <c r="DR2" s="2" t="s">
-        <v>906</v>
+        <v>913</v>
       </c>
       <c r="DS2" s="2" t="s">
-        <v>908</v>
+        <v>915</v>
       </c>
       <c r="DT2" s="2" t="s">
-        <v>910</v>
+        <v>917</v>
       </c>
       <c r="DU2" s="2" t="s">
-        <v>912</v>
+        <v>919</v>
       </c>
       <c r="DV2" s="2" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="DW2" s="2" t="s">
-        <v>916</v>
+        <v>923</v>
       </c>
       <c r="DX2" s="2" t="s">
-        <v>918</v>
+        <v>925</v>
       </c>
       <c r="DY2" s="2" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="DZ2" s="2" t="s">
-        <v>927</v>
+        <v>934</v>
       </c>
       <c r="EA2" s="2" t="s">
-        <v>929</v>
+        <v>936</v>
       </c>
       <c r="EB2" s="2" t="s">
-        <v>931</v>
+        <v>938</v>
       </c>
       <c r="EC2" s="2" t="s">
-        <v>933</v>
+        <v>940</v>
       </c>
       <c r="ED2" s="2" t="s">
-        <v>935</v>
+        <v>942</v>
       </c>
       <c r="EE2" s="2" t="s">
-        <v>937</v>
+        <v>944</v>
       </c>
       <c r="EF2" s="2" t="s">
-        <v>939</v>
+        <v>946</v>
       </c>
       <c r="EG2" s="2" t="s">
-        <v>941</v>
+        <v>948</v>
       </c>
       <c r="EH2" s="2" t="s">
-        <v>943</v>
+        <v>950</v>
       </c>
       <c r="EI2" s="2" t="s">
-        <v>945</v>
+        <v>952</v>
       </c>
       <c r="EJ2" s="2" t="s">
-        <v>947</v>
+        <v>954</v>
       </c>
       <c r="EK2" s="2" t="s">
-        <v>949</v>
+        <v>956</v>
       </c>
       <c r="EL2" s="2" t="s">
-        <v>951</v>
+        <v>958</v>
       </c>
       <c r="EM2" s="2" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="EN2" s="2" t="s">
-        <v>955</v>
+        <v>962</v>
       </c>
       <c r="EO2" s="2" t="s">
-        <v>957</v>
+        <v>964</v>
       </c>
       <c r="EP2" s="2" t="s">
-        <v>959</v>
+        <v>966</v>
       </c>
       <c r="EQ2" s="2" t="s">
-        <v>970</v>
+        <v>977</v>
       </c>
       <c r="ER2" s="2" t="s">
-        <v>972</v>
+        <v>979</v>
       </c>
       <c r="ES2" s="2" t="s">
-        <v>974</v>
+        <v>981</v>
       </c>
       <c r="ET2" s="2" t="s">
-        <v>976</v>
+        <v>983</v>
       </c>
       <c r="EU2" s="2" t="s">
-        <v>978</v>
+        <v>985</v>
       </c>
       <c r="EV2" s="2" t="s">
-        <v>980</v>
+        <v>987</v>
       </c>
       <c r="EW2" s="2" t="s">
-        <v>982</v>
+        <v>989</v>
       </c>
       <c r="EX2" s="2" t="s">
-        <v>984</v>
+        <v>991</v>
       </c>
       <c r="EY2" s="2" t="s">
-        <v>986</v>
+        <v>993</v>
       </c>
       <c r="EZ2" s="2" t="s">
-        <v>988</v>
+        <v>995</v>
       </c>
       <c r="FA2" s="2" t="s">
-        <v>996</v>
+        <v>1003</v>
       </c>
       <c r="FB2" s="2" t="s">
-        <v>998</v>
+        <v>1005</v>
       </c>
       <c r="FC2" s="2" t="s">
-        <v>1000</v>
+        <v>1007</v>
       </c>
       <c r="FD2" s="2" t="s">
-        <v>1002</v>
+        <v>1009</v>
       </c>
       <c r="FE2" s="2" t="s">
-        <v>1004</v>
+        <v>1011</v>
       </c>
       <c r="FF2" s="2" t="s">
-        <v>1006</v>
+        <v>1013</v>
       </c>
       <c r="FG2" s="2" t="s">
-        <v>1008</v>
+        <v>1015</v>
       </c>
       <c r="FH2" s="2" t="s">
-        <v>1010</v>
+        <v>1017</v>
       </c>
       <c r="FI2" s="2" t="s">
-        <v>1012</v>
+        <v>1019</v>
       </c>
       <c r="FJ2" s="2" t="s">
-        <v>1014</v>
+        <v>1021</v>
       </c>
       <c r="FK2" s="2" t="s">
-        <v>1016</v>
+        <v>1023</v>
       </c>
       <c r="FL2" s="2" t="s">
-        <v>1018</v>
+        <v>1025</v>
       </c>
       <c r="FM2" s="2" t="s">
-        <v>1020</v>
+        <v>1027</v>
       </c>
       <c r="FN2" s="2" t="s">
-        <v>1022</v>
+        <v>1029</v>
       </c>
       <c r="FO2" s="2" t="s">
-        <v>1024</v>
+        <v>1031</v>
       </c>
       <c r="FP2" s="2" t="s">
-        <v>1026</v>
+        <v>1033</v>
       </c>
       <c r="FQ2" s="2" t="s">
-        <v>1028</v>
+        <v>1035</v>
       </c>
       <c r="FR2" s="2" t="s">
-        <v>1030</v>
+        <v>1037</v>
       </c>
       <c r="FS2" s="2" t="s">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="FT2" s="2" t="s">
-        <v>1034</v>
+        <v>1041</v>
       </c>
       <c r="FU2" s="2" t="s">
-        <v>1036</v>
+        <v>1043</v>
       </c>
       <c r="FV2" s="2" t="s">
-        <v>1038</v>
+        <v>1045</v>
       </c>
       <c r="FW2" s="2" t="s">
-        <v>1040</v>
+        <v>1047</v>
       </c>
       <c r="FX2" s="2" t="s">
-        <v>1042</v>
+        <v>1049</v>
       </c>
       <c r="FY2" s="2" t="s">
-        <v>1044</v>
+        <v>1051</v>
       </c>
       <c r="FZ2" s="2" t="s">
-        <v>1046</v>
+        <v>1053</v>
       </c>
       <c r="GA2" s="2" t="s">
-        <v>1048</v>
+        <v>1055</v>
       </c>
       <c r="GB2" s="2" t="s">
-        <v>1050</v>
+        <v>1057</v>
       </c>
       <c r="GC2" s="2" t="s">
-        <v>1052</v>
+        <v>1059</v>
       </c>
       <c r="GD2" s="2" t="s">
-        <v>1054</v>
+        <v>1061</v>
       </c>
       <c r="GE2" s="2" t="s">
-        <v>1056</v>
+        <v>1063</v>
       </c>
       <c r="GF2" s="2" t="s">
-        <v>1058</v>
+        <v>1065</v>
       </c>
       <c r="GG2" s="2" t="s">
-        <v>1060</v>
+        <v>1067</v>
       </c>
       <c r="GH2" s="2" t="s">
-        <v>1062</v>
+        <v>1069</v>
       </c>
       <c r="GI2" s="2" t="s">
-        <v>1064</v>
+        <v>1071</v>
       </c>
       <c r="GJ2" s="2" t="s">
-        <v>1066</v>
+        <v>1073</v>
       </c>
       <c r="GK2" s="2" t="s">
-        <v>1068</v>
+        <v>1075</v>
       </c>
       <c r="GL2" s="2" t="s">
-        <v>1070</v>
+        <v>1077</v>
       </c>
       <c r="GM2" s="2" t="s">
-        <v>1072</v>
+        <v>1079</v>
       </c>
       <c r="GN2" s="2" t="s">
-        <v>1074</v>
+        <v>1081</v>
       </c>
       <c r="GO2" s="2" t="s">
-        <v>1076</v>
+        <v>1083</v>
       </c>
       <c r="GP2" s="2" t="s">
-        <v>1078</v>
+        <v>1085</v>
       </c>
       <c r="GQ2" s="2" t="s">
-        <v>1080</v>
+        <v>1087</v>
       </c>
       <c r="GR2" s="2" t="s">
-        <v>1082</v>
+        <v>1089</v>
       </c>
       <c r="GS2" s="2" t="s">
-        <v>1084</v>
+        <v>1091</v>
       </c>
       <c r="GT2" s="2" t="s">
-        <v>1086</v>
+        <v>1093</v>
       </c>
       <c r="GU2" s="2" t="s">
-        <v>1088</v>
+        <v>1095</v>
       </c>
       <c r="GV2" s="2" t="s">
-        <v>1090</v>
+        <v>1097</v>
       </c>
       <c r="GW2" s="2" t="s">
-        <v>1092</v>
+        <v>1099</v>
       </c>
       <c r="GX2" s="2" t="s">
-        <v>1097</v>
+        <v>1104</v>
       </c>
       <c r="GY2" s="2" t="s">
-        <v>1099</v>
+        <v>1106</v>
       </c>
       <c r="GZ2" s="2" t="s">
-        <v>1101</v>
+        <v>1108</v>
       </c>
       <c r="HA2" s="2" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="HB2" s="2" t="s">
-        <v>1105</v>
+        <v>1112</v>
       </c>
       <c r="HC2" s="2" t="s">
-        <v>1107</v>
+        <v>1114</v>
       </c>
       <c r="HD2" s="2" t="s">
-        <v>1109</v>
+        <v>1116</v>
       </c>
       <c r="HE2" s="2" t="s">
-        <v>1111</v>
+        <v>1118</v>
       </c>
       <c r="HF2" s="2" t="s">
-        <v>1113</v>
+        <v>1120</v>
       </c>
       <c r="HG2" s="2" t="s">
-        <v>1115</v>
+        <v>1122</v>
       </c>
       <c r="HH2" s="2" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="HI2" s="2" t="s">
-        <v>1119</v>
+        <v>1126</v>
       </c>
       <c r="HJ2" s="2" t="s">
-        <v>1121</v>
+        <v>1128</v>
       </c>
       <c r="HK2" s="2" t="s">
-        <v>1123</v>
+        <v>1130</v>
       </c>
       <c r="HL2" s="2" t="s">
-        <v>1125</v>
+        <v>1132</v>
       </c>
       <c r="HM2" s="2" t="s">
-        <v>1127</v>
+        <v>1134</v>
       </c>
       <c r="HN2" s="2" t="s">
-        <v>1129</v>
+        <v>1136</v>
       </c>
       <c r="HO2" s="2" t="s">
-        <v>1131</v>
+        <v>1138</v>
       </c>
       <c r="HP2" s="2" t="s">
-        <v>1133</v>
+        <v>1140</v>
       </c>
       <c r="HQ2" s="2" t="s">
-        <v>1135</v>
+        <v>1142</v>
       </c>
       <c r="HR2" s="2" t="s">
-        <v>1137</v>
+        <v>1144</v>
       </c>
       <c r="HS2" s="2" t="s">
-        <v>1139</v>
+        <v>1146</v>
       </c>
       <c r="HT2" s="2" t="s">
-        <v>1141</v>
+        <v>1148</v>
       </c>
       <c r="HU2" s="2" t="s">
-        <v>1143</v>
+        <v>1150</v>
       </c>
       <c r="HV2" s="2" t="s">
-        <v>1145</v>
+        <v>1152</v>
       </c>
       <c r="HW2" s="2" t="s">
-        <v>1147</v>
+        <v>1154</v>
       </c>
       <c r="HX2" s="2" t="s">
-        <v>1149</v>
+        <v>1156</v>
       </c>
       <c r="HY2" s="2" t="s">
-        <v>1151</v>
+        <v>1158</v>
       </c>
       <c r="HZ2" s="2" t="s">
-        <v>1153</v>
+        <v>1160</v>
       </c>
       <c r="IA2" s="2" t="s">
-        <v>1155</v>
+        <v>1162</v>
       </c>
       <c r="IB2" s="2" t="s">
-        <v>1157</v>
+        <v>1164</v>
       </c>
       <c r="IC2" s="2" t="s">
-        <v>1159</v>
+        <v>1166</v>
       </c>
       <c r="ID2" s="2" t="s">
-        <v>1161</v>
+        <v>1168</v>
       </c>
       <c r="IE2" s="2" t="s">
-        <v>1163</v>
+        <v>1170</v>
       </c>
       <c r="IF2" s="2" t="s">
-        <v>1165</v>
+        <v>1172</v>
       </c>
       <c r="IG2" s="2" t="s">
-        <v>1167</v>
+        <v>1174</v>
       </c>
       <c r="IH2" s="2" t="s">
-        <v>1169</v>
+        <v>1176</v>
       </c>
       <c r="II2" s="2" t="s">
-        <v>1171</v>
+        <v>1178</v>
       </c>
       <c r="IJ2" s="2" t="s">
-        <v>1173</v>
+        <v>1180</v>
       </c>
       <c r="IK2" s="2" t="s">
-        <v>1175</v>
+        <v>1182</v>
       </c>
       <c r="IL2" s="2" t="s">
-        <v>1177</v>
+        <v>1184</v>
       </c>
       <c r="IM2" s="2" t="s">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="IN2" s="2" t="s">
-        <v>1181</v>
+        <v>1188</v>
       </c>
       <c r="IO2" s="2" t="s">
-        <v>1183</v>
+        <v>1190</v>
       </c>
       <c r="IP2" s="2" t="s">
-        <v>1185</v>
+        <v>1192</v>
       </c>
       <c r="IQ2" s="2" t="s">
-        <v>1187</v>
+        <v>1194</v>
       </c>
       <c r="IR2" s="2" t="s">
-        <v>1189</v>
+        <v>1196</v>
       </c>
       <c r="IS2" s="2" t="s">
-        <v>1191</v>
+        <v>1198</v>
       </c>
       <c r="IT2" s="2" t="s">
-        <v>1193</v>
+        <v>1200</v>
       </c>
       <c r="IU2" s="2" t="s">
-        <v>1195</v>
+        <v>1202</v>
       </c>
       <c r="IV2" s="2" t="s">
-        <v>1197</v>
+        <v>1204</v>
       </c>
       <c r="IW2" s="2" t="s">
-        <v>1199</v>
+        <v>1206</v>
       </c>
       <c r="IX2" s="2" t="s">
-        <v>1201</v>
+        <v>1208</v>
       </c>
       <c r="IY2" s="2" t="s">
-        <v>1203</v>
+        <v>1210</v>
       </c>
       <c r="IZ2" s="2" t="s">
-        <v>1205</v>
+        <v>1212</v>
       </c>
       <c r="JA2" s="2" t="s">
-        <v>1207</v>
+        <v>1214</v>
       </c>
       <c r="JB2" s="2" t="s">
-        <v>1209</v>
+        <v>1216</v>
       </c>
       <c r="JC2" s="2" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="JD2" s="2" t="s">
-        <v>1213</v>
+        <v>1220</v>
       </c>
       <c r="JE2" s="2" t="s">
-        <v>1215</v>
+        <v>1222</v>
       </c>
       <c r="JF2" s="2" t="s">
-        <v>1217</v>
+        <v>1224</v>
       </c>
       <c r="JG2" s="2" t="s">
-        <v>1219</v>
+        <v>1226</v>
       </c>
       <c r="JH2" s="2" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="JI2" s="2" t="s">
-        <v>1223</v>
+        <v>1230</v>
       </c>
       <c r="JJ2" s="2" t="s">
-        <v>1225</v>
+        <v>1232</v>
       </c>
       <c r="JK2" s="2" t="s">
-        <v>1227</v>
+        <v>1234</v>
       </c>
       <c r="JL2" s="2" t="s">
-        <v>1229</v>
+        <v>1236</v>
       </c>
       <c r="JM2" s="2" t="s">
-        <v>1231</v>
+        <v>1238</v>
       </c>
       <c r="JN2" s="2" t="s">
-        <v>1233</v>
+        <v>1240</v>
       </c>
       <c r="JO2" s="2" t="s">
-        <v>1235</v>
+        <v>1242</v>
       </c>
       <c r="JP2" s="2" t="s">
-        <v>1237</v>
+        <v>1244</v>
       </c>
       <c r="JQ2" s="2" t="s">
-        <v>1239</v>
+        <v>1246</v>
       </c>
       <c r="JR2" s="2" t="s">
-        <v>1241</v>
+        <v>1248</v>
       </c>
       <c r="JS2" s="2" t="s">
-        <v>1243</v>
+        <v>1250</v>
       </c>
     </row>
   </sheetData>
@@ -7033,247 +7062,247 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="M1:GX289"/>
+  <dimension ref="M1:GX294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="13:206">
       <c r="M1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="N1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AB1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="BO1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="BS1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="BX1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="CL1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="CN1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="CO1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="CZ1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="DC1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="DY1" t="s">
-        <v>919</v>
+        <v>926</v>
       </c>
       <c r="EQ1" t="s">
-        <v>960</v>
+        <v>967</v>
       </c>
       <c r="FA1" t="s">
-        <v>989</v>
+        <v>996</v>
       </c>
       <c r="GX1" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="2" spans="13:206">
       <c r="M2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AB2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="BO2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="BS2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="BX2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="CL2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="CN2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="CO2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="CZ2" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="DC2" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="DY2" t="s">
-        <v>920</v>
+        <v>927</v>
       </c>
       <c r="EQ2" t="s">
-        <v>961</v>
+        <v>968</v>
       </c>
       <c r="FA2" t="s">
-        <v>990</v>
+        <v>997</v>
       </c>
       <c r="GX2" t="s">
-        <v>991</v>
+        <v>998</v>
       </c>
     </row>
     <row r="3" spans="13:206">
       <c r="M3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="N3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="P3" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AB3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="BO3" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="BX3" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="CL3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="CN3" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="CO3" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="CZ3" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="DC3" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="DY3" t="s">
-        <v>921</v>
+        <v>928</v>
       </c>
       <c r="EQ3" t="s">
-        <v>962</v>
+        <v>969</v>
       </c>
       <c r="FA3" t="s">
-        <v>991</v>
+        <v>998</v>
       </c>
       <c r="GX3" t="s">
-        <v>1094</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="4" spans="13:206">
       <c r="M4" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="N4" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="P4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AB4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="CL4" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="CN4" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="CZ4" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="DC4" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="DY4" t="s">
-        <v>922</v>
+        <v>929</v>
       </c>
       <c r="EQ4" t="s">
-        <v>963</v>
+        <v>970</v>
       </c>
       <c r="FA4" t="s">
-        <v>992</v>
+        <v>999</v>
       </c>
       <c r="GX4" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="5" spans="13:206">
       <c r="M5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N5" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="P5" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AB5" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="CL5" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="CN5" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="DC5" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="DY5" t="s">
-        <v>923</v>
+        <v>930</v>
       </c>
       <c r="EQ5" t="s">
-        <v>964</v>
+        <v>971</v>
       </c>
       <c r="FA5" t="s">
-        <v>993</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6" spans="13:206">
       <c r="M6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="P6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AB6" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="CL6" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="CN6" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="DC6" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="EQ6" t="s">
-        <v>965</v>
+        <v>972</v>
       </c>
       <c r="FA6" t="s">
         <v>116</v>
@@ -7281,1615 +7310,1640 @@
     </row>
     <row r="7" spans="13:206">
       <c r="M7" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="P7" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AB7" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="CL7" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="CN7" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="DC7" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="EQ7" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="FA7" t="s">
-        <v>994</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="8" spans="13:206">
       <c r="M8" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AB8" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="CL8" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="CN8" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="DC8" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="EQ8" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
     </row>
     <row r="9" spans="13:206">
       <c r="M9" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AB9" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="CL9" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="DC9" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="EQ9" t="s">
-        <v>968</v>
+        <v>975</v>
       </c>
     </row>
     <row r="10" spans="13:206">
       <c r="M10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AB10" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="CL10" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="DC10" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="11" spans="13:206">
       <c r="M11" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AB11" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="CL11" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="DC11" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="12" spans="13:206">
       <c r="M12" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AB12" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="CL12" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="DC12" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="13" spans="13:206">
       <c r="M13" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AB13" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="CL13" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="DC13" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="14" spans="13:206">
       <c r="M14" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AB14" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="CL14" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="DC14" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="15" spans="13:206">
       <c r="M15" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AB15" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="CL15" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="DC15" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="16" spans="13:206">
       <c r="M16" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AB16" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="DC16" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="17" spans="13:107">
       <c r="M17" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AB17" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="DC17" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="18" spans="13:107">
       <c r="M18" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AB18" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="DC18" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="19" spans="13:107">
       <c r="M19" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AB19" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="DC19" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="20" spans="13:107">
       <c r="M20" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AB20" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="DC20" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="21" spans="13:107">
       <c r="M21" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AB21" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="DC21" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="22" spans="13:107">
       <c r="M22" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AB22" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="DC22" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="23" spans="13:107">
       <c r="M23" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AB23" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="DC23" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="24" spans="13:107">
       <c r="M24" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AB24" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="DC24" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="25" spans="13:107">
       <c r="M25" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AB25" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="DC25" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="26" spans="13:107">
       <c r="M26" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AB26" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="DC26" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="27" spans="13:107">
       <c r="M27" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AB27" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="DC27" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="28" spans="13:107">
       <c r="M28" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AB28" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="DC28" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="29" spans="13:107">
       <c r="M29" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AB29" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="DC29" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="30" spans="13:107">
       <c r="M30" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AB30" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="DC30" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="31" spans="13:107">
       <c r="AB31" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="DC31" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="32" spans="13:107">
       <c r="AB32" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="DC32" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="33" spans="107:107">
       <c r="DC33" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="34" spans="107:107">
       <c r="DC34" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="35" spans="107:107">
       <c r="DC35" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="36" spans="107:107">
       <c r="DC36" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="37" spans="107:107">
       <c r="DC37" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="38" spans="107:107">
       <c r="DC38" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="39" spans="107:107">
       <c r="DC39" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="40" spans="107:107">
       <c r="DC40" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="41" spans="107:107">
       <c r="DC41" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="42" spans="107:107">
       <c r="DC42" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="43" spans="107:107">
       <c r="DC43" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="44" spans="107:107">
       <c r="DC44" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="45" spans="107:107">
       <c r="DC45" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="46" spans="107:107">
       <c r="DC46" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="47" spans="107:107">
       <c r="DC47" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="48" spans="107:107">
       <c r="DC48" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="49" spans="107:107">
       <c r="DC49" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="50" spans="107:107">
       <c r="DC50" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="51" spans="107:107">
       <c r="DC51" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="52" spans="107:107">
       <c r="DC52" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="53" spans="107:107">
       <c r="DC53" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="54" spans="107:107">
       <c r="DC54" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="55" spans="107:107">
       <c r="DC55" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="56" spans="107:107">
       <c r="DC56" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="57" spans="107:107">
       <c r="DC57" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="58" spans="107:107">
       <c r="DC58" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="59" spans="107:107">
       <c r="DC59" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="60" spans="107:107">
       <c r="DC60" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="61" spans="107:107">
       <c r="DC61" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="62" spans="107:107">
       <c r="DC62" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="63" spans="107:107">
       <c r="DC63" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="64" spans="107:107">
       <c r="DC64" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="65" spans="107:107">
       <c r="DC65" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="66" spans="107:107">
       <c r="DC66" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="67" spans="107:107">
       <c r="DC67" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="68" spans="107:107">
       <c r="DC68" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="69" spans="107:107">
       <c r="DC69" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="70" spans="107:107">
       <c r="DC70" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="71" spans="107:107">
       <c r="DC71" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="72" spans="107:107">
       <c r="DC72" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="73" spans="107:107">
       <c r="DC73" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="74" spans="107:107">
       <c r="DC74" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="75" spans="107:107">
       <c r="DC75" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="76" spans="107:107">
       <c r="DC76" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="77" spans="107:107">
       <c r="DC77" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="78" spans="107:107">
       <c r="DC78" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="79" spans="107:107">
       <c r="DC79" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="80" spans="107:107">
       <c r="DC80" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="81" spans="107:107">
       <c r="DC81" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="82" spans="107:107">
       <c r="DC82" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="83" spans="107:107">
       <c r="DC83" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="84" spans="107:107">
       <c r="DC84" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="85" spans="107:107">
       <c r="DC85" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="86" spans="107:107">
       <c r="DC86" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="87" spans="107:107">
       <c r="DC87" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="88" spans="107:107">
       <c r="DC88" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="89" spans="107:107">
       <c r="DC89" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="90" spans="107:107">
       <c r="DC90" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="91" spans="107:107">
       <c r="DC91" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="92" spans="107:107">
       <c r="DC92" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="93" spans="107:107">
       <c r="DC93" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="94" spans="107:107">
       <c r="DC94" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="95" spans="107:107">
       <c r="DC95" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="96" spans="107:107">
       <c r="DC96" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="97" spans="107:107">
       <c r="DC97" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="98" spans="107:107">
       <c r="DC98" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="99" spans="107:107">
       <c r="DC99" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="100" spans="107:107">
       <c r="DC100" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="101" spans="107:107">
       <c r="DC101" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="102" spans="107:107">
       <c r="DC102" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="103" spans="107:107">
       <c r="DC103" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="104" spans="107:107">
       <c r="DC104" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="105" spans="107:107">
       <c r="DC105" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="106" spans="107:107">
       <c r="DC106" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="107" spans="107:107">
       <c r="DC107" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="108" spans="107:107">
       <c r="DC108" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="109" spans="107:107">
       <c r="DC109" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="110" spans="107:107">
       <c r="DC110" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="111" spans="107:107">
       <c r="DC111" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="112" spans="107:107">
       <c r="DC112" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="113" spans="107:107">
       <c r="DC113" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="114" spans="107:107">
       <c r="DC114" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="115" spans="107:107">
       <c r="DC115" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="116" spans="107:107">
       <c r="DC116" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="117" spans="107:107">
       <c r="DC117" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="118" spans="107:107">
       <c r="DC118" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="119" spans="107:107">
       <c r="DC119" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="120" spans="107:107">
       <c r="DC120" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="121" spans="107:107">
       <c r="DC121" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="122" spans="107:107">
       <c r="DC122" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="123" spans="107:107">
       <c r="DC123" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="124" spans="107:107">
       <c r="DC124" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
     </row>
     <row r="125" spans="107:107">
       <c r="DC125" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="126" spans="107:107">
       <c r="DC126" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
     </row>
     <row r="127" spans="107:107">
       <c r="DC127" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="128" spans="107:107">
       <c r="DC128" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="129" spans="107:107">
       <c r="DC129" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="130" spans="107:107">
       <c r="DC130" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
     </row>
     <row r="131" spans="107:107">
       <c r="DC131" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
     </row>
     <row r="132" spans="107:107">
       <c r="DC132" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
     </row>
     <row r="133" spans="107:107">
       <c r="DC133" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
     </row>
     <row r="134" spans="107:107">
       <c r="DC134" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
     </row>
     <row r="135" spans="107:107">
       <c r="DC135" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="136" spans="107:107">
       <c r="DC136" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
     </row>
     <row r="137" spans="107:107">
       <c r="DC137" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
     </row>
     <row r="138" spans="107:107">
       <c r="DC138" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
     </row>
     <row r="139" spans="107:107">
       <c r="DC139" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="140" spans="107:107">
       <c r="DC140" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
     </row>
     <row r="141" spans="107:107">
       <c r="DC141" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
     </row>
     <row r="142" spans="107:107">
       <c r="DC142" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="143" spans="107:107">
       <c r="DC143" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
     </row>
     <row r="144" spans="107:107">
       <c r="DC144" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="145" spans="107:107">
       <c r="DC145" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
     </row>
     <row r="146" spans="107:107">
       <c r="DC146" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
     </row>
     <row r="147" spans="107:107">
       <c r="DC147" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
     </row>
     <row r="148" spans="107:107">
       <c r="DC148" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
     </row>
     <row r="149" spans="107:107">
       <c r="DC149" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
     </row>
     <row r="150" spans="107:107">
       <c r="DC150" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
     </row>
     <row r="151" spans="107:107">
       <c r="DC151" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
     </row>
     <row r="152" spans="107:107">
       <c r="DC152" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
     </row>
     <row r="153" spans="107:107">
       <c r="DC153" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
     </row>
     <row r="154" spans="107:107">
       <c r="DC154" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
     </row>
     <row r="155" spans="107:107">
       <c r="DC155" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
     </row>
     <row r="156" spans="107:107">
       <c r="DC156" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
     </row>
     <row r="157" spans="107:107">
       <c r="DC157" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
     </row>
     <row r="158" spans="107:107">
       <c r="DC158" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
     </row>
     <row r="159" spans="107:107">
       <c r="DC159" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
     </row>
     <row r="160" spans="107:107">
       <c r="DC160" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="161" spans="107:107">
       <c r="DC161" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
     </row>
     <row r="162" spans="107:107">
       <c r="DC162" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
     </row>
     <row r="163" spans="107:107">
       <c r="DC163" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
     </row>
     <row r="164" spans="107:107">
       <c r="DC164" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
     </row>
     <row r="165" spans="107:107">
       <c r="DC165" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
     </row>
     <row r="166" spans="107:107">
       <c r="DC166" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
     </row>
     <row r="167" spans="107:107">
       <c r="DC167" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
     </row>
     <row r="168" spans="107:107">
       <c r="DC168" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
     </row>
     <row r="169" spans="107:107">
       <c r="DC169" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
     </row>
     <row r="170" spans="107:107">
       <c r="DC170" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
     </row>
     <row r="171" spans="107:107">
       <c r="DC171" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
     </row>
     <row r="172" spans="107:107">
       <c r="DC172" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
     </row>
     <row r="173" spans="107:107">
       <c r="DC173" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
     </row>
     <row r="174" spans="107:107">
       <c r="DC174" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
     </row>
     <row r="175" spans="107:107">
       <c r="DC175" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
     </row>
     <row r="176" spans="107:107">
       <c r="DC176" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
     </row>
     <row r="177" spans="107:107">
       <c r="DC177" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
     </row>
     <row r="178" spans="107:107">
       <c r="DC178" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
     </row>
     <row r="179" spans="107:107">
       <c r="DC179" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
     </row>
     <row r="180" spans="107:107">
       <c r="DC180" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
     </row>
     <row r="181" spans="107:107">
       <c r="DC181" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
     </row>
     <row r="182" spans="107:107">
       <c r="DC182" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
     </row>
     <row r="183" spans="107:107">
       <c r="DC183" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
     </row>
     <row r="184" spans="107:107">
       <c r="DC184" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
     </row>
     <row r="185" spans="107:107">
       <c r="DC185" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
     </row>
     <row r="186" spans="107:107">
       <c r="DC186" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
     </row>
     <row r="187" spans="107:107">
       <c r="DC187" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
     </row>
     <row r="188" spans="107:107">
       <c r="DC188" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
     </row>
     <row r="189" spans="107:107">
       <c r="DC189" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
     </row>
     <row r="190" spans="107:107">
       <c r="DC190" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
     </row>
     <row r="191" spans="107:107">
       <c r="DC191" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
     </row>
     <row r="192" spans="107:107">
       <c r="DC192" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
     </row>
     <row r="193" spans="107:107">
       <c r="DC193" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
     </row>
     <row r="194" spans="107:107">
       <c r="DC194" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
     </row>
     <row r="195" spans="107:107">
       <c r="DC195" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
     </row>
     <row r="196" spans="107:107">
       <c r="DC196" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
     </row>
     <row r="197" spans="107:107">
       <c r="DC197" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
     </row>
     <row r="198" spans="107:107">
       <c r="DC198" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
     </row>
     <row r="199" spans="107:107">
       <c r="DC199" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
     </row>
     <row r="200" spans="107:107">
       <c r="DC200" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
     </row>
     <row r="201" spans="107:107">
       <c r="DC201" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
     </row>
     <row r="202" spans="107:107">
       <c r="DC202" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
     </row>
     <row r="203" spans="107:107">
       <c r="DC203" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
     </row>
     <row r="204" spans="107:107">
       <c r="DC204" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
     </row>
     <row r="205" spans="107:107">
       <c r="DC205" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
     </row>
     <row r="206" spans="107:107">
       <c r="DC206" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
     </row>
     <row r="207" spans="107:107">
       <c r="DC207" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
     </row>
     <row r="208" spans="107:107">
       <c r="DC208" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
     </row>
     <row r="209" spans="107:107">
       <c r="DC209" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
     </row>
     <row r="210" spans="107:107">
       <c r="DC210" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
     </row>
     <row r="211" spans="107:107">
       <c r="DC211" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
     </row>
     <row r="212" spans="107:107">
       <c r="DC212" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
     </row>
     <row r="213" spans="107:107">
       <c r="DC213" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
     </row>
     <row r="214" spans="107:107">
       <c r="DC214" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
     </row>
     <row r="215" spans="107:107">
       <c r="DC215" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
     </row>
     <row r="216" spans="107:107">
       <c r="DC216" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
     </row>
     <row r="217" spans="107:107">
       <c r="DC217" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="218" spans="107:107">
       <c r="DC218" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
     </row>
     <row r="219" spans="107:107">
       <c r="DC219" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
     </row>
     <row r="220" spans="107:107">
       <c r="DC220" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
     </row>
     <row r="221" spans="107:107">
       <c r="DC221" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="222" spans="107:107">
       <c r="DC222" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
     </row>
     <row r="223" spans="107:107">
       <c r="DC223" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
     </row>
     <row r="224" spans="107:107">
       <c r="DC224" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
     </row>
     <row r="225" spans="107:107">
       <c r="DC225" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
     </row>
     <row r="226" spans="107:107">
       <c r="DC226" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
     </row>
     <row r="227" spans="107:107">
       <c r="DC227" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
     </row>
     <row r="228" spans="107:107">
       <c r="DC228" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
     </row>
     <row r="229" spans="107:107">
       <c r="DC229" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
     </row>
     <row r="230" spans="107:107">
       <c r="DC230" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
     </row>
     <row r="231" spans="107:107">
       <c r="DC231" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
     </row>
     <row r="232" spans="107:107">
       <c r="DC232" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
     </row>
     <row r="233" spans="107:107">
       <c r="DC233" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
     </row>
     <row r="234" spans="107:107">
       <c r="DC234" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
     </row>
     <row r="235" spans="107:107">
       <c r="DC235" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
     </row>
     <row r="236" spans="107:107">
       <c r="DC236" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
     </row>
     <row r="237" spans="107:107">
       <c r="DC237" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
     </row>
     <row r="238" spans="107:107">
       <c r="DC238" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
     </row>
     <row r="239" spans="107:107">
       <c r="DC239" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
     </row>
     <row r="240" spans="107:107">
       <c r="DC240" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
     </row>
     <row r="241" spans="107:107">
       <c r="DC241" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
     </row>
     <row r="242" spans="107:107">
       <c r="DC242" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
     </row>
     <row r="243" spans="107:107">
       <c r="DC243" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
     </row>
     <row r="244" spans="107:107">
       <c r="DC244" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
     </row>
     <row r="245" spans="107:107">
       <c r="DC245" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
     </row>
     <row r="246" spans="107:107">
       <c r="DC246" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
     </row>
     <row r="247" spans="107:107">
       <c r="DC247" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
     </row>
     <row r="248" spans="107:107">
       <c r="DC248" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
     </row>
     <row r="249" spans="107:107">
       <c r="DC249" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
     </row>
     <row r="250" spans="107:107">
       <c r="DC250" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
     </row>
     <row r="251" spans="107:107">
       <c r="DC251" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
     </row>
     <row r="252" spans="107:107">
       <c r="DC252" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
     </row>
     <row r="253" spans="107:107">
       <c r="DC253" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
     </row>
     <row r="254" spans="107:107">
       <c r="DC254" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
     </row>
     <row r="255" spans="107:107">
       <c r="DC255" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
     </row>
     <row r="256" spans="107:107">
       <c r="DC256" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
     </row>
     <row r="257" spans="107:107">
       <c r="DC257" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
     </row>
     <row r="258" spans="107:107">
       <c r="DC258" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
     </row>
     <row r="259" spans="107:107">
       <c r="DC259" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
     </row>
     <row r="260" spans="107:107">
       <c r="DC260" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
     </row>
     <row r="261" spans="107:107">
       <c r="DC261" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
     </row>
     <row r="262" spans="107:107">
       <c r="DC262" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
     </row>
     <row r="263" spans="107:107">
       <c r="DC263" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
     </row>
     <row r="264" spans="107:107">
       <c r="DC264" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
     </row>
     <row r="265" spans="107:107">
       <c r="DC265" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
     </row>
     <row r="266" spans="107:107">
       <c r="DC266" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="267" spans="107:107">
       <c r="DC267" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
     </row>
     <row r="268" spans="107:107">
       <c r="DC268" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
     </row>
     <row r="269" spans="107:107">
       <c r="DC269" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
     </row>
     <row r="270" spans="107:107">
       <c r="DC270" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
     </row>
     <row r="271" spans="107:107">
       <c r="DC271" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
     </row>
     <row r="272" spans="107:107">
       <c r="DC272" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
     </row>
     <row r="273" spans="107:107">
       <c r="DC273" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
     </row>
     <row r="274" spans="107:107">
       <c r="DC274" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
     </row>
     <row r="275" spans="107:107">
       <c r="DC275" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
     </row>
     <row r="276" spans="107:107">
       <c r="DC276" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
     </row>
     <row r="277" spans="107:107">
       <c r="DC277" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
     </row>
     <row r="278" spans="107:107">
       <c r="DC278" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
     </row>
     <row r="279" spans="107:107">
       <c r="DC279" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
     </row>
     <row r="280" spans="107:107">
       <c r="DC280" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
     </row>
     <row r="281" spans="107:107">
       <c r="DC281" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
     </row>
     <row r="282" spans="107:107">
       <c r="DC282" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
     </row>
     <row r="283" spans="107:107">
       <c r="DC283" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
     </row>
     <row r="284" spans="107:107">
       <c r="DC284" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
     </row>
     <row r="285" spans="107:107">
       <c r="DC285" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
     </row>
     <row r="286" spans="107:107">
       <c r="DC286" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
     </row>
     <row r="287" spans="107:107">
       <c r="DC287" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
     </row>
     <row r="288" spans="107:107">
       <c r="DC288" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
     </row>
     <row r="289" spans="107:107">
       <c r="DC289" t="s">
-        <v>874</v>
+        <v>876</v>
+      </c>
+    </row>
+    <row r="290" spans="107:107">
+      <c r="DC290" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="291" spans="107:107">
+      <c r="DC291" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="292" spans="107:107">
+      <c r="DC292" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="293" spans="107:107">
+      <c r="DC293" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="294" spans="107:107">
+      <c r="DC294" t="s">
+        <v>881</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000056/metadata_template_ERC000056.xlsx
+++ b/templates/ERC000056/metadata_template_ERC000056.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="1251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="1250">
   <si>
     <t>alias</t>
   </si>
@@ -884,7 +884,7 @@
     <t>culture result organism</t>
   </si>
   <si>
-    <t>(Optional) Taxonomic information about the cultured organism(s). (Units: m2)</t>
+    <t>(Optional) Taxonomic information about the cultured organism(s).</t>
   </si>
   <si>
     <t>culture target microbial analyte</t>
@@ -896,7 +896,7 @@
     <t>biological sample replicate</t>
   </si>
   <si>
-    <t>(Optional) Measurements of biologically distinct samples that show biological variation. (Units: year)</t>
+    <t>(Optional) Measurements of biologically distinct samples that show biological variation.</t>
   </si>
   <si>
     <t>technical sample replicate</t>
@@ -1076,7 +1076,7 @@
     <t>sample transport container</t>
   </si>
   <si>
-    <t>(Optional) Container in which the sample was stored during transport. indicate the location name. (Units: J/°C)</t>
+    <t>(Optional) Container in which the sample was stored during transport. indicate the location name.</t>
   </si>
   <si>
     <t>sample transport duration</t>
@@ -1256,7 +1256,7 @@
     <t>soil texture classification</t>
   </si>
   <si>
-    <t>(Optional) One of the 12 soil texture classes use to describe soil texture based on the relative proportion of different grain sizes of mineral particles [sand (50 um to 2 mm), silt (2 um to 50 um), and clay (&lt;2 um)] in a soil. (Units: °C)</t>
+    <t>(Optional) One of the 12 soil texture classes use to describe soil texture based on the relative proportion of different grain sizes of mineral particles [sand (50 um to 2 mm), silt (2 um to 50 um), and clay (&lt;2 um)] in a soil.</t>
   </si>
   <si>
     <t>soil sediment porosity</t>
@@ -1280,7 +1280,7 @@
     <t>collection site geographic feature</t>
   </si>
   <si>
-    <t>(Optional) Text or terms that describe the geographic feature where the food sample was obtained by the researcher. this field accepts selected terms listed under the following ontologies: anthropogenic geographic feature (http://purl.obolibrary.org/obo/envo_00000002), for example agricultural fairground [envo:01000986]; garden [envo:00000011} or any of its subclasses; market [envo:01000987]; water well [envo:01000002]; or human construction (http://purl.obolibrary.org/obo/envo_00000070). (Units: m2)</t>
+    <t>(Optional) Text or terms that describe the geographic feature where the food sample was obtained by the researcher. this field accepts selected terms listed under the following ontologies: anthropogenic geographic feature (http://purl.obolibrary.org/obo/envo_00000002), for example agricultural fairground [envo:01000986]; garden [envo:00000011} or any of its subclasses; market [envo:01000987]; water well [envo:01000002]; or human construction (http://purl.obolibrary.org/obo/envo_00000070).</t>
   </si>
   <si>
     <t>area sampled size</t>
@@ -1298,7 +1298,7 @@
     <t>study design</t>
   </si>
   <si>
-    <t>(Optional) A plan specification comprised of protocols (which may specify how and what kinds of data will be gathered) that are executed as part of an investigation and is realized during a study design execution. this field accepts terms under study design (http://purl.obolibrary.org/obo/obi_0500000). if the proper descriptor is not listed please use text to describe the study design. multiple terms can be separated by pipes. (Units: kg s−3)</t>
+    <t>(Optional) A plan specification comprised of protocols (which may specify how and what kinds of data will be gathered) that are executed as part of an investigation and is realized during a study design execution. this field accepts terms under study design (http://purl.obolibrary.org/obo/obi_0500000). if the proper descriptor is not listed please use text to describe the study design. multiple terms can be separated by pipes.</t>
   </si>
   <si>
     <t>project name</t>
@@ -1328,7 +1328,7 @@
     <t>farm equipment sanitization frequency</t>
   </si>
   <si>
-    <t>(Optional) The number of times farm equipment is cleaned. frequency of cleaning might be on a daily basis, weekly, monthly, quarterly or annually. (Units: m2)</t>
+    <t>(Optional) The number of times farm equipment is cleaned. frequency of cleaning might be on a daily basis, weekly, monthly, quarterly or annually.</t>
   </si>
   <si>
     <t>farm watering water source</t>
@@ -1370,13 +1370,13 @@
     <t>food production characteristics</t>
   </si>
   <si>
-    <t>(Optional) Descriptors of the food production system such as wild caught, free-range, organic, free-range, industrial, dairy, beef. (Units: °C)</t>
+    <t>(Optional) Descriptors of the food production system such as wild caught, free-range, organic, free-range, industrial, dairy, beef.</t>
   </si>
   <si>
     <t>food animal group size</t>
   </si>
   <si>
-    <t>(Optional) The number of food animals of the same species that are maintained together as a unit, i.e. a herd or flock. (Units: year)</t>
+    <t>(Optional) The number of food animals of the same species that are maintained together as a unit, i.e. a herd or flock.</t>
   </si>
   <si>
     <t>fertilizer administration date</t>
@@ -1730,25 +1730,25 @@
     <t>sampling floor</t>
   </si>
   <si>
-    <t>(Optional) The floor of the building, where the sampling room is located (Units: °C)</t>
+    <t>(Optional) The floor of the building, where the sampling room is located</t>
   </si>
   <si>
     <t>average daily occupancy</t>
   </si>
   <si>
-    <t>(Optional) Daily average occupancy of room. indicate the number of person(s) daily occupying the sampling room. (Units: °C)</t>
+    <t>(Optional) Daily average occupancy of room. indicate the number of person(s) daily occupying the sampling room.</t>
   </si>
   <si>
     <t>sample surface moisture</t>
   </si>
   <si>
-    <t>(Optional) Degree of water held on a sampled surface. if present, user can state the degree of water held on surface (intermittent moisture, submerged). if no surface moisture is present indicate not present. (Units: year)</t>
+    <t>(Optional) Degree of water held on a sampled surface. if present, user can state the degree of water held on surface (intermittent moisture, submerged). if no surface moisture is present indicate not present.</t>
   </si>
   <si>
     <t>sampling room id or name</t>
   </si>
   <si>
-    <t>(Optional) Explain how and for how long the soil sample was stored before dna extraction (fresh/frozen/other). (Units: year)</t>
+    <t>(Optional) Explain how and for how long the soil sample was stored before dna extraction (fresh/frozen/other).</t>
   </si>
   <si>
     <t>fermentation relative humidity</t>
@@ -3002,13 +3002,13 @@
     <t>extreme weather date</t>
   </si>
   <si>
-    <t>(Optional) Date of unusual weather events that may have affected microbial populations. multiple terms can be separated by pipes, listed in reverse chronological order. (Units: J/°C)</t>
+    <t>(Optional) Date of unusual weather events that may have affected microbial populations. multiple terms can be separated by pipes, listed in reverse chronological order.</t>
   </si>
   <si>
     <t>extreme weather event</t>
   </si>
   <si>
-    <t>(Optional) Unusual weather events that may have affected microbial populations. multiple terms can be separated by pipes, listed in reverse chronological order. (Units: m)</t>
+    <t>(Optional) Unusual weather events that may have affected microbial populations. multiple terms can be separated by pipes, listed in reverse chronological order.</t>
   </si>
   <si>
     <t>season</t>
@@ -3074,7 +3074,7 @@
     <t>fermentation chemical additives</t>
   </si>
   <si>
-    <t>(Optional) Any chemicals that are added to the fermentation process to achieve the desired final product. (Units: J/°C)</t>
+    <t>(Optional) Any chemicals that are added to the fermentation process to achieve the desired final product.</t>
   </si>
   <si>
     <t>fermentation chemical additives percentage</t>
@@ -3086,19 +3086,19 @@
     <t>study treatment</t>
   </si>
   <si>
-    <t>(Optional) A process in which the act is intended to modify or alter some other material entity. from the study design, each treatment is comprised of one level of one or multiple factors. this field accepts terms listed under treatment (http://purl.obolibrary.org/obo/mco_0000866). if the proper descriptor is not listed please use text to describe the study treatment. multiple terms can be separated by one or more pipes. (Units: %)</t>
+    <t>(Optional) A process in which the act is intended to modify or alter some other material entity. from the study design, each treatment is comprised of one level of one or multiple factors. this field accepts terms listed under treatment (http://purl.obolibrary.org/obo/mco_0000866). if the proper descriptor is not listed please use text to describe the study treatment. multiple terms can be separated by one or more pipes.</t>
   </si>
   <si>
     <t>spike-in organism</t>
   </si>
   <si>
-    <t>(Optional) Taxonomic information about the spike-in organism(s). this field accepts terms under organism (http://purl.obolibrary.org/obo/ncit_c14250). this field also accepts identification numbers from ncbi under https://www.ncbi.nlm.nih.gov/taxonomy. multiple terms can be separated by pipes. (Units: g/m3)</t>
+    <t>(Optional) Taxonomic information about the spike-in organism(s). this field accepts terms under organism (http://purl.obolibrary.org/obo/ncit_c14250). this field also accepts identification numbers from ncbi under https://www.ncbi.nlm.nih.gov/taxonomy. multiple terms can be separated by pipes.</t>
   </si>
   <si>
     <t>spike-in organism count</t>
   </si>
   <si>
-    <t>(Optional) Total cell count of any organism (or group of organisms) per gram, volume or area of sample, should include name of organism followed by count. the method that was used for the enumeration (e.g. qpcr, atp, mpn, etc.) should also be provided (example: total prokaryotes; 3.5e7 cells per ml; qpcr). (Units: mm)</t>
+    <t>(Optional) Total cell count of any organism (or group of organisms) per gram, volume or area of sample, should include name of organism followed by count. the method that was used for the enumeration (e.g. qpcr, atp, mpn, etc.) should also be provided (example: total prokaryotes; 3.5e7 cells per ml; qpcr).</t>
   </si>
   <si>
     <t>fermentation temperature</t>
@@ -3110,31 +3110,31 @@
     <t>spike-in with heavy metals</t>
   </si>
   <si>
-    <t>(Optional) Heavy metals used in research study to assess effects of exposure on microbiome of a specific site. please list heavy metals and concentration used for spike-in. (Units: year)</t>
+    <t>(Optional) Heavy metals used in research study to assess effects of exposure on microbiome of a specific site. please list heavy metals and concentration used for spike-in.</t>
   </si>
   <si>
     <t>microbial starter inoculation</t>
   </si>
   <si>
-    <t>(Optional) The amount of starter culture used to inoculate a new batch. (Units: m3/day)</t>
+    <t>(Optional) The amount of starter culture used to inoculate a new batch.</t>
   </si>
   <si>
     <t>microbial starter source</t>
   </si>
   <si>
-    <t>(Optional) The source from which the microbial starter culture was sourced. if commercially supplied, list supplier. (Units: year)</t>
+    <t>(Optional) The source from which the microbial starter culture was sourced. if commercially supplied, list supplier.</t>
   </si>
   <si>
     <t>microbial starter preparation</t>
   </si>
   <si>
-    <t>(Optional) Information about the protocol or method used to prepare the starter inoculum. (Units: year)</t>
+    <t>(Optional) Information about the protocol or method used to prepare the starter inoculum.</t>
   </si>
   <si>
     <t>spike-in bacterial serovar or serotype</t>
   </si>
   <si>
-    <t>(Optional) Taxonomic information about the spike-in organism(s) at the serovar or serotype level. this field accepts terms under organism (http://purl.obolibrary.org/obo/ncit_c14250). this field also accepts identification numbers from ncbi under https://www.ncbi.nlm.nih.gov/taxonomy. multiple terms can be separated by pipes. (Units: year)</t>
+    <t>(Optional) Taxonomic information about the spike-in organism(s) at the serovar or serotype level. this field accepts terms under organism (http://purl.obolibrary.org/obo/ncit_c14250). this field also accepts identification numbers from ncbi under https://www.ncbi.nlm.nih.gov/taxonomy. multiple terms can be separated by pipes.</t>
   </si>
   <si>
     <t>antimicrobial phenotype of spike-in bacteria</t>
@@ -3152,13 +3152,13 @@
     <t>microbial starter organism count</t>
   </si>
   <si>
-    <t>(Optional) Total cell count of starter culture per gram, volume or area of sample and the method that was used for the enumeration (e.g. qpcr, atp, mpn, etc.) should also be provided. (example : total prokaryotes; 3.5e7 cells per ml; qpcr). (Units: m2)</t>
+    <t>(Optional) Total cell count of starter culture per gram, volume or area of sample and the method that was used for the enumeration (e.g. qpcr, atp, mpn, etc.) should also be provided. (example : total prokaryotes; 3.5e7 cells per ml; qpcr).</t>
   </si>
   <si>
     <t>spike-in with antibiotics</t>
   </si>
   <si>
-    <t>(Optional) Antimicrobials used in research study to assess effects of exposure on microbiome of a specific site. please list antimicrobial, common name and/or class and concentration used for spike-in. (Units: m2)</t>
+    <t>(Optional) Antimicrobials used in research study to assess effects of exposure on microbiome of a specific site. please list antimicrobial, common name and/or class and concentration used for spike-in.</t>
   </si>
   <si>
     <t>study incubation temperature</t>
@@ -3182,7 +3182,7 @@
     <t>biocide</t>
   </si>
   <si>
-    <t>(Optional) Substance intended for preventing, neutralizing, destroying, repelling, or mitigating the effects of any pest or microorganism; that inhibits the growth, reproduction, and activity of organisms, including fungal cells; decreases the number of fungi or pests present; deters microbial growth and degradation of other ingredients in the formulation. indicate the biocide used on the location where the sample was taken. multiple terms can be separated by pipes. (Units: °C)</t>
+    <t>(Optional) Substance intended for preventing, neutralizing, destroying, repelling, or mitigating the effects of any pest or microorganism; that inhibits the growth, reproduction, and activity of organisms, including fungal cells; decreases the number of fungi or pests present; deters microbial growth and degradation of other ingredients in the formulation. indicate the biocide used on the location where the sample was taken. multiple terms can be separated by pipes.</t>
   </si>
   <si>
     <t>negative control type</t>
@@ -3272,25 +3272,25 @@
     <t>microbiological culture medium</t>
   </si>
   <si>
-    <t>(Optional) A culture medium used to select for, grow, and maintain prokaryotic microorganisms. can be in either liquid (broth) or solidified (e.g. with agar) forms. this field accepts terms listed under microbiological culture medium (http://purl.obolibrary.org/obo/micro_0000067). if the proper descriptor is not listed please use text to describe the culture medium. (Units: Pa)</t>
+    <t>(Optional) A culture medium used to select for, grow, and maintain prokaryotic microorganisms. can be in either liquid (broth) or solidified (e.g. with agar) forms. this field accepts terms listed under microbiological culture medium (http://purl.obolibrary.org/obo/micro_0000067). if the proper descriptor is not listed please use text to describe the culture medium.</t>
   </si>
   <si>
     <t>spike-in growth medium</t>
   </si>
   <si>
-    <t>(Optional) A liquid or gel containing nutrients, salts, and other factors formulated to support the growth of microorganisms, cells, or plants (national cancer institute thesaurus). a growth medium is a culture medium which has the disposition to encourage growth of particular bacteria to the exclusion of others in the same growth environment. in this case, list the culture medium used to propagate the spike-in bacteria during preparation of spike-in inoculum. this field accepts terms listed under microbiological culture medium (http://purl.obolibrary.org/obo/micro_0000067). if the proper descriptor is not listed please use text to describe the spike in growth media. (Units: W/m2)</t>
+    <t>(Optional) A liquid or gel containing nutrients, salts, and other factors formulated to support the growth of microorganisms, cells, or plants (national cancer institute thesaurus). a growth medium is a culture medium which has the disposition to encourage growth of particular bacteria to the exclusion of others in the same growth environment. in this case, list the culture medium used to propagate the spike-in bacteria during preparation of spike-in inoculum. this field accepts terms listed under microbiological culture medium (http://purl.obolibrary.org/obo/micro_0000067). if the proper descriptor is not listed please use text to describe the spike in growth media.</t>
   </si>
   <si>
     <t>fermentation medium</t>
   </si>
   <si>
-    <t>(Optional) The growth medium used for the fermented food fermentation process, which supplies the required nutrients. usually this includes a carbon and nitrogen source, water, micronutrients and chemical additives. (Units: m)</t>
+    <t>(Optional) The growth medium used for the fermented food fermentation process, which supplies the required nutrients. usually this includes a carbon and nitrogen source, water, micronutrients and chemical additives.</t>
   </si>
   <si>
     <t>growth medium</t>
   </si>
   <si>
-    <t>(Optional) A liquid or gel containing nutrients, salts, and other factors formulated to support the growth of microorganisms, cells, or plants (national cancer institute thesaurus). the name of the medium used to grow the microorganism. (Units: year)</t>
+    <t>(Optional) A liquid or gel containing nutrients, salts, and other factors formulated to support the growth of microorganisms, cells, or plants (national cancer institute thesaurus). the name of the medium used to grow the microorganism.</t>
   </si>
   <si>
     <t>isolation and growth condition</t>
@@ -3344,7 +3344,7 @@
     <t>lot number</t>
   </si>
   <si>
-    <t>(Optional) A distinctive alpha-numeric identification code assigned by the manufacturer or distributor to a specific quantity of manufactured material or product within a batch. synonym: batch number. the submitter should provide lot number of the item followed by the item name for which the lot number was provided. (Units: %)</t>
+    <t>(Optional) A distinctive alpha-numeric identification code assigned by the manufacturer or distributor to a specific quantity of manufactured material or product within a batch. synonym: batch number. the submitter should provide lot number of the item followed by the item name for which the lot number was provided.</t>
   </si>
   <si>
     <t>chemical</t>
@@ -3497,7 +3497,7 @@
     <t>food cleaning process</t>
   </si>
   <si>
-    <t>(Optional) The process of cleaning food to separate other environmental materials from the food source. multiple terms can be separated by pipes. (Units: m)</t>
+    <t>(Optional) The process of cleaning food to separate other environmental materials from the food source. multiple terms can be separated by pipes.</t>
   </si>
   <si>
     <t>hygienic food production area</t>
@@ -3509,31 +3509,31 @@
     <t>food contact surface</t>
   </si>
   <si>
-    <t>(Optional) The specific container or coating materials in direct contact with the food. multiple values can be assigned. this field accepts terms listed under food contact surface (http://purl.obolibrary.org/obo/foodon_03500010). (Units: J/°C)</t>
+    <t>(Optional) The specific container or coating materials in direct contact with the food. multiple values can be assigned. this field accepts terms listed under food contact surface (http://purl.obolibrary.org/obo/foodon_03500010).</t>
   </si>
   <si>
     <t>food cooking process</t>
   </si>
   <si>
-    <t>(Optional) The transformation of raw food by the application of heat. this field accepts terms listed under food cooking (http://purl.obolibrary.org/obo/foodon_03450002). (Units: %)</t>
+    <t>(Optional) The transformation of raw food by the application of heat. this field accepts terms listed under food cooking (http://purl.obolibrary.org/obo/foodon_03450002).</t>
   </si>
   <si>
     <t>food product by quality</t>
   </si>
   <si>
-    <t>(Optional) Descriptors for describing food visually or via other senses, which is useful for tasks like food inspection where little prior knowledge of how the food came to be is available. some terms like "food (frozen)" are both a quality descriptor and the output of a process. this field accepts terms listed under food product by quality (http://purl.obolibrary.org/obo/foodon_00002454). (Units: year)</t>
+    <t>(Optional) Descriptors for describing food visually or via other senses, which is useful for tasks like food inspection where little prior knowledge of how the food came to be is available. some terms like "food (frozen)" are both a quality descriptor and the output of a process. this field accepts terms listed under food product by quality (http://purl.obolibrary.org/obo/foodon_00002454).</t>
   </si>
   <si>
     <t>food animal antimicrobial route of administration</t>
   </si>
   <si>
-    <t>(Optional) The route by which the antimicrobial is administered into the body of the food animal. (Units: m2)</t>
+    <t>(Optional) The route by which the antimicrobial is administered into the body of the food animal.</t>
   </si>
   <si>
     <t>food allergen labeling</t>
   </si>
   <si>
-    <t>(Optional) A label indication that the product contains a recognized allergen. this field accepts terms listed under dietary claim or use (http://purl.obolibrary.org/obo/foodon_03510213). (Units: W/m2)</t>
+    <t>(Optional) A label indication that the product contains a recognized allergen. this field accepts terms listed under dietary claim or use (http://purl.obolibrary.org/obo/foodon_03510213).</t>
   </si>
   <si>
     <t>food product type</t>
@@ -3545,25 +3545,25 @@
     <t>food animal source sex category</t>
   </si>
   <si>
-    <t>(Optional) The sex and reproductive status of the food animal. (Units: °C)</t>
+    <t>(Optional) The sex and reproductive status of the food animal.</t>
   </si>
   <si>
     <t>animal intrusion near sample source</t>
   </si>
   <si>
-    <t>(Optional) Identification of animals intruding on the sample or sample site including invertebrates (such as pests or pollinators) and vertebrates (such as wildlife or domesticated animals). this field accepts terms under organism (http://purl.obolibrary.org/obo/ncit_c14250). this field also accepts identification numbers from ncbi under https://www.ncbi.nlm.nih.gov/taxonomy. multiple terms can be separated by pipes. (Units: °C)</t>
+    <t>(Optional) Identification of animals intruding on the sample or sample site including invertebrates (such as pests or pollinators) and vertebrates (such as wildlife or domesticated animals). this field accepts terms under organism (http://purl.obolibrary.org/obo/ncit_c14250). this field also accepts identification numbers from ncbi under https://www.ncbi.nlm.nih.gov/taxonomy. multiple terms can be separated by pipes.</t>
   </si>
   <si>
     <t>food packing medium integrity</t>
   </si>
   <si>
-    <t>(Optional) A term label and term id to describe the state of the packing material and text to explain the exact condition. this field accepts terms listed under food packing medium integrity (http://purl.obolibrary.org/obo/foodon_03530218). (Units: °C)</t>
+    <t>(Optional) A term label and term id to describe the state of the packing material and text to explain the exact condition. this field accepts terms listed under food packing medium integrity (http://purl.obolibrary.org/obo/foodon_03530218).</t>
   </si>
   <si>
     <t>microbial starter</t>
   </si>
   <si>
-    <t>(Optional) Any type of microorganisms used in food production. this field accepts terms listed under live organisms for food production (http://purl.obolibrary.org/obo/foodon_0344453). (Units: °C)</t>
+    <t>(Optional) Any type of microorganisms used in food production. this field accepts terms listed under live organisms for food production (http://purl.obolibrary.org/obo/foodon_0344453).</t>
   </si>
   <si>
     <t>food treatment process</t>
@@ -3575,7 +3575,7 @@
     <t>food preservation process</t>
   </si>
   <si>
-    <t>(Optional) The methods contributing to the prevention or retardation of microbial, enzymatic or oxidative spoilage and thus to the extension of shelf life. this field accepts terms listed under food preservation process (http://purl.obolibrary.org/obo/foodon_03470107). (Units: J/°C)</t>
+    <t>(Optional) The methods contributing to the prevention or retardation of microbial, enzymatic or oxidative spoilage and thus to the extension of shelf life. this field accepts terms listed under food preservation process (http://purl.obolibrary.org/obo/foodon_03470107).</t>
   </si>
   <si>
     <t>microbial starter ncbi taxonomy id</t>
@@ -3605,7 +3605,7 @@
     <t>food ingredient</t>
   </si>
   <si>
-    <t>(Optional) In this field, please list individual ingredients for multi-component food [foodon:00002501] and simple foods that is not captured in food_type. please use terms that are present in foodon. multiple terms can be separated by one or more pipes |, but please consider limiting this list to the top 5 ingredients listed in order as on the food label. see also, https://www.fda.gov/food/food-ingredients-packaging/overview-food-ingredients-additives-colors. (Units: year)</t>
+    <t>(Optional) In this field, please list individual ingredients for multi-component food [foodon:00002501] and simple foods that is not captured in food_type. please use terms that are present in foodon. multiple terms can be separated by one or more pipes |, but please consider limiting this list to the top 5 ingredients listed in order as on the food label. see also, https://www.fda.gov/food/food-ingredients-packaging/overview-food-ingredients-additives-colors.</t>
   </si>
   <si>
     <t>food stored by consumer (storage duration)</t>
@@ -3623,13 +3623,13 @@
     <t>part of plant or animal</t>
   </si>
   <si>
-    <t>(Optional) The anatomical part of the organism being involved in food production or consumption; e.g., a carrot is the root of the plant (root vegetable). this field accepts terms listed under part of plant or animal (http://purl.obolibrary.org/obo/foodon_03420116). (Units: year)</t>
+    <t>(Optional) The anatomical part of the organism being involved in food production or consumption; e.g., a carrot is the root of the plant (root vegetable). this field accepts terms listed under part of plant or animal (http://purl.obolibrary.org/obo/foodon_03420116).</t>
   </si>
   <si>
     <t>hazard analysis critical control points (haccp) guide food safety term</t>
   </si>
   <si>
-    <t>(Optional) Hazard analysis critical control points (haccp) food safety terms; this field accepts terms listed under haccp guide food safety term (http://purl.obolibrary.org/obo/foodon_03530221). (Units: year)</t>
+    <t>(Optional) Hazard analysis critical control points (haccp) food safety terms; this field accepts terms listed under haccp guide food safety term (http://purl.obolibrary.org/obo/foodon_03530221).</t>
   </si>
   <si>
     <t>dietary claim or use</t>
@@ -3641,7 +3641,7 @@
     <t>degree of plant part maturity</t>
   </si>
   <si>
-    <t>(Optional) A description of the stage of development of a plant or plant part based on maturity or ripeness. this field accepts terms listed under degree of plant maturity (http://purl.obolibrary.org/obo/foodon_03530050). (Units: year)</t>
+    <t>(Optional) A description of the stage of development of a plant or plant part based on maturity or ripeness. this field accepts terms listed under degree of plant maturity (http://purl.obolibrary.org/obo/foodon_03530050).</t>
   </si>
   <si>
     <t>food production environmental monitoring zone</t>
@@ -3659,19 +3659,19 @@
     <t>food traceability list category</t>
   </si>
   <si>
-    <t>(Optional) The fda is proposing to establish additional traceability recordkeeping requirements (beyond what is already required in existing regulations) for persons who manufacture, process, pack, or hold foods the agency has designated for inclusion on the food traceability list. the food traceability list (ftl) identifies the foods for which the additional traceability records described in the proposed rule would be required. the term “food traceability list” (ftl) refers not only to the foods specifically listed (https://www.fda.gov/media/142303/download), but also to any foods that contain listed foods as ingredients. (Units: mm)</t>
+    <t>(Optional) The fda is proposing to establish additional traceability recordkeeping requirements (beyond what is already required in existing regulations) for persons who manufacture, process, pack, or hold foods the agency has designated for inclusion on the food traceability list. the food traceability list (ftl) identifies the foods for which the additional traceability records described in the proposed rule would be required. the term “food traceability list” (ftl) refers not only to the foods specifically listed (https://www.fda.gov/media/142303/download), but also to any foods that contain listed foods as ingredients.</t>
   </si>
   <si>
     <t>food animal antimicrobial frequency</t>
   </si>
   <si>
-    <t>(Optional) The frequency per day that the antimicrobial was administered to the food animal. (Units: m2)</t>
+    <t>(Optional) The frequency per day that the antimicrobial was administered to the food animal. (Units: day)</t>
   </si>
   <si>
     <t>intended consumer</t>
   </si>
   <si>
-    <t>(Optional) Food consumer type, human or animal, for which the food product is produced and marketed. this field accepts terms listed under food consumer group (http://purl.obolibrary.org/obo/foodon_03510136) or ncbi taxid. (Units: m2)</t>
+    <t>(Optional) Food consumer type, human or animal, for which the food product is produced and marketed. this field accepts terms listed under food consumer group (http://purl.obolibrary.org/obo/foodon_03510136) or ncbi taxid.</t>
   </si>
   <si>
     <t>quantity purchased</t>
@@ -3683,13 +3683,13 @@
     <t>food container or wrapping</t>
   </si>
   <si>
-    <t>(Optional) Type of container or wrapping defined by the main container material, the container form, and the material of the liner lids or ends. also type of container or wrapping by form; prefer description by material first, then by form. this field accepts terms listed under food container or wrapping (http://purl.obolibrary.org/obo/foodon_03490100). (Units: °C)</t>
+    <t>(Optional) Type of container or wrapping defined by the main container material, the container form, and the material of the liner lids or ends. also type of container or wrapping by form; prefer description by material first, then by form. this field accepts terms listed under food container or wrapping (http://purl.obolibrary.org/obo/foodon_03490100).</t>
   </si>
   <si>
     <t>food additive</t>
   </si>
   <si>
-    <t>(Optional) A substance or substances added to food to maintain or improve safety and freshness, to improve or maintain nutritional value, or improve taste, texture and appearance. this field accepts terms listed under food additive (http://purl.obolibrary.org/obo/foodon_03412972). multiple terms can be separated by one or more pipes, but please consider limiting this list to the top 5 ingredients listed in order as on the food label. see also, https://www.fda.gov/food/food-ingredients-packaging/overview-food-ingredients-additives-colors. (Units: g/m3)</t>
+    <t>(Optional) A substance or substances added to food to maintain or improve safety and freshness, to improve or maintain nutritional value, or improve taste, texture and appearance. this field accepts terms listed under food additive (http://purl.obolibrary.org/obo/foodon_03412972). multiple terms can be separated by one or more pipes, but please consider limiting this list to the top 5 ingredients listed in order as on the food label. see also, https://www.fda.gov/food/food-ingredients-packaging/overview-food-ingredients-additives-colors.</t>
   </si>
   <si>
     <t>food source age</t>
@@ -3701,25 +3701,25 @@
     <t>food animal antimicrobial intended use</t>
   </si>
   <si>
-    <t>(Optional) The prescribed intended use of or the condition treated by the antimicrobial given to the food animal by any route of administration. (Units: year)</t>
+    <t>(Optional) The prescribed intended use of or the condition treated by the antimicrobial given to the food animal by any route of administration.</t>
   </si>
   <si>
     <t>food packing medium</t>
   </si>
   <si>
-    <t>(Optional) The medium in which the food is packed for preservation and handling or the medium surrounding homemade foods, e.g., peaches cooked in sugar syrup. the packing medium may provide a controlled environment for the food. it may also serve to improve palatability and consumer appeal. this includes edible packing media (e.g. fruit juice), gas other than air (e.g. carbon dioxide), vacuum packed, or packed with aerosol propellant. this field accepts terms under food packing medium (http://purl.obolibrary.org/obo/foodon_03480020). multiple terms may apply and can be separated by pipes. (Units: m2)</t>
+    <t>(Optional) The medium in which the food is packed for preservation and handling or the medium surrounding homemade foods, e.g., peaches cooked in sugar syrup. the packing medium may provide a controlled environment for the food. it may also serve to improve palatability and consumer appeal. this includes edible packing media (e.g. fruit juice), gas other than air (e.g. carbon dioxide), vacuum packed, or packed with aerosol propellant. this field accepts terms under food packing medium (http://purl.obolibrary.org/obo/foodon_03480020). multiple terms may apply and can be separated by pipes.</t>
   </si>
   <si>
     <t>specific intended consumer</t>
   </si>
   <si>
-    <t>(Optional) Food consumer type, human or animal, for which the food product is produced and marketed. this field accepts terms listed under food consumer group (http://purl.obolibrary.org/obo/foodon_03510136). (Units: m2)</t>
+    <t>(Optional) Food consumer type, human or animal, for which the food product is produced and marketed. this field accepts terms listed under food consumer group (http://purl.obolibrary.org/obo/foodon_03510136).</t>
   </si>
   <si>
     <t>purchase date</t>
   </si>
   <si>
-    <t>(Optional) The date a food product was purchased by consumer. (Units: m2)</t>
+    <t>(Optional) The date a food product was purchased by consumer.</t>
   </si>
   <si>
     <t>food stored by consumer (storage temperature)</t>
@@ -3731,7 +3731,7 @@
     <t>food package capacity</t>
   </si>
   <si>
-    <t>(Optional) The maximum number of product units within a package (Units: year)</t>
+    <t>(Optional) The maximum number of product units within a package</t>
   </si>
   <si>
     <t>food distribution point geographic location (city)</t>
@@ -3743,13 +3743,10 @@
     <t>food product origin geographic location</t>
   </si>
   <si>
-    <t>(Optional) A reference to a place on the earth, by its name or by its geographical location that describes the origin of the food commodity, either in terms of its cultivation or production. this field accepts terms listed under geographic location (http://purl.obolibrary.org/obo/gaz_00000448). (Units: m)</t>
+    <t>(Optional) A reference to a place on the earth, by its name or by its geographical location that describes the origin of the food commodity, either in terms of its cultivation or production. this field accepts terms listed under geographic location (http://purl.obolibrary.org/obo/gaz_00000448).</t>
   </si>
   <si>
     <t>food distribution point geographic location</t>
-  </si>
-  <si>
-    <t>(Optional) A reference to a place on the earth, by its name or by its geographical location that refers to a distribution point along the food chain. this field accepts terms listed under geographic location (http://purl.obolibrary.org/obo/gaz_00000448). reference: adam diamond, james barham. moving food along the value chain: innovations in regional food distribution. u.s. dept. of agriculture, agricultural marketing service. washington, dc. march 2012. http://dx.doi.org/10.9752/ms045.03-2012. (Units: m)</t>
   </si>
   <si>
     <t>production labeling claims</t>
@@ -6142,28 +6139,28 @@
         <v>1233</v>
       </c>
       <c r="JL1" s="1" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="JM1" s="1" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="JN1" s="1" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="JO1" s="1" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="JP1" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="JQ1" s="1" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="JR1" s="1" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="JS1" s="1" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="2" spans="1:279" ht="150" customHeight="1">
@@ -6978,31 +6975,31 @@
         <v>1232</v>
       </c>
       <c r="JK2" s="2" t="s">
-        <v>1234</v>
+        <v>1230</v>
       </c>
       <c r="JL2" s="2" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="JM2" s="2" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="JN2" s="2" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="JO2" s="2" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="JP2" s="2" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="JQ2" s="2" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="JR2" s="2" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="JS2" s="2" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000056/metadata_template_ERC000056.xlsx
+++ b/templates/ERC000056/metadata_template_ERC000056.xlsx
@@ -36,7 +36,7 @@
     <definedName name="singlecellorviralparticlelysisapproach">'cv_sample'!$GX$1:$GX$4</definedName>
     <definedName name="soiltype">'cv_sample'!$AB$1:$AB$32</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
-    <definedName name="surfacematerial">'cv_sample'!$CL$1:$CL$15</definedName>
+    <definedName name="surfacematerial">'cv_sample'!$CL$1:$CL$16</definedName>
     <definedName name="trophiclevel">'cv_sample'!$M$1:$M$30</definedName>
     <definedName name="ventilationtype">'cv_sample'!$CO$1:$CO$3</definedName>
   </definedNames>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="1250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="1251">
   <si>
     <t>alias</t>
   </si>
@@ -1625,10 +1625,13 @@
     <t>carpet</t>
   </si>
   <si>
+    <t>concrete</t>
+  </si>
+  <si>
     <t>cinder blocks</t>
   </si>
   <si>
-    <t>concrete</t>
+    <t>epoxy resin</t>
   </si>
   <si>
     <t>glass</t>
@@ -5593,574 +5596,574 @@
         <v>522</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="DL1" s="1" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="DM1" s="1" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="DN1" s="1" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="DO1" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="DP1" s="1" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="DQ1" s="1" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="DR1" s="1" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="DS1" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="DT1" s="1" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="DU1" s="1" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="DV1" s="1" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="DW1" s="1" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="DX1" s="1" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="DY1" s="1" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="DZ1" s="1" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="EA1" s="1" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="EB1" s="1" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="EC1" s="1" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="ED1" s="1" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="EE1" s="1" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="EH1" s="1" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="EI1" s="1" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="EJ1" s="1" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="EK1" s="1" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="EL1" s="1" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="EM1" s="1" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="EN1" s="1" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="EO1" s="1" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="EP1" s="1" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="EQ1" s="1" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="ER1" s="1" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="ES1" s="1" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="ET1" s="1" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="EU1" s="1" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="EV1" s="1" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="EW1" s="1" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="EX1" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="EY1" s="1" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="EZ1" s="1" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="FA1" s="1" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="FB1" s="1" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="FC1" s="1" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="FD1" s="1" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="FE1" s="1" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="FF1" s="1" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="FG1" s="1" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="FH1" s="1" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="FI1" s="1" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="FJ1" s="1" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="FK1" s="1" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="FL1" s="1" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="FM1" s="1" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="FN1" s="1" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="FO1" s="1" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="FP1" s="1" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="FQ1" s="1" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="FR1" s="1" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="FS1" s="1" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="FT1" s="1" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="FU1" s="1" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="FV1" s="1" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="FW1" s="1" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="FX1" s="1" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="FY1" s="1" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="FZ1" s="1" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="GA1" s="1" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="GB1" s="1" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="GC1" s="1" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="GD1" s="1" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="GE1" s="1" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="GF1" s="1" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="GG1" s="1" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="GH1" s="1" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="GI1" s="1" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="GJ1" s="1" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="GK1" s="1" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="GL1" s="1" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="GM1" s="1" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="GN1" s="1" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="GO1" s="1" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="GP1" s="1" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="GQ1" s="1" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="GR1" s="1" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="GS1" s="1" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="GT1" s="1" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="GU1" s="1" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="GV1" s="1" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="GW1" s="1" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="GX1" s="1" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="GY1" s="1" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="GZ1" s="1" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="HA1" s="1" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="HB1" s="1" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="HC1" s="1" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="HD1" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="HE1" s="1" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="HF1" s="1" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="HG1" s="1" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="HH1" s="1" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="HI1" s="1" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="HJ1" s="1" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="HK1" s="1" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="HL1" s="1" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="HM1" s="1" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="HN1" s="1" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="HO1" s="1" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="HP1" s="1" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="HQ1" s="1" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="HR1" s="1" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="HS1" s="1" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="HT1" s="1" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="HU1" s="1" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="HV1" s="1" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="HW1" s="1" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="HX1" s="1" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="HY1" s="1" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="HZ1" s="1" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="IA1" s="1" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="IB1" s="1" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="IC1" s="1" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="ID1" s="1" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="IE1" s="1" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="IF1" s="1" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="IG1" s="1" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="IH1" s="1" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="II1" s="1" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="IJ1" s="1" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="IK1" s="1" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="IL1" s="1" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="IM1" s="1" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="IN1" s="1" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="IO1" s="1" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="IP1" s="1" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="IQ1" s="1" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="IR1" s="1" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="IS1" s="1" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="IT1" s="1" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="IU1" s="1" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="IV1" s="1" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="IW1" s="1" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="IX1" s="1" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="IY1" s="1" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="IZ1" s="1" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="JA1" s="1" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="JB1" s="1" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="JC1" s="1" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="JD1" s="1" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="JE1" s="1" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="JF1" s="1" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="JG1" s="1" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="JH1" s="1" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="JI1" s="1" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="JJ1" s="1" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="JK1" s="1" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="JL1" s="1" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="JM1" s="1" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="JN1" s="1" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="JO1" s="1" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="JP1" s="1" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="JQ1" s="1" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="JR1" s="1" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="JS1" s="1" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="2" spans="1:279" ht="150" customHeight="1">
@@ -6432,574 +6435,574 @@
         <v>523</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="DC2" s="2" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="DD2" s="2" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="DE2" s="2" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="DF2" s="2" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="DK2" s="2" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="DL2" s="2" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="DM2" s="2" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="DN2" s="2" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="DO2" s="2" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="DP2" s="2" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="DQ2" s="2" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="DR2" s="2" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="DS2" s="2" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="DT2" s="2" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="DU2" s="2" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="DV2" s="2" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="DW2" s="2" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="DX2" s="2" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="DY2" s="2" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="DZ2" s="2" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="EA2" s="2" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="EB2" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="EC2" s="2" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="ED2" s="2" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="EE2" s="2" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="EF2" s="2" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="EG2" s="2" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="EH2" s="2" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="EI2" s="2" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="EJ2" s="2" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="EK2" s="2" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="EL2" s="2" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="EM2" s="2" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="EN2" s="2" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="EO2" s="2" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="EP2" s="2" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="EQ2" s="2" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="ER2" s="2" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="ES2" s="2" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="ET2" s="2" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="EU2" s="2" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="EV2" s="2" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="EW2" s="2" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="EX2" s="2" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="EY2" s="2" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="EZ2" s="2" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="FA2" s="2" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="FB2" s="2" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="FC2" s="2" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="FD2" s="2" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="FE2" s="2" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="FF2" s="2" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="FG2" s="2" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="FH2" s="2" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="FI2" s="2" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="FJ2" s="2" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="FK2" s="2" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="FL2" s="2" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="FM2" s="2" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="FN2" s="2" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="FO2" s="2" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="FP2" s="2" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="FQ2" s="2" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="FR2" s="2" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="FS2" s="2" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="FT2" s="2" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="FU2" s="2" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="FV2" s="2" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="FW2" s="2" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="FX2" s="2" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="FY2" s="2" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="FZ2" s="2" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="GA2" s="2" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="GB2" s="2" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="GC2" s="2" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="GD2" s="2" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="GE2" s="2" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="GF2" s="2" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="GG2" s="2" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="GH2" s="2" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="GI2" s="2" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="GJ2" s="2" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="GK2" s="2" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="GL2" s="2" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="GM2" s="2" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="GN2" s="2" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="GO2" s="2" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="GP2" s="2" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="GQ2" s="2" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="GR2" s="2" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="GS2" s="2" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="GT2" s="2" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="GU2" s="2" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="GV2" s="2" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="GW2" s="2" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="GX2" s="2" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="GY2" s="2" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="GZ2" s="2" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="HA2" s="2" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="HB2" s="2" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="HC2" s="2" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="HD2" s="2" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="HE2" s="2" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="HF2" s="2" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="HG2" s="2" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="HH2" s="2" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="HI2" s="2" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="HJ2" s="2" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="HK2" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="HL2" s="2" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="HM2" s="2" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="HN2" s="2" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="HO2" s="2" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="HP2" s="2" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="HQ2" s="2" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="HR2" s="2" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="HS2" s="2" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="HT2" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="HU2" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="HV2" s="2" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="HW2" s="2" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="HX2" s="2" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="HY2" s="2" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="HZ2" s="2" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="IA2" s="2" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="IB2" s="2" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="IC2" s="2" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="ID2" s="2" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="IE2" s="2" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="IF2" s="2" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="IG2" s="2" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="IH2" s="2" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="II2" s="2" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="IJ2" s="2" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="IK2" s="2" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="IL2" s="2" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="IM2" s="2" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="IN2" s="2" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="IO2" s="2" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="IP2" s="2" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="IQ2" s="2" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="IR2" s="2" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="IS2" s="2" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="IT2" s="2" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="IU2" s="2" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="IV2" s="2" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="IW2" s="2" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="IX2" s="2" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="IY2" s="2" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="IZ2" s="2" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="JA2" s="2" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="JB2" s="2" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="JC2" s="2" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="JD2" s="2" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="JE2" s="2" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="JF2" s="2" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="JG2" s="2" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="JH2" s="2" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="JI2" s="2" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="JJ2" s="2" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="JK2" s="2" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="JL2" s="2" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="JM2" s="2" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="JN2" s="2" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="JO2" s="2" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="JP2" s="2" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="JQ2" s="2" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="JR2" s="2" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="JS2" s="2" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
     </row>
   </sheetData>
@@ -7088,28 +7091,28 @@
         <v>524</v>
       </c>
       <c r="CN1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="CO1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="CZ1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="DC1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="DY1" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="EQ1" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="FA1" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="GX1" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="2" spans="13:206">
@@ -7138,28 +7141,28 @@
         <v>525</v>
       </c>
       <c r="CN2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="CO2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="CZ2" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="DC2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="DY2" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="EQ2" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="FA2" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="GX2" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="3" spans="13:206">
@@ -7185,28 +7188,28 @@
         <v>526</v>
       </c>
       <c r="CN3" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="CO3" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="CZ3" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="DC3" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="DY3" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="EQ3" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="FA3" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="GX3" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="4" spans="13:206">
@@ -7226,25 +7229,25 @@
         <v>527</v>
       </c>
       <c r="CN4" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="CZ4" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="DC4" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="DY4" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="EQ4" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="FA4" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="GX4" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="5" spans="13:206">
@@ -7264,19 +7267,19 @@
         <v>528</v>
       </c>
       <c r="CN5" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="DC5" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="DY5" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="EQ5" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="FA5" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="6" spans="13:206">
@@ -7293,13 +7296,13 @@
         <v>529</v>
       </c>
       <c r="CN6" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="DC6" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="EQ6" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="FA6" t="s">
         <v>116</v>
@@ -7319,16 +7322,16 @@
         <v>530</v>
       </c>
       <c r="CN7" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="DC7" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="EQ7" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="FA7" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="8" spans="13:206">
@@ -7342,13 +7345,13 @@
         <v>531</v>
       </c>
       <c r="CN8" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="DC8" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="EQ8" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
     </row>
     <row r="9" spans="13:206">
@@ -7362,10 +7365,10 @@
         <v>532</v>
       </c>
       <c r="DC9" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="EQ9" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
     </row>
     <row r="10" spans="13:206">
@@ -7379,7 +7382,7 @@
         <v>533</v>
       </c>
       <c r="DC10" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="11" spans="13:206">
@@ -7393,7 +7396,7 @@
         <v>534</v>
       </c>
       <c r="DC11" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="12" spans="13:206">
@@ -7407,7 +7410,7 @@
         <v>535</v>
       </c>
       <c r="DC12" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="13" spans="13:206">
@@ -7421,7 +7424,7 @@
         <v>536</v>
       </c>
       <c r="DC13" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="14" spans="13:206">
@@ -7435,7 +7438,7 @@
         <v>537</v>
       </c>
       <c r="DC14" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="15" spans="13:206">
@@ -7449,7 +7452,7 @@
         <v>538</v>
       </c>
       <c r="DC15" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="16" spans="13:206">
@@ -7459,8 +7462,11 @@
       <c r="AB16" t="s">
         <v>375</v>
       </c>
+      <c r="CL16" t="s">
+        <v>539</v>
+      </c>
       <c r="DC16" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="17" spans="13:107">
@@ -7471,7 +7477,7 @@
         <v>376</v>
       </c>
       <c r="DC17" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="18" spans="13:107">
@@ -7482,7 +7488,7 @@
         <v>377</v>
       </c>
       <c r="DC18" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="19" spans="13:107">
@@ -7493,7 +7499,7 @@
         <v>378</v>
       </c>
       <c r="DC19" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="20" spans="13:107">
@@ -7504,7 +7510,7 @@
         <v>379</v>
       </c>
       <c r="DC20" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="21" spans="13:107">
@@ -7515,7 +7521,7 @@
         <v>380</v>
       </c>
       <c r="DC21" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="22" spans="13:107">
@@ -7526,7 +7532,7 @@
         <v>381</v>
       </c>
       <c r="DC22" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="23" spans="13:107">
@@ -7537,7 +7543,7 @@
         <v>382</v>
       </c>
       <c r="DC23" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="24" spans="13:107">
@@ -7548,7 +7554,7 @@
         <v>383</v>
       </c>
       <c r="DC24" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="25" spans="13:107">
@@ -7559,7 +7565,7 @@
         <v>384</v>
       </c>
       <c r="DC25" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="26" spans="13:107">
@@ -7570,7 +7576,7 @@
         <v>385</v>
       </c>
       <c r="DC26" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="27" spans="13:107">
@@ -7581,7 +7587,7 @@
         <v>386</v>
       </c>
       <c r="DC27" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="28" spans="13:107">
@@ -7592,7 +7598,7 @@
         <v>387</v>
       </c>
       <c r="DC28" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="29" spans="13:107">
@@ -7603,7 +7609,7 @@
         <v>388</v>
       </c>
       <c r="DC29" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="30" spans="13:107">
@@ -7614,7 +7620,7 @@
         <v>389</v>
       </c>
       <c r="DC30" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="31" spans="13:107">
@@ -7622,7 +7628,7 @@
         <v>390</v>
       </c>
       <c r="DC31" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="32" spans="13:107">
@@ -7630,1317 +7636,1317 @@
         <v>391</v>
       </c>
       <c r="DC32" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="33" spans="107:107">
       <c r="DC33" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="34" spans="107:107">
       <c r="DC34" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="35" spans="107:107">
       <c r="DC35" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="36" spans="107:107">
       <c r="DC36" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="37" spans="107:107">
       <c r="DC37" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="38" spans="107:107">
       <c r="DC38" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="39" spans="107:107">
       <c r="DC39" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="40" spans="107:107">
       <c r="DC40" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="41" spans="107:107">
       <c r="DC41" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="42" spans="107:107">
       <c r="DC42" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="43" spans="107:107">
       <c r="DC43" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="44" spans="107:107">
       <c r="DC44" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="45" spans="107:107">
       <c r="DC45" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="46" spans="107:107">
       <c r="DC46" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="47" spans="107:107">
       <c r="DC47" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="48" spans="107:107">
       <c r="DC48" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="49" spans="107:107">
       <c r="DC49" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="50" spans="107:107">
       <c r="DC50" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="51" spans="107:107">
       <c r="DC51" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="52" spans="107:107">
       <c r="DC52" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="53" spans="107:107">
       <c r="DC53" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="54" spans="107:107">
       <c r="DC54" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="55" spans="107:107">
       <c r="DC55" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="56" spans="107:107">
       <c r="DC56" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="57" spans="107:107">
       <c r="DC57" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="58" spans="107:107">
       <c r="DC58" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="59" spans="107:107">
       <c r="DC59" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="60" spans="107:107">
       <c r="DC60" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="61" spans="107:107">
       <c r="DC61" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="62" spans="107:107">
       <c r="DC62" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="63" spans="107:107">
       <c r="DC63" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="64" spans="107:107">
       <c r="DC64" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="65" spans="107:107">
       <c r="DC65" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="66" spans="107:107">
       <c r="DC66" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="67" spans="107:107">
       <c r="DC67" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="68" spans="107:107">
       <c r="DC68" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="69" spans="107:107">
       <c r="DC69" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="70" spans="107:107">
       <c r="DC70" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="71" spans="107:107">
       <c r="DC71" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="72" spans="107:107">
       <c r="DC72" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="73" spans="107:107">
       <c r="DC73" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="74" spans="107:107">
       <c r="DC74" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="75" spans="107:107">
       <c r="DC75" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="76" spans="107:107">
       <c r="DC76" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="77" spans="107:107">
       <c r="DC77" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="78" spans="107:107">
       <c r="DC78" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="79" spans="107:107">
       <c r="DC79" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="80" spans="107:107">
       <c r="DC80" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="81" spans="107:107">
       <c r="DC81" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="82" spans="107:107">
       <c r="DC82" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="83" spans="107:107">
       <c r="DC83" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="84" spans="107:107">
       <c r="DC84" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="85" spans="107:107">
       <c r="DC85" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="86" spans="107:107">
       <c r="DC86" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="87" spans="107:107">
       <c r="DC87" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="88" spans="107:107">
       <c r="DC88" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="89" spans="107:107">
       <c r="DC89" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="90" spans="107:107">
       <c r="DC90" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="91" spans="107:107">
       <c r="DC91" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="92" spans="107:107">
       <c r="DC92" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="93" spans="107:107">
       <c r="DC93" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="94" spans="107:107">
       <c r="DC94" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="95" spans="107:107">
       <c r="DC95" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="96" spans="107:107">
       <c r="DC96" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="97" spans="107:107">
       <c r="DC97" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="98" spans="107:107">
       <c r="DC98" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="99" spans="107:107">
       <c r="DC99" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="100" spans="107:107">
       <c r="DC100" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="101" spans="107:107">
       <c r="DC101" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="102" spans="107:107">
       <c r="DC102" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="103" spans="107:107">
       <c r="DC103" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="104" spans="107:107">
       <c r="DC104" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="105" spans="107:107">
       <c r="DC105" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="106" spans="107:107">
       <c r="DC106" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="107" spans="107:107">
       <c r="DC107" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="108" spans="107:107">
       <c r="DC108" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="109" spans="107:107">
       <c r="DC109" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="110" spans="107:107">
       <c r="DC110" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="111" spans="107:107">
       <c r="DC111" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="112" spans="107:107">
       <c r="DC112" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="113" spans="107:107">
       <c r="DC113" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="114" spans="107:107">
       <c r="DC114" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="115" spans="107:107">
       <c r="DC115" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="116" spans="107:107">
       <c r="DC116" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="117" spans="107:107">
       <c r="DC117" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="118" spans="107:107">
       <c r="DC118" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="119" spans="107:107">
       <c r="DC119" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="120" spans="107:107">
       <c r="DC120" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="121" spans="107:107">
       <c r="DC121" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="122" spans="107:107">
       <c r="DC122" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="123" spans="107:107">
       <c r="DC123" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="124" spans="107:107">
       <c r="DC124" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="125" spans="107:107">
       <c r="DC125" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="126" spans="107:107">
       <c r="DC126" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="127" spans="107:107">
       <c r="DC127" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="128" spans="107:107">
       <c r="DC128" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="129" spans="107:107">
       <c r="DC129" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="130" spans="107:107">
       <c r="DC130" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="131" spans="107:107">
       <c r="DC131" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="132" spans="107:107">
       <c r="DC132" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="133" spans="107:107">
       <c r="DC133" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="134" spans="107:107">
       <c r="DC134" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="135" spans="107:107">
       <c r="DC135" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="136" spans="107:107">
       <c r="DC136" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="137" spans="107:107">
       <c r="DC137" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="138" spans="107:107">
       <c r="DC138" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="139" spans="107:107">
       <c r="DC139" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="140" spans="107:107">
       <c r="DC140" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="141" spans="107:107">
       <c r="DC141" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="142" spans="107:107">
       <c r="DC142" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="143" spans="107:107">
       <c r="DC143" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="144" spans="107:107">
       <c r="DC144" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="145" spans="107:107">
       <c r="DC145" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="146" spans="107:107">
       <c r="DC146" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="147" spans="107:107">
       <c r="DC147" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="148" spans="107:107">
       <c r="DC148" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="149" spans="107:107">
       <c r="DC149" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="150" spans="107:107">
       <c r="DC150" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="151" spans="107:107">
       <c r="DC151" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="152" spans="107:107">
       <c r="DC152" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="153" spans="107:107">
       <c r="DC153" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="154" spans="107:107">
       <c r="DC154" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="155" spans="107:107">
       <c r="DC155" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="156" spans="107:107">
       <c r="DC156" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="157" spans="107:107">
       <c r="DC157" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="158" spans="107:107">
       <c r="DC158" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="159" spans="107:107">
       <c r="DC159" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="160" spans="107:107">
       <c r="DC160" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="161" spans="107:107">
       <c r="DC161" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="162" spans="107:107">
       <c r="DC162" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="163" spans="107:107">
       <c r="DC163" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="164" spans="107:107">
       <c r="DC164" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="165" spans="107:107">
       <c r="DC165" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="166" spans="107:107">
       <c r="DC166" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="167" spans="107:107">
       <c r="DC167" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="168" spans="107:107">
       <c r="DC168" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="169" spans="107:107">
       <c r="DC169" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="170" spans="107:107">
       <c r="DC170" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="171" spans="107:107">
       <c r="DC171" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="172" spans="107:107">
       <c r="DC172" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="173" spans="107:107">
       <c r="DC173" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="174" spans="107:107">
       <c r="DC174" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="175" spans="107:107">
       <c r="DC175" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="176" spans="107:107">
       <c r="DC176" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="177" spans="107:107">
       <c r="DC177" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="178" spans="107:107">
       <c r="DC178" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="179" spans="107:107">
       <c r="DC179" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="180" spans="107:107">
       <c r="DC180" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="181" spans="107:107">
       <c r="DC181" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="182" spans="107:107">
       <c r="DC182" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="183" spans="107:107">
       <c r="DC183" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="184" spans="107:107">
       <c r="DC184" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="185" spans="107:107">
       <c r="DC185" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="186" spans="107:107">
       <c r="DC186" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="187" spans="107:107">
       <c r="DC187" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="188" spans="107:107">
       <c r="DC188" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="189" spans="107:107">
       <c r="DC189" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="190" spans="107:107">
       <c r="DC190" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="191" spans="107:107">
       <c r="DC191" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="192" spans="107:107">
       <c r="DC192" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="193" spans="107:107">
       <c r="DC193" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="194" spans="107:107">
       <c r="DC194" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="195" spans="107:107">
       <c r="DC195" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="196" spans="107:107">
       <c r="DC196" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="197" spans="107:107">
       <c r="DC197" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="198" spans="107:107">
       <c r="DC198" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="199" spans="107:107">
       <c r="DC199" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="200" spans="107:107">
       <c r="DC200" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="201" spans="107:107">
       <c r="DC201" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="202" spans="107:107">
       <c r="DC202" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="203" spans="107:107">
       <c r="DC203" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="204" spans="107:107">
       <c r="DC204" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="205" spans="107:107">
       <c r="DC205" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
     </row>
     <row r="206" spans="107:107">
       <c r="DC206" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="207" spans="107:107">
       <c r="DC207" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="208" spans="107:107">
       <c r="DC208" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
     </row>
     <row r="209" spans="107:107">
       <c r="DC209" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="210" spans="107:107">
       <c r="DC210" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="211" spans="107:107">
       <c r="DC211" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="212" spans="107:107">
       <c r="DC212" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="213" spans="107:107">
       <c r="DC213" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="214" spans="107:107">
       <c r="DC214" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="215" spans="107:107">
       <c r="DC215" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="216" spans="107:107">
       <c r="DC216" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="217" spans="107:107">
       <c r="DC217" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="218" spans="107:107">
       <c r="DC218" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="219" spans="107:107">
       <c r="DC219" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="220" spans="107:107">
       <c r="DC220" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="221" spans="107:107">
       <c r="DC221" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="222" spans="107:107">
       <c r="DC222" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="223" spans="107:107">
       <c r="DC223" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="224" spans="107:107">
       <c r="DC224" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="225" spans="107:107">
       <c r="DC225" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="226" spans="107:107">
       <c r="DC226" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="227" spans="107:107">
       <c r="DC227" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="228" spans="107:107">
       <c r="DC228" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="229" spans="107:107">
       <c r="DC229" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="230" spans="107:107">
       <c r="DC230" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="231" spans="107:107">
       <c r="DC231" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="232" spans="107:107">
       <c r="DC232" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="233" spans="107:107">
       <c r="DC233" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="234" spans="107:107">
       <c r="DC234" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="235" spans="107:107">
       <c r="DC235" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="236" spans="107:107">
       <c r="DC236" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="237" spans="107:107">
       <c r="DC237" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="238" spans="107:107">
       <c r="DC238" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="239" spans="107:107">
       <c r="DC239" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="240" spans="107:107">
       <c r="DC240" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="241" spans="107:107">
       <c r="DC241" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="242" spans="107:107">
       <c r="DC242" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="243" spans="107:107">
       <c r="DC243" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="244" spans="107:107">
       <c r="DC244" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="245" spans="107:107">
       <c r="DC245" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="246" spans="107:107">
       <c r="DC246" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="247" spans="107:107">
       <c r="DC247" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="248" spans="107:107">
       <c r="DC248" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="249" spans="107:107">
       <c r="DC249" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
     </row>
     <row r="250" spans="107:107">
       <c r="DC250" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="251" spans="107:107">
       <c r="DC251" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="252" spans="107:107">
       <c r="DC252" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="253" spans="107:107">
       <c r="DC253" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
     </row>
     <row r="254" spans="107:107">
       <c r="DC254" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="255" spans="107:107">
       <c r="DC255" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="256" spans="107:107">
       <c r="DC256" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
     </row>
     <row r="257" spans="107:107">
       <c r="DC257" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="258" spans="107:107">
       <c r="DC258" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="259" spans="107:107">
       <c r="DC259" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="260" spans="107:107">
       <c r="DC260" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="261" spans="107:107">
       <c r="DC261" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="262" spans="107:107">
       <c r="DC262" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="263" spans="107:107">
       <c r="DC263" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="264" spans="107:107">
       <c r="DC264" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="265" spans="107:107">
       <c r="DC265" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="266" spans="107:107">
       <c r="DC266" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
     <row r="267" spans="107:107">
       <c r="DC267" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="268" spans="107:107">
       <c r="DC268" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="269" spans="107:107">
       <c r="DC269" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="270" spans="107:107">
       <c r="DC270" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
     </row>
     <row r="271" spans="107:107">
       <c r="DC271" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="272" spans="107:107">
       <c r="DC272" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="273" spans="107:107">
       <c r="DC273" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="274" spans="107:107">
       <c r="DC274" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="275" spans="107:107">
       <c r="DC275" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="276" spans="107:107">
       <c r="DC276" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
     </row>
     <row r="277" spans="107:107">
       <c r="DC277" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="278" spans="107:107">
       <c r="DC278" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="279" spans="107:107">
       <c r="DC279" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="280" spans="107:107">
       <c r="DC280" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="281" spans="107:107">
       <c r="DC281" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="282" spans="107:107">
       <c r="DC282" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="283" spans="107:107">
       <c r="DC283" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="284" spans="107:107">
       <c r="DC284" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
     <row r="285" spans="107:107">
       <c r="DC285" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="286" spans="107:107">
       <c r="DC286" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
     </row>
     <row r="287" spans="107:107">
       <c r="DC287" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="288" spans="107:107">
       <c r="DC288" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
     </row>
     <row r="289" spans="107:107">
       <c r="DC289" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="290" spans="107:107">
       <c r="DC290" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="291" spans="107:107">
       <c r="DC291" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
     </row>
     <row r="292" spans="107:107">
       <c r="DC292" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
     </row>
     <row r="293" spans="107:107">
       <c r="DC293" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
     </row>
     <row r="294" spans="107:107">
       <c r="DC294" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000056/metadata_template_ERC000056.xlsx
+++ b/templates/ERC000056/metadata_template_ERC000056.xlsx
@@ -24,7 +24,7 @@
     <definedName name="growthhabit">'cv_sample'!$CZ$1:$CZ$4</definedName>
     <definedName name="historytillage">'cv_sample'!$EQ$1:$EQ$9</definedName>
     <definedName name="hostpredictionapproach">'cv_sample'!$FA$1:$FA$7</definedName>
-    <definedName name="indoorsurface">'cv_sample'!$CN$1:$CN$8</definedName>
+    <definedName name="indoorsurface">'cv_sample'!$CN$1:$CN$9</definedName>
     <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="1251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1263" uniqueCount="1252">
   <si>
     <t>alias</t>
   </si>
@@ -1689,6 +1689,9 @@
   </si>
   <si>
     <t>door</t>
+  </si>
+  <si>
+    <t>floor</t>
   </si>
   <si>
     <t>shelving</t>
@@ -5602,568 +5605,568 @@
         <v>542</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="DL1" s="1" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="DM1" s="1" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="DN1" s="1" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="DO1" s="1" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="DP1" s="1" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="DQ1" s="1" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="DR1" s="1" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="DS1" s="1" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="DT1" s="1" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="DU1" s="1" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="DV1" s="1" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="DW1" s="1" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="DX1" s="1" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="DY1" s="1" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="DZ1" s="1" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="EA1" s="1" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="EB1" s="1" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="EC1" s="1" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="ED1" s="1" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="EE1" s="1" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="EH1" s="1" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="EI1" s="1" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="EJ1" s="1" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="EK1" s="1" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="EL1" s="1" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="EM1" s="1" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="EN1" s="1" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="EO1" s="1" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="EP1" s="1" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="EQ1" s="1" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="ER1" s="1" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="ES1" s="1" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="ET1" s="1" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="EU1" s="1" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="EV1" s="1" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="EW1" s="1" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="EX1" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="EY1" s="1" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="EZ1" s="1" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="FA1" s="1" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="FB1" s="1" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="FC1" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="FD1" s="1" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="FE1" s="1" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="FF1" s="1" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="FG1" s="1" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="FH1" s="1" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="FI1" s="1" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="FJ1" s="1" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="FK1" s="1" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="FL1" s="1" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="FM1" s="1" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="FN1" s="1" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="FO1" s="1" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="FP1" s="1" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="FQ1" s="1" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="FR1" s="1" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="FS1" s="1" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="FT1" s="1" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="FU1" s="1" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="FV1" s="1" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="FW1" s="1" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="FX1" s="1" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="FY1" s="1" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="FZ1" s="1" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="GA1" s="1" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="GB1" s="1" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="GC1" s="1" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="GD1" s="1" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="GE1" s="1" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="GF1" s="1" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="GG1" s="1" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="GH1" s="1" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="GI1" s="1" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="GJ1" s="1" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="GK1" s="1" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="GL1" s="1" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="GM1" s="1" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="GN1" s="1" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="GO1" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="GP1" s="1" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="GQ1" s="1" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="GR1" s="1" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="GS1" s="1" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="GT1" s="1" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="GU1" s="1" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="GV1" s="1" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="GW1" s="1" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="GX1" s="1" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="GY1" s="1" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="GZ1" s="1" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="HA1" s="1" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="HB1" s="1" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="HC1" s="1" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="HD1" s="1" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="HE1" s="1" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="HF1" s="1" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="HG1" s="1" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="HH1" s="1" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="HI1" s="1" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="HJ1" s="1" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="HK1" s="1" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="HL1" s="1" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="HM1" s="1" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="HN1" s="1" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="HO1" s="1" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="HP1" s="1" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="HQ1" s="1" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="HR1" s="1" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="HS1" s="1" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="HT1" s="1" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="HU1" s="1" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="HV1" s="1" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="HW1" s="1" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="HX1" s="1" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="HY1" s="1" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="HZ1" s="1" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="IA1" s="1" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="IB1" s="1" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="IC1" s="1" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="ID1" s="1" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="IE1" s="1" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="IF1" s="1" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="IG1" s="1" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="IH1" s="1" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="II1" s="1" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="IJ1" s="1" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="IK1" s="1" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="IL1" s="1" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="IM1" s="1" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="IN1" s="1" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="IO1" s="1" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="IP1" s="1" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="IQ1" s="1" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="IR1" s="1" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="IS1" s="1" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="IT1" s="1" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="IU1" s="1" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="IV1" s="1" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="IW1" s="1" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="IX1" s="1" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="IY1" s="1" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="IZ1" s="1" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="JA1" s="1" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="JB1" s="1" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="JC1" s="1" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="JD1" s="1" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="JE1" s="1" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="JF1" s="1" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="JG1" s="1" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="JH1" s="1" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="JI1" s="1" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="JJ1" s="1" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="JK1" s="1" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="JL1" s="1" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="JM1" s="1" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="JN1" s="1" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="JO1" s="1" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="JP1" s="1" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="JQ1" s="1" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="JR1" s="1" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="JS1" s="1" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="2" spans="1:279" ht="150" customHeight="1">
@@ -6441,568 +6444,568 @@
         <v>543</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="DC2" s="2" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="DD2" s="2" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="DE2" s="2" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="DF2" s="2" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="DK2" s="2" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="DL2" s="2" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="DM2" s="2" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="DN2" s="2" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="DO2" s="2" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="DP2" s="2" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="DQ2" s="2" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="DR2" s="2" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="DS2" s="2" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="DT2" s="2" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="DU2" s="2" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="DV2" s="2" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="DW2" s="2" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="DX2" s="2" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="DY2" s="2" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="DZ2" s="2" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="EA2" s="2" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="EB2" s="2" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="EC2" s="2" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="ED2" s="2" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="EE2" s="2" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="EF2" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="EG2" s="2" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="EH2" s="2" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="EI2" s="2" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="EJ2" s="2" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="EK2" s="2" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="EL2" s="2" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="EM2" s="2" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="EN2" s="2" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="EO2" s="2" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="EP2" s="2" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="EQ2" s="2" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="ER2" s="2" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="ES2" s="2" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="ET2" s="2" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="EU2" s="2" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="EV2" s="2" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="EW2" s="2" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="EX2" s="2" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="EY2" s="2" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="EZ2" s="2" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="FA2" s="2" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="FB2" s="2" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="FC2" s="2" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="FD2" s="2" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="FE2" s="2" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="FF2" s="2" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="FG2" s="2" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="FH2" s="2" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="FI2" s="2" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="FJ2" s="2" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="FK2" s="2" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="FL2" s="2" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="FM2" s="2" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="FN2" s="2" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="FO2" s="2" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="FP2" s="2" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="FQ2" s="2" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="FR2" s="2" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="FS2" s="2" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="FT2" s="2" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="FU2" s="2" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="FV2" s="2" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="FW2" s="2" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="FX2" s="2" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="FY2" s="2" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="FZ2" s="2" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="GA2" s="2" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="GB2" s="2" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="GC2" s="2" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="GD2" s="2" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="GE2" s="2" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="GF2" s="2" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="GG2" s="2" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="GH2" s="2" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="GI2" s="2" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="GJ2" s="2" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="GK2" s="2" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="GL2" s="2" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="GM2" s="2" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="GN2" s="2" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="GO2" s="2" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="GP2" s="2" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="GQ2" s="2" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="GR2" s="2" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="GS2" s="2" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="GT2" s="2" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="GU2" s="2" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="GV2" s="2" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="GW2" s="2" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="GX2" s="2" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="GY2" s="2" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="GZ2" s="2" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="HA2" s="2" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="HB2" s="2" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="HC2" s="2" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="HD2" s="2" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="HE2" s="2" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="HF2" s="2" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="HG2" s="2" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="HH2" s="2" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="HI2" s="2" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="HJ2" s="2" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="HK2" s="2" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="HL2" s="2" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="HM2" s="2" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="HN2" s="2" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="HO2" s="2" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="HP2" s="2" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="HQ2" s="2" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="HR2" s="2" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="HS2" s="2" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="HT2" s="2" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="HU2" s="2" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="HV2" s="2" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="HW2" s="2" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="HX2" s="2" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="HY2" s="2" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="HZ2" s="2" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="IA2" s="2" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="IB2" s="2" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="IC2" s="2" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="ID2" s="2" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="IE2" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="IF2" s="2" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="IG2" s="2" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="IH2" s="2" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="II2" s="2" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="IJ2" s="2" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="IK2" s="2" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="IL2" s="2" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="IM2" s="2" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="IN2" s="2" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="IO2" s="2" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="IP2" s="2" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="IQ2" s="2" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="IR2" s="2" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="IS2" s="2" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="IT2" s="2" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="IU2" s="2" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="IV2" s="2" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="IW2" s="2" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="IX2" s="2" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="IY2" s="2" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="IZ2" s="2" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="JA2" s="2" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="JB2" s="2" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="JC2" s="2" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="JD2" s="2" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="JE2" s="2" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="JF2" s="2" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="JG2" s="2" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="JH2" s="2" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="JI2" s="2" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="JJ2" s="2" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="JK2" s="2" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="JL2" s="2" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="JM2" s="2" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="JN2" s="2" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="JO2" s="2" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="JP2" s="2" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="JQ2" s="2" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="JR2" s="2" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="JS2" s="2" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
   </sheetData>
@@ -7094,25 +7097,25 @@
         <v>544</v>
       </c>
       <c r="CO1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="CZ1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="DC1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="DY1" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="EQ1" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="FA1" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="GX1" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="2" spans="13:206">
@@ -7144,25 +7147,25 @@
         <v>545</v>
       </c>
       <c r="CO2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="CZ2" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="DC2" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="DY2" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="EQ2" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="FA2" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="GX2" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="3" spans="13:206">
@@ -7191,25 +7194,25 @@
         <v>546</v>
       </c>
       <c r="CO3" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="CZ3" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="DC3" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="DY3" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="EQ3" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="FA3" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="GX3" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="4" spans="13:206">
@@ -7232,22 +7235,22 @@
         <v>547</v>
       </c>
       <c r="CZ4" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="DC4" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="DY4" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="EQ4" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="FA4" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="GX4" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="5" spans="13:206">
@@ -7270,16 +7273,16 @@
         <v>548</v>
       </c>
       <c r="DC5" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="DY5" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="EQ5" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="FA5" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="6" spans="13:206">
@@ -7299,10 +7302,10 @@
         <v>549</v>
       </c>
       <c r="DC6" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="EQ6" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="FA6" t="s">
         <v>116</v>
@@ -7325,13 +7328,13 @@
         <v>550</v>
       </c>
       <c r="DC7" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="EQ7" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="FA7" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="8" spans="13:206">
@@ -7348,10 +7351,10 @@
         <v>551</v>
       </c>
       <c r="DC8" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="EQ8" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
     </row>
     <row r="9" spans="13:206">
@@ -7364,11 +7367,14 @@
       <c r="CL9" t="s">
         <v>532</v>
       </c>
+      <c r="CN9" t="s">
+        <v>552</v>
+      </c>
       <c r="DC9" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="EQ9" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="10" spans="13:206">
@@ -7382,7 +7388,7 @@
         <v>533</v>
       </c>
       <c r="DC10" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="11" spans="13:206">
@@ -7396,7 +7402,7 @@
         <v>534</v>
       </c>
       <c r="DC11" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="12" spans="13:206">
@@ -7410,7 +7416,7 @@
         <v>535</v>
       </c>
       <c r="DC12" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="13" spans="13:206">
@@ -7424,7 +7430,7 @@
         <v>536</v>
       </c>
       <c r="DC13" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="14" spans="13:206">
@@ -7438,7 +7444,7 @@
         <v>537</v>
       </c>
       <c r="DC14" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="15" spans="13:206">
@@ -7452,7 +7458,7 @@
         <v>538</v>
       </c>
       <c r="DC15" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="16" spans="13:206">
@@ -7466,7 +7472,7 @@
         <v>539</v>
       </c>
       <c r="DC16" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="17" spans="13:107">
@@ -7477,7 +7483,7 @@
         <v>376</v>
       </c>
       <c r="DC17" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="18" spans="13:107">
@@ -7488,7 +7494,7 @@
         <v>377</v>
       </c>
       <c r="DC18" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="19" spans="13:107">
@@ -7499,7 +7505,7 @@
         <v>378</v>
       </c>
       <c r="DC19" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="20" spans="13:107">
@@ -7510,7 +7516,7 @@
         <v>379</v>
       </c>
       <c r="DC20" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="21" spans="13:107">
@@ -7521,7 +7527,7 @@
         <v>380</v>
       </c>
       <c r="DC21" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="22" spans="13:107">
@@ -7532,7 +7538,7 @@
         <v>381</v>
       </c>
       <c r="DC22" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="23" spans="13:107">
@@ -7543,7 +7549,7 @@
         <v>382</v>
       </c>
       <c r="DC23" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="24" spans="13:107">
@@ -7554,7 +7560,7 @@
         <v>383</v>
       </c>
       <c r="DC24" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="25" spans="13:107">
@@ -7565,7 +7571,7 @@
         <v>384</v>
       </c>
       <c r="DC25" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="26" spans="13:107">
@@ -7576,7 +7582,7 @@
         <v>385</v>
       </c>
       <c r="DC26" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="27" spans="13:107">
@@ -7587,7 +7593,7 @@
         <v>386</v>
       </c>
       <c r="DC27" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="28" spans="13:107">
@@ -7598,7 +7604,7 @@
         <v>387</v>
       </c>
       <c r="DC28" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="29" spans="13:107">
@@ -7609,7 +7615,7 @@
         <v>388</v>
       </c>
       <c r="DC29" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="30" spans="13:107">
@@ -7620,7 +7626,7 @@
         <v>389</v>
       </c>
       <c r="DC30" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="31" spans="13:107">
@@ -7628,7 +7634,7 @@
         <v>390</v>
       </c>
       <c r="DC31" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="32" spans="13:107">
@@ -7636,1317 +7642,1317 @@
         <v>391</v>
       </c>
       <c r="DC32" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="33" spans="107:107">
       <c r="DC33" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="34" spans="107:107">
       <c r="DC34" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="35" spans="107:107">
       <c r="DC35" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="36" spans="107:107">
       <c r="DC36" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="37" spans="107:107">
       <c r="DC37" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="38" spans="107:107">
       <c r="DC38" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="39" spans="107:107">
       <c r="DC39" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="40" spans="107:107">
       <c r="DC40" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="41" spans="107:107">
       <c r="DC41" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="42" spans="107:107">
       <c r="DC42" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="43" spans="107:107">
       <c r="DC43" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="44" spans="107:107">
       <c r="DC44" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="45" spans="107:107">
       <c r="DC45" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="46" spans="107:107">
       <c r="DC46" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="47" spans="107:107">
       <c r="DC47" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="48" spans="107:107">
       <c r="DC48" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="49" spans="107:107">
       <c r="DC49" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="50" spans="107:107">
       <c r="DC50" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="51" spans="107:107">
       <c r="DC51" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="52" spans="107:107">
       <c r="DC52" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="53" spans="107:107">
       <c r="DC53" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="54" spans="107:107">
       <c r="DC54" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="55" spans="107:107">
       <c r="DC55" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="56" spans="107:107">
       <c r="DC56" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="57" spans="107:107">
       <c r="DC57" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="58" spans="107:107">
       <c r="DC58" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="59" spans="107:107">
       <c r="DC59" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="60" spans="107:107">
       <c r="DC60" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="61" spans="107:107">
       <c r="DC61" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="62" spans="107:107">
       <c r="DC62" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="63" spans="107:107">
       <c r="DC63" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="64" spans="107:107">
       <c r="DC64" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="65" spans="107:107">
       <c r="DC65" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="66" spans="107:107">
       <c r="DC66" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="67" spans="107:107">
       <c r="DC67" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="68" spans="107:107">
       <c r="DC68" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="69" spans="107:107">
       <c r="DC69" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="70" spans="107:107">
       <c r="DC70" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="71" spans="107:107">
       <c r="DC71" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="72" spans="107:107">
       <c r="DC72" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="73" spans="107:107">
       <c r="DC73" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="74" spans="107:107">
       <c r="DC74" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="75" spans="107:107">
       <c r="DC75" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="76" spans="107:107">
       <c r="DC76" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="77" spans="107:107">
       <c r="DC77" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="78" spans="107:107">
       <c r="DC78" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="79" spans="107:107">
       <c r="DC79" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="80" spans="107:107">
       <c r="DC80" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="81" spans="107:107">
       <c r="DC81" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="82" spans="107:107">
       <c r="DC82" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="83" spans="107:107">
       <c r="DC83" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="84" spans="107:107">
       <c r="DC84" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="85" spans="107:107">
       <c r="DC85" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="86" spans="107:107">
       <c r="DC86" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="87" spans="107:107">
       <c r="DC87" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="88" spans="107:107">
       <c r="DC88" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="89" spans="107:107">
       <c r="DC89" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="90" spans="107:107">
       <c r="DC90" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="91" spans="107:107">
       <c r="DC91" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="92" spans="107:107">
       <c r="DC92" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="93" spans="107:107">
       <c r="DC93" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="94" spans="107:107">
       <c r="DC94" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="95" spans="107:107">
       <c r="DC95" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="96" spans="107:107">
       <c r="DC96" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="97" spans="107:107">
       <c r="DC97" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="98" spans="107:107">
       <c r="DC98" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="99" spans="107:107">
       <c r="DC99" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="100" spans="107:107">
       <c r="DC100" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="101" spans="107:107">
       <c r="DC101" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="102" spans="107:107">
       <c r="DC102" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="103" spans="107:107">
       <c r="DC103" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="104" spans="107:107">
       <c r="DC104" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="105" spans="107:107">
       <c r="DC105" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="106" spans="107:107">
       <c r="DC106" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="107" spans="107:107">
       <c r="DC107" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="108" spans="107:107">
       <c r="DC108" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="109" spans="107:107">
       <c r="DC109" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="110" spans="107:107">
       <c r="DC110" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="111" spans="107:107">
       <c r="DC111" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="112" spans="107:107">
       <c r="DC112" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="113" spans="107:107">
       <c r="DC113" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="114" spans="107:107">
       <c r="DC114" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="115" spans="107:107">
       <c r="DC115" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="116" spans="107:107">
       <c r="DC116" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="117" spans="107:107">
       <c r="DC117" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="118" spans="107:107">
       <c r="DC118" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="119" spans="107:107">
       <c r="DC119" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="120" spans="107:107">
       <c r="DC120" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="121" spans="107:107">
       <c r="DC121" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="122" spans="107:107">
       <c r="DC122" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="123" spans="107:107">
       <c r="DC123" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="124" spans="107:107">
       <c r="DC124" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="125" spans="107:107">
       <c r="DC125" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="126" spans="107:107">
       <c r="DC126" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="127" spans="107:107">
       <c r="DC127" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="128" spans="107:107">
       <c r="DC128" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="129" spans="107:107">
       <c r="DC129" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="130" spans="107:107">
       <c r="DC130" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="131" spans="107:107">
       <c r="DC131" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="132" spans="107:107">
       <c r="DC132" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="133" spans="107:107">
       <c r="DC133" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="134" spans="107:107">
       <c r="DC134" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="135" spans="107:107">
       <c r="DC135" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="136" spans="107:107">
       <c r="DC136" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="137" spans="107:107">
       <c r="DC137" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="138" spans="107:107">
       <c r="DC138" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="139" spans="107:107">
       <c r="DC139" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="140" spans="107:107">
       <c r="DC140" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="141" spans="107:107">
       <c r="DC141" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="142" spans="107:107">
       <c r="DC142" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="143" spans="107:107">
       <c r="DC143" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="144" spans="107:107">
       <c r="DC144" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="145" spans="107:107">
       <c r="DC145" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="146" spans="107:107">
       <c r="DC146" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="147" spans="107:107">
       <c r="DC147" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="148" spans="107:107">
       <c r="DC148" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="149" spans="107:107">
       <c r="DC149" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="150" spans="107:107">
       <c r="DC150" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="151" spans="107:107">
       <c r="DC151" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="152" spans="107:107">
       <c r="DC152" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="153" spans="107:107">
       <c r="DC153" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="154" spans="107:107">
       <c r="DC154" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="155" spans="107:107">
       <c r="DC155" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="156" spans="107:107">
       <c r="DC156" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="157" spans="107:107">
       <c r="DC157" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="158" spans="107:107">
       <c r="DC158" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="159" spans="107:107">
       <c r="DC159" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="160" spans="107:107">
       <c r="DC160" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="161" spans="107:107">
       <c r="DC161" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="162" spans="107:107">
       <c r="DC162" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="163" spans="107:107">
       <c r="DC163" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="164" spans="107:107">
       <c r="DC164" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="165" spans="107:107">
       <c r="DC165" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="166" spans="107:107">
       <c r="DC166" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="167" spans="107:107">
       <c r="DC167" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="168" spans="107:107">
       <c r="DC168" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="169" spans="107:107">
       <c r="DC169" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="170" spans="107:107">
       <c r="DC170" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="171" spans="107:107">
       <c r="DC171" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="172" spans="107:107">
       <c r="DC172" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="173" spans="107:107">
       <c r="DC173" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="174" spans="107:107">
       <c r="DC174" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="175" spans="107:107">
       <c r="DC175" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="176" spans="107:107">
       <c r="DC176" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="177" spans="107:107">
       <c r="DC177" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="178" spans="107:107">
       <c r="DC178" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="179" spans="107:107">
       <c r="DC179" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="180" spans="107:107">
       <c r="DC180" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="181" spans="107:107">
       <c r="DC181" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="182" spans="107:107">
       <c r="DC182" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="183" spans="107:107">
       <c r="DC183" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="184" spans="107:107">
       <c r="DC184" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="185" spans="107:107">
       <c r="DC185" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="186" spans="107:107">
       <c r="DC186" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="187" spans="107:107">
       <c r="DC187" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="188" spans="107:107">
       <c r="DC188" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="189" spans="107:107">
       <c r="DC189" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="190" spans="107:107">
       <c r="DC190" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="191" spans="107:107">
       <c r="DC191" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="192" spans="107:107">
       <c r="DC192" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="193" spans="107:107">
       <c r="DC193" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="194" spans="107:107">
       <c r="DC194" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="195" spans="107:107">
       <c r="DC195" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="196" spans="107:107">
       <c r="DC196" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="197" spans="107:107">
       <c r="DC197" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="198" spans="107:107">
       <c r="DC198" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="199" spans="107:107">
       <c r="DC199" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="200" spans="107:107">
       <c r="DC200" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="201" spans="107:107">
       <c r="DC201" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="202" spans="107:107">
       <c r="DC202" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="203" spans="107:107">
       <c r="DC203" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="204" spans="107:107">
       <c r="DC204" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
     </row>
     <row r="205" spans="107:107">
       <c r="DC205" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="206" spans="107:107">
       <c r="DC206" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="207" spans="107:107">
       <c r="DC207" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
     </row>
     <row r="208" spans="107:107">
       <c r="DC208" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="209" spans="107:107">
       <c r="DC209" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="210" spans="107:107">
       <c r="DC210" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="211" spans="107:107">
       <c r="DC211" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="212" spans="107:107">
       <c r="DC212" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="213" spans="107:107">
       <c r="DC213" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="214" spans="107:107">
       <c r="DC214" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="215" spans="107:107">
       <c r="DC215" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="216" spans="107:107">
       <c r="DC216" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="217" spans="107:107">
       <c r="DC217" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="218" spans="107:107">
       <c r="DC218" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="219" spans="107:107">
       <c r="DC219" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="220" spans="107:107">
       <c r="DC220" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="221" spans="107:107">
       <c r="DC221" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="222" spans="107:107">
       <c r="DC222" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="223" spans="107:107">
       <c r="DC223" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="224" spans="107:107">
       <c r="DC224" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="225" spans="107:107">
       <c r="DC225" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="226" spans="107:107">
       <c r="DC226" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="227" spans="107:107">
       <c r="DC227" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="228" spans="107:107">
       <c r="DC228" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="229" spans="107:107">
       <c r="DC229" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="230" spans="107:107">
       <c r="DC230" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="231" spans="107:107">
       <c r="DC231" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="232" spans="107:107">
       <c r="DC232" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="233" spans="107:107">
       <c r="DC233" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="234" spans="107:107">
       <c r="DC234" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="235" spans="107:107">
       <c r="DC235" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="236" spans="107:107">
       <c r="DC236" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="237" spans="107:107">
       <c r="DC237" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="238" spans="107:107">
       <c r="DC238" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="239" spans="107:107">
       <c r="DC239" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="240" spans="107:107">
       <c r="DC240" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="241" spans="107:107">
       <c r="DC241" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="242" spans="107:107">
       <c r="DC242" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="243" spans="107:107">
       <c r="DC243" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="244" spans="107:107">
       <c r="DC244" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="245" spans="107:107">
       <c r="DC245" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="246" spans="107:107">
       <c r="DC246" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="247" spans="107:107">
       <c r="DC247" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="248" spans="107:107">
       <c r="DC248" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
     </row>
     <row r="249" spans="107:107">
       <c r="DC249" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="250" spans="107:107">
       <c r="DC250" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="251" spans="107:107">
       <c r="DC251" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="252" spans="107:107">
       <c r="DC252" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
     </row>
     <row r="253" spans="107:107">
       <c r="DC253" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="254" spans="107:107">
       <c r="DC254" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="255" spans="107:107">
       <c r="DC255" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
     </row>
     <row r="256" spans="107:107">
       <c r="DC256" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="257" spans="107:107">
       <c r="DC257" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="258" spans="107:107">
       <c r="DC258" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="259" spans="107:107">
       <c r="DC259" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="260" spans="107:107">
       <c r="DC260" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="261" spans="107:107">
       <c r="DC261" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="262" spans="107:107">
       <c r="DC262" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="263" spans="107:107">
       <c r="DC263" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="264" spans="107:107">
       <c r="DC264" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="265" spans="107:107">
       <c r="DC265" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
     <row r="266" spans="107:107">
       <c r="DC266" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="267" spans="107:107">
       <c r="DC267" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="268" spans="107:107">
       <c r="DC268" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="269" spans="107:107">
       <c r="DC269" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
     </row>
     <row r="270" spans="107:107">
       <c r="DC270" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="271" spans="107:107">
       <c r="DC271" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="272" spans="107:107">
       <c r="DC272" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="273" spans="107:107">
       <c r="DC273" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="274" spans="107:107">
       <c r="DC274" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="275" spans="107:107">
       <c r="DC275" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
     </row>
     <row r="276" spans="107:107">
       <c r="DC276" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="277" spans="107:107">
       <c r="DC277" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="278" spans="107:107">
       <c r="DC278" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="279" spans="107:107">
       <c r="DC279" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="280" spans="107:107">
       <c r="DC280" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="281" spans="107:107">
       <c r="DC281" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="282" spans="107:107">
       <c r="DC282" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="283" spans="107:107">
       <c r="DC283" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
     <row r="284" spans="107:107">
       <c r="DC284" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="285" spans="107:107">
       <c r="DC285" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
     </row>
     <row r="286" spans="107:107">
       <c r="DC286" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="287" spans="107:107">
       <c r="DC287" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
     </row>
     <row r="288" spans="107:107">
       <c r="DC288" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="289" spans="107:107">
       <c r="DC289" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="290" spans="107:107">
       <c r="DC290" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
     </row>
     <row r="291" spans="107:107">
       <c r="DC291" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
     </row>
     <row r="292" spans="107:107">
       <c r="DC292" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
     </row>
     <row r="293" spans="107:107">
       <c r="DC293" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
     </row>
     <row r="294" spans="107:107">
       <c r="DC294" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000056/metadata_template_ERC000056.xlsx
+++ b/templates/ERC000056/metadata_template_ERC000056.xlsx
@@ -25,7 +25,7 @@
     <definedName name="historytillage">'cv_sample'!$EQ$1:$EQ$9</definedName>
     <definedName name="hostpredictionapproach">'cv_sample'!$FA$1:$FA$7</definedName>
     <definedName name="indoorsurface">'cv_sample'!$CN$1:$CN$9</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$89</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1263" uniqueCount="1252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="1253">
   <si>
     <t>alias</t>
   </si>
@@ -741,6 +741,9 @@
   </si>
   <si>
     <t>UG 100</t>
+  </si>
+  <si>
+    <t>UG 200</t>
   </si>
   <si>
     <t>Vega</t>
@@ -4330,7 +4333,7 @@
         <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -4374,7 +4377,7 @@
         <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -4401,7 +4404,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N88"/>
+  <dimension ref="G1:N89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -5138,6 +5141,11 @@
     </row>
     <row r="88" spans="14:14">
       <c r="N88" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="89" spans="14:14">
+      <c r="N89" t="s">
         <v>117</v>
       </c>
     </row>
@@ -5159,27 +5167,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -5199,122 +5207,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -5338,1674 +5346,1674 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="DA1" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="DB1" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="DC1" s="1" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="DD1" s="1" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="DE1" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="DJ1" s="1" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="DL1" s="1" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="DM1" s="1" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="DN1" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="DO1" s="1" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="DP1" s="1" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="DQ1" s="1" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="DR1" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="DS1" s="1" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="DT1" s="1" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="DU1" s="1" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="DV1" s="1" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="DW1" s="1" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="DX1" s="1" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="DY1" s="1" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="DZ1" s="1" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="EA1" s="1" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="EB1" s="1" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="EC1" s="1" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="ED1" s="1" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="EE1" s="1" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="EH1" s="1" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="EI1" s="1" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="EJ1" s="1" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="EK1" s="1" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="EL1" s="1" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="EM1" s="1" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="EN1" s="1" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="EO1" s="1" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="EP1" s="1" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="EQ1" s="1" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="ER1" s="1" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="ES1" s="1" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="ET1" s="1" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="EU1" s="1" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="EV1" s="1" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="EW1" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="EX1" s="1" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="EY1" s="1" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="EZ1" s="1" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="FA1" s="1" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="FB1" s="1" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="FC1" s="1" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="FD1" s="1" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="FE1" s="1" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="FF1" s="1" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="FG1" s="1" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="FH1" s="1" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="FI1" s="1" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="FJ1" s="1" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="FK1" s="1" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="FL1" s="1" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="FM1" s="1" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="FN1" s="1" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="FO1" s="1" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="FP1" s="1" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="FQ1" s="1" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="FR1" s="1" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="FS1" s="1" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="FT1" s="1" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="FU1" s="1" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="FV1" s="1" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="FW1" s="1" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="FX1" s="1" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="FY1" s="1" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="FZ1" s="1" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="GA1" s="1" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="GB1" s="1" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="GC1" s="1" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="GD1" s="1" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="GE1" s="1" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="GF1" s="1" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="GG1" s="1" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="GH1" s="1" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="GI1" s="1" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="GJ1" s="1" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="GK1" s="1" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="GL1" s="1" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="GM1" s="1" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="GN1" s="1" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="GO1" s="1" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="GP1" s="1" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="GQ1" s="1" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="GR1" s="1" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="GS1" s="1" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="GT1" s="1" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="GU1" s="1" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="GV1" s="1" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="GW1" s="1" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="GX1" s="1" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="GY1" s="1" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="GZ1" s="1" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="HA1" s="1" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="HB1" s="1" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="HC1" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="HD1" s="1" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="HE1" s="1" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="HF1" s="1" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="HG1" s="1" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="HH1" s="1" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="HI1" s="1" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="HJ1" s="1" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="HK1" s="1" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="HL1" s="1" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="HM1" s="1" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="HN1" s="1" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="HO1" s="1" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="HP1" s="1" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="HQ1" s="1" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="HR1" s="1" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="HS1" s="1" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="HT1" s="1" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="HU1" s="1" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="HV1" s="1" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="HW1" s="1" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="HX1" s="1" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="HY1" s="1" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="HZ1" s="1" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="IA1" s="1" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="IB1" s="1" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="IC1" s="1" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="ID1" s="1" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="IE1" s="1" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="IF1" s="1" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="IG1" s="1" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="IH1" s="1" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="II1" s="1" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="IJ1" s="1" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="IK1" s="1" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="IL1" s="1" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="IM1" s="1" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="IN1" s="1" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="IO1" s="1" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="IP1" s="1" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="IQ1" s="1" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="IR1" s="1" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="IS1" s="1" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="IT1" s="1" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="IU1" s="1" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="IV1" s="1" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="IW1" s="1" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="IX1" s="1" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="IY1" s="1" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="IZ1" s="1" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="JA1" s="1" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="JB1" s="1" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="JC1" s="1" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="JD1" s="1" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="JE1" s="1" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="JF1" s="1" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="JG1" s="1" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="JH1" s="1" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="JI1" s="1" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="JJ1" s="1" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="JK1" s="1" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="JL1" s="1" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="JM1" s="1" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="JN1" s="1" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="JO1" s="1" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="JP1" s="1" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="JQ1" s="1" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="JR1" s="1" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="JS1" s="1" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="2" spans="1:279" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="CU2" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="CV2" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="CW2" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="CX2" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="CY2" s="2" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="CZ2" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="DA2" s="2" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="DB2" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="DC2" s="2" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="DD2" s="2" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="DE2" s="2" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="DF2" s="2" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="DG2" s="2" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="DH2" s="2" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="DI2" s="2" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="DJ2" s="2" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="DK2" s="2" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="DL2" s="2" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="DM2" s="2" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="DN2" s="2" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="DO2" s="2" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="DP2" s="2" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="DQ2" s="2" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="DR2" s="2" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="DS2" s="2" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="DT2" s="2" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="DU2" s="2" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="DV2" s="2" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="DW2" s="2" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="DX2" s="2" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="DY2" s="2" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="DZ2" s="2" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="EA2" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="EB2" s="2" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="EC2" s="2" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="ED2" s="2" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="EE2" s="2" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="EF2" s="2" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="EG2" s="2" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="EH2" s="2" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="EI2" s="2" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="EJ2" s="2" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="EK2" s="2" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="EL2" s="2" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="EM2" s="2" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="EN2" s="2" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="EO2" s="2" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="EP2" s="2" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="EQ2" s="2" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="ER2" s="2" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="ES2" s="2" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="ET2" s="2" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="EU2" s="2" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="EV2" s="2" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="EW2" s="2" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="EX2" s="2" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="EY2" s="2" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="EZ2" s="2" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="FA2" s="2" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="FB2" s="2" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="FC2" s="2" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="FD2" s="2" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="FE2" s="2" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="FF2" s="2" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="FG2" s="2" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="FH2" s="2" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="FI2" s="2" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="FJ2" s="2" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="FK2" s="2" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="FL2" s="2" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="FM2" s="2" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="FN2" s="2" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="FO2" s="2" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="FP2" s="2" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="FQ2" s="2" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="FR2" s="2" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="FS2" s="2" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="FT2" s="2" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="FU2" s="2" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="FV2" s="2" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="FW2" s="2" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="FX2" s="2" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="FY2" s="2" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="FZ2" s="2" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="GA2" s="2" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="GB2" s="2" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="GC2" s="2" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="GD2" s="2" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="GE2" s="2" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="GF2" s="2" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="GG2" s="2" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="GH2" s="2" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="GI2" s="2" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="GJ2" s="2" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="GK2" s="2" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="GL2" s="2" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="GM2" s="2" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="GN2" s="2" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="GO2" s="2" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="GP2" s="2" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="GQ2" s="2" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="GR2" s="2" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="GS2" s="2" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="GT2" s="2" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="GU2" s="2" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="GV2" s="2" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="GW2" s="2" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="GX2" s="2" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="GY2" s="2" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="GZ2" s="2" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="HA2" s="2" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="HB2" s="2" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="HC2" s="2" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="HD2" s="2" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="HE2" s="2" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="HF2" s="2" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="HG2" s="2" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="HH2" s="2" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="HI2" s="2" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="HJ2" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="HK2" s="2" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="HL2" s="2" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="HM2" s="2" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="HN2" s="2" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="HO2" s="2" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="HP2" s="2" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="HQ2" s="2" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="HR2" s="2" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="HS2" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="HT2" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="HU2" s="2" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="HV2" s="2" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="HW2" s="2" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="HX2" s="2" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="HY2" s="2" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="HZ2" s="2" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="IA2" s="2" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="IB2" s="2" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="IC2" s="2" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="ID2" s="2" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="IE2" s="2" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="IF2" s="2" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="IG2" s="2" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="IH2" s="2" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="II2" s="2" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="IJ2" s="2" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="IK2" s="2" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="IL2" s="2" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="IM2" s="2" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="IN2" s="2" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="IO2" s="2" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="IP2" s="2" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="IQ2" s="2" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="IR2" s="2" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="IS2" s="2" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="IT2" s="2" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="IU2" s="2" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="IV2" s="2" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="IW2" s="2" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="IX2" s="2" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="IY2" s="2" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="IZ2" s="2" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="JA2" s="2" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="JB2" s="2" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="JC2" s="2" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="JD2" s="2" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="JE2" s="2" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="JF2" s="2" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="JG2" s="2" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="JH2" s="2" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="JI2" s="2" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="JJ2" s="2" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="JK2" s="2" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="JL2" s="2" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="JM2" s="2" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="JN2" s="2" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="JO2" s="2" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="JP2" s="2" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="JQ2" s="2" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="JR2" s="2" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="JS2" s="2" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
     </row>
   </sheetData>
@@ -7070,242 +7078,242 @@
   <sheetData>
     <row r="1" spans="13:206">
       <c r="M1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AB1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="BO1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="BS1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="BX1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="CL1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="CN1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="CO1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="CZ1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="DC1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="DY1" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="EQ1" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="FA1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="GX1" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="2" spans="13:206">
       <c r="M2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AB2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="BO2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="BS2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="BX2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="CL2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="CN2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="CO2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="CZ2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="DC2" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="DY2" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="EQ2" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="FA2" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="GX2" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="3" spans="13:206">
       <c r="M3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AB3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="BO3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="BX3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="CL3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="CN3" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="CO3" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="CZ3" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="DC3" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="DY3" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="EQ3" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="FA3" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="GX3" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="4" spans="13:206">
       <c r="M4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AB4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="CL4" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="CN4" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="CZ4" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="DC4" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="DY4" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="EQ4" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="FA4" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="GX4" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="5" spans="13:206">
       <c r="M5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AB5" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="CL5" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="CN5" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="DC5" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="DY5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="EQ5" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="FA5" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="6" spans="13:206">
       <c r="M6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AB6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="CL6" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="CN6" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="DC6" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="EQ6" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="FA6" t="s">
         <v>116</v>
@@ -7313,1646 +7321,1646 @@
     </row>
     <row r="7" spans="13:206">
       <c r="M7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AB7" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="CL7" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="CN7" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="DC7" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="EQ7" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="FA7" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="8" spans="13:206">
       <c r="M8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AB8" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="CL8" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="CN8" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="DC8" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="EQ8" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="9" spans="13:206">
       <c r="M9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AB9" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="CL9" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="CN9" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="DC9" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="EQ9" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="10" spans="13:206">
       <c r="M10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AB10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="CL10" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="DC10" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="11" spans="13:206">
       <c r="M11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AB11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="CL11" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="DC11" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="12" spans="13:206">
       <c r="M12" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AB12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="CL12" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="DC12" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="13" spans="13:206">
       <c r="M13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AB13" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="CL13" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="DC13" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="14" spans="13:206">
       <c r="M14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AB14" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="CL14" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="DC14" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="15" spans="13:206">
       <c r="M15" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AB15" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="CL15" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="DC15" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="16" spans="13:206">
       <c r="M16" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AB16" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="CL16" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="DC16" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="17" spans="13:107">
       <c r="M17" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AB17" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="DC17" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="18" spans="13:107">
       <c r="M18" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AB18" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="DC18" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="19" spans="13:107">
       <c r="M19" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AB19" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="DC19" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="20" spans="13:107">
       <c r="M20" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AB20" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="DC20" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="21" spans="13:107">
       <c r="M21" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AB21" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="DC21" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="22" spans="13:107">
       <c r="M22" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AB22" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="DC22" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="23" spans="13:107">
       <c r="M23" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AB23" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="DC23" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="24" spans="13:107">
       <c r="M24" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AB24" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="DC24" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="25" spans="13:107">
       <c r="M25" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AB25" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="DC25" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="26" spans="13:107">
       <c r="M26" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AB26" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="DC26" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="27" spans="13:107">
       <c r="M27" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AB27" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="DC27" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="28" spans="13:107">
       <c r="M28" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AB28" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="DC28" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="29" spans="13:107">
       <c r="M29" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AB29" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="DC29" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="30" spans="13:107">
       <c r="M30" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AB30" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="DC30" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="31" spans="13:107">
       <c r="AB31" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="DC31" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="32" spans="13:107">
       <c r="AB32" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="DC32" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="33" spans="107:107">
       <c r="DC33" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="34" spans="107:107">
       <c r="DC34" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="35" spans="107:107">
       <c r="DC35" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="36" spans="107:107">
       <c r="DC36" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="37" spans="107:107">
       <c r="DC37" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="38" spans="107:107">
       <c r="DC38" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="39" spans="107:107">
       <c r="DC39" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="40" spans="107:107">
       <c r="DC40" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="41" spans="107:107">
       <c r="DC41" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="42" spans="107:107">
       <c r="DC42" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="43" spans="107:107">
       <c r="DC43" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="44" spans="107:107">
       <c r="DC44" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="45" spans="107:107">
       <c r="DC45" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="46" spans="107:107">
       <c r="DC46" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="47" spans="107:107">
       <c r="DC47" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="48" spans="107:107">
       <c r="DC48" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="49" spans="107:107">
       <c r="DC49" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="50" spans="107:107">
       <c r="DC50" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="51" spans="107:107">
       <c r="DC51" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="52" spans="107:107">
       <c r="DC52" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="53" spans="107:107">
       <c r="DC53" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="54" spans="107:107">
       <c r="DC54" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="55" spans="107:107">
       <c r="DC55" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="56" spans="107:107">
       <c r="DC56" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="57" spans="107:107">
       <c r="DC57" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="58" spans="107:107">
       <c r="DC58" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="59" spans="107:107">
       <c r="DC59" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="60" spans="107:107">
       <c r="DC60" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="61" spans="107:107">
       <c r="DC61" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="62" spans="107:107">
       <c r="DC62" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="63" spans="107:107">
       <c r="DC63" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="64" spans="107:107">
       <c r="DC64" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="65" spans="107:107">
       <c r="DC65" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="66" spans="107:107">
       <c r="DC66" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="67" spans="107:107">
       <c r="DC67" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="68" spans="107:107">
       <c r="DC68" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="69" spans="107:107">
       <c r="DC69" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="70" spans="107:107">
       <c r="DC70" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="71" spans="107:107">
       <c r="DC71" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="72" spans="107:107">
       <c r="DC72" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="73" spans="107:107">
       <c r="DC73" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="74" spans="107:107">
       <c r="DC74" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="75" spans="107:107">
       <c r="DC75" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="76" spans="107:107">
       <c r="DC76" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="77" spans="107:107">
       <c r="DC77" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="78" spans="107:107">
       <c r="DC78" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="79" spans="107:107">
       <c r="DC79" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="80" spans="107:107">
       <c r="DC80" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="81" spans="107:107">
       <c r="DC81" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="82" spans="107:107">
       <c r="DC82" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="83" spans="107:107">
       <c r="DC83" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="84" spans="107:107">
       <c r="DC84" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="85" spans="107:107">
       <c r="DC85" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="86" spans="107:107">
       <c r="DC86" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="87" spans="107:107">
       <c r="DC87" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="88" spans="107:107">
       <c r="DC88" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="89" spans="107:107">
       <c r="DC89" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="90" spans="107:107">
       <c r="DC90" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="91" spans="107:107">
       <c r="DC91" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="92" spans="107:107">
       <c r="DC92" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="93" spans="107:107">
       <c r="DC93" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="94" spans="107:107">
       <c r="DC94" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="95" spans="107:107">
       <c r="DC95" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="96" spans="107:107">
       <c r="DC96" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="97" spans="107:107">
       <c r="DC97" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="98" spans="107:107">
       <c r="DC98" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="99" spans="107:107">
       <c r="DC99" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="100" spans="107:107">
       <c r="DC100" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="101" spans="107:107">
       <c r="DC101" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="102" spans="107:107">
       <c r="DC102" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="103" spans="107:107">
       <c r="DC103" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="104" spans="107:107">
       <c r="DC104" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="105" spans="107:107">
       <c r="DC105" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="106" spans="107:107">
       <c r="DC106" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="107" spans="107:107">
       <c r="DC107" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="108" spans="107:107">
       <c r="DC108" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="109" spans="107:107">
       <c r="DC109" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="110" spans="107:107">
       <c r="DC110" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="111" spans="107:107">
       <c r="DC111" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="112" spans="107:107">
       <c r="DC112" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="113" spans="107:107">
       <c r="DC113" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="114" spans="107:107">
       <c r="DC114" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="115" spans="107:107">
       <c r="DC115" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="116" spans="107:107">
       <c r="DC116" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="117" spans="107:107">
       <c r="DC117" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="118" spans="107:107">
       <c r="DC118" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="119" spans="107:107">
       <c r="DC119" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="120" spans="107:107">
       <c r="DC120" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="121" spans="107:107">
       <c r="DC121" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="122" spans="107:107">
       <c r="DC122" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="123" spans="107:107">
       <c r="DC123" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="124" spans="107:107">
       <c r="DC124" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="125" spans="107:107">
       <c r="DC125" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="126" spans="107:107">
       <c r="DC126" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="127" spans="107:107">
       <c r="DC127" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="128" spans="107:107">
       <c r="DC128" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="129" spans="107:107">
       <c r="DC129" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="130" spans="107:107">
       <c r="DC130" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="131" spans="107:107">
       <c r="DC131" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="132" spans="107:107">
       <c r="DC132" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="133" spans="107:107">
       <c r="DC133" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="134" spans="107:107">
       <c r="DC134" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="135" spans="107:107">
       <c r="DC135" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="136" spans="107:107">
       <c r="DC136" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="137" spans="107:107">
       <c r="DC137" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="138" spans="107:107">
       <c r="DC138" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="139" spans="107:107">
       <c r="DC139" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="140" spans="107:107">
       <c r="DC140" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="141" spans="107:107">
       <c r="DC141" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="142" spans="107:107">
       <c r="DC142" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="143" spans="107:107">
       <c r="DC143" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="144" spans="107:107">
       <c r="DC144" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="145" spans="107:107">
       <c r="DC145" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="146" spans="107:107">
       <c r="DC146" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="147" spans="107:107">
       <c r="DC147" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="148" spans="107:107">
       <c r="DC148" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="149" spans="107:107">
       <c r="DC149" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="150" spans="107:107">
       <c r="DC150" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="151" spans="107:107">
       <c r="DC151" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="152" spans="107:107">
       <c r="DC152" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="153" spans="107:107">
       <c r="DC153" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="154" spans="107:107">
       <c r="DC154" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="155" spans="107:107">
       <c r="DC155" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="156" spans="107:107">
       <c r="DC156" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="157" spans="107:107">
       <c r="DC157" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="158" spans="107:107">
       <c r="DC158" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="159" spans="107:107">
       <c r="DC159" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="160" spans="107:107">
       <c r="DC160" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="161" spans="107:107">
       <c r="DC161" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="162" spans="107:107">
       <c r="DC162" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="163" spans="107:107">
       <c r="DC163" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="164" spans="107:107">
       <c r="DC164" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="165" spans="107:107">
       <c r="DC165" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="166" spans="107:107">
       <c r="DC166" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="167" spans="107:107">
       <c r="DC167" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="168" spans="107:107">
       <c r="DC168" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="169" spans="107:107">
       <c r="DC169" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="170" spans="107:107">
       <c r="DC170" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="171" spans="107:107">
       <c r="DC171" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="172" spans="107:107">
       <c r="DC172" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="173" spans="107:107">
       <c r="DC173" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="174" spans="107:107">
       <c r="DC174" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="175" spans="107:107">
       <c r="DC175" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="176" spans="107:107">
       <c r="DC176" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="177" spans="107:107">
       <c r="DC177" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="178" spans="107:107">
       <c r="DC178" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="179" spans="107:107">
       <c r="DC179" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="180" spans="107:107">
       <c r="DC180" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="181" spans="107:107">
       <c r="DC181" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="182" spans="107:107">
       <c r="DC182" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="183" spans="107:107">
       <c r="DC183" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="184" spans="107:107">
       <c r="DC184" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="185" spans="107:107">
       <c r="DC185" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="186" spans="107:107">
       <c r="DC186" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="187" spans="107:107">
       <c r="DC187" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="188" spans="107:107">
       <c r="DC188" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="189" spans="107:107">
       <c r="DC189" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="190" spans="107:107">
       <c r="DC190" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="191" spans="107:107">
       <c r="DC191" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="192" spans="107:107">
       <c r="DC192" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="193" spans="107:107">
       <c r="DC193" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="194" spans="107:107">
       <c r="DC194" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="195" spans="107:107">
       <c r="DC195" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="196" spans="107:107">
       <c r="DC196" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="197" spans="107:107">
       <c r="DC197" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="198" spans="107:107">
       <c r="DC198" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="199" spans="107:107">
       <c r="DC199" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="200" spans="107:107">
       <c r="DC200" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="201" spans="107:107">
       <c r="DC201" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="202" spans="107:107">
       <c r="DC202" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="203" spans="107:107">
       <c r="DC203" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
     </row>
     <row r="204" spans="107:107">
       <c r="DC204" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="205" spans="107:107">
       <c r="DC205" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="206" spans="107:107">
       <c r="DC206" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
     </row>
     <row r="207" spans="107:107">
       <c r="DC207" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="208" spans="107:107">
       <c r="DC208" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="209" spans="107:107">
       <c r="DC209" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="210" spans="107:107">
       <c r="DC210" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="211" spans="107:107">
       <c r="DC211" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="212" spans="107:107">
       <c r="DC212" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="213" spans="107:107">
       <c r="DC213" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="214" spans="107:107">
       <c r="DC214" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="215" spans="107:107">
       <c r="DC215" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="216" spans="107:107">
       <c r="DC216" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="217" spans="107:107">
       <c r="DC217" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="218" spans="107:107">
       <c r="DC218" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="219" spans="107:107">
       <c r="DC219" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="220" spans="107:107">
       <c r="DC220" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="221" spans="107:107">
       <c r="DC221" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="222" spans="107:107">
       <c r="DC222" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="223" spans="107:107">
       <c r="DC223" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="224" spans="107:107">
       <c r="DC224" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="225" spans="107:107">
       <c r="DC225" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="226" spans="107:107">
       <c r="DC226" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="227" spans="107:107">
       <c r="DC227" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="228" spans="107:107">
       <c r="DC228" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="229" spans="107:107">
       <c r="DC229" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="230" spans="107:107">
       <c r="DC230" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="231" spans="107:107">
       <c r="DC231" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="232" spans="107:107">
       <c r="DC232" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="233" spans="107:107">
       <c r="DC233" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="234" spans="107:107">
       <c r="DC234" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="235" spans="107:107">
       <c r="DC235" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="236" spans="107:107">
       <c r="DC236" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="237" spans="107:107">
       <c r="DC237" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="238" spans="107:107">
       <c r="DC238" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="239" spans="107:107">
       <c r="DC239" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="240" spans="107:107">
       <c r="DC240" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="241" spans="107:107">
       <c r="DC241" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="242" spans="107:107">
       <c r="DC242" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="243" spans="107:107">
       <c r="DC243" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="244" spans="107:107">
       <c r="DC244" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="245" spans="107:107">
       <c r="DC245" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="246" spans="107:107">
       <c r="DC246" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="247" spans="107:107">
       <c r="DC247" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
     </row>
     <row r="248" spans="107:107">
       <c r="DC248" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="249" spans="107:107">
       <c r="DC249" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="250" spans="107:107">
       <c r="DC250" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="251" spans="107:107">
       <c r="DC251" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
     </row>
     <row r="252" spans="107:107">
       <c r="DC252" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="253" spans="107:107">
       <c r="DC253" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="254" spans="107:107">
       <c r="DC254" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
     </row>
     <row r="255" spans="107:107">
       <c r="DC255" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="256" spans="107:107">
       <c r="DC256" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="257" spans="107:107">
       <c r="DC257" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="258" spans="107:107">
       <c r="DC258" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="259" spans="107:107">
       <c r="DC259" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="260" spans="107:107">
       <c r="DC260" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="261" spans="107:107">
       <c r="DC261" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="262" spans="107:107">
       <c r="DC262" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="263" spans="107:107">
       <c r="DC263" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="264" spans="107:107">
       <c r="DC264" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
     <row r="265" spans="107:107">
       <c r="DC265" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="266" spans="107:107">
       <c r="DC266" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="267" spans="107:107">
       <c r="DC267" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="268" spans="107:107">
       <c r="DC268" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
     </row>
     <row r="269" spans="107:107">
       <c r="DC269" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="270" spans="107:107">
       <c r="DC270" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="271" spans="107:107">
       <c r="DC271" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="272" spans="107:107">
       <c r="DC272" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="273" spans="107:107">
       <c r="DC273" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="274" spans="107:107">
       <c r="DC274" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
     </row>
     <row r="275" spans="107:107">
       <c r="DC275" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="276" spans="107:107">
       <c r="DC276" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="277" spans="107:107">
       <c r="DC277" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="278" spans="107:107">
       <c r="DC278" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="279" spans="107:107">
       <c r="DC279" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="280" spans="107:107">
       <c r="DC280" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="281" spans="107:107">
       <c r="DC281" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="282" spans="107:107">
       <c r="DC282" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
     <row r="283" spans="107:107">
       <c r="DC283" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="284" spans="107:107">
       <c r="DC284" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
     </row>
     <row r="285" spans="107:107">
       <c r="DC285" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="286" spans="107:107">
       <c r="DC286" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
     </row>
     <row r="287" spans="107:107">
       <c r="DC287" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="288" spans="107:107">
       <c r="DC288" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="289" spans="107:107">
       <c r="DC289" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
     </row>
     <row r="290" spans="107:107">
       <c r="DC290" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
     </row>
     <row r="291" spans="107:107">
       <c r="DC291" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
     </row>
     <row r="292" spans="107:107">
       <c r="DC292" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
     </row>
     <row r="293" spans="107:107">
       <c r="DC293" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
     </row>
     <row r="294" spans="107:107">
       <c r="DC294" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
     </row>
   </sheetData>
